--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4617" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4617" uniqueCount="717">
   <si>
     <t>Account</t>
   </si>
@@ -1305,10 +1305,10 @@
 Cost is scaled as a fraction of CAPEX unless specific parameters are added to indicate more/less frequent replacements (e.g. GCMR)</t>
   </si>
   <si>
-    <t>Annualized RPV Replacements</t>
-  </si>
-  <si>
-    <t>Annualized Core Barrel Replacements</t>
+    <t>Annualized Outer Vessel Structure Replacements</t>
+  </si>
+  <si>
+    <t>Annualized Inner Vessel Structure Replacements</t>
   </si>
   <si>
     <t>Annualized Moderator Replacements</t>
@@ -1317,10 +1317,10 @@
     <t>Annualized Reflector Replacements</t>
   </si>
   <si>
-    <t>Annualized Reactivity Control Replacements</t>
-  </si>
-  <si>
-    <t>Annualized Integrated Heat Transfer System Replacements</t>
+    <t>Annualized Reactor Control Devices Replacements</t>
+  </si>
+  <si>
+    <t>Annualized Main Heat Transport System Replacements</t>
   </si>
   <si>
     <t>Annualized Misc. Replacements</t>
@@ -2255,6 +2255,9 @@
   </si>
   <si>
     <t>Remotely Monitored</t>
+  </si>
+  <si>
+    <t>Annualized Moderator Booster Replacements</t>
   </si>
 </sst>
 </file>
@@ -19192,7 +19195,7 @@
       <c r="AF172" s="79"/>
       <c r="AG172" s="77"/>
     </row>
-    <row r="173" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="37">
         <v>751</v>
       </c>
@@ -19205,7 +19208,7 @@
       </c>
       <c r="D173" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized RPV Replacements</v>
+        <v xml:space="preserve">            Annualized Outer Vessel Structure Replacements</v>
       </c>
       <c r="E173" s="39"/>
       <c r="F173" s="39"/>
@@ -19243,7 +19246,7 @@
       <c r="AF173" s="79"/>
       <c r="AG173" s="77"/>
     </row>
-    <row r="174" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="37">
         <v>752</v>
       </c>
@@ -19256,7 +19259,7 @@
       </c>
       <c r="D174" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Core Barrel Replacements</v>
+        <v xml:space="preserve">            Annualized Inner Vessel Structure Replacements</v>
       </c>
       <c r="E174" s="39"/>
       <c r="F174" s="39"/>
@@ -19391,7 +19394,7 @@
       </c>
       <c r="D177" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Reactivity Control Replacements</v>
+        <v xml:space="preserve">            Annualized Reactor Control Devices Replacements</v>
       </c>
       <c r="E177" s="39"/>
       <c r="F177" s="39"/>
@@ -19423,20 +19426,20 @@
       <c r="AF177" s="79"/>
       <c r="AG177" s="77"/>
     </row>
-    <row r="178" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="37">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B178" s="38">
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
       <c r="C178" s="56" t="s">
-        <v>405</v>
+        <v>716</v>
       </c>
       <c r="D178" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Integrated Heat Transfer System Replacements</v>
+        <v xml:space="preserve">            Annualized Moderator Booster Replacements</v>
       </c>
       <c r="E178" s="39"/>
       <c r="F178" s="39"/>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -692,7 +692,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3660" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3660" uniqueCount="798">
   <si>
     <t>Account</t>
   </si>
@@ -3173,6 +3173,18 @@
     <t>Nth of a kind licening was estimated to take 30-42 months  https://www.nrc.gov/docs/ML2426/ML24268A310.pdf
 Now, it is estimated to take 6- 12 months https://www.govinfo.gov/content/pkg/FR-2026-05-01/pdf/2026-08550.pdf
 Therefor, the cost is estimated to be reduced 4 times (a factor of 0.25). Since MOUSE is using learning rates, this factor is converted to a learning rate of 0.2 assuming 100 units</t>
+  </si>
+  <si>
+    <t>Annualized Outer Vessel Structure Replacements</t>
+  </si>
+  <si>
+    <t>Annualized Inner Vessel Structure Replacements</t>
+  </si>
+  <si>
+    <t>Annualized Reactor Control Devices Replacements</t>
+  </si>
+  <si>
+    <t>Annualized Moderator Booster Replacements</t>
   </si>
 </sst>
 </file>
@@ -21654,11 +21666,11 @@
         <v>2</v>
       </c>
       <c r="C173" s="55" t="s">
-        <v>404</v>
+        <v>794</v>
       </c>
       <c r="D173" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized RPV Replacements</v>
+        <v xml:space="preserve">            Annualized Outer Vessel Structure Replacements</v>
       </c>
       <c r="E173" s="39"/>
       <c r="F173" s="39"/>
@@ -21705,11 +21717,11 @@
         <v>2</v>
       </c>
       <c r="C174" s="55" t="s">
-        <v>405</v>
+        <v>795</v>
       </c>
       <c r="D174" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Core Barrel Replacements</v>
+        <v xml:space="preserve">            Annualized Inner Vessel Structure Replacements</v>
       </c>
       <c r="E174" s="39"/>
       <c r="F174" s="39"/>
@@ -21840,11 +21852,11 @@
         <v>2</v>
       </c>
       <c r="C177" s="55" t="s">
-        <v>408</v>
+        <v>796</v>
       </c>
       <c r="D177" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Reactivity Control Replacements</v>
+        <v xml:space="preserve">            Annualized Reactor Control Devices Replacements</v>
       </c>
       <c r="E177" s="39"/>
       <c r="F177" s="39"/>
@@ -21878,18 +21890,18 @@
     </row>
     <row r="178" spans="1:33" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="37">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B178" s="38">
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
       <c r="C178" s="55" t="s">
-        <v>409</v>
+        <v>797</v>
       </c>
       <c r="D178" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Integrated Heat Transfer System Replacements</v>
+        <v xml:space="preserve">            Annualized Moderator Booster Replacements</v>
       </c>
       <c r="E178" s="39"/>
       <c r="F178" s="39"/>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -21,7 +21,7 @@
     <sheet name="Central Facility Database" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cost Database'!$A$1:$AB$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cost Database'!$A$1:$AB$192</definedName>
     <definedName name="CRF">#REF!</definedName>
     <definedName name="DiscountRate">#REF!</definedName>
     <definedName name="FacilityLifetime">#REF!</definedName>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4617" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4625" uniqueCount="726">
   <si>
     <t>Account</t>
   </si>
@@ -2258,6 +2258,33 @@
   </si>
   <si>
     <t>Annualized Moderator Booster Replacements</t>
+  </si>
+  <si>
+    <t>Annualized Plant Maintenance (Misc.)</t>
+  </si>
+  <si>
+    <t>Annualized Building and Structural Maintenance (Accounts 212–215)</t>
+  </si>
+  <si>
+    <t>Annualized Main Heat Transport System Maintenance (Accounts 222.1–222.3 and 222.6)</t>
+  </si>
+  <si>
+    <t>Annualized Safety System Maintenance (Account 223)</t>
+  </si>
+  <si>
+    <t>Annualized Reactor Plant Equipment Maintenance (Accounts 221.11, 226, and 228)</t>
+  </si>
+  <si>
+    <t>Annualized Reactor I&amp;C Maintenance (Account 227)</t>
+  </si>
+  <si>
+    <t>Annualized Energy Conversion System Maintenance (Account 23)</t>
+  </si>
+  <si>
+    <t>Annualized Electrical Equipment Maintenance (Account 24)</t>
+  </si>
+  <si>
+    <t>Annualized Miscellaneous Equipment Maintenance (Account 26)</t>
   </si>
 </sst>
 </file>
@@ -5388,7 +5415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ184"/>
+  <dimension ref="A1:AJ192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="3" customWidth="1"/>
@@ -18572,7 +18599,7 @@
         <v>381</v>
       </c>
       <c r="D165" s="39" t="str">
-        <f t="shared" ref="D162:D181" si="43">REPT("   ", B165*2) &amp; C165</f>
+        <f t="shared" ref="D162:D189" si="43">REPT("   ", B165*2) &amp; C165</f>
         <v xml:space="preserve">            Operators </v>
       </c>
       <c r="E165" s="39" t="s">
@@ -19480,11 +19507,11 @@
         <v>2</v>
       </c>
       <c r="C179" s="56" t="s">
-        <v>406</v>
+        <v>717</v>
       </c>
       <c r="D179" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Misc. Replacements</v>
+        <v xml:space="preserve">            Annualized Plant Maintenance (Misc.)</v>
       </c>
       <c r="E179" s="39"/>
       <c r="F179" s="39"/>
@@ -19516,27 +19543,20 @@
       <c r="AF179" s="79"/>
       <c r="AG179" s="77"/>
     </row>
-    <row r="180" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="37">
-        <v>78</v>
+        <v>759.1</v>
       </c>
       <c r="B180" s="38">
-        <f>IF(ISNUMBER(A180),
-    IF(AND(A180=INT(A180), MOD(A180, 10) = 0), 0,
-        IF(AND(A180=INT(A180), LEN(A180)=2), 1,
-            IF(AND(A180=INT(A180), LEN(A180)=3), 2,
-                LEN(A180) - FIND(".", A180) + 2)
-        )
-    ),
-"")</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(A180),IF(AND(A180=INT(A180),MOD(A180,10)=0),0,IF(AND(A180=INT(A180),LEN(A180)=2),1,IF(AND(A180=INT(A180),LEN(A180)=3),2,LEN(A180)-FIND(".",A180)+2))),"")</f>
+        <v>3</v>
       </c>
       <c r="C180" s="56" t="s">
-        <v>407</v>
+        <v>718</v>
       </c>
       <c r="D180" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">      Annualized Decommissioning Cost</v>
+        <f>REPT("   ",B180*2)&amp;C180</f>
+        <v>                  Annualized Building and Structural Maintenance (Accounts 212–215)</v>
       </c>
       <c r="E180" s="39"/>
       <c r="F180" s="39"/>
@@ -19544,20 +19564,18 @@
       <c r="H180" s="39"/>
       <c r="I180" s="39"/>
       <c r="J180" s="43"/>
-      <c r="K180" s="72"/>
+      <c r="K180" s="61"/>
       <c r="L180" s="49"/>
-      <c r="M180" s="45"/>
+      <c r="M180" s="59"/>
       <c r="N180" s="49"/>
       <c r="O180" s="49"/>
       <c r="P180" s="49"/>
       <c r="Q180" s="66"/>
-      <c r="R180" s="73"/>
-      <c r="S180" s="59"/>
-      <c r="T180" s="59"/>
+      <c r="R180" s="49"/>
+      <c r="S180" s="143"/>
+      <c r="T180" s="143"/>
       <c r="U180" s="49"/>
-      <c r="V180" s="59" t="s">
-        <v>408</v>
-      </c>
+      <c r="V180" s="143"/>
       <c r="W180" s="77"/>
       <c r="X180" s="80"/>
       <c r="Y180" s="80"/>
@@ -19570,46 +19588,39 @@
       <c r="AF180" s="79"/>
       <c r="AG180" s="77"/>
     </row>
-    <row r="181" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="37">
-        <v>80</v>
+        <v>759.2</v>
       </c>
       <c r="B181" s="38">
-        <f>IF(ISNUMBER(A181),
-IF(AND(A181=INT(A181), MOD(A181, 10) = 0), 0,
-IF(AND(A181=INT(A181), LEN(A181)=2), 1,
-IF(AND(A181=INT(A181), LEN(A181)=3), 2,
-LEN(A181) - FIND(".", A181) + 2)
-)
-),
-"")</f>
-        <v>0</v>
-      </c>
-      <c r="C181" s="71" t="s">
-        <v>409</v>
+        <f>IF(ISNUMBER(A181),IF(AND(A181=INT(A181),MOD(A181,10)=0),0,IF(AND(A181=INT(A181),LEN(A181)=2),1,IF(AND(A181=INT(A181),LEN(A181)=3),2,LEN(A181)-FIND(".",A181)+2))),"")</f>
+        <v>3</v>
+      </c>
+      <c r="C181" s="56" t="s">
+        <v>719</v>
       </c>
       <c r="D181" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v>Annualized Fuel Cost</v>
+        <f>REPT("   ",B181*2)&amp;C181</f>
+        <v>                  Annualized Main Heat Transport System Maintenance (Accounts 222.1–222.3 and 222.6)</v>
       </c>
       <c r="E181" s="39"/>
       <c r="F181" s="39"/>
       <c r="G181" s="39"/>
       <c r="H181" s="39"/>
       <c r="I181" s="39"/>
-      <c r="J181" s="40"/>
-      <c r="K181" s="40"/>
-      <c r="L181" s="38"/>
-      <c r="M181" s="41"/>
-      <c r="N181" s="38"/>
-      <c r="O181" s="38"/>
-      <c r="P181" s="38"/>
-      <c r="Q181" s="40"/>
-      <c r="R181" s="38"/>
-      <c r="S181" s="41"/>
-      <c r="T181" s="38"/>
-      <c r="U181" s="38"/>
-      <c r="V181" s="38"/>
+      <c r="J181" s="43"/>
+      <c r="K181" s="61"/>
+      <c r="L181" s="49"/>
+      <c r="M181" s="59"/>
+      <c r="N181" s="49"/>
+      <c r="O181" s="49"/>
+      <c r="P181" s="49"/>
+      <c r="Q181" s="66"/>
+      <c r="R181" s="49"/>
+      <c r="S181" s="143"/>
+      <c r="T181" s="143"/>
+      <c r="U181" s="49"/>
+      <c r="V181" s="143"/>
       <c r="W181" s="77"/>
       <c r="X181" s="80"/>
       <c r="Y181" s="80"/>
@@ -19622,121 +19633,65 @@
       <c r="AF181" s="79"/>
       <c r="AG181" s="77"/>
     </row>
-    <row r="182" spans="1:33" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="37">
-        <v>81</v>
+        <v>759.3</v>
       </c>
       <c r="B182" s="38">
-        <f>IF(ISNUMBER(A182),
-IF(AND(A182=INT(A182), MOD(A182, 10) = 0), 0,
-IF(AND(A182=INT(A182), LEN(A182)=2), 1,
-IF(AND(A182=INT(A182), LEN(A182)=3), 2,
-LEN(A182) - FIND(".", A182) + 2)
-)
-),
-"")</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(A182),IF(AND(A182=INT(A182),MOD(A182,10)=0),0,IF(AND(A182=INT(A182),LEN(A182)=2),1,IF(AND(A182=INT(A182),LEN(A182)=3),2,LEN(A182)-FIND(".",A182)+2))),"")</f>
+        <v>3</v>
       </c>
       <c r="C182" s="56" t="s">
-        <v>410</v>
+        <v>720</v>
       </c>
       <c r="D182" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">      Refueling Operations</v>
-      </c>
-      <c r="E182" s="39" t="s">
-        <v>264</v>
-      </c>
+        <f>REPT("   ",B182*2)&amp;C182</f>
+        <v>                  Annualized Safety System Maintenance (Account 223)</v>
+      </c>
+      <c r="E182" s="39"/>
       <c r="F182" s="39"/>
       <c r="G182" s="39"/>
       <c r="H182" s="39"/>
       <c r="I182" s="39"/>
       <c r="J182" s="43"/>
-      <c r="K182" s="61">
-        <v>178500</v>
-      </c>
-      <c r="L182" s="49" t="s">
-        <v>382</v>
-      </c>
-      <c r="M182" s="59" t="s">
-        <v>383</v>
-      </c>
+      <c r="K182" s="61"/>
+      <c r="L182" s="49"/>
+      <c r="M182" s="59"/>
       <c r="N182" s="49"/>
       <c r="O182" s="49"/>
-      <c r="P182" s="49">
-        <v>1</v>
-      </c>
-      <c r="Q182" s="66">
-        <v>2024</v>
-      </c>
-      <c r="R182" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="S182" s="59"/>
-      <c r="T182" s="59" t="s">
-        <v>384</v>
-      </c>
+      <c r="P182" s="49"/>
+      <c r="Q182" s="66"/>
+      <c r="R182" s="49"/>
+      <c r="S182" s="143"/>
+      <c r="T182" s="143"/>
       <c r="U182" s="49"/>
-      <c r="V182" s="49"/>
-      <c r="W182" s="77" t="s">
-        <v>43</v>
-      </c>
-      <c r="X182" s="80">
-        <f>0.9*$J182</f>
-        <v>0</v>
-      </c>
-      <c r="Y182" s="80">
-        <f>1.5*J182</f>
-        <v>0</v>
-      </c>
-      <c r="Z182" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA182" s="79">
-        <f>0.9*K182</f>
-        <v>160650</v>
-      </c>
-      <c r="AB182" s="79">
-        <f>1.3*K182</f>
-        <v>232050</v>
-      </c>
-      <c r="AC182" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD182" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE182" s="79" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF182" s="79" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG182" s="77" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="183" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="V182" s="143"/>
+      <c r="W182" s="77"/>
+      <c r="X182" s="80"/>
+      <c r="Y182" s="80"/>
+      <c r="Z182" s="77"/>
+      <c r="AA182" s="79"/>
+      <c r="AB182" s="79"/>
+      <c r="AC182" s="77"/>
+      <c r="AD182" s="79"/>
+      <c r="AE182" s="79"/>
+      <c r="AF182" s="79"/>
+      <c r="AG182" s="77"/>
+    </row>
+    <row r="183" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="37">
-        <v>82</v>
+        <v>759.4</v>
       </c>
       <c r="B183" s="38">
-        <f>IF(ISNUMBER(A183),
-IF(AND(A183=INT(A183), MOD(A183, 10) = 0), 0,
-IF(AND(A183=INT(A183), LEN(A183)=2), 1,
-IF(AND(A183=INT(A183), LEN(A183)=3), 2,
-LEN(A183) - FIND(".", A183) + 2)
-)
-),
-"")</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(A183),IF(AND(A183=INT(A183),MOD(A183,10)=0),0,IF(AND(A183=INT(A183),LEN(A183)=2),1,IF(AND(A183=INT(A183),LEN(A183)=3),2,LEN(A183)-FIND(".",A183)+2))),"")</f>
+        <v>3</v>
       </c>
       <c r="C183" s="56" t="s">
-        <v>411</v>
+        <v>721</v>
       </c>
       <c r="D183" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">      Additional Nuclear Fuel</v>
+        <f>REPT("   ",B183*2)&amp;C183</f>
+        <v>                  Annualized Reactor Plant Equipment Maintenance (Accounts 221.11, 226, and 228)</v>
       </c>
       <c r="E183" s="39"/>
       <c r="F183" s="39"/>
@@ -19752,10 +19707,10 @@
       <c r="P183" s="49"/>
       <c r="Q183" s="66"/>
       <c r="R183" s="49"/>
-      <c r="S183" s="59"/>
-      <c r="T183" s="49"/>
+      <c r="S183" s="143"/>
+      <c r="T183" s="143"/>
       <c r="U183" s="49"/>
-      <c r="V183" s="49"/>
+      <c r="V183" s="143"/>
       <c r="W183" s="77"/>
       <c r="X183" s="80"/>
       <c r="Y183" s="80"/>
@@ -19768,105 +19723,537 @@
       <c r="AF183" s="79"/>
       <c r="AG183" s="77"/>
     </row>
-    <row r="184" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="37">
-        <v>83</v>
+        <v>759.5</v>
       </c>
       <c r="B184" s="38">
-        <f>IF(ISNUMBER(A184),
-IF(AND(A184=INT(A184), MOD(A184, 10) = 0), 0,
-IF(AND(A184=INT(A184), LEN(A184)=2), 1,
-IF(AND(A184=INT(A184), LEN(A184)=3), 2,
-LEN(A184) - FIND(".", A184) + 2)
-)
-),
-"")</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(A184),IF(AND(A184=INT(A184),MOD(A184,10)=0),0,IF(AND(A184=INT(A184),LEN(A184)=2),1,IF(AND(A184=INT(A184),LEN(A184)=3),2,LEN(A184)-FIND(".",A184)+2))),"")</f>
+        <v>3</v>
       </c>
       <c r="C184" s="56" t="s">
-        <v>412</v>
+        <v>722</v>
       </c>
       <c r="D184" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">      Spent Fuel Management</v>
-      </c>
-      <c r="E184" s="39" t="s">
-        <v>35</v>
-      </c>
+        <f>REPT("   ",B184*2)&amp;C184</f>
+        <v>                  Annualized Reactor I&amp;C Maintenance (Account 227)</v>
+      </c>
+      <c r="E184" s="39"/>
       <c r="F184" s="39"/>
       <c r="G184" s="39"/>
       <c r="H184" s="39"/>
       <c r="I184" s="39"/>
       <c r="J184" s="43"/>
-      <c r="K184" s="61">
-        <v>1</v>
-      </c>
-      <c r="L184" s="49" t="s">
-        <v>413</v>
-      </c>
-      <c r="M184" s="59" t="s">
-        <v>414</v>
-      </c>
+      <c r="K184" s="61"/>
+      <c r="L184" s="49"/>
+      <c r="M184" s="59"/>
       <c r="N184" s="49"/>
       <c r="O184" s="49"/>
-      <c r="P184" s="49">
+      <c r="P184" s="49"/>
+      <c r="Q184" s="66"/>
+      <c r="R184" s="49"/>
+      <c r="S184" s="143"/>
+      <c r="T184" s="143"/>
+      <c r="U184" s="49"/>
+      <c r="V184" s="143"/>
+      <c r="W184" s="77"/>
+      <c r="X184" s="80"/>
+      <c r="Y184" s="80"/>
+      <c r="Z184" s="77"/>
+      <c r="AA184" s="79"/>
+      <c r="AB184" s="79"/>
+      <c r="AC184" s="77"/>
+      <c r="AD184" s="79"/>
+      <c r="AE184" s="79"/>
+      <c r="AF184" s="79"/>
+      <c r="AG184" s="77"/>
+    </row>
+    <row r="185" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="37">
+        <v>759.6</v>
+      </c>
+      <c r="B185" s="38">
+        <f>IF(ISNUMBER(A185),IF(AND(A185=INT(A185),MOD(A185,10)=0),0,IF(AND(A185=INT(A185),LEN(A185)=2),1,IF(AND(A185=INT(A185),LEN(A185)=3),2,LEN(A185)-FIND(".",A185)+2))),"")</f>
+        <v>3</v>
+      </c>
+      <c r="C185" s="56" t="s">
+        <v>723</v>
+      </c>
+      <c r="D185" s="39" t="str">
+        <f>REPT("   ",B185*2)&amp;C185</f>
+        <v>                  Annualized Energy Conversion System Maintenance (Account 23)</v>
+      </c>
+      <c r="E185" s="39"/>
+      <c r="F185" s="39"/>
+      <c r="G185" s="39"/>
+      <c r="H185" s="39"/>
+      <c r="I185" s="39"/>
+      <c r="J185" s="43"/>
+      <c r="K185" s="61"/>
+      <c r="L185" s="49"/>
+      <c r="M185" s="59"/>
+      <c r="N185" s="49"/>
+      <c r="O185" s="49"/>
+      <c r="P185" s="49"/>
+      <c r="Q185" s="66"/>
+      <c r="R185" s="49"/>
+      <c r="S185" s="143"/>
+      <c r="T185" s="143"/>
+      <c r="U185" s="49"/>
+      <c r="V185" s="143"/>
+      <c r="W185" s="77"/>
+      <c r="X185" s="80"/>
+      <c r="Y185" s="80"/>
+      <c r="Z185" s="77"/>
+      <c r="AA185" s="79"/>
+      <c r="AB185" s="79"/>
+      <c r="AC185" s="77"/>
+      <c r="AD185" s="79"/>
+      <c r="AE185" s="79"/>
+      <c r="AF185" s="79"/>
+      <c r="AG185" s="77"/>
+    </row>
+    <row r="186" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="37">
+        <v>759.7</v>
+      </c>
+      <c r="B186" s="38">
+        <f>IF(ISNUMBER(A186),IF(AND(A186=INT(A186),MOD(A186,10)=0),0,IF(AND(A186=INT(A186),LEN(A186)=2),1,IF(AND(A186=INT(A186),LEN(A186)=3),2,LEN(A186)-FIND(".",A186)+2))),"")</f>
+        <v>3</v>
+      </c>
+      <c r="C186" s="56" t="s">
+        <v>724</v>
+      </c>
+      <c r="D186" s="39" t="str">
+        <f>REPT("   ",B186*2)&amp;C186</f>
+        <v>                  Annualized Electrical Equipment Maintenance (Account 24)</v>
+      </c>
+      <c r="E186" s="39"/>
+      <c r="F186" s="39"/>
+      <c r="G186" s="39"/>
+      <c r="H186" s="39"/>
+      <c r="I186" s="39"/>
+      <c r="J186" s="43"/>
+      <c r="K186" s="61"/>
+      <c r="L186" s="49"/>
+      <c r="M186" s="59"/>
+      <c r="N186" s="49"/>
+      <c r="O186" s="49"/>
+      <c r="P186" s="49"/>
+      <c r="Q186" s="66"/>
+      <c r="R186" s="49"/>
+      <c r="S186" s="143"/>
+      <c r="T186" s="143"/>
+      <c r="U186" s="49"/>
+      <c r="V186" s="143"/>
+      <c r="W186" s="77"/>
+      <c r="X186" s="80"/>
+      <c r="Y186" s="80"/>
+      <c r="Z186" s="77"/>
+      <c r="AA186" s="79"/>
+      <c r="AB186" s="79"/>
+      <c r="AC186" s="77"/>
+      <c r="AD186" s="79"/>
+      <c r="AE186" s="79"/>
+      <c r="AF186" s="79"/>
+      <c r="AG186" s="77"/>
+    </row>
+    <row r="187" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="37">
+        <v>759.8</v>
+      </c>
+      <c r="B187" s="38">
+        <f>IF(ISNUMBER(A187),IF(AND(A187=INT(A187),MOD(A187,10)=0),0,IF(AND(A187=INT(A187),LEN(A187)=2),1,IF(AND(A187=INT(A187),LEN(A187)=3),2,LEN(A187)-FIND(".",A187)+2))),"")</f>
+        <v>3</v>
+      </c>
+      <c r="C187" s="56" t="s">
+        <v>725</v>
+      </c>
+      <c r="D187" s="39" t="str">
+        <f>REPT("   ",B187*2)&amp;C187</f>
+        <v>                  Annualized Miscellaneous Equipment Maintenance (Account 26)</v>
+      </c>
+      <c r="E187" s="39"/>
+      <c r="F187" s="39"/>
+      <c r="G187" s="39"/>
+      <c r="H187" s="39"/>
+      <c r="I187" s="39"/>
+      <c r="J187" s="43"/>
+      <c r="K187" s="61"/>
+      <c r="L187" s="49"/>
+      <c r="M187" s="59"/>
+      <c r="N187" s="49"/>
+      <c r="O187" s="49"/>
+      <c r="P187" s="49"/>
+      <c r="Q187" s="66"/>
+      <c r="R187" s="49"/>
+      <c r="S187" s="143"/>
+      <c r="T187" s="143"/>
+      <c r="U187" s="49"/>
+      <c r="V187" s="143"/>
+      <c r="W187" s="77"/>
+      <c r="X187" s="80"/>
+      <c r="Y187" s="80"/>
+      <c r="Z187" s="77"/>
+      <c r="AA187" s="79"/>
+      <c r="AB187" s="79"/>
+      <c r="AC187" s="77"/>
+      <c r="AD187" s="79"/>
+      <c r="AE187" s="79"/>
+      <c r="AF187" s="79"/>
+      <c r="AG187" s="77"/>
+    </row>
+    <row r="188" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="37">
+        <v>78</v>
+      </c>
+      <c r="B188" s="38">
+        <f>IF(ISNUMBER(A188),
+    IF(AND(A188=INT(A188), MOD(A188, 10) = 0), 0,
+        IF(AND(A188=INT(A188), LEN(A188)=2), 1,
+            IF(AND(A188=INT(A188), LEN(A188)=3), 2,
+                LEN(A188) - FIND(".", A188) + 2)
+        )
+    ),
+"")</f>
         <v>1</v>
       </c>
-      <c r="Q184" s="66">
+      <c r="C188" s="56" t="s">
+        <v>407</v>
+      </c>
+      <c r="D188" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">      Annualized Decommissioning Cost</v>
+      </c>
+      <c r="E188" s="39"/>
+      <c r="F188" s="39"/>
+      <c r="G188" s="39"/>
+      <c r="H188" s="39"/>
+      <c r="I188" s="39"/>
+      <c r="J188" s="43"/>
+      <c r="K188" s="72"/>
+      <c r="L188" s="49"/>
+      <c r="M188" s="45"/>
+      <c r="N188" s="49"/>
+      <c r="O188" s="49"/>
+      <c r="P188" s="49"/>
+      <c r="Q188" s="66"/>
+      <c r="R188" s="73"/>
+      <c r="S188" s="59"/>
+      <c r="T188" s="59"/>
+      <c r="U188" s="49"/>
+      <c r="V188" s="59" t="s">
+        <v>408</v>
+      </c>
+      <c r="W188" s="77"/>
+      <c r="X188" s="80"/>
+      <c r="Y188" s="80"/>
+      <c r="Z188" s="77"/>
+      <c r="AA188" s="79"/>
+      <c r="AB188" s="79"/>
+      <c r="AC188" s="77"/>
+      <c r="AD188" s="79"/>
+      <c r="AE188" s="79"/>
+      <c r="AF188" s="79"/>
+      <c r="AG188" s="77"/>
+    </row>
+    <row r="189" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="37">
+        <v>80</v>
+      </c>
+      <c r="B189" s="38">
+        <f>IF(ISNUMBER(A189),
+IF(AND(A189=INT(A189), MOD(A189, 10) = 0), 0,
+IF(AND(A189=INT(A189), LEN(A189)=2), 1,
+IF(AND(A189=INT(A189), LEN(A189)=3), 2,
+LEN(A189) - FIND(".", A189) + 2)
+)
+),
+"")</f>
+        <v>0</v>
+      </c>
+      <c r="C189" s="71" t="s">
+        <v>409</v>
+      </c>
+      <c r="D189" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v>Annualized Fuel Cost</v>
+      </c>
+      <c r="E189" s="39"/>
+      <c r="F189" s="39"/>
+      <c r="G189" s="39"/>
+      <c r="H189" s="39"/>
+      <c r="I189" s="39"/>
+      <c r="J189" s="40"/>
+      <c r="K189" s="40"/>
+      <c r="L189" s="38"/>
+      <c r="M189" s="41"/>
+      <c r="N189" s="38"/>
+      <c r="O189" s="38"/>
+      <c r="P189" s="38"/>
+      <c r="Q189" s="40"/>
+      <c r="R189" s="38"/>
+      <c r="S189" s="41"/>
+      <c r="T189" s="38"/>
+      <c r="U189" s="38"/>
+      <c r="V189" s="38"/>
+      <c r="W189" s="77"/>
+      <c r="X189" s="80"/>
+      <c r="Y189" s="80"/>
+      <c r="Z189" s="77"/>
+      <c r="AA189" s="79"/>
+      <c r="AB189" s="79"/>
+      <c r="AC189" s="77"/>
+      <c r="AD189" s="79"/>
+      <c r="AE189" s="79"/>
+      <c r="AF189" s="79"/>
+      <c r="AG189" s="77"/>
+    </row>
+    <row r="190" spans="1:33" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="37">
+        <v>81</v>
+      </c>
+      <c r="B190" s="38">
+        <f>IF(ISNUMBER(A190),
+IF(AND(A190=INT(A190), MOD(A190, 10) = 0), 0,
+IF(AND(A190=INT(A190), LEN(A190)=2), 1,
+IF(AND(A190=INT(A190), LEN(A190)=3), 2,
+LEN(A190) - FIND(".", A190) + 2)
+)
+),
+"")</f>
+        <v>1</v>
+      </c>
+      <c r="C190" s="56" t="s">
+        <v>410</v>
+      </c>
+      <c r="D190" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">      Refueling Operations</v>
+      </c>
+      <c r="E190" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="F190" s="39"/>
+      <c r="G190" s="39"/>
+      <c r="H190" s="39"/>
+      <c r="I190" s="39"/>
+      <c r="J190" s="43"/>
+      <c r="K190" s="61">
+        <v>178500</v>
+      </c>
+      <c r="L190" s="49" t="s">
+        <v>382</v>
+      </c>
+      <c r="M190" s="59" t="s">
+        <v>383</v>
+      </c>
+      <c r="N190" s="49"/>
+      <c r="O190" s="49"/>
+      <c r="P190" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q190" s="66">
         <v>2024</v>
       </c>
-      <c r="R184" s="49" t="s">
+      <c r="R190" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="S190" s="59"/>
+      <c r="T190" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="U190" s="49"/>
+      <c r="V190" s="49"/>
+      <c r="W190" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X190" s="80">
+        <f>0.9*$J190</f>
+        <v>0</v>
+      </c>
+      <c r="Y190" s="80">
+        <f>1.5*J190</f>
+        <v>0</v>
+      </c>
+      <c r="Z190" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA190" s="79">
+        <f>0.9*K190</f>
+        <v>160650</v>
+      </c>
+      <c r="AB190" s="79">
+        <f>1.3*K190</f>
+        <v>232050</v>
+      </c>
+      <c r="AC190" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD190" s="79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE190" s="79" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF190" s="79" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG190" s="77" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="191" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="37">
+        <v>82</v>
+      </c>
+      <c r="B191" s="38">
+        <f>IF(ISNUMBER(A191),
+IF(AND(A191=INT(A191), MOD(A191, 10) = 0), 0,
+IF(AND(A191=INT(A191), LEN(A191)=2), 1,
+IF(AND(A191=INT(A191), LEN(A191)=3), 2,
+LEN(A191) - FIND(".", A191) + 2)
+)
+),
+"")</f>
+        <v>1</v>
+      </c>
+      <c r="C191" s="56" t="s">
+        <v>411</v>
+      </c>
+      <c r="D191" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">      Additional Nuclear Fuel</v>
+      </c>
+      <c r="E191" s="39"/>
+      <c r="F191" s="39"/>
+      <c r="G191" s="39"/>
+      <c r="H191" s="39"/>
+      <c r="I191" s="39"/>
+      <c r="J191" s="43"/>
+      <c r="K191" s="61"/>
+      <c r="L191" s="49"/>
+      <c r="M191" s="59"/>
+      <c r="N191" s="49"/>
+      <c r="O191" s="49"/>
+      <c r="P191" s="49"/>
+      <c r="Q191" s="66"/>
+      <c r="R191" s="49"/>
+      <c r="S191" s="59"/>
+      <c r="T191" s="49"/>
+      <c r="U191" s="49"/>
+      <c r="V191" s="49"/>
+      <c r="W191" s="77"/>
+      <c r="X191" s="80"/>
+      <c r="Y191" s="80"/>
+      <c r="Z191" s="77"/>
+      <c r="AA191" s="79"/>
+      <c r="AB191" s="79"/>
+      <c r="AC191" s="77"/>
+      <c r="AD191" s="79"/>
+      <c r="AE191" s="79"/>
+      <c r="AF191" s="79"/>
+      <c r="AG191" s="77"/>
+    </row>
+    <row r="192" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="37">
+        <v>83</v>
+      </c>
+      <c r="B192" s="38">
+        <f>IF(ISNUMBER(A192),
+IF(AND(A192=INT(A192), MOD(A192, 10) = 0), 0,
+IF(AND(A192=INT(A192), LEN(A192)=2), 1,
+IF(AND(A192=INT(A192), LEN(A192)=3), 2,
+LEN(A192) - FIND(".", A192) + 2)
+)
+),
+"")</f>
+        <v>1</v>
+      </c>
+      <c r="C192" s="56" t="s">
+        <v>412</v>
+      </c>
+      <c r="D192" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">      Spent Fuel Management</v>
+      </c>
+      <c r="E192" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F192" s="39"/>
+      <c r="G192" s="39"/>
+      <c r="H192" s="39"/>
+      <c r="I192" s="39"/>
+      <c r="J192" s="43"/>
+      <c r="K192" s="61">
+        <v>1</v>
+      </c>
+      <c r="L192" s="49" t="s">
+        <v>413</v>
+      </c>
+      <c r="M192" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="N192" s="49"/>
+      <c r="O192" s="49"/>
+      <c r="P192" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q192" s="66">
+        <v>2024</v>
+      </c>
+      <c r="R192" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S184" s="59"/>
-      <c r="T184" s="49"/>
-      <c r="U184" s="49"/>
-      <c r="V184" s="49"/>
-      <c r="W184" s="77" t="s">
+      <c r="S192" s="59"/>
+      <c r="T192" s="49"/>
+      <c r="U192" s="49"/>
+      <c r="V192" s="49"/>
+      <c r="W192" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="X184" s="80">
-        <f>0.9*$J184</f>
-        <v>0</v>
-      </c>
-      <c r="Y184" s="80">
-        <f>1.5*J184</f>
-        <v>0</v>
-      </c>
-      <c r="Z184" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA184" s="79">
-        <f>0.9*K184</f>
+      <c r="X192" s="80">
+        <f>0.9*$J192</f>
+        <v>0</v>
+      </c>
+      <c r="Y192" s="80">
+        <f>1.5*J192</f>
+        <v>0</v>
+      </c>
+      <c r="Z192" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA192" s="79">
+        <f>0.9*K192</f>
         <v>0.9</v>
       </c>
-      <c r="AB184" s="79">
-        <f>1.3*K184</f>
+      <c r="AB192" s="79">
+        <f>1.3*K192</f>
         <v>1.3</v>
       </c>
-      <c r="AC184" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD184" s="79" t="s">
+      <c r="AC192" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD192" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="AE184" s="79" t="s">
+      <c r="AE192" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="AF184" s="79" t="s">
+      <c r="AF192" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="AG184" s="77" t="s">
+      <c r="AG192" s="77" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB184" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AB192" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="53">
     <mergeCell ref="T138:T143"/>
     <mergeCell ref="U30:U32"/>
     <mergeCell ref="S52:S54"/>
-    <mergeCell ref="T173:T179"/>
+    <mergeCell ref="T173:T187"/>
     <mergeCell ref="U15:U17"/>
     <mergeCell ref="U46:U48"/>
     <mergeCell ref="S145:S150"/>
@@ -19874,7 +20261,7 @@
     <mergeCell ref="S61:S63"/>
     <mergeCell ref="U61:U63"/>
     <mergeCell ref="U57:U59"/>
-    <mergeCell ref="S173:S179"/>
+    <mergeCell ref="S173:S187"/>
     <mergeCell ref="U76:U80"/>
     <mergeCell ref="S57:S59"/>
     <mergeCell ref="S37:S39"/>
@@ -19897,7 +20284,7 @@
     <mergeCell ref="T109:T110"/>
     <mergeCell ref="S138:S143"/>
     <mergeCell ref="T11:T13"/>
-    <mergeCell ref="V173:V179"/>
+    <mergeCell ref="V173:V187"/>
     <mergeCell ref="S30:S32"/>
     <mergeCell ref="S15:S17"/>
     <mergeCell ref="T37:T39"/>
@@ -19976,7 +20363,7 @@
       <formula>$B108=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A74:V99 A107:V107 A173:R179">
+  <conditionalFormatting sqref="A74:V99 A107:V107 A173:R187">
     <cfRule type="expression" dxfId="286" priority="487">
       <formula>$B74=2</formula>
     </cfRule>
@@ -20031,18 +20418,18 @@
       <formula>$B152=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A181:V184">
+  <conditionalFormatting sqref="A189:V192">
     <cfRule type="expression" dxfId="273" priority="649">
-      <formula>$B181=3</formula>
+      <formula>$B189=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="272" priority="650">
-      <formula>$B181=2</formula>
+      <formula>$B189=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="271" priority="651">
-      <formula>$B181&lt;2</formula>
+      <formula>$B189&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="270" priority="652">
-      <formula>$B181=0</formula>
+      <formula>$B189=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A109:F111 A112:V114 U116:V122 U123:U124 A127:S128 U127:V128 A138:B143 U138:V143 A144:V144 N145:V145 N146:R146 U146:V151 K147:R147 A151:T151 T155:V160 A161:V164 A165:J166 A167:L171 U169:V171">
@@ -20053,7 +20440,7 @@
       <formula>$B1=2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A7:AG51 A173:R179">
+  <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A7:AG51 A173:R187">
     <cfRule type="expression" dxfId="267" priority="489">
       <formula>$B1=0</formula>
     </cfRule>
@@ -20069,12 +20456,12 @@
       <formula>$B7&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG87 A100:B106 A112:AG123 A124:U124 W124:AG124 A125:AG134 A135:V135 A136:Y136 A137:AG137 S173:AG173 U174:U179 W174:AG179 A180:AG184 A97:AG97">
+  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG87 A100:B106 A112:AG123 A124:U124 W124:AG124 A125:AG134 A135:V135 A136:Y136 A137:AG137 S173:AG173 U174:U187 W174:AG187 A188:AG192 A97:AG97">
     <cfRule type="expression" dxfId="263" priority="750">
       <formula>$B49=2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG87 A97:AG97 A100:B106 A112:AG123 A124:U124 W124:AG124 A125:AG134 A135:V135 A136:Y136 A137:AG137 S173:AG173 U174:U179 W174:AG179 A180:AG184">
+  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG87 A97:AG97 A100:B106 A112:AG123 A124:U124 W124:AG124 A125:AG134 A135:V135 A136:Y136 A137:AG137 S173:AG173 U174:U187 W174:AG187 A188:AG192">
     <cfRule type="expression" dxfId="262" priority="751">
       <formula>$B49&lt;2</formula>
     </cfRule>
@@ -20132,7 +20519,7 @@
       <formula>$B144=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A180:AG184 A55:AG75 A83:AG87 A125:AG134 A135:V135 A136:Y136 A137:AG137 A112:AG123 A76:V82 A100:B106 A49:AG51 F52:AG52 F53:U54 A52:E54 W53:AG54 A124:U124 W124:AG124 S173:AG173 U174:U179 W174:AG179">
+  <conditionalFormatting sqref="A188:AG192 A55:AG75 A83:AG87 A125:AG134 A135:V135 A136:Y136 A137:AG137 A112:AG123 A76:V82 A100:B106 A49:AG51 F52:AG52 F53:U54 A52:E54 W53:AG54 A124:U124 W124:AG124 S173:AG173 U174:U187 W174:AG187">
     <cfRule type="expression" dxfId="248" priority="749">
       <formula>$B49=3</formula>
     </cfRule>
@@ -20206,7 +20593,7 @@
       <formula>$B138=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D80 D82 D87:D137 D144:D184">
+  <conditionalFormatting sqref="D2:D80 D82 D87:D137 D144:D192">
     <cfRule type="colorScale" priority="1037">
       <colorScale>
         <cfvo type="min"/>
@@ -20398,7 +20785,7 @@
       <formula>$B106=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:U54 W53:AG54 A55:AG75 A107:AG108 A109:V112 A112:AG123 A124:U124 W124:AG124 A125:AG134 A129:V144 S173:AG173 U174:U179 W174:AG179 A180:AG184">
+  <conditionalFormatting sqref="F53:U54 W53:AG54 A55:AG75 A107:AG108 A109:V112 A112:AG123 A124:U124 W124:AG124 A125:AG134 A129:V144 S173:AG173 U174:U187 W174:AG187 A188:AG192">
     <cfRule type="expression" dxfId="188" priority="752">
       <formula>$B53=0</formula>
     </cfRule>
@@ -21102,31 +21489,31 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="15">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q152 Q154:Q184 Q185:R192" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q152 Q154:Q192 Q185:R192" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1950</formula1>
       <formula2>2025</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J130 J133:J134 J137:J144 J148:J184 K2:K9 K11:K48 K52:K54 K57:K59 K61:K63 K67:K79 K87 K97:K107 K109:K150 K152:K184 N1:N67 N71:N83 N88:N106 N105:N1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J130 J133:J134 J137:J144 J148:J192 K2:K9 K11:K48 K52:K54 K57:K59 K61:K63 K67:K79 K87 K97:K107 K109:K150 K152:K192 N1:N67 N71:N83 N88:N106 N105:N1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M359:M369" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Land Area, Power MWe, Excavation Volume,  Reactor Building Slab Roof Volume,	Reactor Building  Basement Volume, Reactor Building  Exterior Walls Volume,		Turbine Building Slab Roof Volume,	Turbine Building  Basement Volume,	Turbine Building  Exterior Wall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 L182:L1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 L190:L1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"$/acres, $/MWe, $/m^3, $/MWt"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P185:P338" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P80 P82:P137 P144:P184" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P80 P82:P137 P144:P192" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O80 O82:O134 O137 O144:O184" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O80 O82:O134 O137 O144:O192" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"acres, MWe, m^3, MWt, Kg, Drums, kW, $, m^2, kg/s"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L80 L82:L113 L115:L137 L144:L184" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L80 L82:L113 L115:L137 L144:L192" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"$/m^2,$/MWeHour,$/FTE, $/acres, $/MWe, $/m^3, $/MWt, $/Kg, $/Drum, $/(kg.sec), $/SWU, unitless, $/kWe"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O135:O136" xr:uid="{00000000-0002-0000-0000-000008000000}">
@@ -21142,10 +21529,10 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E184" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E192" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>"standard, nonstandard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R184" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R192" xr:uid="{00000000-0002-0000-0000-00000D000000}">
       <formula1>"NA, General, Labor, Material, Equipment,Lab and Mat and Equip, 'Lab and Equip"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L114" xr:uid="{00000000-0002-0000-0000-00000E000000}">

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -692,7 +692,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3660" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3668" uniqueCount="807">
   <si>
     <t>Account</t>
   </si>
@@ -3185,6 +3185,33 @@
   </si>
   <si>
     <t>Annualized Moderator Booster Replacements</t>
+  </si>
+  <si>
+    <t>Annualized Plant Maintenance (Misc.)</t>
+  </si>
+  <si>
+    <t>Annualized Building and Structural Maintenance (Accounts 212–215)</t>
+  </si>
+  <si>
+    <t>Annualized Main Heat Transport System Maintenance (Accounts 222.1–222.3 and 222.6)</t>
+  </si>
+  <si>
+    <t>Annualized Safety System Maintenance (Account 223)</t>
+  </si>
+  <si>
+    <t>Annualized Reactor Plant Equipment Maintenance (Accounts 221.11, 226, and 228)</t>
+  </si>
+  <si>
+    <t>Annualized Reactor I&amp;C Maintenance (Account 227)</t>
+  </si>
+  <si>
+    <t>Annualized Energy Conversion System Maintenance (Account 23)</t>
+  </si>
+  <si>
+    <t>Annualized Electrical Equipment Maintenance (Account 24)</t>
+  </si>
+  <si>
+    <t>Annualized Miscellaneous Equipment Maintenance (Account 26)</t>
   </si>
 </sst>
 </file>
@@ -7850,7 +7877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG184"/>
+  <dimension ref="A1:AG192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="3" customWidth="1"/>
@@ -21034,7 +21061,7 @@
         <v>384</v>
       </c>
       <c r="D165" s="39" t="str">
-        <f t="shared" ref="D162:D181" si="43">REPT("   ", B165*2) &amp; C165</f>
+        <f t="shared" ref="D162:D189" si="43">REPT("   ", B165*2) &amp; C165</f>
         <v xml:space="preserve">            Operators </v>
       </c>
       <c r="E165" s="39" t="s">
@@ -21942,11 +21969,11 @@
         <v>2</v>
       </c>
       <c r="C179" s="55" t="s">
-        <v>410</v>
+        <v>798</v>
       </c>
       <c r="D179" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Misc. Replacements</v>
+        <v xml:space="preserve">            Annualized Plant Maintenance (Misc.)</v>
       </c>
       <c r="E179" s="39"/>
       <c r="F179" s="39"/>
@@ -21978,27 +22005,20 @@
       <c r="AF179" s="76"/>
       <c r="AG179" s="74"/>
     </row>
-    <row r="180" spans="1:33" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="37">
-        <v>78</v>
+        <v>759.1</v>
       </c>
       <c r="B180" s="38">
-        <f>IF(ISNUMBER(A180),
-    IF(AND(A180=INT(A180), MOD(A180, 10) = 0), 0,
-        IF(AND(A180=INT(A180), LEN(A180)=2), 1,
-            IF(AND(A180=INT(A180), LEN(A180)=3), 2,
-                LEN(A180) - FIND(".", A180) + 2)
-        )
-    ),
-"")</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(A180),IF(AND(A180=INT(A180),MOD(A180,10)=0),0,IF(AND(A180=INT(A180),LEN(A180)=2),1,IF(AND(A180=INT(A180),LEN(A180)=3),2,LEN(A180)-FIND(".",A180)+2))),"")</f>
+        <v>3</v>
       </c>
       <c r="C180" s="55" t="s">
-        <v>411</v>
+        <v>799</v>
       </c>
       <c r="D180" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">      Annualized Decommissioning Cost</v>
+        <f>REPT("   ",B180*2)&amp;C180</f>
+        <v>                  Annualized Building and Structural Maintenance (Accounts 212–215)</v>
       </c>
       <c r="E180" s="39"/>
       <c r="F180" s="39"/>
@@ -22006,20 +22026,18 @@
       <c r="H180" s="39"/>
       <c r="I180" s="39"/>
       <c r="J180" s="43"/>
-      <c r="K180" s="70"/>
+      <c r="K180" s="60"/>
       <c r="L180" s="49"/>
-      <c r="M180" s="45"/>
+      <c r="M180" s="58"/>
       <c r="N180" s="49"/>
       <c r="O180" s="49"/>
       <c r="P180" s="49"/>
       <c r="Q180" s="65"/>
       <c r="R180" s="49"/>
-      <c r="S180" s="58"/>
-      <c r="T180" s="58"/>
+      <c r="S180" s="209"/>
+      <c r="T180" s="209"/>
       <c r="U180" s="49"/>
-      <c r="V180" s="58" t="s">
-        <v>412</v>
-      </c>
+      <c r="V180" s="209"/>
       <c r="W180" s="74"/>
       <c r="X180" s="77"/>
       <c r="Y180" s="77"/>
@@ -22032,46 +22050,39 @@
       <c r="AF180" s="76"/>
       <c r="AG180" s="74"/>
     </row>
-    <row r="181" spans="1:33" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="37">
-        <v>80</v>
+        <v>759.2</v>
       </c>
       <c r="B181" s="38">
-        <f>IF(ISNUMBER(A181),
-IF(AND(A181=INT(A181), MOD(A181, 10) = 0), 0,
-IF(AND(A181=INT(A181), LEN(A181)=2), 1,
-IF(AND(A181=INT(A181), LEN(A181)=3), 2,
-LEN(A181) - FIND(".", A181) + 2)
-)
-),
-"")</f>
-        <v>0</v>
-      </c>
-      <c r="C181" s="69" t="s">
-        <v>413</v>
+        <f>IF(ISNUMBER(A181),IF(AND(A181=INT(A181),MOD(A181,10)=0),0,IF(AND(A181=INT(A181),LEN(A181)=2),1,IF(AND(A181=INT(A181),LEN(A181)=3),2,LEN(A181)-FIND(".",A181)+2))),"")</f>
+        <v>3</v>
+      </c>
+      <c r="C181" s="55" t="s">
+        <v>800</v>
       </c>
       <c r="D181" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v>Annualized Fuel Cost</v>
+        <f>REPT("   ",B181*2)&amp;C181</f>
+        <v>                  Annualized Main Heat Transport System Maintenance (Accounts 222.1–222.3 and 222.6)</v>
       </c>
       <c r="E181" s="39"/>
       <c r="F181" s="39"/>
       <c r="G181" s="39"/>
       <c r="H181" s="39"/>
       <c r="I181" s="39"/>
-      <c r="J181" s="40"/>
-      <c r="K181" s="40"/>
-      <c r="L181" s="38"/>
-      <c r="M181" s="41"/>
-      <c r="N181" s="38"/>
-      <c r="O181" s="38"/>
-      <c r="P181" s="38"/>
-      <c r="Q181" s="40"/>
-      <c r="R181" s="38"/>
-      <c r="S181" s="41"/>
-      <c r="T181" s="38"/>
-      <c r="U181" s="38"/>
-      <c r="V181" s="38"/>
+      <c r="J181" s="43"/>
+      <c r="K181" s="60"/>
+      <c r="L181" s="49"/>
+      <c r="M181" s="58"/>
+      <c r="N181" s="49"/>
+      <c r="O181" s="49"/>
+      <c r="P181" s="49"/>
+      <c r="Q181" s="65"/>
+      <c r="R181" s="49"/>
+      <c r="S181" s="209"/>
+      <c r="T181" s="209"/>
+      <c r="U181" s="49"/>
+      <c r="V181" s="209"/>
       <c r="W181" s="74"/>
       <c r="X181" s="77"/>
       <c r="Y181" s="77"/>
@@ -22084,121 +22095,65 @@
       <c r="AF181" s="76"/>
       <c r="AG181" s="74"/>
     </row>
-    <row r="182" spans="1:33" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="37">
-        <v>81</v>
+        <v>759.3</v>
       </c>
       <c r="B182" s="38">
-        <f>IF(ISNUMBER(A182),
-IF(AND(A182=INT(A182), MOD(A182, 10) = 0), 0,
-IF(AND(A182=INT(A182), LEN(A182)=2), 1,
-IF(AND(A182=INT(A182), LEN(A182)=3), 2,
-LEN(A182) - FIND(".", A182) + 2)
-)
-),
-"")</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(A182),IF(AND(A182=INT(A182),MOD(A182,10)=0),0,IF(AND(A182=INT(A182),LEN(A182)=2),1,IF(AND(A182=INT(A182),LEN(A182)=3),2,LEN(A182)-FIND(".",A182)+2))),"")</f>
+        <v>3</v>
       </c>
       <c r="C182" s="55" t="s">
-        <v>414</v>
+        <v>801</v>
       </c>
       <c r="D182" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">      Refueling Operations</v>
-      </c>
-      <c r="E182" s="39" t="s">
-        <v>267</v>
-      </c>
+        <f>REPT("   ",B182*2)&amp;C182</f>
+        <v>                  Annualized Safety System Maintenance (Account 223)</v>
+      </c>
+      <c r="E182" s="39"/>
       <c r="F182" s="39"/>
       <c r="G182" s="39"/>
       <c r="H182" s="39"/>
       <c r="I182" s="39"/>
       <c r="J182" s="43"/>
-      <c r="K182" s="60">
-        <v>178500</v>
-      </c>
-      <c r="L182" s="49" t="s">
-        <v>385</v>
-      </c>
-      <c r="M182" s="58" t="s">
-        <v>386</v>
-      </c>
+      <c r="K182" s="60"/>
+      <c r="L182" s="49"/>
+      <c r="M182" s="58"/>
       <c r="N182" s="49"/>
       <c r="O182" s="49"/>
-      <c r="P182" s="49">
-        <v>1</v>
-      </c>
-      <c r="Q182" s="65">
-        <v>2024</v>
-      </c>
-      <c r="R182" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S182" s="58"/>
-      <c r="T182" s="58" t="s">
-        <v>387</v>
-      </c>
+      <c r="P182" s="49"/>
+      <c r="Q182" s="65"/>
+      <c r="R182" s="49"/>
+      <c r="S182" s="209"/>
+      <c r="T182" s="209"/>
       <c r="U182" s="49"/>
-      <c r="V182" s="49"/>
-      <c r="W182" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="X182" s="77">
-        <f>0.9*$J182</f>
-        <v>0</v>
-      </c>
-      <c r="Y182" s="77">
-        <f>1.5*J182</f>
-        <v>0</v>
-      </c>
-      <c r="Z182" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA182" s="76">
-        <f>0.9*K182</f>
-        <v>160650</v>
-      </c>
-      <c r="AB182" s="76">
-        <f>1.3*K182</f>
-        <v>232050</v>
-      </c>
-      <c r="AC182" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD182" s="76" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE182" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF182" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG182" s="74" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="183" spans="1:33" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="V182" s="209"/>
+      <c r="W182" s="74"/>
+      <c r="X182" s="77"/>
+      <c r="Y182" s="77"/>
+      <c r="Z182" s="74"/>
+      <c r="AA182" s="76"/>
+      <c r="AB182" s="76"/>
+      <c r="AC182" s="74"/>
+      <c r="AD182" s="76"/>
+      <c r="AE182" s="76"/>
+      <c r="AF182" s="76"/>
+      <c r="AG182" s="74"/>
+    </row>
+    <row r="183" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="37">
-        <v>82</v>
+        <v>759.4</v>
       </c>
       <c r="B183" s="38">
-        <f>IF(ISNUMBER(A183),
-IF(AND(A183=INT(A183), MOD(A183, 10) = 0), 0,
-IF(AND(A183=INT(A183), LEN(A183)=2), 1,
-IF(AND(A183=INT(A183), LEN(A183)=3), 2,
-LEN(A183) - FIND(".", A183) + 2)
-)
-),
-"")</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(A183),IF(AND(A183=INT(A183),MOD(A183,10)=0),0,IF(AND(A183=INT(A183),LEN(A183)=2),1,IF(AND(A183=INT(A183),LEN(A183)=3),2,LEN(A183)-FIND(".",A183)+2))),"")</f>
+        <v>3</v>
       </c>
       <c r="C183" s="55" t="s">
-        <v>415</v>
+        <v>802</v>
       </c>
       <c r="D183" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">      Additional Nuclear Fuel</v>
+        <f>REPT("   ",B183*2)&amp;C183</f>
+        <v>                  Annualized Reactor Plant Equipment Maintenance (Accounts 221.11, 226, and 228)</v>
       </c>
       <c r="E183" s="39"/>
       <c r="F183" s="39"/>
@@ -22214,10 +22169,10 @@
       <c r="P183" s="49"/>
       <c r="Q183" s="65"/>
       <c r="R183" s="49"/>
-      <c r="S183" s="58"/>
-      <c r="T183" s="49"/>
+      <c r="S183" s="209"/>
+      <c r="T183" s="209"/>
       <c r="U183" s="49"/>
-      <c r="V183" s="49"/>
+      <c r="V183" s="209"/>
       <c r="W183" s="74"/>
       <c r="X183" s="77"/>
       <c r="Y183" s="77"/>
@@ -22230,95 +22185,527 @@
       <c r="AF183" s="76"/>
       <c r="AG183" s="74"/>
     </row>
-    <row r="184" spans="1:33" ht="38.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="37">
-        <v>83</v>
+        <v>759.5</v>
       </c>
       <c r="B184" s="38">
-        <f>IF(ISNUMBER(A184),
-IF(AND(A184=INT(A184), MOD(A184, 10) = 0), 0,
-IF(AND(A184=INT(A184), LEN(A184)=2), 1,
-IF(AND(A184=INT(A184), LEN(A184)=3), 2,
-LEN(A184) - FIND(".", A184) + 2)
-)
-),
-"")</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(A184),IF(AND(A184=INT(A184),MOD(A184,10)=0),0,IF(AND(A184=INT(A184),LEN(A184)=2),1,IF(AND(A184=INT(A184),LEN(A184)=3),2,LEN(A184)-FIND(".",A184)+2))),"")</f>
+        <v>3</v>
       </c>
       <c r="C184" s="55" t="s">
-        <v>416</v>
+        <v>803</v>
       </c>
       <c r="D184" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">      Spent Fuel Management</v>
-      </c>
-      <c r="E184" s="39" t="s">
-        <v>35</v>
-      </c>
+        <f>REPT("   ",B184*2)&amp;C184</f>
+        <v>                  Annualized Reactor I&amp;C Maintenance (Account 227)</v>
+      </c>
+      <c r="E184" s="39"/>
       <c r="F184" s="39"/>
       <c r="G184" s="39"/>
       <c r="H184" s="39"/>
       <c r="I184" s="39"/>
       <c r="J184" s="43"/>
-      <c r="K184" s="60">
-        <v>1</v>
-      </c>
-      <c r="L184" s="49" t="s">
-        <v>417</v>
-      </c>
-      <c r="M184" s="58" t="s">
-        <v>418</v>
-      </c>
+      <c r="K184" s="60"/>
+      <c r="L184" s="49"/>
+      <c r="M184" s="58"/>
       <c r="N184" s="49"/>
       <c r="O184" s="49"/>
-      <c r="P184" s="49">
+      <c r="P184" s="49"/>
+      <c r="Q184" s="65"/>
+      <c r="R184" s="49"/>
+      <c r="S184" s="209"/>
+      <c r="T184" s="209"/>
+      <c r="U184" s="49"/>
+      <c r="V184" s="209"/>
+      <c r="W184" s="74"/>
+      <c r="X184" s="77"/>
+      <c r="Y184" s="77"/>
+      <c r="Z184" s="74"/>
+      <c r="AA184" s="76"/>
+      <c r="AB184" s="76"/>
+      <c r="AC184" s="74"/>
+      <c r="AD184" s="76"/>
+      <c r="AE184" s="76"/>
+      <c r="AF184" s="76"/>
+      <c r="AG184" s="74"/>
+    </row>
+    <row r="185" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="37">
+        <v>759.6</v>
+      </c>
+      <c r="B185" s="38">
+        <f>IF(ISNUMBER(A185),IF(AND(A185=INT(A185),MOD(A185,10)=0),0,IF(AND(A185=INT(A185),LEN(A185)=2),1,IF(AND(A185=INT(A185),LEN(A185)=3),2,LEN(A185)-FIND(".",A185)+2))),"")</f>
+        <v>3</v>
+      </c>
+      <c r="C185" s="55" t="s">
+        <v>804</v>
+      </c>
+      <c r="D185" s="39" t="str">
+        <f>REPT("   ",B185*2)&amp;C185</f>
+        <v>                  Annualized Energy Conversion System Maintenance (Account 23)</v>
+      </c>
+      <c r="E185" s="39"/>
+      <c r="F185" s="39"/>
+      <c r="G185" s="39"/>
+      <c r="H185" s="39"/>
+      <c r="I185" s="39"/>
+      <c r="J185" s="43"/>
+      <c r="K185" s="60"/>
+      <c r="L185" s="49"/>
+      <c r="M185" s="58"/>
+      <c r="N185" s="49"/>
+      <c r="O185" s="49"/>
+      <c r="P185" s="49"/>
+      <c r="Q185" s="65"/>
+      <c r="R185" s="49"/>
+      <c r="S185" s="209"/>
+      <c r="T185" s="209"/>
+      <c r="U185" s="49"/>
+      <c r="V185" s="209"/>
+      <c r="W185" s="74"/>
+      <c r="X185" s="77"/>
+      <c r="Y185" s="77"/>
+      <c r="Z185" s="74"/>
+      <c r="AA185" s="76"/>
+      <c r="AB185" s="76"/>
+      <c r="AC185" s="74"/>
+      <c r="AD185" s="76"/>
+      <c r="AE185" s="76"/>
+      <c r="AF185" s="76"/>
+      <c r="AG185" s="74"/>
+    </row>
+    <row r="186" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="37">
+        <v>759.7</v>
+      </c>
+      <c r="B186" s="38">
+        <f>IF(ISNUMBER(A186),IF(AND(A186=INT(A186),MOD(A186,10)=0),0,IF(AND(A186=INT(A186),LEN(A186)=2),1,IF(AND(A186=INT(A186),LEN(A186)=3),2,LEN(A186)-FIND(".",A186)+2))),"")</f>
+        <v>3</v>
+      </c>
+      <c r="C186" s="55" t="s">
+        <v>805</v>
+      </c>
+      <c r="D186" s="39" t="str">
+        <f>REPT("   ",B186*2)&amp;C186</f>
+        <v>                  Annualized Electrical Equipment Maintenance (Account 24)</v>
+      </c>
+      <c r="E186" s="39"/>
+      <c r="F186" s="39"/>
+      <c r="G186" s="39"/>
+      <c r="H186" s="39"/>
+      <c r="I186" s="39"/>
+      <c r="J186" s="43"/>
+      <c r="K186" s="60"/>
+      <c r="L186" s="49"/>
+      <c r="M186" s="58"/>
+      <c r="N186" s="49"/>
+      <c r="O186" s="49"/>
+      <c r="P186" s="49"/>
+      <c r="Q186" s="65"/>
+      <c r="R186" s="49"/>
+      <c r="S186" s="209"/>
+      <c r="T186" s="209"/>
+      <c r="U186" s="49"/>
+      <c r="V186" s="209"/>
+      <c r="W186" s="74"/>
+      <c r="X186" s="77"/>
+      <c r="Y186" s="77"/>
+      <c r="Z186" s="74"/>
+      <c r="AA186" s="76"/>
+      <c r="AB186" s="76"/>
+      <c r="AC186" s="74"/>
+      <c r="AD186" s="76"/>
+      <c r="AE186" s="76"/>
+      <c r="AF186" s="76"/>
+      <c r="AG186" s="74"/>
+    </row>
+    <row r="187" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="37">
+        <v>759.8</v>
+      </c>
+      <c r="B187" s="38">
+        <f>IF(ISNUMBER(A187),IF(AND(A187=INT(A187),MOD(A187,10)=0),0,IF(AND(A187=INT(A187),LEN(A187)=2),1,IF(AND(A187=INT(A187),LEN(A187)=3),2,LEN(A187)-FIND(".",A187)+2))),"")</f>
+        <v>3</v>
+      </c>
+      <c r="C187" s="55" t="s">
+        <v>806</v>
+      </c>
+      <c r="D187" s="39" t="str">
+        <f>REPT("   ",B187*2)&amp;C187</f>
+        <v>                  Annualized Miscellaneous Equipment Maintenance (Account 26)</v>
+      </c>
+      <c r="E187" s="39"/>
+      <c r="F187" s="39"/>
+      <c r="G187" s="39"/>
+      <c r="H187" s="39"/>
+      <c r="I187" s="39"/>
+      <c r="J187" s="43"/>
+      <c r="K187" s="60"/>
+      <c r="L187" s="49"/>
+      <c r="M187" s="58"/>
+      <c r="N187" s="49"/>
+      <c r="O187" s="49"/>
+      <c r="P187" s="49"/>
+      <c r="Q187" s="65"/>
+      <c r="R187" s="49"/>
+      <c r="S187" s="209"/>
+      <c r="T187" s="209"/>
+      <c r="U187" s="49"/>
+      <c r="V187" s="209"/>
+      <c r="W187" s="74"/>
+      <c r="X187" s="77"/>
+      <c r="Y187" s="77"/>
+      <c r="Z187" s="74"/>
+      <c r="AA187" s="76"/>
+      <c r="AB187" s="76"/>
+      <c r="AC187" s="74"/>
+      <c r="AD187" s="76"/>
+      <c r="AE187" s="76"/>
+      <c r="AF187" s="76"/>
+      <c r="AG187" s="74"/>
+    </row>
+    <row r="188" spans="1:33" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="37">
+        <v>78</v>
+      </c>
+      <c r="B188" s="38">
+        <f>IF(ISNUMBER(A188),
+    IF(AND(A188=INT(A188), MOD(A188, 10) = 0), 0,
+        IF(AND(A188=INT(A188), LEN(A188)=2), 1,
+            IF(AND(A188=INT(A188), LEN(A188)=3), 2,
+                LEN(A188) - FIND(".", A188) + 2)
+        )
+    ),
+"")</f>
         <v>1</v>
       </c>
-      <c r="Q184" s="65">
+      <c r="C188" s="55" t="s">
+        <v>411</v>
+      </c>
+      <c r="D188" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">      Annualized Decommissioning Cost</v>
+      </c>
+      <c r="E188" s="39"/>
+      <c r="F188" s="39"/>
+      <c r="G188" s="39"/>
+      <c r="H188" s="39"/>
+      <c r="I188" s="39"/>
+      <c r="J188" s="43"/>
+      <c r="K188" s="70"/>
+      <c r="L188" s="49"/>
+      <c r="M188" s="45"/>
+      <c r="N188" s="49"/>
+      <c r="O188" s="49"/>
+      <c r="P188" s="49"/>
+      <c r="Q188" s="65"/>
+      <c r="R188" s="49"/>
+      <c r="S188" s="58"/>
+      <c r="T188" s="58"/>
+      <c r="U188" s="49"/>
+      <c r="V188" s="58" t="s">
+        <v>412</v>
+      </c>
+      <c r="W188" s="74"/>
+      <c r="X188" s="77"/>
+      <c r="Y188" s="77"/>
+      <c r="Z188" s="74"/>
+      <c r="AA188" s="76"/>
+      <c r="AB188" s="76"/>
+      <c r="AC188" s="74"/>
+      <c r="AD188" s="76"/>
+      <c r="AE188" s="76"/>
+      <c r="AF188" s="76"/>
+      <c r="AG188" s="74"/>
+    </row>
+    <row r="189" spans="1:33" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="37">
+        <v>80</v>
+      </c>
+      <c r="B189" s="38">
+        <f>IF(ISNUMBER(A189),
+IF(AND(A189=INT(A189), MOD(A189, 10) = 0), 0,
+IF(AND(A189=INT(A189), LEN(A189)=2), 1,
+IF(AND(A189=INT(A189), LEN(A189)=3), 2,
+LEN(A189) - FIND(".", A189) + 2)
+)
+),
+"")</f>
+        <v>0</v>
+      </c>
+      <c r="C189" s="69" t="s">
+        <v>413</v>
+      </c>
+      <c r="D189" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v>Annualized Fuel Cost</v>
+      </c>
+      <c r="E189" s="39"/>
+      <c r="F189" s="39"/>
+      <c r="G189" s="39"/>
+      <c r="H189" s="39"/>
+      <c r="I189" s="39"/>
+      <c r="J189" s="40"/>
+      <c r="K189" s="40"/>
+      <c r="L189" s="38"/>
+      <c r="M189" s="41"/>
+      <c r="N189" s="38"/>
+      <c r="O189" s="38"/>
+      <c r="P189" s="38"/>
+      <c r="Q189" s="40"/>
+      <c r="R189" s="38"/>
+      <c r="S189" s="41"/>
+      <c r="T189" s="38"/>
+      <c r="U189" s="38"/>
+      <c r="V189" s="38"/>
+      <c r="W189" s="74"/>
+      <c r="X189" s="77"/>
+      <c r="Y189" s="77"/>
+      <c r="Z189" s="74"/>
+      <c r="AA189" s="76"/>
+      <c r="AB189" s="76"/>
+      <c r="AC189" s="74"/>
+      <c r="AD189" s="76"/>
+      <c r="AE189" s="76"/>
+      <c r="AF189" s="76"/>
+      <c r="AG189" s="74"/>
+    </row>
+    <row r="190" spans="1:33" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="37">
+        <v>81</v>
+      </c>
+      <c r="B190" s="38">
+        <f>IF(ISNUMBER(A190),
+IF(AND(A190=INT(A190), MOD(A190, 10) = 0), 0,
+IF(AND(A190=INT(A190), LEN(A190)=2), 1,
+IF(AND(A190=INT(A190), LEN(A190)=3), 2,
+LEN(A190) - FIND(".", A190) + 2)
+)
+),
+"")</f>
+        <v>1</v>
+      </c>
+      <c r="C190" s="55" t="s">
+        <v>414</v>
+      </c>
+      <c r="D190" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">      Refueling Operations</v>
+      </c>
+      <c r="E190" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="F190" s="39"/>
+      <c r="G190" s="39"/>
+      <c r="H190" s="39"/>
+      <c r="I190" s="39"/>
+      <c r="J190" s="43"/>
+      <c r="K190" s="60">
+        <v>178500</v>
+      </c>
+      <c r="L190" s="49" t="s">
+        <v>385</v>
+      </c>
+      <c r="M190" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="N190" s="49"/>
+      <c r="O190" s="49"/>
+      <c r="P190" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q190" s="65">
         <v>2024</v>
       </c>
-      <c r="R184" s="49" t="s">
+      <c r="R190" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="S190" s="58"/>
+      <c r="T190" s="58" t="s">
+        <v>387</v>
+      </c>
+      <c r="U190" s="49"/>
+      <c r="V190" s="49"/>
+      <c r="W190" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X190" s="77">
+        <f>0.9*$J190</f>
+        <v>0</v>
+      </c>
+      <c r="Y190" s="77">
+        <f>1.5*J190</f>
+        <v>0</v>
+      </c>
+      <c r="Z190" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA190" s="76">
+        <f>0.9*K190</f>
+        <v>160650</v>
+      </c>
+      <c r="AB190" s="76">
+        <f>1.3*K190</f>
+        <v>232050</v>
+      </c>
+      <c r="AC190" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD190" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE190" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF190" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG190" s="74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="191" spans="1:33" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="37">
+        <v>82</v>
+      </c>
+      <c r="B191" s="38">
+        <f>IF(ISNUMBER(A191),
+IF(AND(A191=INT(A191), MOD(A191, 10) = 0), 0,
+IF(AND(A191=INT(A191), LEN(A191)=2), 1,
+IF(AND(A191=INT(A191), LEN(A191)=3), 2,
+LEN(A191) - FIND(".", A191) + 2)
+)
+),
+"")</f>
+        <v>1</v>
+      </c>
+      <c r="C191" s="55" t="s">
+        <v>415</v>
+      </c>
+      <c r="D191" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">      Additional Nuclear Fuel</v>
+      </c>
+      <c r="E191" s="39"/>
+      <c r="F191" s="39"/>
+      <c r="G191" s="39"/>
+      <c r="H191" s="39"/>
+      <c r="I191" s="39"/>
+      <c r="J191" s="43"/>
+      <c r="K191" s="60"/>
+      <c r="L191" s="49"/>
+      <c r="M191" s="58"/>
+      <c r="N191" s="49"/>
+      <c r="O191" s="49"/>
+      <c r="P191" s="49"/>
+      <c r="Q191" s="65"/>
+      <c r="R191" s="49"/>
+      <c r="S191" s="58"/>
+      <c r="T191" s="49"/>
+      <c r="U191" s="49"/>
+      <c r="V191" s="49"/>
+      <c r="W191" s="74"/>
+      <c r="X191" s="77"/>
+      <c r="Y191" s="77"/>
+      <c r="Z191" s="74"/>
+      <c r="AA191" s="76"/>
+      <c r="AB191" s="76"/>
+      <c r="AC191" s="74"/>
+      <c r="AD191" s="76"/>
+      <c r="AE191" s="76"/>
+      <c r="AF191" s="76"/>
+      <c r="AG191" s="74"/>
+    </row>
+    <row r="192" spans="1:33" ht="38.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="37">
+        <v>83</v>
+      </c>
+      <c r="B192" s="38">
+        <f>IF(ISNUMBER(A192),
+IF(AND(A192=INT(A192), MOD(A192, 10) = 0), 0,
+IF(AND(A192=INT(A192), LEN(A192)=2), 1,
+IF(AND(A192=INT(A192), LEN(A192)=3), 2,
+LEN(A192) - FIND(".", A192) + 2)
+)
+),
+"")</f>
+        <v>1</v>
+      </c>
+      <c r="C192" s="55" t="s">
+        <v>416</v>
+      </c>
+      <c r="D192" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">      Spent Fuel Management</v>
+      </c>
+      <c r="E192" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F192" s="39"/>
+      <c r="G192" s="39"/>
+      <c r="H192" s="39"/>
+      <c r="I192" s="39"/>
+      <c r="J192" s="43"/>
+      <c r="K192" s="60">
+        <v>1</v>
+      </c>
+      <c r="L192" s="49" t="s">
+        <v>417</v>
+      </c>
+      <c r="M192" s="58" t="s">
+        <v>418</v>
+      </c>
+      <c r="N192" s="49"/>
+      <c r="O192" s="49"/>
+      <c r="P192" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q192" s="65">
+        <v>2024</v>
+      </c>
+      <c r="R192" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="S184" s="58"/>
-      <c r="T184" s="49"/>
-      <c r="U184" s="49"/>
-      <c r="V184" s="49"/>
-      <c r="W184" s="74" t="s">
+      <c r="S192" s="58"/>
+      <c r="T192" s="49"/>
+      <c r="U192" s="49"/>
+      <c r="V192" s="49"/>
+      <c r="W192" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="X184" s="77">
-        <f>0.9*$J184</f>
-        <v>0</v>
-      </c>
-      <c r="Y184" s="77">
-        <f>1.5*J184</f>
-        <v>0</v>
-      </c>
-      <c r="Z184" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA184" s="76">
-        <f>0.9*K184</f>
+      <c r="X192" s="77">
+        <f>0.9*$J192</f>
+        <v>0</v>
+      </c>
+      <c r="Y192" s="77">
+        <f>1.5*J192</f>
+        <v>0</v>
+      </c>
+      <c r="Z192" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA192" s="76">
+        <f>0.9*K192</f>
         <v>0.9</v>
       </c>
-      <c r="AB184" s="76">
-        <f>1.3*K184</f>
+      <c r="AB192" s="76">
+        <f>1.3*K192</f>
         <v>1.3</v>
       </c>
-      <c r="AC184" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD184" s="76" t="s">
+      <c r="AC192" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD192" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="AE184" s="76" t="s">
+      <c r="AE192" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="AF184" s="76" t="s">
+      <c r="AF192" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="AG184" s="74" t="s">
+      <c r="AG192" s="74" t="s">
         <v>48</v>
       </c>
     </row>
@@ -22492,7 +22879,7 @@
       <formula>$B149=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A178:V181">
+  <conditionalFormatting sqref="A178:V189">
     <cfRule type="expression" dxfId="374" priority="649">
       <formula>$B178=3</formula>
     </cfRule>
@@ -22530,12 +22917,12 @@
       <formula>$B7&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG84 A97:B103 A109:AG120 A121:U121 W121:AG121 A122:AG131 A132:V132 A133:Y133 A134:AG134 S170:AG170 U171:U176 W171:AG176 A177:AG181 A94:AG94">
+  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG84 A97:B103 A109:AG120 A121:U121 W121:AG121 A122:AG131 A132:V132 A133:Y133 A134:AG134 S170:AG170 U171:U176 W171:AG176 A177:AG189 A94:AG94">
     <cfRule type="expression" dxfId="364" priority="750">
       <formula>$B49=2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG84 A94:AG94 A97:B103 A109:AG120 A121:U121 W121:AG121 A122:AG131 A132:V132 A133:Y133 A134:AG134 S170:AG170 U171:U176 W171:AG176 A177:AG181">
+  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG84 A94:AG94 A97:B103 A109:AG120 A121:U121 W121:AG121 A122:AG131 A132:V132 A133:Y133 A134:AG134 S170:AG170 U171:U176 W171:AG176 A177:AG189">
     <cfRule type="expression" dxfId="363" priority="751">
       <formula>$B49&lt;2</formula>
     </cfRule>
@@ -22593,7 +22980,7 @@
       <formula>$B141=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A177:AG181 A55:AG75 A83:AG84 A122:AG131 A132:V132 A133:Y133 A134:AG134 A109:AG120 A76:V82 A97:B103 A49:AG51 F52:AG52 F53:U54 A52:E54 W53:AG54 A121:U121 W121:AG121 S170:AG170 U171:U176 W171:AG176">
+  <conditionalFormatting sqref="A177:AG189 A55:AG75 A83:AG84 A122:AG131 A132:V132 A133:Y133 A134:AG134 A109:AG120 A76:V82 A97:B103 A49:AG51 F52:AG52 F53:U54 A52:E54 W53:AG54 A121:U121 W121:AG121 S170:AG170 U171:U176 W171:AG176">
     <cfRule type="expression" dxfId="349" priority="749">
       <formula>$B49=3</formula>
     </cfRule>
@@ -22667,7 +23054,7 @@
       <formula>$B135=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D80 D82 D84:D134 D141:D181">
+  <conditionalFormatting sqref="D2:D80 D82 D84:D134 D141:D197">
     <cfRule type="colorScale" priority="1037">
       <colorScale>
         <cfvo type="min"/>
@@ -22859,7 +23246,7 @@
       <formula>$B103=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:U54 W53:AG54 A55:AG75 A104:AG105 A106:V109 A109:AG120 A121:U121 W121:AG121 A122:AG131 A126:V141 S170:AG170 U171:U176 W171:AG176 A177:AG181">
+  <conditionalFormatting sqref="F53:U54 W53:AG54 A55:AG75 A104:AG105 A106:V109 A109:AG120 A121:U121 W121:AG121 A122:AG131 A126:V141 S170:AG170 U171:U176 W171:AG176 A177:AG189">
     <cfRule type="expression" dxfId="289" priority="752">
       <formula>$B53=0</formula>
     </cfRule>
@@ -23563,31 +23950,31 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="15">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q149 Q151:Q181 Q182:R189" ns2:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q149 Q151:Q197 Q190:R197" ns2:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1950</formula1>
       <formula2>2025</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J127 J130:J131 J134:J141 J145:J181 K2:K9 K11:K48 K52:K54 K57:K59 K61:K63 K67:K79 K84 K94:K104 K106:K147 K149:K181 N1:N67 N71:N83 N85:N103 N105:N1048576" ns2:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J127 J130:J131 J134:J141 J145:J189 K2:K9 K11:K48 K52:K54 K57:K59 K61:K63 K67:K79 K84 K94:K104 K106:K147 K149:K189 N1:N67 N71:N83 N85:N103 N105:N1048576" ns2:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M356:M366" ns2:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Land Area, Power MWe, Excavation Volume,  Reactor Building Slab Roof Volume,	Reactor Building  Basement Volume, Reactor Building  Exterior Walls Volume,		Turbine Building Slab Roof Volume,	Turbine Building  Basement Volume,	Turbine Building  Exterior Wall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 L182:L1048576" ns2:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 L190:L1048576" ns2:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"$/acres, $/MWe, $/m^3, $/MWt"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P182:P335" ns2:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P190:P335" ns2:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P80 P82:P134 P141:P181" ns2:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P80 P82:P134 P141:P197" ns2:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O80 O82:O131 O134 O141:O181" ns2:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O80 O82:O131 O134 O141:O197" ns2:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"acres, MWe, m^3, MWt, Kg, Drums, kW, $, m^2, kg/s"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L80 L82:L110 L112:L134 L141:L181" ns2:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L80 L82:L110 L112:L134 L141:L197" ns2:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"$/m^2,$/MWeHour,$/FTE, $/acres, $/MWe, $/m^3, $/MWt, $/Kg, $/Drum, $/(kg.sec), $/SWU, unitless, $/kWe"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O132:O133" ns2:uid="{00000000-0002-0000-0000-000008000000}">
@@ -23603,10 +23990,10 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E181" ns2:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E197" ns2:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>"standard, nonstandard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R181" ns2:uid="{00000000-0002-0000-0000-00000D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R197" ns2:uid="{00000000-0002-0000-0000-00000D000000}">
       <formula1>"NA, General, Labor, Material, Equipment,Lab and Mat and Equip, 'Lab and Equip"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L111" ns2:uid="{00000000-0002-0000-0000-00000E000000}">

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -1876,7 +1876,7 @@
     <t>$/FTE</t>
   </si>
   <si>
-    <t>Number of Operators</t>
+    <t>Number of On-Site Operators per Shift</t>
   </si>
   <si>
     <t>de Candido, I., A. Al Rashdan, A. Abou-Jaoude, and J. Buongiorno. 2024. “Assessment of Technoeconomic Opportunities in Automation for Nuclear Microreactors.” Nuclear Science and Engineering, 1–20. https://doi.org/10.1080/00295639.2024.2372511.</t>
@@ -2694,7 +2694,7 @@
     <t>Operators (Testing Only)</t>
   </si>
   <si>
-    <t>MFG Testing Number of Operators</t>
+    <t>MFG Testing Number of On-Site Operators per Shift</t>
   </si>
   <si>
     <t>Warehouse Staff</t>
@@ -3015,7 +3015,7 @@
     <t>Shift To Headcount</t>
   </si>
   <si>
-    <t>SER Number of Operators Per Shift</t>
+    <t>SER Number of On-Site Operators per Shift Per Shift</t>
   </si>
   <si>
     <t>SER Security Staff Per Shift</t>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -1249,7 +1249,7 @@
     <t>$/FTE</t>
   </si>
   <si>
-    <t>Number of Operators</t>
+    <t>Number of On-Site Operators per Shift</t>
   </si>
   <si>
     <t>de Candido, I., A. Al Rashdan, A. Abou-Jaoude, and J. Buongiorno. 2024. “Assessment of Technoeconomic Opportunities in Automation for Nuclear Microreactors.” Nuclear Science and Engineering, 1–20. https://doi.org/10.1080/00295639.2024.2372511.</t>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost Database" sheetId="1" r:id="Rd09f38df92c548d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MARVEL_Cost" sheetId="2" r:id="R6ecdd67b153c4627"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Variables" sheetId="3" r:id="Rb5533a590ac94c81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inflation Adjustment" sheetId="4" r:id="Re92964ed09ba40fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economics Parameters" sheetId="5" r:id="R97da12fc1c7a4202"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manufacturing Campus Database" sheetId="7" r:id="Rda28546308ae4396"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servicing Campus Database" sheetId="8" r:id="R8147a9e33a154705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost Database" sheetId="1" r:id="Raee221fb551f4d08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MARVEL_Cost" sheetId="2" r:id="Ra299e229cc5c4b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Variables" sheetId="3" r:id="R1136f3a8c77840bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inflation Adjustment" sheetId="4" r:id="R0212ed239f5e42b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economics Parameters" sheetId="5" r:id="R6434e323901e4bda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manufacturing Campus Database" sheetId="7" r:id="R9ee7b8ca55e84603"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servicing Campus Database" sheetId="8" r:id="Rb07cc31647744dd1"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CRF">#REF!</x:definedName>
@@ -2898,9 +2898,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Operators (Testing Only)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MFG Testing Number of On-Site Operators per Shift</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Warehouse Staff</x:t>
@@ -23915,19 +23912,19 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="Rb6a757536a1e48b8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="Rb22de9407a7a4819"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="Raab305e837174012"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="Rb61430fcc4a24a97"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="Rb92345b2f55d443a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="Rc169c2b43ada43e9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U109" r:id="Re832671e46cd41d8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U120" r:id="Rc193e8d6960548f2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U130" r:id="Rd271ce1e6d804b70"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U131" r:id="Rbf16ca840e6b4b6c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U135" r:id="Redb2433ebaf34e6b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U136" r:id="R06ceb00dfb4546b6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U169" r:id="R1ce9ec4ce48942c6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="Rbd0c5c3805ef4e05"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="Rc7e9d4e2578d49ef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="R34b91720f5c04dba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="R385e030e8c444c8f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="R8c6725ede10446b6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="Re933932b96c44a93"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U109" r:id="R638f7fcf1223489d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U120" r:id="R33d13cad100f41f0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U130" r:id="R105ba6ec51324274"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U131" r:id="R9bfe1e2cd16644b2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U135" r:id="R3e4024a1c8064ba8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U136" r:id="R63a66a6acd284df3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U169" r:id="R46a3c2895cc349e7"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -26772,8 +26769,8 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3074a36633e4412a"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e6e4ec42ff14067"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bf8797f5b7e46bc"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb11a00de6a8420b"/>
 </x:worksheet>
 </file>
 
@@ -30629,8 +30626,8 @@
       <x:c r="L48" s="103" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="M48" s="110" t="s">
-        <x:v>672</x:v>
+      <x:c r="M48" s="110" t="str">
+        <x:v>MFG Testing Number of Operators</x:v>
       </x:c>
       <x:c r="N48" s="103"/>
       <x:c r="O48" s="103"/>
@@ -30696,7 +30693,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C49" s="109" t="s">
-        <x:v>673</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="D49" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -30717,7 +30714,7 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="M49" s="58" t="s">
-        <x:v>674</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="N49" s="103"/>
       <x:c r="O49" s="103"/>
@@ -30731,10 +30728,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="S49" s="58" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="T49" s="58" t="s">
         <x:v>675</x:v>
-      </x:c>
-      <x:c r="T49" s="58" t="s">
-        <x:v>676</x:v>
       </x:c>
       <x:c r="U49" s="103"/>
       <x:c r="V49" s="103"/>
@@ -30806,7 +30803,7 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="M50" s="58" t="s">
-        <x:v>677</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="N50" s="103"/>
       <x:c r="O50" s="103"/>
@@ -30872,7 +30869,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C51" s="109" t="s">
-        <x:v>678</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="D51" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -30893,7 +30890,7 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="M51" s="58" t="s">
-        <x:v>679</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="N51" s="103"/>
       <x:c r="O51" s="103"/>
@@ -30959,7 +30956,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C52" s="109" t="s">
-        <x:v>680</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D52" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -30980,7 +30977,7 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="M52" s="183" t="s">
-        <x:v>681</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="N52" s="103"/>
       <x:c r="O52" s="103"/>
@@ -31042,7 +31039,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C53" s="109" t="s">
-        <x:v>682</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="D53" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31115,7 +31112,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C54" s="109" t="s">
-        <x:v>683</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="D54" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31188,7 +31185,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C55" s="109" t="s">
-        <x:v>684</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="D55" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31277,7 +31274,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C56" s="109" t="s">
-        <x:v>685</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="D56" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31366,7 +31363,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C57" s="109" t="s">
-        <x:v>686</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="D57" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31411,7 +31408,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C58" s="109" t="s">
-        <x:v>687</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="D58" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31482,7 +31479,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C59" s="109" t="s">
-        <x:v>688</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="D59" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31553,7 +31550,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C60" s="109" t="s">
-        <x:v>689</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="D60" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31624,7 +31621,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C61" s="109" t="s">
-        <x:v>690</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="D61" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31713,7 +31710,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C62" s="109" t="s">
-        <x:v>691</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="D62" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31802,7 +31799,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C63" s="109" t="s">
-        <x:v>692</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="D63" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31891,7 +31888,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C64" s="109" t="s">
-        <x:v>693</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="D64" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -31962,7 +31959,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C65" s="109" t="s">
-        <x:v>694</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="D65" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -32031,7 +32028,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C66" s="109" t="s">
-        <x:v>695</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="D66" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -32056,7 +32053,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="M66" s="183" t="s">
-        <x:v>696</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="N66" s="103"/>
       <x:c r="O66" s="103" t="s">
@@ -32126,7 +32123,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C67" s="109" t="s">
-        <x:v>697</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="D67" s="93" t="str">
         <x:f t="shared" si="25"/>
@@ -32533,13 +32530,13 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="R728af51f0c224e1d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="R321f3d02a8984c75"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U66" r:id="R7671ba8ce6054bb2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="R41634fb1c3ba42d4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="Rb9ef6038711449fe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U66" r:id="Re89ec1ce24494120"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8672e896a47a4873"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3962e203a664540"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47ea54c41ff7458f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec0e2daf42104d54"/>
 </x:worksheet>
 </file>
 
@@ -32771,7 +32768,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="M3" s="100" t="s">
-        <x:v>698</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="N3" s="121"/>
       <x:c r="O3" s="100" t="s">
@@ -32867,7 +32864,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="M4" s="100" t="s">
-        <x:v>699</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="N4" s="121"/>
       <x:c r="O4" s="100" t="s">
@@ -33370,7 +33367,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="M11" s="100" t="s">
-        <x:v>700</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="N11" s="121"/>
       <x:c r="O11" s="100" t="s">
@@ -33473,7 +33470,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="M12" s="100" t="s">
-        <x:v>700</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="N12" s="121"/>
       <x:c r="O12" s="100" t="s">
@@ -33563,7 +33560,7 @@
         <x:v>614</x:v>
       </x:c>
       <x:c r="M13" s="125" t="s">
-        <x:v>701</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="N13" s="126">
         <x:v>1</x:v>
@@ -33702,7 +33699,7 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="M15" s="100" t="s">
-        <x:v>702</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="N15" s="121"/>
       <x:c r="O15" s="100"/>
@@ -33766,7 +33763,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C16" s="98" t="s">
-        <x:v>703</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="D16" s="93" t="str">
         <x:f t="shared" si="1"/>
@@ -33792,7 +33789,7 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="M16" s="100" t="s">
-        <x:v>704</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="N16" s="121"/>
       <x:c r="O16" s="100"/>
@@ -33882,7 +33879,7 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="M17" s="100" t="s">
-        <x:v>705</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="N17" s="121"/>
       <x:c r="O17" s="100"/>
@@ -33991,7 +33988,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C19" s="98" t="s">
-        <x:v>706</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="D19" s="93" t="str">
         <x:f t="shared" si="1"/>
@@ -34036,7 +34033,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C20" s="150" t="s">
-        <x:v>707</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="D20" s="151" t="str">
         <x:f t="shared" si="1"/>
@@ -34062,7 +34059,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="M20" s="155" t="s">
-        <x:v>708</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="N20" s="142" t="n">
         <x:f>338988/(3.2808^2)</x:f>
@@ -34081,7 +34078,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="S20" s="144" t="s">
-        <x:v>709</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="T20" s="170"/>
       <x:c r="U20" s="171"/>
@@ -34133,7 +34130,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C21" s="98" t="s">
-        <x:v>710</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="D21" s="93"/>
       <x:c r="E21" s="93"/>
@@ -34175,7 +34172,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C22" s="150" t="s">
-        <x:v>711</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="D22" s="151" t="str">
         <x:f t="shared" ref="D22" si="13">REPT("   ", B22*2) &amp; C22</x:f>
@@ -34201,7 +34198,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="M22" s="155" t="s">
-        <x:v>712</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="N22" s="142">
         <x:v>1</x:v>
@@ -34219,7 +34216,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="S22" s="144" t="s">
-        <x:v>713</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="T22" s="170"/>
       <x:c r="U22" s="171"/>
@@ -34322,7 +34319,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C24" s="98" t="s">
-        <x:v>714</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="D24" s="93" t="str">
         <x:f t="shared" ref="D24:D31" si="18">REPT("   ", B24*2) &amp; C24</x:f>
@@ -34348,7 +34345,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="M24" s="98" t="s">
-        <x:v>715</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="N24" s="142">
         <x:v>1</x:v>
@@ -34417,7 +34414,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C25" s="98" t="s">
-        <x:v>716</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="D25" s="93" t="str">
         <x:f t="shared" si="18"/>
@@ -34443,7 +34440,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="M25" s="98" t="s">
-        <x:v>717</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="N25" s="142">
         <x:v>1</x:v>
@@ -34520,7 +34517,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C26" s="98" t="s">
-        <x:v>718</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="D26" s="93" t="str">
         <x:f t="shared" si="18"/>
@@ -34565,7 +34562,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C27" s="98" t="s">
-        <x:v>719</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="D27" s="93" t="str">
         <x:f t="shared" si="18"/>
@@ -34591,7 +34588,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="M27" s="155" t="s">
-        <x:v>720</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="N27" s="142">
         <x:v>1</x:v>
@@ -34609,7 +34606,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="S27" s="144" t="s">
-        <x:v>713</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="T27" s="102"/>
       <x:c r="U27" s="122"/>
@@ -34661,7 +34658,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C28" s="98" t="s">
-        <x:v>721</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D28" s="93" t="str">
         <x:f t="shared" si="18"/>
@@ -34683,7 +34680,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="M28" s="155" t="s">
-        <x:v>722</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="N28" s="121">
         <x:v>1</x:v>
@@ -34701,11 +34698,11 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="S28" s="102" t="s">
-        <x:v>723</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="T28" s="102"/>
       <x:c r="U28" s="140" t="s">
-        <x:v>724</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="V28" s="103"/>
       <x:c r="W28" s="145" t="s">
@@ -34755,7 +34752,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C29" s="98" t="s">
-        <x:v>725</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="D29" s="93" t="str">
         <x:f t="shared" si="18"/>
@@ -34777,7 +34774,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="M29" s="155" t="s">
-        <x:v>726</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="N29" s="121">
         <x:v>1</x:v>
@@ -34795,7 +34792,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="S29" s="144" t="s">
-        <x:v>713</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="T29" s="102"/>
       <x:c r="U29" s="122"/>
@@ -34847,7 +34844,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C30" s="98" t="s">
-        <x:v>727</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="D30" s="93" t="str">
         <x:f t="shared" si="18"/>
@@ -34892,7 +34889,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C31" s="98" t="s">
-        <x:v>728</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="D31" s="93" t="str">
         <x:f t="shared" si="18"/>
@@ -34921,7 +34918,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="S31" s="144" t="s">
-        <x:v>729</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="T31" s="102"/>
       <x:c r="U31" s="122"/>
@@ -35017,7 +35014,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C33" s="150" t="s">
-        <x:v>730</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="D33" s="151" t="str">
         <x:f>REPT("   ", B33*2) &amp; C33</x:f>
@@ -35037,7 +35034,7 @@
       </x:c>
       <x:c r="L33" s="142"/>
       <x:c r="M33" s="155" t="s">
-        <x:v>731</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="N33" s="142">
         <x:v>300</x:v>
@@ -35114,7 +35111,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C34" s="150" t="s">
-        <x:v>732</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="D34" s="151" t="str">
         <x:f>REPT("   ", B34*2) &amp; C34</x:f>
@@ -35134,7 +35131,7 @@
       </x:c>
       <x:c r="L34" s="142"/>
       <x:c r="M34" s="155" t="s">
-        <x:v>731</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="N34" s="142">
         <x:v>300</x:v>
@@ -35211,7 +35208,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C35" s="150" t="s">
-        <x:v>733</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="D35" s="151" t="str">
         <x:f>REPT("   ", B35*2) &amp; C35</x:f>
@@ -35232,7 +35229,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="M35" s="155" t="s">
-        <x:v>734</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="N35" s="142">
         <x:v>1</x:v>
@@ -35329,7 +35326,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="M36" s="155" t="s">
-        <x:v>735</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="N36" s="142">
         <x:v>1</x:v>
@@ -35443,7 +35440,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C38" s="98" t="s">
-        <x:v>736</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="D38" s="93" t="str">
         <x:f>REPT("   ", B38*2) &amp; C38</x:f>
@@ -35453,7 +35450,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F38" s="93" t="s">
-        <x:v>737</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="G38" s="94">
         <x:v>1</x:v>
@@ -35527,7 +35524,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C39" s="150" t="s">
-        <x:v>738</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="D39" s="151" t="str">
         <x:f t="shared" ref="D39" si="35">REPT("   ", B39*2) &amp; C39</x:f>
@@ -35551,7 +35548,7 @@
       </x:c>
       <x:c r="L39" s="142"/>
       <x:c r="M39" s="155" t="s">
-        <x:v>739</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="N39" s="198" t="n">
         <x:f>200/3600</x:f>
@@ -35570,10 +35567,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="S39" s="144" t="s">
+        <x:v>739</x:v>
+      </x:c>
+      <x:c r="T39" s="170" t="s">
         <x:v>740</x:v>
-      </x:c>
-      <x:c r="T39" s="170" t="s">
-        <x:v>741</x:v>
       </x:c>
       <x:c r="U39" s="171" t="s">
         <x:v>306</x:v>
@@ -35625,7 +35622,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C40" s="98" t="s">
-        <x:v>742</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="D40" s="93" t="str">
         <x:f>REPT("   ", B40*2) &amp; C40</x:f>
@@ -35635,7 +35632,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F40" s="93" t="s">
-        <x:v>743</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="G40" s="94">
         <x:v>1</x:v>
@@ -35663,7 +35660,7 @@
       <x:c r="T40" s="102"/>
       <x:c r="U40" s="122"/>
       <x:c r="V40" s="103" t="s">
-        <x:v>744</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="W40" s="96" t="s">
         <x:v>43</x:v>
@@ -35721,7 +35718,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F41" s="93" t="s">
-        <x:v>737</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="G41" s="94">
         <x:v>1</x:v>
@@ -35745,13 +35742,13 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="S41" s="102" t="s">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="T41" s="102" t="s">
         <x:v>745</x:v>
       </x:c>
-      <x:c r="T41" s="102" t="s">
+      <x:c r="U41" s="140" t="s">
         <x:v>746</x:v>
-      </x:c>
-      <x:c r="U41" s="140" t="s">
-        <x:v>747</x:v>
       </x:c>
       <x:c r="V41" s="103"/>
       <x:c r="W41" s="145" t="s">
@@ -35800,7 +35797,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C42" s="98" t="s">
-        <x:v>748</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="D42" s="93" t="str">
         <x:f>REPT("   ", B42*2) &amp; C42</x:f>
@@ -35823,7 +35820,7 @@
       </x:c>
       <x:c r="L42" s="100"/>
       <x:c r="M42" s="93" t="s">
-        <x:v>749</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="N42" s="121"/>
       <x:c r="O42" s="100"/>
@@ -35835,7 +35832,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="S42" s="102" t="s">
-        <x:v>750</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="T42" s="102"/>
       <x:c r="U42" s="122"/>
@@ -35886,7 +35883,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C43" s="98" t="s">
-        <x:v>751</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="D43" s="93" t="str">
         <x:f>REPT("   ", B43*2) &amp; C43</x:f>
@@ -35909,7 +35906,7 @@
       <x:c r="K43" s="120"/>
       <x:c r="L43" s="100"/>
       <x:c r="M43" s="93" t="s">
-        <x:v>752</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="N43" s="121"/>
       <x:c r="O43" s="100"/>
@@ -36054,7 +36051,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="M45" s="155" t="s">
-        <x:v>753</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="N45" s="142">
         <x:v>1</x:v>
@@ -36131,7 +36128,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C46" s="150" t="s">
-        <x:v>754</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="D46" s="151" t="str">
         <x:f>REPT("   ", B46*2) &amp; C46</x:f>
@@ -36141,7 +36138,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F46" s="151" t="s">
-        <x:v>755</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="G46" s="153">
         <x:v>1</x:v>
@@ -36164,7 +36161,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="S46" s="144" t="s">
-        <x:v>713</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="T46" s="102"/>
       <x:c r="U46" s="122"/>
@@ -36233,7 +36230,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F47" s="151" t="s">
-        <x:v>756</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="G47" s="153">
         <x:v>1</x:v>
@@ -36331,7 +36328,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="M48" s="155" t="s">
-        <x:v>757</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="N48" s="142">
         <x:v>1</x:v>
@@ -36430,7 +36427,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="M49" s="155" t="s">
-        <x:v>699</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="N49" s="142">
         <x:v>300</x:v>
@@ -36555,7 +36552,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F51" s="93" t="s">
-        <x:v>758</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="G51" s="94">
         <x:v>1</x:v>
@@ -36642,7 +36639,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F52" s="93" t="s">
-        <x:v>759</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="G52" s="94">
         <x:v>1</x:v>
@@ -36717,7 +36714,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C53" s="168" t="s">
-        <x:v>760</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="D53" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -36762,7 +36759,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C54" s="168" t="s">
-        <x:v>761</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="D54" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -36772,7 +36769,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F54" s="93" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="G54" s="94">
         <x:v>1</x:v>
@@ -36847,7 +36844,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C55" s="168" t="s">
-        <x:v>763</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="D55" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -36857,7 +36854,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F55" s="93" t="s">
-        <x:v>764</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="G55" s="94">
         <x:v>1</x:v>
@@ -36932,7 +36929,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C56" s="168" t="s">
-        <x:v>765</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="D56" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -36942,7 +36939,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F56" s="93" t="s">
-        <x:v>766</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="G56" s="94">
         <x:v>1</x:v>
@@ -37017,7 +37014,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C57" s="168" t="s">
-        <x:v>767</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D57" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -37027,7 +37024,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F57" s="93" t="s">
-        <x:v>768</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="G57" s="94">
         <x:v>1</x:v>
@@ -37102,7 +37099,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C58" s="168" t="s">
-        <x:v>769</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="D58" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -37147,7 +37144,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C59" s="168" t="s">
-        <x:v>770</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="D59" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -37157,7 +37154,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F59" s="93" t="s">
-        <x:v>771</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="G59" s="94">
         <x:v>1</x:v>
@@ -37180,7 +37177,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="S59" s="110" t="s">
-        <x:v>729</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="T59" s="110"/>
       <x:c r="U59" s="200"/>
@@ -37232,7 +37229,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C60" s="168" t="s">
-        <x:v>772</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="D60" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -37265,7 +37262,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="S60" s="110" t="s">
-        <x:v>729</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="T60" s="110"/>
       <x:c r="U60" s="200"/>
@@ -37385,7 +37382,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="M62" s="178" t="s">
-        <x:v>700</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="N62" s="103">
         <x:v>1068</x:v>
@@ -37462,7 +37459,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F63" s="93" t="s">
-        <x:v>773</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="G63" s="94">
         <x:v>1</x:v>
@@ -37546,7 +37543,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F64" s="93" t="s">
-        <x:v>774</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="G64" s="94">
         <x:v>1</x:v>
@@ -37630,7 +37627,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F65" s="93" t="s">
-        <x:v>775</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="G65" s="94">
         <x:v>1</x:v>
@@ -37704,7 +37701,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C66" s="168" t="s">
-        <x:v>776</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="D66" s="93" t="str">
         <x:f>REPT("   ", B66*2) &amp; C66</x:f>
@@ -37714,7 +37711,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F66" s="93" t="s">
-        <x:v>777</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="G66" s="94">
         <x:v>1</x:v>
@@ -38263,7 +38260,7 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="M75" s="93" t="s">
-        <x:v>749</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="N75" s="103"/>
       <x:c r="O75" s="103"/>
@@ -38339,7 +38336,7 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="F76" s="93" t="s">
-        <x:v>778</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="G76" s="94">
         <x:v>1</x:v>
@@ -38354,7 +38351,7 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="M76" s="58" t="s">
-        <x:v>779</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="N76" s="103"/>
       <x:c r="O76" s="103"/>
@@ -38420,7 +38417,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C77" s="109" t="s">
-        <x:v>678</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="D77" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -38430,7 +38427,7 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="F77" s="93" t="s">
-        <x:v>778</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="G77" s="94">
         <x:v>1</x:v>
@@ -38445,7 +38442,7 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="M77" s="58" t="s">
-        <x:v>780</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="N77" s="103"/>
       <x:c r="O77" s="103"/>
@@ -38511,7 +38508,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C78" s="109" t="s">
-        <x:v>781</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="D78" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -38532,7 +38529,7 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="M78" s="183" t="s">
-        <x:v>782</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="N78" s="103"/>
       <x:c r="O78" s="103"/>
@@ -38594,7 +38591,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C79" s="109" t="s">
-        <x:v>682</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="D79" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -38655,7 +38652,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C80" s="109" t="s">
-        <x:v>683</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="D80" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -38716,7 +38713,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C81" s="109" t="s">
-        <x:v>686</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="D81" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -38761,7 +38758,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C82" s="109" t="s">
-        <x:v>783</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="D82" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -38820,7 +38817,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C83" s="109" t="s">
-        <x:v>784</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="D83" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -38879,7 +38876,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C84" s="109" t="s">
-        <x:v>689</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="D84" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -38938,7 +38935,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C85" s="109" t="s">
-        <x:v>690</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="D85" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -38963,7 +38960,7 @@
         <x:v>426</x:v>
       </x:c>
       <x:c r="M85" s="93" t="s">
-        <x:v>785</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="N85" s="103"/>
       <x:c r="O85" s="103"/>
@@ -39027,7 +39024,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C86" s="109" t="s">
-        <x:v>694</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="D86" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39086,7 +39083,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C87" s="109" t="s">
-        <x:v>786</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="D87" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39131,7 +39128,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C88" s="109" t="s">
-        <x:v>787</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="D88" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39141,7 +39138,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F88" s="93" t="s">
-        <x:v>788</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="G88" s="94">
         <x:v>1</x:v>
@@ -39164,12 +39161,12 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="S88" s="110" t="s">
-        <x:v>789</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="T88" s="111"/>
       <x:c r="U88" s="182"/>
       <x:c r="V88" s="103" t="s">
-        <x:v>790</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="W88" s="96" t="s">
         <x:v>43</x:v>
@@ -39216,7 +39213,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C89" s="109" t="s">
-        <x:v>791</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="D89" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39226,7 +39223,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F89" s="93" t="s">
-        <x:v>792</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="G89" s="94">
         <x:v>1</x:v>
@@ -39321,7 +39318,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C90" s="109" t="s">
-        <x:v>793</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="D90" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39331,7 +39328,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F90" s="93" t="s">
-        <x:v>794</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="G90" s="94">
         <x:v>1</x:v>
@@ -39354,12 +39351,12 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="S90" s="110" t="s">
-        <x:v>789</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="T90" s="111"/>
       <x:c r="U90" s="182"/>
       <x:c r="V90" s="103" t="s">
-        <x:v>790</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="W90" s="96" t="s">
         <x:v>43</x:v>
@@ -39406,7 +39403,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C91" s="109" t="s">
-        <x:v>695</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="D91" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39431,7 +39428,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="M91" s="110" t="s">
-        <x:v>795</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="N91" s="103"/>
       <x:c r="O91" s="103" t="s">
@@ -39501,7 +39498,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C92" s="109" t="s">
-        <x:v>697</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="D92" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39546,7 +39543,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C93" s="109" t="s">
-        <x:v>796</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="D93" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39591,7 +39588,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C94" s="168" t="s">
-        <x:v>797</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="D94" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39601,7 +39598,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F94" s="93" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="G94" s="94">
         <x:v>1</x:v>
@@ -39675,7 +39672,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C95" s="168" t="s">
-        <x:v>798</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="D95" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39685,7 +39682,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F95" s="93" t="s">
-        <x:v>764</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="G95" s="94">
         <x:v>1</x:v>
@@ -39759,7 +39756,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C96" s="168" t="s">
-        <x:v>799</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="D96" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39769,7 +39766,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F96" s="93" t="s">
-        <x:v>766</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="G96" s="94">
         <x:v>1</x:v>
@@ -39843,7 +39840,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C97" s="168" t="s">
-        <x:v>800</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="D97" s="93" t="str">
         <x:f t="shared" si="44"/>
@@ -39853,7 +39850,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="F97" s="93" t="s">
-        <x:v>768</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="G97" s="94">
         <x:v>1</x:v>
@@ -40267,14 +40264,14 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="R2ad1b1489ade4d8f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="Rff2748059c9a4aea"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="R86c49c6e4be44f11"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="Rf90db87564f247b2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U91" r:id="R453239ad03994f92"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="R068b229e001347fe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="Rc2677a276c53417e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="Rdc4d9a12530b4af2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="Rb2482be7c8cc4fba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U91" r:id="R70fd82d2dd914985"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re973f8de94c44059"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f53923f849d4d4d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0408c5e59efc4cb8"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73b17a3281fd49a5"/>
 </x:worksheet>
 </file>
--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannbn/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396B7A26-B56F-DE47-84C2-CDB0D8DE6E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F6E66C-7A4E-0649-AAD6-8993B7B57FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7123,6 +7123,114 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2ABC046-3547-9390-8110-2C1ED17FE39B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3ED3600-9A72-7A2E-D279-FB6A7B8E306D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7177,6 +7285,114 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>584200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0024F735-21E0-4121-B717-94EC49AD7E18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>584200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7ED2439-8D13-6B90-CF3C-7EE7333B5DCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7224,6 +7440,114 @@
             <a:srgbClr val="000000"/>
           </a:solidFill>
           <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>431800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8946A51-B997-79FA-8123-ABD74F135478}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E33490CB-640B-7AEE-C7DE-535CA439729F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
           <a:headEnd/>
           <a:tailEnd/>
         </a:ln>
@@ -18438,8 +18762,8 @@
       <c r="V131" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="W131" s="74" t="s">
-        <v>157</v>
+      <c r="W131" s="3" t="s">
+        <v>340</v>
       </c>
       <c r="X131" s="77">
         <f t="shared" si="28"/>
@@ -18796,7 +19120,7 @@
       </c>
       <c r="V136" s="49"/>
       <c r="W136" s="74" t="s">
-        <v>157</v>
+        <v>340</v>
       </c>
       <c r="X136" s="77">
         <f>0.9*$J136</f>
@@ -28479,7 +28803,7 @@
       <c r="AF18" s="97"/>
       <c r="AG18" s="96"/>
     </row>
-    <row r="19" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" ht="71" x14ac:dyDescent="0.2">
       <c r="A19" s="107">
         <v>214.31</v>
       </c>
@@ -28975,7 +29299,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="71" x14ac:dyDescent="0.2">
       <c r="A25" s="148">
         <v>225</v>
       </c>
@@ -29334,7 +29658,7 @@
       <c r="AF29" s="97"/>
       <c r="AG29" s="96"/>
     </row>
-    <row r="30" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="71" x14ac:dyDescent="0.2">
       <c r="A30" s="148">
         <v>283</v>
       </c>
@@ -29427,7 +29751,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="71" x14ac:dyDescent="0.2">
       <c r="A31" s="148">
         <v>284</v>
       </c>
@@ -30573,7 +30897,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:33" ht="71" x14ac:dyDescent="0.2">
       <c r="A49" s="107">
         <v>712</v>
       </c>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannbn/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735ABA1F-1CC1-5149-97F7-4E9572C4D8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FDA0AA-A281-F041-BB3D-1C90CC64D0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4663" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4672" uniqueCount="743">
   <si>
     <t>Account</t>
   </si>
@@ -2314,6 +2314,48 @@
   </si>
   <si>
     <t>Ganda stainless_steel cost used as a proxy for SS304 shutdown-rod cladding.</t>
+  </si>
+  <si>
+    <t>Other Reactor Plant Equipment (based on MARVEL)</t>
+  </si>
+  <si>
+    <t>Other Reactor Plant Equipment (Helium purification)</t>
+  </si>
+  <si>
+    <t>Material RequiringSpecialConsideration</t>
+  </si>
+  <si>
+    <t>5-Ci americium–beryllium neutron source</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/doi/epdf/10.1080/00295450.2026.2659431?needAccess=true</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hanna, Botros, Stacie Strain, Vincent F. Schwartz, and Abdalla Abou-Jaoude. "Cost Breakdown and Evolution of the MARVEL Microreactor Project." </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Nuclear Technology</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (2026): 1-27.</t>
+    </r>
+  </si>
+  <si>
+    <t>Primary Loop Purification</t>
   </si>
 </sst>
 </file>
@@ -2329,7 +2371,7 @@
     <numFmt numFmtId="168" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2443,8 +2485,21 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="13"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2459,6 +2514,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFBA"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -2647,7 +2708,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3003,22 +3064,34 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3026,8 +3099,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3052,14 +3125,14 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3069,16 +3142,11 @@
     <cellStyle name="Normal 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Normal 2 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
-  <dxfs count="303">
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
+  <dxfs count="313">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3092,7 +3160,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3118,16 +3200,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -3146,7 +3226,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3154,6 +3234,13 @@
       <font>
         <b/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -3191,6 +3278,32 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
@@ -3199,6 +3312,63 @@
       <font>
         <b/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -3236,77 +3406,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79995117038483843"/>
@@ -3337,14 +3436,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3358,14 +3457,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3377,7 +3469,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3448,41 +3547,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -3518,19 +3582,16 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -3547,23 +3608,14 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3618,6 +3670,502 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray125"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray0625"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray125"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray125"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3687,40 +4235,21 @@
     <dxf>
       <font>
         <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray125"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3741,158 +4270,9 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray0625"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -3946,156 +4326,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
       </font>
@@ -4118,90 +4348,6 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4266,6 +4412,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -4276,6 +4429,18 @@
           <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4313,7 +4478,45 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4325,9 +4528,25 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -4351,9 +4570,39 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4412,7 +4661,54 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4426,62 +4722,26 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
+        <i/>
       </font>
-    </dxf>
-    <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
+        <patternFill patternType="gray0625"/>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
+        <patternFill patternType="gray0625"/>
       </fill>
     </dxf>
     <dxf>
@@ -4562,13 +4822,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -4576,46 +4829,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray0625"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray0625"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4637,74 +4851,6 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4739,14 +4885,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4819,6 +4965,53 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -4852,13 +5045,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
       </font>
@@ -4874,46 +5060,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4942,11 +5088,6 @@
           <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -5010,6 +5151,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -5018,6 +5166,18 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5034,61 +5194,6 @@
           <bgColor theme="6" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -5118,6 +5223,42 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5178,6 +5319,168 @@
             <a:srgbClr val="000000"/>
           </a:solidFill>
           <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F91C925-E512-BDB7-6392-29E459EAD232}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D5D3CD2-D2CB-E462-08C7-A445034646A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD4FAEF2-EC7C-2CDB-5F17-F071F9019DE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
           <a:headEnd/>
           <a:tailEnd/>
         </a:ln>
@@ -5416,7 +5719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ192"/>
+  <dimension ref="A1:AJ193"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="3" customWidth="1"/>
@@ -5661,7 +5964,7 @@
       <c r="T3" s="143" t="s">
         <v>41</v>
       </c>
-      <c r="U3" s="146" t="s">
+      <c r="U3" s="150" t="s">
         <v>42</v>
       </c>
       <c r="V3" s="49"/>
@@ -5757,8 +6060,8 @@
       <c r="S4" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="141"/>
-      <c r="U4" s="141"/>
+      <c r="T4" s="145"/>
+      <c r="U4" s="145"/>
       <c r="V4" s="49"/>
       <c r="W4" s="74" t="s">
         <v>43</v>
@@ -5849,7 +6152,7 @@
       <c r="T5" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="U5" s="146" t="s">
+      <c r="U5" s="150" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="49"/>
@@ -5941,7 +6244,7 @@
       <c r="T6" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="U6" s="141"/>
+      <c r="U6" s="145"/>
       <c r="V6" s="49"/>
       <c r="W6" s="74" t="s">
         <v>43</v>
@@ -6289,7 +6592,7 @@
       <c r="T11" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="142" t="s">
+      <c r="U11" s="148" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="49"/>
@@ -6382,9 +6685,9 @@
       <c r="R12" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="S12" s="140"/>
-      <c r="T12" s="140"/>
-      <c r="U12" s="140"/>
+      <c r="S12" s="144"/>
+      <c r="T12" s="144"/>
+      <c r="U12" s="144"/>
       <c r="V12" s="49"/>
       <c r="W12" s="74" t="s">
         <v>77</v>
@@ -6475,9 +6778,9 @@
       <c r="R13" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="S13" s="141"/>
-      <c r="T13" s="141"/>
-      <c r="U13" s="141"/>
+      <c r="S13" s="145"/>
+      <c r="T13" s="145"/>
+      <c r="U13" s="145"/>
       <c r="V13" s="49"/>
       <c r="W13" s="74" t="s">
         <v>77</v>
@@ -6612,7 +6915,7 @@
       <c r="T15" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U15" s="142" t="s">
+      <c r="U15" s="148" t="s">
         <v>76</v>
       </c>
       <c r="V15" s="49"/>
@@ -6698,9 +7001,9 @@
       <c r="R16" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S16" s="140"/>
-      <c r="T16" s="140"/>
-      <c r="U16" s="140"/>
+      <c r="S16" s="144"/>
+      <c r="T16" s="144"/>
+      <c r="U16" s="144"/>
       <c r="V16" s="49"/>
       <c r="W16" s="74" t="s">
         <v>77</v>
@@ -6784,9 +7087,9 @@
       <c r="R17" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S17" s="141"/>
-      <c r="T17" s="141"/>
-      <c r="U17" s="141"/>
+      <c r="S17" s="145"/>
+      <c r="T17" s="145"/>
+      <c r="U17" s="145"/>
       <c r="V17" s="49"/>
       <c r="W17" s="74" t="s">
         <v>77</v>
@@ -7158,7 +7461,7 @@
       <c r="T22" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U22" s="142" t="s">
+      <c r="U22" s="148" t="s">
         <v>76</v>
       </c>
       <c r="V22" s="49"/>
@@ -7244,9 +7547,9 @@
       <c r="R23" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S23" s="140"/>
-      <c r="T23" s="140"/>
-      <c r="U23" s="140"/>
+      <c r="S23" s="144"/>
+      <c r="T23" s="144"/>
+      <c r="U23" s="144"/>
       <c r="V23" s="49"/>
       <c r="W23" s="74" t="s">
         <v>77</v>
@@ -7330,9 +7633,9 @@
       <c r="R24" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S24" s="141"/>
-      <c r="T24" s="141"/>
-      <c r="U24" s="141"/>
+      <c r="S24" s="145"/>
+      <c r="T24" s="145"/>
+      <c r="U24" s="145"/>
       <c r="V24" s="49"/>
       <c r="W24" s="74" t="s">
         <v>77</v>
@@ -7467,7 +7770,7 @@
       <c r="T26" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U26" s="142" t="s">
+      <c r="U26" s="148" t="s">
         <v>76</v>
       </c>
       <c r="V26" s="49"/>
@@ -7553,9 +7856,9 @@
       <c r="R27" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S27" s="140"/>
-      <c r="T27" s="140"/>
-      <c r="U27" s="140"/>
+      <c r="S27" s="144"/>
+      <c r="T27" s="144"/>
+      <c r="U27" s="144"/>
       <c r="V27" s="49"/>
       <c r="W27" s="74" t="s">
         <v>77</v>
@@ -7639,9 +7942,9 @@
       <c r="R28" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S28" s="141"/>
-      <c r="T28" s="141"/>
-      <c r="U28" s="141"/>
+      <c r="S28" s="145"/>
+      <c r="T28" s="145"/>
+      <c r="U28" s="145"/>
       <c r="V28" s="49"/>
       <c r="W28" s="74" t="s">
         <v>77</v>
@@ -7784,7 +8087,7 @@
       <c r="T30" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U30" s="142" t="s">
+      <c r="U30" s="148" t="s">
         <v>76</v>
       </c>
       <c r="V30" s="49"/>
@@ -7874,9 +8177,9 @@
       <c r="R31" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S31" s="140"/>
-      <c r="T31" s="140"/>
-      <c r="U31" s="140"/>
+      <c r="S31" s="144"/>
+      <c r="T31" s="144"/>
+      <c r="U31" s="144"/>
       <c r="V31" s="49"/>
       <c r="W31" s="74" t="s">
         <v>77</v>
@@ -7964,9 +8267,9 @@
       <c r="R32" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S32" s="141"/>
-      <c r="T32" s="141"/>
-      <c r="U32" s="141"/>
+      <c r="S32" s="145"/>
+      <c r="T32" s="145"/>
+      <c r="U32" s="145"/>
       <c r="V32" s="49"/>
       <c r="W32" s="74" t="s">
         <v>77</v>
@@ -8291,7 +8594,7 @@
       <c r="T37" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U37" s="142" t="s">
+      <c r="U37" s="148" t="s">
         <v>76</v>
       </c>
       <c r="V37" s="49"/>
@@ -8375,9 +8678,9 @@
       <c r="R38" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S38" s="140"/>
-      <c r="T38" s="140"/>
-      <c r="U38" s="140"/>
+      <c r="S38" s="144"/>
+      <c r="T38" s="144"/>
+      <c r="U38" s="144"/>
       <c r="V38" s="49"/>
       <c r="W38" s="74" t="s">
         <v>77</v>
@@ -8461,9 +8764,9 @@
       <c r="R39" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S39" s="141"/>
-      <c r="T39" s="141"/>
-      <c r="U39" s="141"/>
+      <c r="S39" s="145"/>
+      <c r="T39" s="145"/>
+      <c r="U39" s="145"/>
       <c r="V39" s="49"/>
       <c r="W39" s="74" t="s">
         <v>77</v>
@@ -8598,7 +8901,7 @@
       <c r="T41" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U41" s="142" t="s">
+      <c r="U41" s="148" t="s">
         <v>76</v>
       </c>
       <c r="V41" s="49"/>
@@ -8684,9 +8987,9 @@
       <c r="R42" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S42" s="140"/>
-      <c r="T42" s="140"/>
-      <c r="U42" s="140"/>
+      <c r="S42" s="144"/>
+      <c r="T42" s="144"/>
+      <c r="U42" s="144"/>
       <c r="V42" s="49"/>
       <c r="W42" s="74" t="s">
         <v>77</v>
@@ -8770,9 +9073,9 @@
       <c r="R43" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S43" s="141"/>
-      <c r="T43" s="141"/>
-      <c r="U43" s="141"/>
+      <c r="S43" s="145"/>
+      <c r="T43" s="145"/>
+      <c r="U43" s="145"/>
       <c r="V43" s="49"/>
       <c r="W43" s="74" t="s">
         <v>77</v>
@@ -8959,7 +9262,7 @@
       <c r="T46" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U46" s="142" t="s">
+      <c r="U46" s="148" t="s">
         <v>76</v>
       </c>
       <c r="V46" s="49"/>
@@ -9045,9 +9348,9 @@
       <c r="R47" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S47" s="140"/>
-      <c r="T47" s="140"/>
-      <c r="U47" s="140"/>
+      <c r="S47" s="144"/>
+      <c r="T47" s="144"/>
+      <c r="U47" s="144"/>
       <c r="V47" s="49"/>
       <c r="W47" s="74" t="s">
         <v>77</v>
@@ -9131,9 +9434,9 @@
       <c r="R48" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S48" s="141"/>
-      <c r="T48" s="141"/>
-      <c r="U48" s="141"/>
+      <c r="S48" s="145"/>
+      <c r="T48" s="145"/>
+      <c r="U48" s="145"/>
       <c r="V48" s="49"/>
       <c r="W48" s="74" t="s">
         <v>77</v>
@@ -9410,10 +9713,10 @@
       <c r="T52" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U52" s="142" t="s">
+      <c r="U52" s="148" t="s">
         <v>76</v>
       </c>
-      <c r="V52" s="148" t="s">
+      <c r="V52" s="149" t="s">
         <v>162</v>
       </c>
       <c r="W52" s="74" t="s">
@@ -9498,10 +9801,10 @@
       <c r="R53" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S53" s="140"/>
-      <c r="T53" s="140"/>
-      <c r="U53" s="140"/>
-      <c r="V53" s="140"/>
+      <c r="S53" s="144"/>
+      <c r="T53" s="144"/>
+      <c r="U53" s="144"/>
+      <c r="V53" s="144"/>
       <c r="W53" s="74" t="s">
         <v>77</v>
       </c>
@@ -9584,10 +9887,10 @@
       <c r="R54" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S54" s="141"/>
-      <c r="T54" s="141"/>
-      <c r="U54" s="141"/>
-      <c r="V54" s="141"/>
+      <c r="S54" s="145"/>
+      <c r="T54" s="145"/>
+      <c r="U54" s="145"/>
+      <c r="V54" s="145"/>
       <c r="W54" s="74" t="s">
         <v>77</v>
       </c>
@@ -9766,7 +10069,7 @@
       <c r="T57" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U57" s="142" t="s">
+      <c r="U57" s="148" t="s">
         <v>76</v>
       </c>
       <c r="V57" s="49"/>
@@ -9852,9 +10155,9 @@
       <c r="R58" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S58" s="140"/>
-      <c r="T58" s="140"/>
-      <c r="U58" s="140"/>
+      <c r="S58" s="144"/>
+      <c r="T58" s="144"/>
+      <c r="U58" s="144"/>
       <c r="V58" s="49"/>
       <c r="W58" s="74" t="s">
         <v>77</v>
@@ -9938,9 +10241,9 @@
       <c r="R59" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S59" s="141"/>
-      <c r="T59" s="141"/>
-      <c r="U59" s="141"/>
+      <c r="S59" s="145"/>
+      <c r="T59" s="145"/>
+      <c r="U59" s="145"/>
       <c r="V59" s="49"/>
       <c r="W59" s="74" t="s">
         <v>77</v>
@@ -10075,7 +10378,7 @@
       <c r="T61" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="U61" s="142" t="s">
+      <c r="U61" s="148" t="s">
         <v>76</v>
       </c>
       <c r="V61" s="49"/>
@@ -10161,9 +10464,9 @@
       <c r="R62" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S62" s="140"/>
-      <c r="T62" s="140"/>
-      <c r="U62" s="140"/>
+      <c r="S62" s="144"/>
+      <c r="T62" s="144"/>
+      <c r="U62" s="144"/>
       <c r="V62" s="49"/>
       <c r="W62" s="74" t="s">
         <v>77</v>
@@ -10247,9 +10550,9 @@
       <c r="R63" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S63" s="141"/>
-      <c r="T63" s="141"/>
-      <c r="U63" s="141"/>
+      <c r="S63" s="145"/>
+      <c r="T63" s="145"/>
+      <c r="U63" s="145"/>
       <c r="V63" s="49"/>
       <c r="W63" s="74" t="s">
         <v>77</v>
@@ -10573,7 +10876,7 @@
       <c r="S68" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T68" s="144" t="s">
+      <c r="T68" s="146" t="s">
         <v>197</v>
       </c>
       <c r="U68" s="55"/>
@@ -10664,7 +10967,7 @@
       <c r="S69" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T69" s="140"/>
+      <c r="T69" s="144"/>
       <c r="U69" s="55"/>
       <c r="V69" s="49"/>
       <c r="W69" s="74" t="s">
@@ -10760,7 +11063,7 @@
       <c r="S70" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T70" s="140"/>
+      <c r="T70" s="144"/>
       <c r="U70" s="55"/>
       <c r="V70" s="49"/>
       <c r="W70" s="74" t="s">
@@ -10863,7 +11166,7 @@
       <c r="S71" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T71" s="140"/>
+      <c r="T71" s="144"/>
       <c r="U71" s="55"/>
       <c r="V71" s="58" t="s">
         <v>203</v>
@@ -10961,7 +11264,7 @@
       <c r="S72" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T72" s="140"/>
+      <c r="T72" s="144"/>
       <c r="U72" s="55"/>
       <c r="V72" s="58"/>
       <c r="W72" s="74" t="s">
@@ -11057,7 +11360,7 @@
       <c r="S73" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T73" s="141"/>
+      <c r="T73" s="145"/>
       <c r="U73" s="55"/>
       <c r="V73" s="58"/>
       <c r="W73" s="74" t="s">
@@ -11254,10 +11557,10 @@
       <c r="S76" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="T76" s="144" t="s">
+      <c r="T76" s="146" t="s">
         <v>210</v>
       </c>
-      <c r="U76" s="145" t="s">
+      <c r="U76" s="152" t="s">
         <v>211</v>
       </c>
       <c r="V76" s="58" t="s">
@@ -11353,8 +11656,8 @@
       <c r="S77" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="T77" s="140"/>
-      <c r="U77" s="140"/>
+      <c r="T77" s="144"/>
+      <c r="U77" s="144"/>
       <c r="V77" s="49"/>
       <c r="W77" s="74" t="s">
         <v>213</v>
@@ -11457,8 +11760,8 @@
       <c r="S78" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="T78" s="140"/>
-      <c r="U78" s="140"/>
+      <c r="T78" s="144"/>
+      <c r="U78" s="144"/>
       <c r="V78" s="49"/>
       <c r="W78" s="74" t="s">
         <v>157</v>
@@ -11553,8 +11856,8 @@
       <c r="S79" s="58" t="s">
         <v>221</v>
       </c>
-      <c r="T79" s="140"/>
-      <c r="U79" s="140"/>
+      <c r="T79" s="144"/>
+      <c r="U79" s="144"/>
       <c r="V79" s="49"/>
       <c r="W79" s="74" t="s">
         <v>157</v>
@@ -11657,8 +11960,8 @@
       <c r="S80" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="T80" s="141"/>
-      <c r="U80" s="141"/>
+      <c r="T80" s="145"/>
+      <c r="U80" s="145"/>
       <c r="V80" s="49"/>
       <c r="W80" s="74" t="s">
         <v>226</v>
@@ -12435,7 +12738,7 @@
       <c r="T89" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="U89" s="145" t="s">
+      <c r="U89" s="152" t="s">
         <v>211</v>
       </c>
       <c r="V89" s="49"/>
@@ -12543,7 +12846,7 @@
       <c r="T90" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="U90" s="140"/>
+      <c r="U90" s="144"/>
       <c r="V90" s="49"/>
       <c r="W90" s="74" t="s">
         <v>226</v>
@@ -12642,7 +12945,7 @@
       <c r="T91" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="U91" s="140"/>
+      <c r="U91" s="144"/>
       <c r="V91" s="49"/>
       <c r="W91" s="74" t="s">
         <v>228</v>
@@ -12739,7 +13042,7 @@
       <c r="T92" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="U92" s="140"/>
+      <c r="U92" s="144"/>
       <c r="V92" s="49"/>
       <c r="W92" s="74" t="s">
         <v>228</v>
@@ -12830,7 +13133,7 @@
       <c r="T93" s="58" t="s">
         <v>231</v>
       </c>
-      <c r="U93" s="140"/>
+      <c r="U93" s="144"/>
       <c r="V93" s="49"/>
       <c r="W93" s="74" t="s">
         <v>157</v>
@@ -12921,7 +13224,7 @@
       <c r="T94" s="58" t="s">
         <v>231</v>
       </c>
-      <c r="U94" s="140"/>
+      <c r="U94" s="144"/>
       <c r="V94" s="49"/>
       <c r="W94" s="74" t="s">
         <v>157</v>
@@ -13010,7 +13313,7 @@
         <v>242</v>
       </c>
       <c r="T95" s="58"/>
-      <c r="U95" s="140"/>
+      <c r="U95" s="144"/>
       <c r="V95" s="49"/>
       <c r="W95" s="74" t="s">
         <v>157</v>
@@ -13099,7 +13402,7 @@
         <v>242</v>
       </c>
       <c r="T96" s="58"/>
-      <c r="U96" s="140"/>
+      <c r="U96" s="144"/>
       <c r="V96" s="49"/>
       <c r="W96" s="74" t="s">
         <v>157</v>
@@ -13177,7 +13480,7 @@
       <c r="R97" s="49"/>
       <c r="S97" s="58"/>
       <c r="T97" s="58"/>
-      <c r="U97" s="140"/>
+      <c r="U97" s="144"/>
       <c r="V97" s="49"/>
       <c r="W97" s="74"/>
       <c r="X97" s="77"/>
@@ -13258,7 +13561,7 @@
         <v>209</v>
       </c>
       <c r="T98" s="58"/>
-      <c r="U98" s="140"/>
+      <c r="U98" s="144"/>
       <c r="V98" s="49"/>
       <c r="W98" s="74" t="s">
         <v>157</v>
@@ -13361,7 +13664,7 @@
         <v>209</v>
       </c>
       <c r="T99" s="58"/>
-      <c r="U99" s="141"/>
+      <c r="U99" s="145"/>
       <c r="V99" s="49"/>
       <c r="W99" s="74" t="s">
         <v>157</v>
@@ -14167,13 +14470,13 @@
       <c r="S109" s="58" t="s">
         <v>272</v>
       </c>
-      <c r="T109" s="144" t="s">
+      <c r="T109" s="146" t="s">
         <v>273</v>
       </c>
-      <c r="U109" s="147" t="s">
+      <c r="U109" s="151" t="s">
         <v>274</v>
       </c>
-      <c r="V109" s="144"/>
+      <c r="V109" s="146"/>
       <c r="W109" s="74" t="s">
         <v>157</v>
       </c>
@@ -14269,9 +14572,9 @@
       <c r="S110" s="58" t="s">
         <v>277</v>
       </c>
-      <c r="T110" s="141"/>
-      <c r="U110" s="141"/>
-      <c r="V110" s="141"/>
+      <c r="T110" s="145"/>
+      <c r="U110" s="145"/>
+      <c r="V110" s="145"/>
       <c r="W110" s="74" t="s">
         <v>157</v>
       </c>
@@ -15458,7 +15761,7 @@
         <v>296</v>
       </c>
       <c r="U123" s="80"/>
-      <c r="V123" s="144" t="s">
+      <c r="V123" s="146" t="s">
         <v>311</v>
       </c>
       <c r="W123" s="74" t="s">
@@ -15558,7 +15861,7 @@
         <v>296</v>
       </c>
       <c r="U124" s="80"/>
-      <c r="V124" s="141"/>
+      <c r="V124" s="145"/>
       <c r="W124" s="74" t="s">
         <v>157</v>
       </c>
@@ -15871,12 +16174,12 @@
         <f t="shared" si="27"/>
         <v>2</v>
       </c>
-      <c r="C129" s="55" t="s">
-        <v>319</v>
+      <c r="C129" s="141" t="s">
+        <v>736</v>
       </c>
       <c r="D129" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v xml:space="preserve">            Other Reactor Plant Equipment</v>
+        <f>REPT("   ", B129*2) &amp; C129</f>
+        <v xml:space="preserve">            Other Reactor Plant Equipment (based on MARVEL)</v>
       </c>
       <c r="E129" s="39" t="s">
         <v>35</v>
@@ -15956,12 +16259,12 @@
       <c r="B130" s="38">
         <v>2</v>
       </c>
-      <c r="C130" s="55" t="s">
-        <v>319</v>
+      <c r="C130" s="141" t="s">
+        <v>737</v>
       </c>
       <c r="D130" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v xml:space="preserve">            Other Reactor Plant Equipment</v>
+        <f>REPT("   ", B130*2) &amp; C130</f>
+        <v xml:space="preserve">            Other Reactor Plant Equipment (Helium purification)</v>
       </c>
       <c r="E130" s="39" t="s">
         <v>35</v>
@@ -15972,8 +16275,12 @@
       <c r="G130" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="H130" s="45"/>
-      <c r="I130" s="45"/>
+      <c r="H130" s="39" t="s">
+        <v>742</v>
+      </c>
+      <c r="I130" s="45" t="b">
+        <v>1</v>
+      </c>
       <c r="J130" s="60"/>
       <c r="K130" s="60">
         <f>8844770/N130*8.15527886031535</f>
@@ -16245,7 +16552,7 @@
         <v>333</v>
       </c>
       <c r="D133" s="39" t="str">
-        <f t="shared" ref="D133:D164" si="33">REPT("   ", B133*2) &amp; C133</f>
+        <f t="shared" ref="D133:D165" si="33">REPT("   ", B133*2) &amp; C133</f>
         <v xml:space="preserve">      Energy Conversion System </v>
       </c>
       <c r="E133" s="39"/>
@@ -16578,10 +16885,10 @@
       <c r="R138" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S138" s="139" t="s">
+      <c r="S138" s="147" t="s">
         <v>344</v>
       </c>
-      <c r="T138" s="139" t="s">
+      <c r="T138" s="147" t="s">
         <v>345</v>
       </c>
       <c r="U138" s="49"/>
@@ -16670,8 +16977,8 @@
       <c r="R139" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S139" s="140"/>
-      <c r="T139" s="140"/>
+      <c r="S139" s="144"/>
+      <c r="T139" s="144"/>
       <c r="U139" s="49"/>
       <c r="V139" s="49"/>
       <c r="W139" s="74" t="s">
@@ -16758,8 +17065,8 @@
       <c r="R140" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S140" s="140"/>
-      <c r="T140" s="140"/>
+      <c r="S140" s="144"/>
+      <c r="T140" s="144"/>
       <c r="U140" s="49"/>
       <c r="V140" s="49"/>
       <c r="W140" s="74" t="s">
@@ -16846,8 +17153,8 @@
       <c r="R141" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S141" s="140"/>
-      <c r="T141" s="140"/>
+      <c r="S141" s="144"/>
+      <c r="T141" s="144"/>
       <c r="U141" s="49"/>
       <c r="V141" s="49"/>
       <c r="W141" s="74" t="s">
@@ -16934,8 +17241,8 @@
       <c r="R142" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S142" s="140"/>
-      <c r="T142" s="140"/>
+      <c r="S142" s="144"/>
+      <c r="T142" s="144"/>
       <c r="U142" s="49"/>
       <c r="V142" s="49"/>
       <c r="W142" s="74" t="s">
@@ -17022,8 +17329,8 @@
       <c r="R143" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S143" s="141"/>
-      <c r="T143" s="141"/>
+      <c r="S143" s="145"/>
+      <c r="T143" s="145"/>
       <c r="U143" s="49"/>
       <c r="V143" s="49"/>
       <c r="W143" s="74" t="s">
@@ -17148,10 +17455,10 @@
       <c r="R145" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S145" s="144" t="s">
+      <c r="S145" s="146" t="s">
         <v>354</v>
       </c>
-      <c r="T145" s="144" t="s">
+      <c r="T145" s="146" t="s">
         <v>355</v>
       </c>
       <c r="U145" s="49"/>
@@ -17235,8 +17542,8 @@
       <c r="R146" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S146" s="140"/>
-      <c r="T146" s="140"/>
+      <c r="S146" s="144"/>
+      <c r="T146" s="144"/>
       <c r="U146" s="49"/>
       <c r="V146" s="49"/>
       <c r="W146" s="74" t="s">
@@ -17320,8 +17627,8 @@
       <c r="R147" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S147" s="140"/>
-      <c r="T147" s="140"/>
+      <c r="S147" s="144"/>
+      <c r="T147" s="144"/>
       <c r="U147" s="49"/>
       <c r="V147" s="49"/>
       <c r="W147" s="74" t="s">
@@ -17411,8 +17718,8 @@
       <c r="R148" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S148" s="140"/>
-      <c r="T148" s="140"/>
+      <c r="S148" s="144"/>
+      <c r="T148" s="144"/>
       <c r="U148" s="49"/>
       <c r="V148" s="49"/>
       <c r="W148" s="74" t="s">
@@ -17509,8 +17816,8 @@
       <c r="R149" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S149" s="140"/>
-      <c r="T149" s="140"/>
+      <c r="S149" s="144"/>
+      <c r="T149" s="144"/>
       <c r="U149" s="49"/>
       <c r="V149" s="49"/>
       <c r="W149" s="74" t="s">
@@ -17603,8 +17910,8 @@
       <c r="R150" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S150" s="141"/>
-      <c r="T150" s="141"/>
+      <c r="S150" s="145"/>
+      <c r="T150" s="145"/>
       <c r="U150" s="49"/>
       <c r="V150" s="49"/>
       <c r="W150" s="74" t="s">
@@ -17735,47 +18042,62 @@
         <v>48</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="50">
-        <v>30</v>
+    <row r="152" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="37">
+        <v>27</v>
       </c>
       <c r="B152" s="38">
         <f>IF(ISNUMBER(A152),
-    IF(AND(A152=INT(A152), MOD(A152, 10) = 0), 0,
-        IF(AND(A152=INT(A152), LEN(A152)=2), 1,
-            IF(AND(A152=INT(A152), LEN(A152)=3), 2,
-                LEN(A152) - FIND(".", A152) + 2)
-        )
-    ),
+IF(AND(A152=INT(A152), MOD(A152, 10) = 0), 0,
+IF(AND(A152=INT(A152), LEN(A152)=2), 1,
+IF(AND(A152=INT(A152), LEN(A152)=3), 2,
+LEN(A152) - FIND(".", A152) + 2)
+)
+),
 "")</f>
-        <v>0</v>
-      </c>
-      <c r="C152" s="55" t="s">
-        <v>370</v>
-      </c>
-      <c r="D152" s="39" t="str">
-        <f t="shared" si="33"/>
-        <v>Capitalized Indirect Services Cost</v>
-      </c>
-      <c r="E152" s="39"/>
+        <v>1</v>
+      </c>
+      <c r="C152" s="140" t="s">
+        <v>738</v>
+      </c>
+      <c r="D152" s="142" t="s">
+        <v>739</v>
+      </c>
+      <c r="E152" s="39" t="s">
+        <v>35</v>
+      </c>
       <c r="F152" s="39"/>
       <c r="G152" s="39"/>
       <c r="H152" s="39"/>
       <c r="I152" s="39"/>
-      <c r="J152" s="67"/>
-      <c r="K152" s="51"/>
-      <c r="L152" s="50"/>
-      <c r="M152" s="50"/>
-      <c r="N152" s="50"/>
-      <c r="O152" s="50"/>
-      <c r="P152" s="50"/>
-      <c r="Q152" s="67"/>
-      <c r="R152" s="50"/>
-      <c r="S152" s="50"/>
-      <c r="T152" s="50"/>
-      <c r="U152" s="50"/>
-      <c r="V152" s="50"/>
-      <c r="W152" s="74"/>
+      <c r="J152" s="60">
+        <v>102000</v>
+      </c>
+      <c r="K152" s="65"/>
+      <c r="L152" s="49"/>
+      <c r="M152" s="58"/>
+      <c r="N152" s="49"/>
+      <c r="O152" s="49"/>
+      <c r="P152" s="49"/>
+      <c r="Q152" s="65">
+        <v>2025</v>
+      </c>
+      <c r="R152" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="S152" s="58" t="s">
+        <v>320</v>
+      </c>
+      <c r="T152" s="58" t="s">
+        <v>741</v>
+      </c>
+      <c r="U152" s="58" t="s">
+        <v>740</v>
+      </c>
+      <c r="V152" s="49"/>
+      <c r="W152" s="74" t="s">
+        <v>340</v>
+      </c>
       <c r="X152" s="77"/>
       <c r="Y152" s="77"/>
       <c r="Z152" s="74"/>
@@ -17787,19 +18109,27 @@
       <c r="AF152" s="76"/>
       <c r="AG152" s="74"/>
     </row>
-    <row r="153" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="50">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B153" s="38">
-        <v>1</v>
+        <f>IF(ISNUMBER(A153),
+    IF(AND(A153=INT(A153), MOD(A153, 10) = 0), 0,
+        IF(AND(A153=INT(A153), LEN(A153)=2), 1,
+            IF(AND(A153=INT(A153), LEN(A153)=3), 2,
+                LEN(A153) - FIND(".", A153) + 2)
+        )
+    ),
+"")</f>
+        <v>0</v>
       </c>
       <c r="C153" s="55" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D153" s="39" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve">      Factory &amp; field indirect costs</v>
+        <v>Capitalized Indirect Services Cost</v>
       </c>
       <c r="E153" s="39"/>
       <c r="F153" s="39"/>
@@ -17807,14 +18137,14 @@
       <c r="H153" s="39"/>
       <c r="I153" s="39"/>
       <c r="J153" s="67"/>
-      <c r="K153" s="68"/>
-      <c r="L153" s="49"/>
-      <c r="M153" s="58"/>
+      <c r="K153" s="51"/>
+      <c r="L153" s="50"/>
+      <c r="M153" s="50"/>
       <c r="N153" s="50"/>
       <c r="O153" s="50"/>
       <c r="P153" s="50"/>
-      <c r="Q153" s="65"/>
-      <c r="R153" s="49"/>
+      <c r="Q153" s="67"/>
+      <c r="R153" s="50"/>
       <c r="S153" s="50"/>
       <c r="T153" s="50"/>
       <c r="U153" s="50"/>
@@ -17831,19 +18161,19 @@
       <c r="AF153" s="76"/>
       <c r="AG153" s="74"/>
     </row>
-    <row r="154" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="50">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B154" s="38">
         <v>1</v>
       </c>
       <c r="C154" s="55" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D154" s="39" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve">      Factory and construction supervision</v>
+        <v xml:space="preserve">      Factory &amp; field indirect costs</v>
       </c>
       <c r="E154" s="39"/>
       <c r="F154" s="39"/>
@@ -17851,9 +18181,9 @@
       <c r="H154" s="39"/>
       <c r="I154" s="39"/>
       <c r="J154" s="67"/>
-      <c r="K154" s="51"/>
-      <c r="L154" s="50"/>
-      <c r="M154" s="50"/>
+      <c r="K154" s="68"/>
+      <c r="L154" s="49"/>
+      <c r="M154" s="58"/>
       <c r="N154" s="50"/>
       <c r="O154" s="50"/>
       <c r="P154" s="50"/>
@@ -17876,108 +18206,70 @@
       <c r="AG154" s="74"/>
     </row>
     <row r="155" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="37">
+      <c r="A155" s="50">
+        <v>32</v>
+      </c>
+      <c r="B155" s="38">
+        <v>1</v>
+      </c>
+      <c r="C155" s="55" t="s">
+        <v>372</v>
+      </c>
+      <c r="D155" s="39" t="str">
+        <f t="shared" si="33"/>
+        <v xml:space="preserve">      Factory and construction supervision</v>
+      </c>
+      <c r="E155" s="39"/>
+      <c r="F155" s="39"/>
+      <c r="G155" s="39"/>
+      <c r="H155" s="39"/>
+      <c r="I155" s="39"/>
+      <c r="J155" s="67"/>
+      <c r="K155" s="51"/>
+      <c r="L155" s="50"/>
+      <c r="M155" s="50"/>
+      <c r="N155" s="50"/>
+      <c r="O155" s="50"/>
+      <c r="P155" s="50"/>
+      <c r="Q155" s="65"/>
+      <c r="R155" s="49"/>
+      <c r="S155" s="50"/>
+      <c r="T155" s="50"/>
+      <c r="U155" s="50"/>
+      <c r="V155" s="50"/>
+      <c r="W155" s="74"/>
+      <c r="X155" s="77"/>
+      <c r="Y155" s="77"/>
+      <c r="Z155" s="74"/>
+      <c r="AA155" s="76"/>
+      <c r="AB155" s="76"/>
+      <c r="AC155" s="74"/>
+      <c r="AD155" s="76"/>
+      <c r="AE155" s="76"/>
+      <c r="AF155" s="76"/>
+      <c r="AG155" s="74"/>
+    </row>
+    <row r="156" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="37">
         <v>33</v>
       </c>
-      <c r="B155" s="38">
-        <f t="shared" ref="B155:B169" si="42">IF(ISNUMBER(A155),
-IF(AND(A155=INT(A155), MOD(A155, 10) = 0), 0,
-IF(AND(A155=INT(A155), LEN(A155)=2), 1,
-IF(AND(A155=INT(A155), LEN(A155)=3), 2,
-LEN(A155) - FIND(".", A155) + 2)
+      <c r="B156" s="38">
+        <f t="shared" ref="B156:B170" si="42">IF(ISNUMBER(A156),
+IF(AND(A156=INT(A156), MOD(A156, 10) = 0), 0,
+IF(AND(A156=INT(A156), LEN(A156)=2), 1,
+IF(AND(A156=INT(A156), LEN(A156)=3), 2,
+LEN(A156) - FIND(".", A156) + 2)
 )
 ),
 "")</f>
         <v>1</v>
       </c>
-      <c r="C155" s="55" t="s">
+      <c r="C156" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="D155" s="39" t="str">
+      <c r="D156" s="39" t="str">
         <f t="shared" si="33"/>
         <v xml:space="preserve">      Startup Costs</v>
-      </c>
-      <c r="E155" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="F155" s="39"/>
-      <c r="G155" s="39"/>
-      <c r="H155" s="39"/>
-      <c r="I155" s="39"/>
-      <c r="J155" s="43">
-        <f>MARVEL_Cost!C58</f>
-        <v>2407166.4</v>
-      </c>
-      <c r="K155" s="44"/>
-      <c r="L155" s="46"/>
-      <c r="M155" s="52"/>
-      <c r="N155" s="46"/>
-      <c r="O155" s="46"/>
-      <c r="P155" s="46"/>
-      <c r="Q155" s="65">
-        <v>2024</v>
-      </c>
-      <c r="R155" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="S155" s="143" t="s">
-        <v>320</v>
-      </c>
-      <c r="T155" s="46"/>
-      <c r="U155" s="46"/>
-      <c r="V155" s="46"/>
-      <c r="W155" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="X155" s="77">
-        <f>0.9*$J155</f>
-        <v>2166449.7599999998</v>
-      </c>
-      <c r="Y155" s="77">
-        <f>1.5*J155</f>
-        <v>3610749.5999999996</v>
-      </c>
-      <c r="Z155" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA155" s="76">
-        <f>0.9*K155</f>
-        <v>0</v>
-      </c>
-      <c r="AB155" s="76">
-        <f>1.3*K155</f>
-        <v>0</v>
-      </c>
-      <c r="AC155" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD155" s="76" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE155" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF155" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG155" s="74" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="156" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="37">
-        <v>34</v>
-      </c>
-      <c r="B156" s="38">
-        <f t="shared" si="42"/>
-        <v>1</v>
-      </c>
-      <c r="C156" s="55" t="s">
-        <v>374</v>
-      </c>
-      <c r="D156" s="39" t="str">
-        <f t="shared" si="33"/>
-        <v xml:space="preserve">      Shipping and Transportation Costs</v>
       </c>
       <c r="E156" s="39" t="s">
         <v>35</v>
@@ -17987,8 +18279,8 @@
       <c r="H156" s="39"/>
       <c r="I156" s="39"/>
       <c r="J156" s="43">
-        <f>0.5*MARVEL_Cost!C62</f>
-        <v>832641.4</v>
+        <f>MARVEL_Cost!C58</f>
+        <v>2407166.4</v>
       </c>
       <c r="K156" s="44"/>
       <c r="L156" s="46"/>
@@ -18002,7 +18294,9 @@
       <c r="R156" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="S156" s="140"/>
+      <c r="S156" s="143" t="s">
+        <v>320</v>
+      </c>
       <c r="T156" s="46"/>
       <c r="U156" s="46"/>
       <c r="V156" s="46"/>
@@ -18011,11 +18305,11 @@
       </c>
       <c r="X156" s="77">
         <f>0.9*$J156</f>
-        <v>749377.26</v>
+        <v>2166449.7599999998</v>
       </c>
       <c r="Y156" s="77">
         <f>1.5*J156</f>
-        <v>1248962.1000000001</v>
+        <v>3610749.5999999996</v>
       </c>
       <c r="Z156" s="74" t="s">
         <v>44</v>
@@ -18044,20 +18338,20 @@
         <v>48</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="37">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B157" s="38">
         <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="C157" s="55" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D157" s="39" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve">      Engineering Services</v>
+        <v xml:space="preserve">      Shipping and Transportation Costs</v>
       </c>
       <c r="E157" s="39" t="s">
         <v>35</v>
@@ -18067,35 +18361,35 @@
       <c r="H157" s="39"/>
       <c r="I157" s="39"/>
       <c r="J157" s="43">
-        <f>MARVEL_Cost!C65</f>
-        <v>620313.58773783164</v>
-      </c>
-      <c r="K157" s="60"/>
-      <c r="L157" s="49"/>
-      <c r="M157" s="58"/>
-      <c r="N157" s="49"/>
-      <c r="O157" s="49"/>
-      <c r="P157" s="49"/>
+        <f>0.5*MARVEL_Cost!C62</f>
+        <v>832641.4</v>
+      </c>
+      <c r="K157" s="44"/>
+      <c r="L157" s="46"/>
+      <c r="M157" s="52"/>
+      <c r="N157" s="46"/>
+      <c r="O157" s="46"/>
+      <c r="P157" s="46"/>
       <c r="Q157" s="65">
         <v>2024</v>
       </c>
-      <c r="R157" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S157" s="140"/>
-      <c r="T157" s="49"/>
-      <c r="U157" s="49"/>
-      <c r="V157" s="49"/>
+      <c r="R157" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="S157" s="144"/>
+      <c r="T157" s="46"/>
+      <c r="U157" s="46"/>
+      <c r="V157" s="46"/>
       <c r="W157" s="74" t="s">
         <v>77</v>
       </c>
       <c r="X157" s="77">
         <f>0.9*$J157</f>
-        <v>558282.22896404844</v>
+        <v>749377.26</v>
       </c>
       <c r="Y157" s="77">
         <f>1.5*J157</f>
-        <v>930470.3816067474</v>
+        <v>1248962.1000000001</v>
       </c>
       <c r="Z157" s="74" t="s">
         <v>44</v>
@@ -18126,18 +18420,18 @@
     </row>
     <row r="158" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="37">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B158" s="38">
         <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="C158" s="55" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D158" s="39" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve">      PM/CM Services</v>
+        <v xml:space="preserve">      Engineering Services</v>
       </c>
       <c r="E158" s="39" t="s">
         <v>35</v>
@@ -18147,8 +18441,8 @@
       <c r="H158" s="39"/>
       <c r="I158" s="39"/>
       <c r="J158" s="43">
-        <f>MARVEL_Cost!C68</f>
-        <v>416958.9359999997</v>
+        <f>MARVEL_Cost!C65</f>
+        <v>620313.58773783164</v>
       </c>
       <c r="K158" s="60"/>
       <c r="L158" s="49"/>
@@ -18162,7 +18456,7 @@
       <c r="R158" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="S158" s="141"/>
+      <c r="S158" s="144"/>
       <c r="T158" s="49"/>
       <c r="U158" s="49"/>
       <c r="V158" s="49"/>
@@ -18171,11 +18465,11 @@
       </c>
       <c r="X158" s="77">
         <f>0.9*$J158</f>
-        <v>375263.04239999974</v>
+        <v>558282.22896404844</v>
       </c>
       <c r="Y158" s="77">
         <f>1.5*J158</f>
-        <v>625438.40399999951</v>
+        <v>930470.3816067474</v>
       </c>
       <c r="Z158" s="74" t="s">
         <v>44</v>
@@ -18206,210 +18500,245 @@
     </row>
     <row r="159" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="37">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B159" s="38">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159" s="55" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D159" s="39" t="str">
         <f t="shared" si="33"/>
-        <v>Capitalized training costs</v>
-      </c>
-      <c r="E159" s="39"/>
+        <v xml:space="preserve">      PM/CM Services</v>
+      </c>
+      <c r="E159" s="39" t="s">
+        <v>35</v>
+      </c>
       <c r="F159" s="39"/>
       <c r="G159" s="39"/>
       <c r="H159" s="39"/>
       <c r="I159" s="39"/>
-      <c r="J159" s="43"/>
+      <c r="J159" s="43">
+        <f>MARVEL_Cost!C68</f>
+        <v>416958.9359999997</v>
+      </c>
       <c r="K159" s="60"/>
       <c r="L159" s="49"/>
       <c r="M159" s="58"/>
       <c r="N159" s="49"/>
       <c r="O159" s="49"/>
       <c r="P159" s="49"/>
-      <c r="Q159" s="65"/>
-      <c r="R159" s="49"/>
-      <c r="S159" s="50"/>
+      <c r="Q159" s="65">
+        <v>2024</v>
+      </c>
+      <c r="R159" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="S159" s="145"/>
       <c r="T159" s="49"/>
       <c r="U159" s="49"/>
       <c r="V159" s="49"/>
-      <c r="W159" s="74"/>
-      <c r="X159" s="77"/>
-      <c r="Y159" s="77"/>
-      <c r="Z159" s="74"/>
-      <c r="AA159" s="76"/>
-      <c r="AB159" s="76"/>
-      <c r="AC159" s="74"/>
-      <c r="AD159" s="76"/>
-      <c r="AE159" s="76"/>
-      <c r="AF159" s="76"/>
-      <c r="AG159" s="74"/>
+      <c r="W159" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="X159" s="77">
+        <f>0.9*$J159</f>
+        <v>375263.04239999974</v>
+      </c>
+      <c r="Y159" s="77">
+        <f>1.5*J159</f>
+        <v>625438.40399999951</v>
+      </c>
+      <c r="Z159" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA159" s="76">
+        <f>0.9*K159</f>
+        <v>0</v>
+      </c>
+      <c r="AB159" s="76">
+        <f>1.3*K159</f>
+        <v>0</v>
+      </c>
+      <c r="AC159" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD159" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE159" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF159" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG159" s="74" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="160" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="37">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B160" s="38">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C160" s="55" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D160" s="39" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve">      staff recruitment and training</v>
-      </c>
-      <c r="E160" s="39" t="s">
-        <v>35</v>
-      </c>
+        <v>Capitalized training costs</v>
+      </c>
+      <c r="E160" s="39"/>
       <c r="F160" s="39"/>
       <c r="G160" s="39"/>
       <c r="H160" s="39"/>
       <c r="I160" s="39"/>
-      <c r="J160" s="43">
-        <v>300000</v>
-      </c>
+      <c r="J160" s="43"/>
       <c r="K160" s="60"/>
       <c r="L160" s="49"/>
       <c r="M160" s="58"/>
       <c r="N160" s="49"/>
       <c r="O160" s="49"/>
       <c r="P160" s="49"/>
-      <c r="Q160" s="65">
-        <v>2024</v>
-      </c>
-      <c r="R160" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S160" s="42"/>
-      <c r="T160" s="49" t="s">
-        <v>379</v>
-      </c>
-      <c r="U160" s="49" t="s">
-        <v>380</v>
-      </c>
+      <c r="Q160" s="65"/>
+      <c r="R160" s="49"/>
+      <c r="S160" s="50"/>
+      <c r="T160" s="49"/>
+      <c r="U160" s="49"/>
       <c r="V160" s="49"/>
-      <c r="W160" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="X160" s="77">
-        <f>0.9*$J160</f>
-        <v>270000</v>
-      </c>
-      <c r="Y160" s="77">
-        <f>1.5*J160</f>
-        <v>450000</v>
-      </c>
-      <c r="Z160" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA160" s="76">
-        <f>0.9*K160</f>
-        <v>0</v>
-      </c>
-      <c r="AB160" s="76">
-        <f>1.3*K160</f>
-        <v>0</v>
-      </c>
-      <c r="AC160" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD160" s="76" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE160" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF160" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG160" s="74" t="s">
-        <v>48</v>
-      </c>
+      <c r="W160" s="74"/>
+      <c r="X160" s="77"/>
+      <c r="Y160" s="77"/>
+      <c r="Z160" s="74"/>
+      <c r="AA160" s="76"/>
+      <c r="AB160" s="76"/>
+      <c r="AC160" s="74"/>
+      <c r="AD160" s="76"/>
+      <c r="AE160" s="76"/>
+      <c r="AF160" s="76"/>
+      <c r="AG160" s="74"/>
     </row>
     <row r="161" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="50">
-        <v>60</v>
+      <c r="A161" s="37">
+        <v>41</v>
       </c>
       <c r="B161" s="38">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C161" s="55" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D161" s="39" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve">Capitalized Financial Costs </v>
-      </c>
-      <c r="E161" s="39"/>
+        <v xml:space="preserve">      staff recruitment and training</v>
+      </c>
+      <c r="E161" s="39" t="s">
+        <v>35</v>
+      </c>
       <c r="F161" s="39"/>
       <c r="G161" s="39"/>
       <c r="H161" s="39"/>
       <c r="I161" s="39"/>
-      <c r="J161" s="67"/>
-      <c r="K161" s="51"/>
-      <c r="L161" s="50"/>
-      <c r="M161" s="50"/>
-      <c r="N161" s="50"/>
-      <c r="O161" s="50"/>
-      <c r="P161" s="50"/>
-      <c r="Q161" s="67"/>
-      <c r="R161" s="50"/>
-      <c r="S161" s="50"/>
-      <c r="T161" s="50"/>
-      <c r="U161" s="50"/>
-      <c r="V161" s="50"/>
-      <c r="W161" s="74"/>
-      <c r="X161" s="77"/>
-      <c r="Y161" s="77"/>
-      <c r="Z161" s="74"/>
-      <c r="AA161" s="76"/>
-      <c r="AB161" s="76"/>
-      <c r="AC161" s="74"/>
-      <c r="AD161" s="76"/>
-      <c r="AE161" s="76"/>
-      <c r="AF161" s="76"/>
-      <c r="AG161" s="74"/>
+      <c r="J161" s="43">
+        <v>300000</v>
+      </c>
+      <c r="K161" s="60"/>
+      <c r="L161" s="49"/>
+      <c r="M161" s="58"/>
+      <c r="N161" s="49"/>
+      <c r="O161" s="49"/>
+      <c r="P161" s="49"/>
+      <c r="Q161" s="65">
+        <v>2024</v>
+      </c>
+      <c r="R161" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="S161" s="42"/>
+      <c r="T161" s="49" t="s">
+        <v>379</v>
+      </c>
+      <c r="U161" s="49" t="s">
+        <v>380</v>
+      </c>
+      <c r="V161" s="49"/>
+      <c r="W161" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X161" s="77">
+        <f>0.9*$J161</f>
+        <v>270000</v>
+      </c>
+      <c r="Y161" s="77">
+        <f>1.5*J161</f>
+        <v>450000</v>
+      </c>
+      <c r="Z161" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA161" s="76">
+        <f>0.9*K161</f>
+        <v>0</v>
+      </c>
+      <c r="AB161" s="76">
+        <f>1.3*K161</f>
+        <v>0</v>
+      </c>
+      <c r="AC161" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD161" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE161" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF161" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG161" s="74" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="162" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="37">
-        <v>62</v>
+      <c r="A162" s="50">
+        <v>60</v>
       </c>
       <c r="B162" s="38">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C162" s="55" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D162" s="39" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve">      Interest</v>
+        <v xml:space="preserve">Capitalized Financial Costs </v>
       </c>
       <c r="E162" s="39"/>
       <c r="F162" s="39"/>
       <c r="G162" s="39"/>
       <c r="H162" s="39"/>
       <c r="I162" s="39"/>
-      <c r="J162" s="43"/>
-      <c r="K162" s="60"/>
-      <c r="L162" s="49"/>
-      <c r="M162" s="58"/>
-      <c r="N162" s="49"/>
-      <c r="O162" s="49"/>
-      <c r="P162" s="49"/>
-      <c r="Q162" s="65"/>
-      <c r="R162" s="49"/>
-      <c r="S162" s="58"/>
-      <c r="T162" s="49"/>
-      <c r="U162" s="49"/>
-      <c r="V162" s="49"/>
+      <c r="J162" s="67"/>
+      <c r="K162" s="51"/>
+      <c r="L162" s="50"/>
+      <c r="M162" s="50"/>
+      <c r="N162" s="50"/>
+      <c r="O162" s="50"/>
+      <c r="P162" s="50"/>
+      <c r="Q162" s="67"/>
+      <c r="R162" s="50"/>
+      <c r="S162" s="50"/>
+      <c r="T162" s="50"/>
+      <c r="U162" s="50"/>
+      <c r="V162" s="50"/>
       <c r="W162" s="74"/>
       <c r="X162" s="77"/>
       <c r="Y162" s="77"/>
@@ -18424,37 +18753,37 @@
     </row>
     <row r="163" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="37">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B163" s="38">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="C163" s="69" t="s">
-        <v>383</v>
+        <v>1</v>
+      </c>
+      <c r="C163" s="55" t="s">
+        <v>382</v>
       </c>
       <c r="D163" s="39" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve">Annualized O&amp;M Cost </v>
+        <v xml:space="preserve">      Interest</v>
       </c>
       <c r="E163" s="39"/>
       <c r="F163" s="39"/>
       <c r="G163" s="39"/>
       <c r="H163" s="39"/>
       <c r="I163" s="39"/>
-      <c r="J163" s="40"/>
-      <c r="K163" s="40"/>
-      <c r="L163" s="38"/>
-      <c r="M163" s="41"/>
-      <c r="N163" s="38"/>
-      <c r="O163" s="38"/>
-      <c r="P163" s="38"/>
-      <c r="Q163" s="40"/>
-      <c r="R163" s="38"/>
-      <c r="S163" s="41"/>
-      <c r="T163" s="38"/>
-      <c r="U163" s="38"/>
-      <c r="V163" s="38"/>
+      <c r="J163" s="43"/>
+      <c r="K163" s="60"/>
+      <c r="L163" s="49"/>
+      <c r="M163" s="58"/>
+      <c r="N163" s="49"/>
+      <c r="O163" s="49"/>
+      <c r="P163" s="49"/>
+      <c r="Q163" s="65"/>
+      <c r="R163" s="49"/>
+      <c r="S163" s="58"/>
+      <c r="T163" s="49"/>
+      <c r="U163" s="49"/>
+      <c r="V163" s="49"/>
       <c r="W163" s="74"/>
       <c r="X163" s="77"/>
       <c r="Y163" s="77"/>
@@ -18469,37 +18798,37 @@
     </row>
     <row r="164" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="37">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B164" s="38">
         <f t="shared" si="42"/>
-        <v>1</v>
-      </c>
-      <c r="C164" s="55" t="s">
-        <v>384</v>
+        <v>0</v>
+      </c>
+      <c r="C164" s="69" t="s">
+        <v>383</v>
       </c>
       <c r="D164" s="39" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve">      O&amp;M Staff</v>
+        <v xml:space="preserve">Annualized O&amp;M Cost </v>
       </c>
       <c r="E164" s="39"/>
       <c r="F164" s="39"/>
       <c r="G164" s="39"/>
       <c r="H164" s="39"/>
       <c r="I164" s="39"/>
-      <c r="J164" s="43"/>
-      <c r="K164" s="60"/>
-      <c r="L164" s="49"/>
-      <c r="M164" s="58"/>
-      <c r="N164" s="49"/>
-      <c r="O164" s="49"/>
-      <c r="P164" s="49"/>
-      <c r="Q164" s="65"/>
-      <c r="R164" s="49"/>
-      <c r="S164" s="58"/>
-      <c r="T164" s="49"/>
-      <c r="U164" s="49"/>
-      <c r="V164" s="49"/>
+      <c r="J164" s="40"/>
+      <c r="K164" s="40"/>
+      <c r="L164" s="38"/>
+      <c r="M164" s="41"/>
+      <c r="N164" s="38"/>
+      <c r="O164" s="38"/>
+      <c r="P164" s="38"/>
+      <c r="Q164" s="40"/>
+      <c r="R164" s="38"/>
+      <c r="S164" s="41"/>
+      <c r="T164" s="38"/>
+      <c r="U164" s="38"/>
+      <c r="V164" s="38"/>
       <c r="W164" s="74"/>
       <c r="X164" s="77"/>
       <c r="Y164" s="77"/>
@@ -18512,117 +18841,71 @@
       <c r="AF164" s="76"/>
       <c r="AG164" s="74"/>
     </row>
-    <row r="165" spans="1:33" ht="71" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="53">
-        <v>711</v>
+    <row r="165" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="37">
+        <v>71</v>
       </c>
       <c r="B165" s="38">
         <f t="shared" si="42"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C165" s="55" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D165" s="39" t="str">
-        <f t="shared" ref="D165:D192" si="43">REPT("   ", B165*2) &amp; C165</f>
-        <v xml:space="preserve">            Operators </v>
-      </c>
-      <c r="E165" s="39" t="s">
-        <v>268</v>
-      </c>
+        <f t="shared" si="33"/>
+        <v xml:space="preserve">      O&amp;M Staff</v>
+      </c>
+      <c r="E165" s="39"/>
       <c r="F165" s="39"/>
       <c r="G165" s="39"/>
       <c r="H165" s="39"/>
       <c r="I165" s="39"/>
       <c r="J165" s="43"/>
-      <c r="K165" s="60">
-        <v>178500</v>
-      </c>
-      <c r="L165" s="49" t="s">
-        <v>386</v>
-      </c>
-      <c r="M165" s="58" t="s">
-        <v>387</v>
-      </c>
+      <c r="K165" s="60"/>
+      <c r="L165" s="49"/>
+      <c r="M165" s="58"/>
       <c r="N165" s="49"/>
       <c r="O165" s="49"/>
-      <c r="P165" s="49">
-        <v>1</v>
-      </c>
-      <c r="Q165" s="65">
-        <v>2024</v>
-      </c>
-      <c r="R165" s="49" t="s">
-        <v>53</v>
-      </c>
+      <c r="P165" s="49"/>
+      <c r="Q165" s="65"/>
+      <c r="R165" s="49"/>
       <c r="S165" s="58"/>
-      <c r="T165" s="58" t="s">
-        <v>388</v>
-      </c>
+      <c r="T165" s="49"/>
       <c r="U165" s="49"/>
       <c r="V165" s="49"/>
-      <c r="W165" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="X165" s="77">
-        <f>0.9*$J165</f>
-        <v>0</v>
-      </c>
-      <c r="Y165" s="77">
-        <f>1.5*J165</f>
-        <v>0</v>
-      </c>
-      <c r="Z165" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA165" s="76">
-        <f>0.9*K165</f>
-        <v>160650</v>
-      </c>
-      <c r="AB165" s="76">
-        <f>1.3*K165</f>
-        <v>232050</v>
-      </c>
-      <c r="AC165" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD165" s="76" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE165" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF165" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG165" s="74" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="166" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W165" s="74"/>
+      <c r="X165" s="77"/>
+      <c r="Y165" s="77"/>
+      <c r="Z165" s="74"/>
+      <c r="AA165" s="76"/>
+      <c r="AB165" s="76"/>
+      <c r="AC165" s="74"/>
+      <c r="AD165" s="76"/>
+      <c r="AE165" s="76"/>
+      <c r="AF165" s="76"/>
+      <c r="AG165" s="74"/>
+    </row>
+    <row r="166" spans="1:33" ht="71" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="53">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B166" s="38">
         <f t="shared" si="42"/>
         <v>2</v>
       </c>
       <c r="C166" s="55" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D166" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">            Remote Monitoring Technicians </v>
+        <f t="shared" ref="D166:D193" si="43">REPT("   ", B166*2) &amp; C166</f>
+        <v xml:space="preserve">            Operators </v>
       </c>
       <c r="E166" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="F166" s="39" t="s">
-        <v>390</v>
-      </c>
-      <c r="G166" s="39" t="s">
-        <v>391</v>
-      </c>
+      <c r="F166" s="39"/>
+      <c r="G166" s="39"/>
       <c r="H166" s="39"/>
       <c r="I166" s="39"/>
       <c r="J166" s="43"/>
@@ -18633,7 +18916,7 @@
         <v>386</v>
       </c>
       <c r="M166" s="58" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="N166" s="49"/>
       <c r="O166" s="49"/>
@@ -18690,26 +18973,30 @@
         <v>48</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="53">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B167" s="38">
         <f t="shared" si="42"/>
         <v>2</v>
       </c>
       <c r="C167" s="55" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D167" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Security Staff </v>
+        <v xml:space="preserve">            Remote Monitoring Technicians </v>
       </c>
       <c r="E167" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="F167" s="39"/>
-      <c r="G167" s="39"/>
+      <c r="F167" s="39" t="s">
+        <v>390</v>
+      </c>
+      <c r="G167" s="39" t="s">
+        <v>391</v>
+      </c>
       <c r="H167" s="39"/>
       <c r="I167" s="39"/>
       <c r="J167" s="43"/>
@@ -18720,7 +19007,7 @@
         <v>386</v>
       </c>
       <c r="M167" s="58" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="N167" s="49"/>
       <c r="O167" s="49"/>
@@ -18777,368 +19064,404 @@
         <v>48</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="37">
-        <v>72</v>
+    <row r="168" spans="1:33" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="53">
+        <v>713</v>
       </c>
       <c r="B168" s="38">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C168" s="55" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D168" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">      Variable Non-Fuel Costs</v>
-      </c>
-      <c r="E168" s="39"/>
+        <v xml:space="preserve">            Security Staff </v>
+      </c>
+      <c r="E168" s="39" t="s">
+        <v>268</v>
+      </c>
       <c r="F168" s="39"/>
       <c r="G168" s="39"/>
       <c r="H168" s="39"/>
       <c r="I168" s="39"/>
       <c r="J168" s="43"/>
-      <c r="K168" s="60"/>
-      <c r="L168" s="49"/>
-      <c r="M168" s="58"/>
+      <c r="K168" s="60">
+        <v>178500</v>
+      </c>
+      <c r="L168" s="49" t="s">
+        <v>386</v>
+      </c>
+      <c r="M168" s="58" t="s">
+        <v>394</v>
+      </c>
       <c r="N168" s="49"/>
       <c r="O168" s="49"/>
-      <c r="P168" s="49"/>
-      <c r="Q168" s="65"/>
-      <c r="R168" s="49"/>
+      <c r="P168" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q168" s="65">
+        <v>2024</v>
+      </c>
+      <c r="R168" s="49" t="s">
+        <v>53</v>
+      </c>
       <c r="S168" s="58"/>
-      <c r="T168" s="58"/>
+      <c r="T168" s="58" t="s">
+        <v>388</v>
+      </c>
       <c r="U168" s="49"/>
       <c r="V168" s="49"/>
-      <c r="W168" s="74"/>
-      <c r="X168" s="77"/>
-      <c r="Y168" s="77"/>
-      <c r="Z168" s="74"/>
-      <c r="AA168" s="76"/>
-      <c r="AB168" s="76"/>
-      <c r="AC168" s="74"/>
-      <c r="AD168" s="76"/>
-      <c r="AE168" s="76"/>
-      <c r="AF168" s="76"/>
-      <c r="AG168" s="74"/>
-    </row>
-    <row r="169" spans="1:33" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W168" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X168" s="77">
+        <f>0.9*$J168</f>
+        <v>0</v>
+      </c>
+      <c r="Y168" s="77">
+        <f>1.5*J168</f>
+        <v>0</v>
+      </c>
+      <c r="Z168" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA168" s="76">
+        <f>0.9*K168</f>
+        <v>160650</v>
+      </c>
+      <c r="AB168" s="76">
+        <f>1.3*K168</f>
+        <v>232050</v>
+      </c>
+      <c r="AC168" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD168" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE168" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF168" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG168" s="74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="169" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="37">
-        <v>721</v>
+        <v>72</v>
       </c>
       <c r="B169" s="38">
         <f t="shared" si="42"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C169" s="55" t="s">
-        <v>302</v>
+        <v>395</v>
       </c>
       <c r="D169" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Coolant</v>
-      </c>
-      <c r="E169" s="39" t="s">
-        <v>268</v>
-      </c>
-      <c r="F169" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="G169" s="39" t="s">
-        <v>303</v>
-      </c>
+        <v xml:space="preserve">      Variable Non-Fuel Costs</v>
+      </c>
+      <c r="E169" s="39"/>
+      <c r="F169" s="39"/>
+      <c r="G169" s="39"/>
       <c r="H169" s="39"/>
       <c r="I169" s="39"/>
       <c r="J169" s="43"/>
-      <c r="K169" s="60">
-        <v>170</v>
-      </c>
-      <c r="L169" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="M169" s="58" t="s">
-        <v>396</v>
-      </c>
+      <c r="K169" s="60"/>
+      <c r="L169" s="49"/>
+      <c r="M169" s="58"/>
       <c r="N169" s="49"/>
-      <c r="O169" s="49" t="s">
-        <v>188</v>
-      </c>
+      <c r="O169" s="49"/>
       <c r="P169" s="49"/>
-      <c r="Q169" s="65">
-        <v>2024</v>
-      </c>
-      <c r="R169" s="49" t="s">
-        <v>219</v>
-      </c>
-      <c r="S169" s="58" t="s">
-        <v>305</v>
-      </c>
-      <c r="T169" s="62" t="s">
-        <v>305</v>
-      </c>
-      <c r="U169" s="80" t="s">
-        <v>306</v>
-      </c>
-      <c r="V169" s="49" t="s">
-        <v>307</v>
-      </c>
-      <c r="W169" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="X169" s="77">
-        <f>0.9*$J169</f>
-        <v>0</v>
-      </c>
-      <c r="Y169" s="77">
-        <f>1.5*J169</f>
-        <v>0</v>
-      </c>
-      <c r="Z169" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA169" s="76">
-        <f>0.9*K169</f>
-        <v>153</v>
-      </c>
-      <c r="AB169" s="76">
-        <f>1.3*K169</f>
-        <v>221</v>
-      </c>
-      <c r="AC169" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD169" s="76" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE169" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF169" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG169" s="74" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="170" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q169" s="65"/>
+      <c r="R169" s="49"/>
+      <c r="S169" s="58"/>
+      <c r="T169" s="58"/>
+      <c r="U169" s="49"/>
+      <c r="V169" s="49"/>
+      <c r="W169" s="74"/>
+      <c r="X169" s="77"/>
+      <c r="Y169" s="77"/>
+      <c r="Z169" s="74"/>
+      <c r="AA169" s="76"/>
+      <c r="AB169" s="76"/>
+      <c r="AC169" s="74"/>
+      <c r="AD169" s="76"/>
+      <c r="AE169" s="76"/>
+      <c r="AF169" s="76"/>
+      <c r="AG169" s="74"/>
+    </row>
+    <row r="170" spans="1:33" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="37">
         <v>721</v>
       </c>
       <c r="B170" s="38">
-        <f>IF(ISNUMBER(A170),
-    IF(AND(A170=INT(A170), MOD(A170, 10) = 0), 0,
-        IF(AND(A170=INT(A170), LEN(A170)=2), 1,
-            IF(AND(A170=INT(A170), LEN(A170)=3), 2,
-                LEN(A170) - FIND(".", A170) + 2)
+        <f t="shared" si="42"/>
+        <v>2</v>
+      </c>
+      <c r="C170" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="D170" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">            Coolant</v>
+      </c>
+      <c r="E170" s="39" t="s">
+        <v>268</v>
+      </c>
+      <c r="F170" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="G170" s="39" t="s">
+        <v>303</v>
+      </c>
+      <c r="H170" s="39"/>
+      <c r="I170" s="39"/>
+      <c r="J170" s="43"/>
+      <c r="K170" s="60">
+        <v>170</v>
+      </c>
+      <c r="L170" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="M170" s="58" t="s">
+        <v>396</v>
+      </c>
+      <c r="N170" s="49"/>
+      <c r="O170" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="P170" s="49"/>
+      <c r="Q170" s="65">
+        <v>2024</v>
+      </c>
+      <c r="R170" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="S170" s="58" t="s">
+        <v>305</v>
+      </c>
+      <c r="T170" s="62" t="s">
+        <v>305</v>
+      </c>
+      <c r="U170" s="80" t="s">
+        <v>306</v>
+      </c>
+      <c r="V170" s="49" t="s">
+        <v>307</v>
+      </c>
+      <c r="W170" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X170" s="77">
+        <f>0.9*$J170</f>
+        <v>0</v>
+      </c>
+      <c r="Y170" s="77">
+        <f>1.5*J170</f>
+        <v>0</v>
+      </c>
+      <c r="Z170" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA170" s="76">
+        <f>0.9*K170</f>
+        <v>153</v>
+      </c>
+      <c r="AB170" s="76">
+        <f>1.3*K170</f>
+        <v>221</v>
+      </c>
+      <c r="AC170" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD170" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE170" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF170" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG170" s="74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="171" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="37">
+        <v>721</v>
+      </c>
+      <c r="B171" s="38">
+        <f>IF(ISNUMBER(A171),
+    IF(AND(A171=INT(A171), MOD(A171, 10) = 0), 0,
+        IF(AND(A171=INT(A171), LEN(A171)=2), 1,
+            IF(AND(A171=INT(A171), LEN(A171)=3), 2,
+                LEN(A171) - FIND(".", A171) + 2)
         )
     ),
 "")</f>
         <v>2</v>
       </c>
-      <c r="C170" s="55" t="s">
+      <c r="C171" s="55" t="s">
         <v>302</v>
       </c>
-      <c r="D170" s="39" t="str">
+      <c r="D171" s="39" t="str">
         <f t="shared" si="43"/>
         <v xml:space="preserve">            Coolant</v>
       </c>
-      <c r="E170" s="39" t="s">
+      <c r="E171" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="F170" s="39" t="s">
+      <c r="F171" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="G170" s="39" t="s">
+      <c r="G171" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="H170" s="39"/>
-      <c r="I170" s="39"/>
-      <c r="J170" s="43"/>
-      <c r="K170" s="60">
+      <c r="H171" s="39"/>
+      <c r="I171" s="39"/>
+      <c r="J171" s="43"/>
+      <c r="K171" s="60">
         <v>118</v>
       </c>
-      <c r="L170" s="49" t="s">
+      <c r="L171" s="49" t="s">
         <v>186</v>
       </c>
-      <c r="M170" s="58" t="s">
+      <c r="M171" s="58" t="s">
         <v>396</v>
       </c>
-      <c r="N170" s="49"/>
-      <c r="O170" s="49" t="s">
+      <c r="N171" s="49"/>
+      <c r="O171" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="P170" s="49"/>
-      <c r="Q170" s="65">
+      <c r="P171" s="49"/>
+      <c r="Q171" s="65">
         <v>2023</v>
       </c>
-      <c r="R170" s="49" t="s">
+      <c r="R171" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S170" s="58" t="s">
+      <c r="S171" s="58" t="s">
         <v>397</v>
       </c>
-      <c r="T170" s="62"/>
-      <c r="U170" s="80"/>
-      <c r="V170" s="49" t="s">
+      <c r="T171" s="62"/>
+      <c r="U171" s="80"/>
+      <c r="V171" s="49" t="s">
         <v>398</v>
       </c>
-      <c r="W170" s="74" t="s">
+      <c r="W171" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="X170" s="77">
-        <f>0.9*$J170</f>
-        <v>0</v>
-      </c>
-      <c r="Y170" s="77">
-        <f>1.5*J170</f>
-        <v>0</v>
-      </c>
-      <c r="Z170" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA170" s="76">
-        <f>0.9*K170</f>
+      <c r="X171" s="77">
+        <f>0.9*$J171</f>
+        <v>0</v>
+      </c>
+      <c r="Y171" s="77">
+        <f>1.5*J171</f>
+        <v>0</v>
+      </c>
+      <c r="Z171" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA171" s="76">
+        <f>0.9*K171</f>
         <v>106.2</v>
       </c>
-      <c r="AB170" s="76">
-        <f>1.3*K170</f>
+      <c r="AB171" s="76">
+        <f>1.3*K171</f>
         <v>153.4</v>
       </c>
-      <c r="AC170" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD170" s="76" t="s">
+      <c r="AC171" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD171" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="AE170" s="76" t="s">
+      <c r="AE171" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="AF170" s="76" t="s">
+      <c r="AF171" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="AG170" s="74" t="s">
+      <c r="AG171" s="74" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="155" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="37">
+    <row r="172" spans="1:33" ht="155" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="37">
         <v>73</v>
       </c>
-      <c r="B171" s="38">
-        <f t="shared" ref="B171:B179" si="44">IF(ISNUMBER(A171),
-IF(AND(A171=INT(A171), MOD(A171, 10) = 0), 0,
-IF(AND(A171=INT(A171), LEN(A171)=2), 1,
-IF(AND(A171=INT(A171), LEN(A171)=3), 2,
-LEN(A171) - FIND(".", A171) + 2)
+      <c r="B172" s="38">
+        <f t="shared" ref="B172:B180" si="44">IF(ISNUMBER(A172),
+IF(AND(A172=INT(A172), MOD(A172, 10) = 0), 0,
+IF(AND(A172=INT(A172), LEN(A172)=2), 1,
+IF(AND(A172=INT(A172), LEN(A172)=3), 2,
+LEN(A172) - FIND(".", A172) + 2)
 )
 ),
 "")</f>
         <v>1</v>
       </c>
-      <c r="C171" s="55" t="s">
+      <c r="C172" s="55" t="s">
         <v>399</v>
       </c>
-      <c r="D171" s="39" t="str">
+      <c r="D172" s="39" t="str">
         <f t="shared" si="43"/>
         <v xml:space="preserve">      Regulatory Costs</v>
       </c>
-      <c r="E171" s="39" t="s">
+      <c r="E172" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="F171" s="39"/>
-      <c r="G171" s="39"/>
-      <c r="H171" s="39"/>
-      <c r="I171" s="39"/>
-      <c r="J171" s="43">
-        <f>(2/100)*5359000</f>
-        <v>107180</v>
-      </c>
-      <c r="K171" s="60"/>
-      <c r="L171" s="49"/>
-      <c r="M171" s="58"/>
-      <c r="N171" s="49"/>
-      <c r="O171" s="49"/>
-      <c r="P171" s="49"/>
-      <c r="Q171" s="65">
-        <v>2024</v>
-      </c>
-      <c r="R171" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S171" s="58" t="s">
-        <v>400</v>
-      </c>
-      <c r="T171" s="62" t="s">
-        <v>401</v>
-      </c>
-      <c r="U171" s="80" t="s">
-        <v>401</v>
-      </c>
-      <c r="V171" s="49"/>
-      <c r="W171" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="X171" s="77">
-        <f>0.9*$J171</f>
-        <v>96462</v>
-      </c>
-      <c r="Y171" s="77">
-        <f>1.5*J171</f>
-        <v>160770</v>
-      </c>
-      <c r="Z171" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA171" s="76"/>
-      <c r="AB171" s="76"/>
-      <c r="AC171" s="74"/>
-      <c r="AD171" s="76"/>
-      <c r="AE171" s="76"/>
-      <c r="AF171" s="76"/>
-      <c r="AG171" s="74"/>
-    </row>
-    <row r="172" spans="1:33" ht="127" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="37">
-        <v>75</v>
-      </c>
-      <c r="B172" s="38">
-        <f t="shared" si="44"/>
-        <v>1</v>
-      </c>
-      <c r="C172" s="55" t="s">
-        <v>402</v>
-      </c>
-      <c r="D172" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">      Capital Plant Expenditures</v>
-      </c>
-      <c r="E172" s="39"/>
       <c r="F172" s="39"/>
       <c r="G172" s="39"/>
       <c r="H172" s="39"/>
       <c r="I172" s="39"/>
-      <c r="J172" s="43"/>
+      <c r="J172" s="43">
+        <f>(2/100)*5359000</f>
+        <v>107180</v>
+      </c>
       <c r="K172" s="60"/>
       <c r="L172" s="49"/>
       <c r="M172" s="58"/>
       <c r="N172" s="49"/>
       <c r="O172" s="49"/>
       <c r="P172" s="49"/>
-      <c r="Q172" s="65"/>
-      <c r="R172" s="49"/>
+      <c r="Q172" s="65">
+        <v>2024</v>
+      </c>
+      <c r="R172" s="49" t="s">
+        <v>53</v>
+      </c>
       <c r="S172" s="58" t="s">
-        <v>403</v>
-      </c>
-      <c r="T172" s="58" t="s">
-        <v>403</v>
-      </c>
-      <c r="U172" s="49"/>
-      <c r="V172" s="58" t="s">
-        <v>404</v>
-      </c>
-      <c r="W172" s="74"/>
-      <c r="X172" s="77"/>
-      <c r="Y172" s="77"/>
-      <c r="Z172" s="74"/>
+        <v>400</v>
+      </c>
+      <c r="T172" s="62" t="s">
+        <v>401</v>
+      </c>
+      <c r="U172" s="80" t="s">
+        <v>401</v>
+      </c>
+      <c r="V172" s="49"/>
+      <c r="W172" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="X172" s="77">
+        <f>0.9*$J172</f>
+        <v>96462</v>
+      </c>
+      <c r="Y172" s="77">
+        <f>1.5*J172</f>
+        <v>160770</v>
+      </c>
+      <c r="Z172" s="74" t="s">
+        <v>44</v>
+      </c>
       <c r="AA172" s="76"/>
       <c r="AB172" s="76"/>
       <c r="AC172" s="74"/>
@@ -19147,20 +19470,20 @@
       <c r="AF172" s="76"/>
       <c r="AG172" s="74"/>
     </row>
-    <row r="173" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:33" ht="127" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="37">
-        <v>751</v>
+        <v>75</v>
       </c>
       <c r="B173" s="38">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C173" s="55" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D173" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Outer Vessel Structure Replacements</v>
+        <v xml:space="preserve">      Capital Plant Expenditures</v>
       </c>
       <c r="E173" s="39"/>
       <c r="F173" s="39"/>
@@ -19176,14 +19499,14 @@
       <c r="P173" s="49"/>
       <c r="Q173" s="65"/>
       <c r="R173" s="49"/>
-      <c r="S173" s="144" t="s">
+      <c r="S173" s="58" t="s">
         <v>403</v>
       </c>
-      <c r="T173" s="144" t="s">
+      <c r="T173" s="58" t="s">
         <v>403</v>
       </c>
       <c r="U173" s="49"/>
-      <c r="V173" s="144" t="s">
+      <c r="V173" s="58" t="s">
         <v>404</v>
       </c>
       <c r="W173" s="74"/>
@@ -19200,18 +19523,18 @@
     </row>
     <row r="174" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="37">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B174" s="38">
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
       <c r="C174" s="55" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D174" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Inner Vessel Structure Replacements</v>
+        <v xml:space="preserve">            Annualized Outer Vessel Structure Replacements</v>
       </c>
       <c r="E174" s="39"/>
       <c r="F174" s="39"/>
@@ -19227,10 +19550,16 @@
       <c r="P174" s="49"/>
       <c r="Q174" s="65"/>
       <c r="R174" s="49"/>
-      <c r="S174" s="140"/>
-      <c r="T174" s="140"/>
+      <c r="S174" s="146" t="s">
+        <v>403</v>
+      </c>
+      <c r="T174" s="146" t="s">
+        <v>403</v>
+      </c>
       <c r="U174" s="49"/>
-      <c r="V174" s="140"/>
+      <c r="V174" s="146" t="s">
+        <v>404</v>
+      </c>
       <c r="W174" s="74"/>
       <c r="X174" s="77"/>
       <c r="Y174" s="77"/>
@@ -19243,20 +19572,20 @@
       <c r="AF174" s="76"/>
       <c r="AG174" s="74"/>
     </row>
-    <row r="175" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="37">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B175" s="38">
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
       <c r="C175" s="55" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D175" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Moderator Replacements</v>
+        <v xml:space="preserve">            Annualized Inner Vessel Structure Replacements</v>
       </c>
       <c r="E175" s="39"/>
       <c r="F175" s="39"/>
@@ -19272,10 +19601,10 @@
       <c r="P175" s="49"/>
       <c r="Q175" s="65"/>
       <c r="R175" s="49"/>
-      <c r="S175" s="140"/>
-      <c r="T175" s="140"/>
+      <c r="S175" s="144"/>
+      <c r="T175" s="144"/>
       <c r="U175" s="49"/>
-      <c r="V175" s="140"/>
+      <c r="V175" s="144"/>
       <c r="W175" s="74"/>
       <c r="X175" s="77"/>
       <c r="Y175" s="77"/>
@@ -19290,18 +19619,18 @@
     </row>
     <row r="176" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="37">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B176" s="38">
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
       <c r="C176" s="55" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D176" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Reflector Replacements</v>
+        <v xml:space="preserve">            Annualized Moderator Replacements</v>
       </c>
       <c r="E176" s="39"/>
       <c r="F176" s="39"/>
@@ -19317,10 +19646,10 @@
       <c r="P176" s="49"/>
       <c r="Q176" s="65"/>
       <c r="R176" s="49"/>
-      <c r="S176" s="140"/>
-      <c r="T176" s="140"/>
+      <c r="S176" s="144"/>
+      <c r="T176" s="144"/>
       <c r="U176" s="49"/>
-      <c r="V176" s="140"/>
+      <c r="V176" s="144"/>
       <c r="W176" s="74"/>
       <c r="X176" s="77"/>
       <c r="Y176" s="77"/>
@@ -19333,20 +19662,20 @@
       <c r="AF176" s="76"/>
       <c r="AG176" s="74"/>
     </row>
-    <row r="177" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="37">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B177" s="38">
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
       <c r="C177" s="55" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D177" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Reactor Control Devices Replacements</v>
+        <v xml:space="preserve">            Annualized Reflector Replacements</v>
       </c>
       <c r="E177" s="39"/>
       <c r="F177" s="39"/>
@@ -19362,10 +19691,10 @@
       <c r="P177" s="49"/>
       <c r="Q177" s="65"/>
       <c r="R177" s="49"/>
-      <c r="S177" s="140"/>
-      <c r="T177" s="140"/>
+      <c r="S177" s="144"/>
+      <c r="T177" s="144"/>
       <c r="U177" s="49"/>
-      <c r="V177" s="140"/>
+      <c r="V177" s="144"/>
       <c r="W177" s="74"/>
       <c r="X177" s="77"/>
       <c r="Y177" s="77"/>
@@ -19380,18 +19709,18 @@
     </row>
     <row r="178" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="37">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B178" s="38">
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
       <c r="C178" s="55" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D178" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Moderator Booster Replacements</v>
+        <v xml:space="preserve">            Annualized Reactor Control Devices Replacements</v>
       </c>
       <c r="E178" s="39"/>
       <c r="F178" s="39"/>
@@ -19407,10 +19736,10 @@
       <c r="P178" s="49"/>
       <c r="Q178" s="65"/>
       <c r="R178" s="49"/>
-      <c r="S178" s="140"/>
-      <c r="T178" s="140"/>
+      <c r="S178" s="144"/>
+      <c r="T178" s="144"/>
       <c r="U178" s="49"/>
-      <c r="V178" s="140"/>
+      <c r="V178" s="144"/>
       <c r="W178" s="74"/>
       <c r="X178" s="77"/>
       <c r="Y178" s="77"/>
@@ -19423,20 +19752,20 @@
       <c r="AF178" s="76"/>
       <c r="AG178" s="74"/>
     </row>
-    <row r="179" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="37">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B179" s="38">
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
       <c r="C179" s="55" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D179" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">            Annualized Plant Maintenance (Misc.)</v>
+        <v xml:space="preserve">            Annualized Moderator Booster Replacements</v>
       </c>
       <c r="E179" s="39"/>
       <c r="F179" s="39"/>
@@ -19452,10 +19781,10 @@
       <c r="P179" s="49"/>
       <c r="Q179" s="65"/>
       <c r="R179" s="49"/>
-      <c r="S179" s="141"/>
-      <c r="T179" s="141"/>
+      <c r="S179" s="144"/>
+      <c r="T179" s="144"/>
       <c r="U179" s="49"/>
-      <c r="V179" s="141"/>
+      <c r="V179" s="144"/>
       <c r="W179" s="74"/>
       <c r="X179" s="77"/>
       <c r="Y179" s="77"/>
@@ -19468,20 +19797,20 @@
       <c r="AF179" s="76"/>
       <c r="AG179" s="74"/>
     </row>
-    <row r="180" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="37">
-        <v>759.1</v>
+        <v>759</v>
       </c>
       <c r="B180" s="38">
-        <f t="shared" ref="B180:B187" si="45">IF(ISNUMBER(A180),IF(AND(A180=INT(A180),MOD(A180,10)=0),0,IF(AND(A180=INT(A180),LEN(A180)=2),1,IF(AND(A180=INT(A180),LEN(A180)=3),2,LEN(A180)-FIND(".",A180)+2))),"")</f>
-        <v>3</v>
+        <f t="shared" si="44"/>
+        <v>2</v>
       </c>
       <c r="C180" s="55" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D180" s="39" t="str">
-        <f t="shared" ref="D180:D187" si="46">REPT("   ",B180*2)&amp;C180</f>
-        <v xml:space="preserve">                  Annualized Building and Structural Maintenance (Accounts 212–215)</v>
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">            Annualized Plant Maintenance (Misc.)</v>
       </c>
       <c r="E180" s="39"/>
       <c r="F180" s="39"/>
@@ -19497,10 +19826,10 @@
       <c r="P180" s="49"/>
       <c r="Q180" s="65"/>
       <c r="R180" s="49"/>
-      <c r="S180" s="141"/>
-      <c r="T180" s="141"/>
+      <c r="S180" s="145"/>
+      <c r="T180" s="145"/>
       <c r="U180" s="49"/>
-      <c r="V180" s="141"/>
+      <c r="V180" s="145"/>
       <c r="W180" s="74"/>
       <c r="X180" s="77"/>
       <c r="Y180" s="77"/>
@@ -19515,18 +19844,18 @@
     </row>
     <row r="181" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="37">
-        <v>759.2</v>
+        <v>759.1</v>
       </c>
       <c r="B181" s="38">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="B181:B188" si="45">IF(ISNUMBER(A181),IF(AND(A181=INT(A181),MOD(A181,10)=0),0,IF(AND(A181=INT(A181),LEN(A181)=2),1,IF(AND(A181=INT(A181),LEN(A181)=3),2,LEN(A181)-FIND(".",A181)+2))),"")</f>
         <v>3</v>
       </c>
       <c r="C181" s="55" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D181" s="39" t="str">
-        <f t="shared" si="46"/>
-        <v xml:space="preserve">                  Annualized Main Heat Transport System Maintenance (Accounts 222.1–222.3 and 222.6)</v>
+        <f t="shared" ref="D181:D188" si="46">REPT("   ",B181*2)&amp;C181</f>
+        <v xml:space="preserve">                  Annualized Building and Structural Maintenance (Accounts 212–215)</v>
       </c>
       <c r="E181" s="39"/>
       <c r="F181" s="39"/>
@@ -19542,10 +19871,10 @@
       <c r="P181" s="49"/>
       <c r="Q181" s="65"/>
       <c r="R181" s="49"/>
-      <c r="S181" s="141"/>
-      <c r="T181" s="141"/>
+      <c r="S181" s="145"/>
+      <c r="T181" s="145"/>
       <c r="U181" s="49"/>
-      <c r="V181" s="141"/>
+      <c r="V181" s="145"/>
       <c r="W181" s="74"/>
       <c r="X181" s="77"/>
       <c r="Y181" s="77"/>
@@ -19560,18 +19889,18 @@
     </row>
     <row r="182" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="37">
-        <v>759.3</v>
+        <v>759.2</v>
       </c>
       <c r="B182" s="38">
         <f t="shared" si="45"/>
         <v>3</v>
       </c>
       <c r="C182" s="55" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D182" s="39" t="str">
         <f t="shared" si="46"/>
-        <v xml:space="preserve">                  Annualized Safety System Maintenance (Account 223)</v>
+        <v xml:space="preserve">                  Annualized Main Heat Transport System Maintenance (Accounts 222.1–222.3 and 222.6)</v>
       </c>
       <c r="E182" s="39"/>
       <c r="F182" s="39"/>
@@ -19587,10 +19916,10 @@
       <c r="P182" s="49"/>
       <c r="Q182" s="65"/>
       <c r="R182" s="49"/>
-      <c r="S182" s="141"/>
-      <c r="T182" s="141"/>
+      <c r="S182" s="145"/>
+      <c r="T182" s="145"/>
       <c r="U182" s="49"/>
-      <c r="V182" s="141"/>
+      <c r="V182" s="145"/>
       <c r="W182" s="74"/>
       <c r="X182" s="77"/>
       <c r="Y182" s="77"/>
@@ -19605,18 +19934,18 @@
     </row>
     <row r="183" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="37">
-        <v>759.4</v>
+        <v>759.3</v>
       </c>
       <c r="B183" s="38">
         <f t="shared" si="45"/>
         <v>3</v>
       </c>
       <c r="C183" s="55" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D183" s="39" t="str">
         <f t="shared" si="46"/>
-        <v xml:space="preserve">                  Annualized Reactor Plant Equipment Maintenance (Accounts 221.11, 226, and 228)</v>
+        <v xml:space="preserve">                  Annualized Safety System Maintenance (Account 223)</v>
       </c>
       <c r="E183" s="39"/>
       <c r="F183" s="39"/>
@@ -19632,10 +19961,10 @@
       <c r="P183" s="49"/>
       <c r="Q183" s="65"/>
       <c r="R183" s="49"/>
-      <c r="S183" s="141"/>
-      <c r="T183" s="141"/>
+      <c r="S183" s="145"/>
+      <c r="T183" s="145"/>
       <c r="U183" s="49"/>
-      <c r="V183" s="141"/>
+      <c r="V183" s="145"/>
       <c r="W183" s="74"/>
       <c r="X183" s="77"/>
       <c r="Y183" s="77"/>
@@ -19650,18 +19979,18 @@
     </row>
     <row r="184" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="37">
-        <v>759.5</v>
+        <v>759.4</v>
       </c>
       <c r="B184" s="38">
         <f t="shared" si="45"/>
         <v>3</v>
       </c>
       <c r="C184" s="55" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D184" s="39" t="str">
         <f t="shared" si="46"/>
-        <v xml:space="preserve">                  Annualized Reactor I&amp;C Maintenance (Account 227)</v>
+        <v xml:space="preserve">                  Annualized Reactor Plant Equipment Maintenance (Accounts 221.11, 226, and 228)</v>
       </c>
       <c r="E184" s="39"/>
       <c r="F184" s="39"/>
@@ -19677,10 +20006,10 @@
       <c r="P184" s="49"/>
       <c r="Q184" s="65"/>
       <c r="R184" s="49"/>
-      <c r="S184" s="141"/>
-      <c r="T184" s="141"/>
+      <c r="S184" s="145"/>
+      <c r="T184" s="145"/>
       <c r="U184" s="49"/>
-      <c r="V184" s="141"/>
+      <c r="V184" s="145"/>
       <c r="W184" s="74"/>
       <c r="X184" s="77"/>
       <c r="Y184" s="77"/>
@@ -19695,18 +20024,18 @@
     </row>
     <row r="185" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="37">
-        <v>759.6</v>
+        <v>759.5</v>
       </c>
       <c r="B185" s="38">
         <f t="shared" si="45"/>
         <v>3</v>
       </c>
       <c r="C185" s="55" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D185" s="39" t="str">
         <f t="shared" si="46"/>
-        <v xml:space="preserve">                  Annualized Energy Conversion System Maintenance (Account 23)</v>
+        <v xml:space="preserve">                  Annualized Reactor I&amp;C Maintenance (Account 227)</v>
       </c>
       <c r="E185" s="39"/>
       <c r="F185" s="39"/>
@@ -19722,10 +20051,10 @@
       <c r="P185" s="49"/>
       <c r="Q185" s="65"/>
       <c r="R185" s="49"/>
-      <c r="S185" s="141"/>
-      <c r="T185" s="141"/>
+      <c r="S185" s="145"/>
+      <c r="T185" s="145"/>
       <c r="U185" s="49"/>
-      <c r="V185" s="141"/>
+      <c r="V185" s="145"/>
       <c r="W185" s="74"/>
       <c r="X185" s="77"/>
       <c r="Y185" s="77"/>
@@ -19740,18 +20069,18 @@
     </row>
     <row r="186" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="37">
-        <v>759.7</v>
+        <v>759.6</v>
       </c>
       <c r="B186" s="38">
         <f t="shared" si="45"/>
         <v>3</v>
       </c>
       <c r="C186" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D186" s="39" t="str">
         <f t="shared" si="46"/>
-        <v xml:space="preserve">                  Annualized Electrical Equipment Maintenance (Account 24)</v>
+        <v xml:space="preserve">                  Annualized Energy Conversion System Maintenance (Account 23)</v>
       </c>
       <c r="E186" s="39"/>
       <c r="F186" s="39"/>
@@ -19767,10 +20096,10 @@
       <c r="P186" s="49"/>
       <c r="Q186" s="65"/>
       <c r="R186" s="49"/>
-      <c r="S186" s="141"/>
-      <c r="T186" s="141"/>
+      <c r="S186" s="145"/>
+      <c r="T186" s="145"/>
       <c r="U186" s="49"/>
-      <c r="V186" s="141"/>
+      <c r="V186" s="145"/>
       <c r="W186" s="74"/>
       <c r="X186" s="77"/>
       <c r="Y186" s="77"/>
@@ -19785,18 +20114,18 @@
     </row>
     <row r="187" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="37">
-        <v>759.8</v>
+        <v>759.7</v>
       </c>
       <c r="B187" s="38">
         <f t="shared" si="45"/>
         <v>3</v>
       </c>
       <c r="C187" s="55" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D187" s="39" t="str">
         <f t="shared" si="46"/>
-        <v xml:space="preserve">                  Annualized Miscellaneous Equipment Maintenance (Account 26)</v>
+        <v xml:space="preserve">                  Annualized Electrical Equipment Maintenance (Account 24)</v>
       </c>
       <c r="E187" s="39"/>
       <c r="F187" s="39"/>
@@ -19812,10 +20141,10 @@
       <c r="P187" s="49"/>
       <c r="Q187" s="65"/>
       <c r="R187" s="49"/>
-      <c r="S187" s="141"/>
-      <c r="T187" s="141"/>
+      <c r="S187" s="145"/>
+      <c r="T187" s="145"/>
       <c r="U187" s="49"/>
-      <c r="V187" s="141"/>
+      <c r="V187" s="145"/>
       <c r="W187" s="74"/>
       <c r="X187" s="77"/>
       <c r="Y187" s="77"/>
@@ -19828,27 +20157,20 @@
       <c r="AF187" s="76"/>
       <c r="AG187" s="74"/>
     </row>
-    <row r="188" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:33" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="37">
-        <v>78</v>
+        <v>759.8</v>
       </c>
       <c r="B188" s="38">
-        <f>IF(ISNUMBER(A188),
-    IF(AND(A188=INT(A188), MOD(A188, 10) = 0), 0,
-        IF(AND(A188=INT(A188), LEN(A188)=2), 1,
-            IF(AND(A188=INT(A188), LEN(A188)=3), 2,
-                LEN(A188) - FIND(".", A188) + 2)
-        )
-    ),
-"")</f>
-        <v>1</v>
+        <f t="shared" si="45"/>
+        <v>3</v>
       </c>
       <c r="C188" s="55" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D188" s="39" t="str">
-        <f t="shared" si="43"/>
-        <v xml:space="preserve">      Annualized Decommissioning Cost</v>
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">                  Annualized Miscellaneous Equipment Maintenance (Account 26)</v>
       </c>
       <c r="E188" s="39"/>
       <c r="F188" s="39"/>
@@ -19856,20 +20178,18 @@
       <c r="H188" s="39"/>
       <c r="I188" s="39"/>
       <c r="J188" s="43"/>
-      <c r="K188" s="70"/>
+      <c r="K188" s="60"/>
       <c r="L188" s="49"/>
-      <c r="M188" s="45"/>
+      <c r="M188" s="58"/>
       <c r="N188" s="49"/>
       <c r="O188" s="49"/>
       <c r="P188" s="49"/>
       <c r="Q188" s="65"/>
       <c r="R188" s="49"/>
-      <c r="S188" s="58"/>
-      <c r="T188" s="58"/>
+      <c r="S188" s="145"/>
+      <c r="T188" s="145"/>
       <c r="U188" s="49"/>
-      <c r="V188" s="58" t="s">
-        <v>421</v>
-      </c>
+      <c r="V188" s="145"/>
       <c r="W188" s="74"/>
       <c r="X188" s="77"/>
       <c r="Y188" s="77"/>
@@ -19882,46 +20202,48 @@
       <c r="AF188" s="76"/>
       <c r="AG188" s="74"/>
     </row>
-    <row r="189" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="37">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B189" s="38">
         <f>IF(ISNUMBER(A189),
-IF(AND(A189=INT(A189), MOD(A189, 10) = 0), 0,
-IF(AND(A189=INT(A189), LEN(A189)=2), 1,
-IF(AND(A189=INT(A189), LEN(A189)=3), 2,
-LEN(A189) - FIND(".", A189) + 2)
-)
-),
+    IF(AND(A189=INT(A189), MOD(A189, 10) = 0), 0,
+        IF(AND(A189=INT(A189), LEN(A189)=2), 1,
+            IF(AND(A189=INT(A189), LEN(A189)=3), 2,
+                LEN(A189) - FIND(".", A189) + 2)
+        )
+    ),
 "")</f>
-        <v>0</v>
-      </c>
-      <c r="C189" s="69" t="s">
-        <v>422</v>
+        <v>1</v>
+      </c>
+      <c r="C189" s="55" t="s">
+        <v>420</v>
       </c>
       <c r="D189" s="39" t="str">
         <f t="shared" si="43"/>
-        <v>Annualized Fuel Cost</v>
+        <v xml:space="preserve">      Annualized Decommissioning Cost</v>
       </c>
       <c r="E189" s="39"/>
       <c r="F189" s="39"/>
       <c r="G189" s="39"/>
       <c r="H189" s="39"/>
       <c r="I189" s="39"/>
-      <c r="J189" s="40"/>
-      <c r="K189" s="40"/>
-      <c r="L189" s="38"/>
-      <c r="M189" s="41"/>
-      <c r="N189" s="38"/>
-      <c r="O189" s="38"/>
-      <c r="P189" s="38"/>
-      <c r="Q189" s="40"/>
-      <c r="R189" s="38"/>
-      <c r="S189" s="41"/>
-      <c r="T189" s="38"/>
-      <c r="U189" s="38"/>
-      <c r="V189" s="38"/>
+      <c r="J189" s="43"/>
+      <c r="K189" s="70"/>
+      <c r="L189" s="49"/>
+      <c r="M189" s="45"/>
+      <c r="N189" s="49"/>
+      <c r="O189" s="49"/>
+      <c r="P189" s="49"/>
+      <c r="Q189" s="65"/>
+      <c r="R189" s="49"/>
+      <c r="S189" s="58"/>
+      <c r="T189" s="58"/>
+      <c r="U189" s="49"/>
+      <c r="V189" s="58" t="s">
+        <v>421</v>
+      </c>
       <c r="W189" s="74"/>
       <c r="X189" s="77"/>
       <c r="Y189" s="77"/>
@@ -19934,9 +20256,9 @@
       <c r="AF189" s="76"/>
       <c r="AG189" s="74"/>
     </row>
-    <row r="190" spans="1:33" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="37">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B190" s="38">
         <f>IF(ISNUMBER(A190),
@@ -19947,90 +20269,48 @@
 )
 ),
 "")</f>
-        <v>1</v>
-      </c>
-      <c r="C190" s="55" t="s">
-        <v>423</v>
+        <v>0</v>
+      </c>
+      <c r="C190" s="69" t="s">
+        <v>422</v>
       </c>
       <c r="D190" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">      Refueling Operations</v>
-      </c>
-      <c r="E190" s="39" t="s">
-        <v>268</v>
-      </c>
+        <v>Annualized Fuel Cost</v>
+      </c>
+      <c r="E190" s="39"/>
       <c r="F190" s="39"/>
       <c r="G190" s="39"/>
       <c r="H190" s="39"/>
       <c r="I190" s="39"/>
-      <c r="J190" s="43"/>
-      <c r="K190" s="60">
-        <v>178500</v>
-      </c>
-      <c r="L190" s="49" t="s">
-        <v>386</v>
-      </c>
-      <c r="M190" s="58" t="s">
-        <v>387</v>
-      </c>
-      <c r="N190" s="49"/>
-      <c r="O190" s="49"/>
-      <c r="P190" s="49">
-        <v>1</v>
-      </c>
-      <c r="Q190" s="65">
-        <v>2024</v>
-      </c>
-      <c r="R190" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S190" s="58"/>
-      <c r="T190" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="U190" s="49"/>
-      <c r="V190" s="49"/>
-      <c r="W190" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="X190" s="77">
-        <f>0.9*$J190</f>
-        <v>0</v>
-      </c>
-      <c r="Y190" s="77">
-        <f>1.5*J190</f>
-        <v>0</v>
-      </c>
-      <c r="Z190" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA190" s="76">
-        <f>0.9*K190</f>
-        <v>160650</v>
-      </c>
-      <c r="AB190" s="76">
-        <f>1.3*K190</f>
-        <v>232050</v>
-      </c>
-      <c r="AC190" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD190" s="76" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE190" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF190" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG190" s="74" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="191" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J190" s="40"/>
+      <c r="K190" s="40"/>
+      <c r="L190" s="38"/>
+      <c r="M190" s="41"/>
+      <c r="N190" s="38"/>
+      <c r="O190" s="38"/>
+      <c r="P190" s="38"/>
+      <c r="Q190" s="40"/>
+      <c r="R190" s="38"/>
+      <c r="S190" s="41"/>
+      <c r="T190" s="38"/>
+      <c r="U190" s="38"/>
+      <c r="V190" s="38"/>
+      <c r="W190" s="74"/>
+      <c r="X190" s="77"/>
+      <c r="Y190" s="77"/>
+      <c r="Z190" s="74"/>
+      <c r="AA190" s="76"/>
+      <c r="AB190" s="76"/>
+      <c r="AC190" s="74"/>
+      <c r="AD190" s="76"/>
+      <c r="AE190" s="76"/>
+      <c r="AF190" s="76"/>
+      <c r="AG190" s="74"/>
+    </row>
+    <row r="191" spans="1:33" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="37">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B191" s="38">
         <f>IF(ISNUMBER(A191),
@@ -20044,45 +20324,87 @@
         <v>1</v>
       </c>
       <c r="C191" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D191" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">      Additional Nuclear Fuel</v>
-      </c>
-      <c r="E191" s="39"/>
+        <v xml:space="preserve">      Refueling Operations</v>
+      </c>
+      <c r="E191" s="39" t="s">
+        <v>268</v>
+      </c>
       <c r="F191" s="39"/>
       <c r="G191" s="39"/>
       <c r="H191" s="39"/>
       <c r="I191" s="39"/>
       <c r="J191" s="43"/>
-      <c r="K191" s="60"/>
-      <c r="L191" s="49"/>
-      <c r="M191" s="58"/>
+      <c r="K191" s="60">
+        <v>178500</v>
+      </c>
+      <c r="L191" s="49" t="s">
+        <v>386</v>
+      </c>
+      <c r="M191" s="58" t="s">
+        <v>387</v>
+      </c>
       <c r="N191" s="49"/>
       <c r="O191" s="49"/>
-      <c r="P191" s="49"/>
-      <c r="Q191" s="65"/>
-      <c r="R191" s="49"/>
+      <c r="P191" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q191" s="65">
+        <v>2024</v>
+      </c>
+      <c r="R191" s="49" t="s">
+        <v>53</v>
+      </c>
       <c r="S191" s="58"/>
-      <c r="T191" s="49"/>
+      <c r="T191" s="58" t="s">
+        <v>388</v>
+      </c>
       <c r="U191" s="49"/>
       <c r="V191" s="49"/>
-      <c r="W191" s="74"/>
-      <c r="X191" s="77"/>
-      <c r="Y191" s="77"/>
-      <c r="Z191" s="74"/>
-      <c r="AA191" s="76"/>
-      <c r="AB191" s="76"/>
-      <c r="AC191" s="74"/>
-      <c r="AD191" s="76"/>
-      <c r="AE191" s="76"/>
-      <c r="AF191" s="76"/>
-      <c r="AG191" s="74"/>
-    </row>
-    <row r="192" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W191" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X191" s="77">
+        <f>0.9*$J191</f>
+        <v>0</v>
+      </c>
+      <c r="Y191" s="77">
+        <f>1.5*J191</f>
+        <v>0</v>
+      </c>
+      <c r="Z191" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA191" s="76">
+        <f>0.9*K191</f>
+        <v>160650</v>
+      </c>
+      <c r="AB191" s="76">
+        <f>1.3*K191</f>
+        <v>232050</v>
+      </c>
+      <c r="AC191" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD191" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE191" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF191" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG191" s="74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="192" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="37">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B192" s="38">
         <f>IF(ISNUMBER(A192),
@@ -20096,105 +20418,152 @@
         <v>1</v>
       </c>
       <c r="C192" s="55" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D192" s="39" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">      Spent Fuel Management</v>
-      </c>
-      <c r="E192" s="39" t="s">
-        <v>35</v>
-      </c>
+        <v xml:space="preserve">      Additional Nuclear Fuel</v>
+      </c>
+      <c r="E192" s="39"/>
       <c r="F192" s="39"/>
       <c r="G192" s="39"/>
       <c r="H192" s="39"/>
       <c r="I192" s="39"/>
       <c r="J192" s="43"/>
-      <c r="K192" s="60">
-        <v>1</v>
-      </c>
-      <c r="L192" s="49" t="s">
-        <v>426</v>
-      </c>
-      <c r="M192" s="58" t="s">
-        <v>427</v>
-      </c>
+      <c r="K192" s="60"/>
+      <c r="L192" s="49"/>
+      <c r="M192" s="58"/>
       <c r="N192" s="49"/>
       <c r="O192" s="49"/>
-      <c r="P192" s="49">
-        <v>1</v>
-      </c>
-      <c r="Q192" s="65">
-        <v>2024</v>
-      </c>
-      <c r="R192" s="49" t="s">
-        <v>86</v>
-      </c>
+      <c r="P192" s="49"/>
+      <c r="Q192" s="65"/>
+      <c r="R192" s="49"/>
       <c r="S192" s="58"/>
       <c r="T192" s="49"/>
       <c r="U192" s="49"/>
       <c r="V192" s="49"/>
-      <c r="W192" s="74" t="s">
+      <c r="W192" s="74"/>
+      <c r="X192" s="77"/>
+      <c r="Y192" s="77"/>
+      <c r="Z192" s="74"/>
+      <c r="AA192" s="76"/>
+      <c r="AB192" s="76"/>
+      <c r="AC192" s="74"/>
+      <c r="AD192" s="76"/>
+      <c r="AE192" s="76"/>
+      <c r="AF192" s="76"/>
+      <c r="AG192" s="74"/>
+    </row>
+    <row r="193" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="37">
+        <v>83</v>
+      </c>
+      <c r="B193" s="38">
+        <f>IF(ISNUMBER(A193),
+IF(AND(A193=INT(A193), MOD(A193, 10) = 0), 0,
+IF(AND(A193=INT(A193), LEN(A193)=2), 1,
+IF(AND(A193=INT(A193), LEN(A193)=3), 2,
+LEN(A193) - FIND(".", A193) + 2)
+)
+),
+"")</f>
+        <v>1</v>
+      </c>
+      <c r="C193" s="55" t="s">
+        <v>425</v>
+      </c>
+      <c r="D193" s="39" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">      Spent Fuel Management</v>
+      </c>
+      <c r="E193" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F193" s="39"/>
+      <c r="G193" s="39"/>
+      <c r="H193" s="39"/>
+      <c r="I193" s="39"/>
+      <c r="J193" s="43"/>
+      <c r="K193" s="60">
+        <v>1</v>
+      </c>
+      <c r="L193" s="49" t="s">
+        <v>426</v>
+      </c>
+      <c r="M193" s="58" t="s">
+        <v>427</v>
+      </c>
+      <c r="N193" s="49"/>
+      <c r="O193" s="49"/>
+      <c r="P193" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q193" s="65">
+        <v>2024</v>
+      </c>
+      <c r="R193" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="S193" s="58"/>
+      <c r="T193" s="49"/>
+      <c r="U193" s="49"/>
+      <c r="V193" s="49"/>
+      <c r="W193" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="X192" s="77">
-        <f>0.9*$J192</f>
-        <v>0</v>
-      </c>
-      <c r="Y192" s="77">
-        <f>1.5*J192</f>
-        <v>0</v>
-      </c>
-      <c r="Z192" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA192" s="76">
-        <f>0.9*K192</f>
+      <c r="X193" s="77">
+        <f>0.9*$J193</f>
+        <v>0</v>
+      </c>
+      <c r="Y193" s="77">
+        <f>1.5*J193</f>
+        <v>0</v>
+      </c>
+      <c r="Z193" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA193" s="76">
+        <f>0.9*K193</f>
         <v>0.9</v>
       </c>
-      <c r="AB192" s="76">
-        <f>1.3*K192</f>
+      <c r="AB193" s="76">
+        <f>1.3*K193</f>
         <v>1.3</v>
       </c>
-      <c r="AC192" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD192" s="76" t="s">
+      <c r="AC193" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD193" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="AE192" s="76" t="s">
+      <c r="AE193" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="AF192" s="76" t="s">
+      <c r="AF193" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="AG192" s="74" t="s">
+      <c r="AG193" s="74" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="T26:T28"/>
-    <mergeCell ref="T41:T43"/>
-    <mergeCell ref="V109:V110"/>
-    <mergeCell ref="T61:T63"/>
-    <mergeCell ref="T76:T80"/>
-    <mergeCell ref="S138:S143"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="V173:V187"/>
-    <mergeCell ref="S30:S32"/>
-    <mergeCell ref="S15:S17"/>
-    <mergeCell ref="T37:T39"/>
-    <mergeCell ref="T46:T48"/>
-    <mergeCell ref="T22:T24"/>
-    <mergeCell ref="U52:U54"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="U26:U28"/>
-    <mergeCell ref="T52:T54"/>
-    <mergeCell ref="V123:V124"/>
-    <mergeCell ref="S155:S158"/>
-    <mergeCell ref="T145:T150"/>
-    <mergeCell ref="V52:V54"/>
+    <mergeCell ref="T138:T143"/>
+    <mergeCell ref="U30:U32"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="T174:T188"/>
+    <mergeCell ref="U15:U17"/>
+    <mergeCell ref="U46:U48"/>
+    <mergeCell ref="S145:S150"/>
+    <mergeCell ref="U41:U43"/>
+    <mergeCell ref="S61:S63"/>
+    <mergeCell ref="U61:U63"/>
+    <mergeCell ref="U57:U59"/>
+    <mergeCell ref="S174:S188"/>
+    <mergeCell ref="U76:U80"/>
+    <mergeCell ref="S57:S59"/>
+    <mergeCell ref="S37:S39"/>
+    <mergeCell ref="U89:U99"/>
     <mergeCell ref="U3:U4"/>
     <mergeCell ref="T57:T59"/>
     <mergeCell ref="T15:T17"/>
@@ -20211,314 +20580,318 @@
     <mergeCell ref="U11:U13"/>
     <mergeCell ref="U37:U39"/>
     <mergeCell ref="T109:T110"/>
-    <mergeCell ref="T138:T143"/>
-    <mergeCell ref="U30:U32"/>
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="T173:T187"/>
-    <mergeCell ref="U15:U17"/>
-    <mergeCell ref="U46:U48"/>
-    <mergeCell ref="S145:S150"/>
-    <mergeCell ref="U41:U43"/>
-    <mergeCell ref="S61:S63"/>
-    <mergeCell ref="U61:U63"/>
-    <mergeCell ref="U57:U59"/>
-    <mergeCell ref="S173:S187"/>
-    <mergeCell ref="U76:U80"/>
-    <mergeCell ref="S57:S59"/>
-    <mergeCell ref="S37:S39"/>
-    <mergeCell ref="U89:U99"/>
+    <mergeCell ref="S138:S143"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="V174:V188"/>
+    <mergeCell ref="S30:S32"/>
+    <mergeCell ref="S15:S17"/>
+    <mergeCell ref="T37:T39"/>
+    <mergeCell ref="T46:T48"/>
+    <mergeCell ref="T22:T24"/>
+    <mergeCell ref="U52:U54"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="U26:U28"/>
+    <mergeCell ref="T52:T54"/>
+    <mergeCell ref="V123:V124"/>
+    <mergeCell ref="S156:S159"/>
+    <mergeCell ref="T145:T150"/>
+    <mergeCell ref="V52:V54"/>
+    <mergeCell ref="T26:T28"/>
+    <mergeCell ref="T41:T43"/>
+    <mergeCell ref="V109:V110"/>
+    <mergeCell ref="T61:T63"/>
+    <mergeCell ref="T76:T80"/>
   </mergeCells>
   <conditionalFormatting sqref="A100:B106">
-    <cfRule type="expression" dxfId="302" priority="573">
+    <cfRule type="expression" dxfId="312" priority="586">
+      <formula>$B100&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="311" priority="585">
+      <formula>$B100=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="310" priority="584">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="301" priority="574">
-      <formula>$B100=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="300" priority="575">
-      <formula>$B100&lt;2</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A109:F111 U116:V122 U123:U124 A138:B143 N145:V145 N146:R146 U146:V151 K147:R147 A151:T151 T155:V160 A161:V164 A165:J166">
-    <cfRule type="expression" dxfId="299" priority="789">
+  <conditionalFormatting sqref="A109:F111 U116:V122 U123:U124 A138:B143 N145:V145 N146:R146 U146:V152 K147:R147 A151:T152 T156:V161 A162:V165 A166:J167">
+    <cfRule type="expression" dxfId="309" priority="800">
       <formula>$B109=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A100:I106">
-    <cfRule type="expression" dxfId="298" priority="36">
+    <cfRule type="expression" dxfId="308" priority="47">
       <formula>$B100=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A150:R150">
-    <cfRule type="expression" dxfId="297" priority="737">
+    <cfRule type="expression" dxfId="307" priority="748">
       <formula>$B150=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A153:R160">
-    <cfRule type="expression" dxfId="296" priority="682">
-      <formula>$B153=3</formula>
+  <conditionalFormatting sqref="A154:R161">
+    <cfRule type="expression" dxfId="306" priority="693">
+      <formula>$B154=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="295" priority="685">
-      <formula>$B153=0</formula>
+    <cfRule type="expression" dxfId="305" priority="694">
+      <formula>$B154=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="294" priority="684">
-      <formula>$B153&lt;2</formula>
+    <cfRule type="expression" dxfId="304" priority="695">
+      <formula>$B154&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="293" priority="683">
-      <formula>$B153=2</formula>
+    <cfRule type="expression" dxfId="303" priority="696">
+      <formula>$B154=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A127:S128 U127:V128 U169:V171">
-    <cfRule type="expression" dxfId="292" priority="582">
+  <conditionalFormatting sqref="A127:S128 U127:V128 U170:V172">
+    <cfRule type="expression" dxfId="302" priority="593">
       <formula>$B127=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108:U108">
-    <cfRule type="expression" dxfId="291" priority="793">
+    <cfRule type="expression" dxfId="301" priority="801">
+      <formula>$B108=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="300" priority="802">
+      <formula>$B108=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="299" priority="803">
+      <formula>$B108&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="298" priority="804">
       <formula>$B108=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="290" priority="792">
-      <formula>$B108&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="289" priority="791">
-      <formula>$B108=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="288" priority="790">
-      <formula>$B108=3</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A74:V99 A107:V107 A173:R187">
-    <cfRule type="expression" dxfId="287" priority="488">
-      <formula>$B74=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="286" priority="487">
+  <conditionalFormatting sqref="A74:V99 A107:V107 A174:R188">
+    <cfRule type="expression" dxfId="297" priority="498">
       <formula>$B74=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="285" priority="489">
+    <cfRule type="expression" dxfId="296" priority="500">
       <formula>$B74&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="295" priority="499">
+      <formula>$B74=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:V83">
-    <cfRule type="expression" dxfId="284" priority="577">
+    <cfRule type="expression" dxfId="294" priority="588">
       <formula>$B76=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A98:V99 D100:D106 A125:V126 A129:V143 A144:AG147 A148:G149 I148:AG149 A150:AG172">
-    <cfRule type="expression" dxfId="283" priority="622">
+  <conditionalFormatting sqref="A98:V99 D100:D106 A125:V126 A129:B130 D129:V130 A131:V143 A144:AG147 A148:G149 I148:AG149 A150:AG151 A152:V152 A153:AG173">
+    <cfRule type="expression" dxfId="293" priority="633">
       <formula>$B98&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A112:V114 U116:V122 U123:U124 A127:S128 U127:V128 A144:AG147 A148:G149 I148:AG149 A150:AG172 A138:B143 U138:V143 U146:V151 A5:S6 A109:F111 A1:AG4 U5:AG6">
-    <cfRule type="expression" dxfId="282" priority="786">
+  <conditionalFormatting sqref="A112:V114 U116:V122 U123:U124 A127:S128 U127:V128 A144:AG147 A148:G149 I148:AG149 A150:AG151 A153:AG173 A138:B143 U138:V143 U146:V152 A5:S6 A109:F111 X152:AG152 A1:AG4 U5:AG6">
+    <cfRule type="expression" dxfId="292" priority="797">
       <formula>$B1=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A125:V126 A129:V143 A98:V99 D100:D106 A144:AG147 A148:G149 I148:AG149 A150:AG172">
-    <cfRule type="expression" dxfId="281" priority="621">
+  <conditionalFormatting sqref="A125:V126 A129:B130 D129:V130 A131:V143 A98:V99 D100:D106 A152:V152 A144:AG147 A148:G149 I148:AG149 A150:AG151 A153:AG173">
+    <cfRule type="expression" dxfId="291" priority="632">
       <formula>$B98=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A125:V126">
-    <cfRule type="expression" dxfId="280" priority="757">
+    <cfRule type="expression" dxfId="290" priority="768">
       <formula>$B125=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A129:V143 A125:V126">
-    <cfRule type="expression" dxfId="279" priority="620">
+  <conditionalFormatting sqref="A131:V143 A125:V126 A129:B130 D129:V130">
+    <cfRule type="expression" dxfId="289" priority="631">
       <formula>$B125=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A152:V152">
-    <cfRule type="expression" dxfId="278" priority="718">
+  <conditionalFormatting sqref="A152:V153">
+    <cfRule type="expression" dxfId="288" priority="729">
       <formula>$B152=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="277" priority="719">
-      <formula>$B152=2</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A153:V153">
+    <cfRule type="expression" dxfId="287" priority="730">
+      <formula>$B153=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="276" priority="720">
-      <formula>$B152&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="275" priority="721">
-      <formula>$B152=0</formula>
+    <cfRule type="expression" dxfId="286" priority="731">
+      <formula>$B153&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A189:V192">
-    <cfRule type="expression" dxfId="274" priority="650">
-      <formula>$B189=3</formula>
+  <conditionalFormatting sqref="A190:V193">
+    <cfRule type="expression" dxfId="285" priority="661">
+      <formula>$B190=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="273" priority="651">
-      <formula>$B189=2</formula>
+    <cfRule type="expression" dxfId="284" priority="662">
+      <formula>$B190=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="272" priority="652">
-      <formula>$B189&lt;2</formula>
+    <cfRule type="expression" dxfId="283" priority="663">
+      <formula>$B190&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="271" priority="653">
-      <formula>$B189=0</formula>
+    <cfRule type="expression" dxfId="282" priority="664">
+      <formula>$B190=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A109:F111 A112:V114 U116:V122 U123:U124 A127:S128 U127:V128 A138:B143 U138:V143 A144:V144 N145:V145 N146:R146 U146:V151 K147:R147 A151:T151 T155:V160 A161:V164 A165:J166 A167:L171 U169:V171">
-    <cfRule type="expression" dxfId="270" priority="788">
+  <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A109:F111 A112:V114 U116:V122 U123:U124 A127:S128 U127:V128 A138:B143 U138:V143 A144:V144 N145:V145 N146:R146 U146:V152 K147:R147 A151:T152 T156:V161 A162:V165 A166:J167 A168:L172 U170:V172">
+    <cfRule type="expression" dxfId="281" priority="798">
+      <formula>$B1=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="280" priority="799">
       <formula>$B1&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="269" priority="787">
-      <formula>$B1=2</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A7:AG51 A173:R187">
-    <cfRule type="expression" dxfId="268" priority="490">
+  <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A7:AG51 A174:R188">
+    <cfRule type="expression" dxfId="279" priority="501">
       <formula>$B1=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:AG48">
-    <cfRule type="expression" dxfId="267" priority="552">
+    <cfRule type="expression" dxfId="278" priority="564">
+      <formula>$B7=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="277" priority="565">
+      <formula>$B7&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="276" priority="563">
       <formula>$B7=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="266" priority="553">
-      <formula>$B7=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="265" priority="554">
-      <formula>$B7&lt;2</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG87 A100:B106 A112:AG123 A124:U124 W124:AG124 A135:V135 A136:Y136 A137:AG137 S173:AG173 U174:U187 W174:AG187 A188:AG192 A97:AG97 A125:AG134">
-    <cfRule type="expression" dxfId="264" priority="751">
+  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG87 A100:B106 A112:AG123 A124:U124 W124:AG124 A125:AG128 A129:B130 D129:AG130 A131:AG134 A135:V135 A136:Y136 A137:AG137 S174:AG174 U175:U188 W175:AG188 A189:AG193 A97:AG97">
+    <cfRule type="expression" dxfId="275" priority="762">
       <formula>$B49=2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG87 A97:AG97 A100:B106 A112:AG123 A124:U124 W124:AG124 A135:V135 A136:Y136 A137:AG137 S173:AG173 U174:U187 W174:AG187 A188:AG192 A125:AG134">
-    <cfRule type="expression" dxfId="263" priority="752">
+  <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG87 A97:AG97 A100:B106 A112:AG123 A124:U124 W124:AG124 A125:AG128 A129:B130 D129:AG130 A131:AG134 A135:V135 A136:Y136 A137:AG137 S174:AG174 U175:U188 W175:AG188 A189:AG193">
+    <cfRule type="expression" dxfId="274" priority="763">
       <formula>$B49&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:AG99">
-    <cfRule type="expression" dxfId="262" priority="65">
+    <cfRule type="expression" dxfId="273" priority="76">
       <formula>$B83=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:AG88">
-    <cfRule type="expression" dxfId="261" priority="62">
+    <cfRule type="expression" dxfId="272" priority="74">
+      <formula>$B88=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="271" priority="73">
       <formula>$B88=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="260" priority="63">
-      <formula>$B88=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="259" priority="64">
+    <cfRule type="expression" dxfId="270" priority="75">
       <formula>$B88&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A89:AG96">
-    <cfRule type="expression" dxfId="258" priority="523">
-      <formula>$B89=3</formula>
+    <cfRule type="expression" dxfId="269" priority="536">
+      <formula>$B89&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="257" priority="524">
+    <cfRule type="expression" dxfId="268" priority="535">
       <formula>$B89=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="256" priority="525">
-      <formula>$B89&lt;2</formula>
+    <cfRule type="expression" dxfId="267" priority="534">
+      <formula>$B89=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A97:AG99 D100:D106 A148:G149 I148:R149 A150:R150">
-    <cfRule type="expression" dxfId="255" priority="734">
+    <cfRule type="expression" dxfId="266" priority="745">
       <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107:AG111">
-    <cfRule type="expression" dxfId="254" priority="509">
+    <cfRule type="expression" dxfId="265" priority="520">
       <formula>$B107&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="253" priority="508">
+    <cfRule type="expression" dxfId="264" priority="519">
       <formula>$B107=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="252" priority="507">
+    <cfRule type="expression" dxfId="263" priority="518">
       <formula>$B107=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A136:AG137">
-    <cfRule type="expression" dxfId="251" priority="482">
+    <cfRule type="expression" dxfId="262" priority="493">
       <formula>$B136=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A144:AG147 A148:G149 I148:AG149 A150:AG172">
-    <cfRule type="expression" dxfId="250" priority="555">
+  <conditionalFormatting sqref="A144:AG147 A148:G149 I148:AG149 A150:AG151 A152:V153 A153:AG173">
+    <cfRule type="expression" dxfId="261" priority="566">
       <formula>$B144=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A188:AG192 A55:AG75 A83:AG87 A135:V135 A136:Y136 A137:AG137 A112:AG123 A76:V82 A100:B106 A49:AG51 F52:AG52 F53:U54 A52:E54 W53:AG54 A124:U124 W124:AG124 S173:AG173 U174:U187 W174:AG187 A125:AG134">
-    <cfRule type="expression" dxfId="249" priority="750">
+  <conditionalFormatting sqref="A189:AG193 A55:AG75 A83:AG87 A125:AG128 A129:B130 D129:AG130 A131:AG134 A135:V135 A136:Y136 A137:AG137 A112:AG123 A76:V82 A100:B106 A49:AG51 F52:AG52 F53:U54 A52:E54 W53:AG54 A124:U124 W124:AG124 S174:AG174 U175:U188 W175:AG188">
+    <cfRule type="expression" dxfId="260" priority="761">
       <formula>$B49=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C100:C101">
-    <cfRule type="expression" dxfId="248" priority="427">
+    <cfRule type="expression" dxfId="259" priority="438">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="247" priority="428">
+    <cfRule type="expression" dxfId="258" priority="439">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="246" priority="429">
+    <cfRule type="expression" dxfId="257" priority="440">
       <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C100:C103">
-    <cfRule type="expression" dxfId="245" priority="420">
+    <cfRule type="expression" dxfId="256" priority="433">
+      <formula>$B100&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="255" priority="431">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="244" priority="422">
-      <formula>$B100&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="243" priority="421">
+    <cfRule type="expression" dxfId="254" priority="432">
       <formula>$B100=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102:C105">
-    <cfRule type="expression" dxfId="242" priority="415">
+    <cfRule type="expression" dxfId="253" priority="426">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="241" priority="414">
+    <cfRule type="expression" dxfId="252" priority="425">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="240" priority="413">
+    <cfRule type="expression" dxfId="251" priority="424">
       <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C104:C106">
-    <cfRule type="expression" dxfId="239" priority="408">
-      <formula>$B104&lt;2</formula>
+    <cfRule type="expression" dxfId="250" priority="417">
+      <formula>$B104=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="238" priority="407">
+    <cfRule type="expression" dxfId="249" priority="418">
       <formula>$B104=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="237" priority="406">
-      <formula>$B104=3</formula>
+    <cfRule type="expression" dxfId="248" priority="419">
+      <formula>$B104&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C105:C106">
-    <cfRule type="expression" dxfId="236" priority="54">
+    <cfRule type="expression" dxfId="247" priority="65">
       <formula>$B105&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="235" priority="52">
+    <cfRule type="expression" dxfId="246" priority="64">
+      <formula>$B105=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="245" priority="63">
       <formula>$B105=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="234" priority="53">
-      <formula>$B105=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C138:T138 C139:R143">
-    <cfRule type="expression" dxfId="233" priority="609">
+    <cfRule type="expression" dxfId="244" priority="623">
+      <formula>$B138=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="243" priority="620">
       <formula>$B138=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="232" priority="610">
+    <cfRule type="expression" dxfId="242" priority="621">
       <formula>$B138=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="231" priority="611">
+    <cfRule type="expression" dxfId="241" priority="622">
       <formula>$B138&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="230" priority="612">
-      <formula>$B138=0</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D80 D82 D87:D137 D144:D192">
-    <cfRule type="colorScale" priority="1038">
+  <conditionalFormatting sqref="D2:D80 D82 D87:D137 D144:D193">
+    <cfRule type="colorScale" priority="1049">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20528,7 +20901,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81">
-    <cfRule type="colorScale" priority="587">
+    <cfRule type="colorScale" priority="598">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20538,7 +20911,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83">
-    <cfRule type="colorScale" priority="633">
+    <cfRule type="colorScale" priority="644">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20548,7 +20921,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D138:D143">
-    <cfRule type="colorScale" priority="613">
+    <cfRule type="colorScale" priority="624">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20558,891 +20931,930 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D100:E106">
-    <cfRule type="expression" dxfId="229" priority="399">
+    <cfRule type="expression" dxfId="240" priority="410">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="228" priority="400">
+    <cfRule type="expression" dxfId="239" priority="412">
+      <formula>$B100&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="238" priority="411">
       <formula>$B100=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="227" priority="401">
-      <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E100:E106">
-    <cfRule type="expression" dxfId="226" priority="396">
+    <cfRule type="expression" dxfId="237" priority="407">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="225" priority="397">
+    <cfRule type="expression" dxfId="236" priority="408">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="224" priority="398">
+    <cfRule type="expression" dxfId="235" priority="409">
       <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E83:Q83 Q127:Q128">
-    <cfRule type="expression" dxfId="223" priority="628">
+    <cfRule type="expression" dxfId="234" priority="639">
       <formula>_xlfn.ISFORMULA(E83)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E138:Q143">
-    <cfRule type="expression" dxfId="222" priority="608">
+    <cfRule type="expression" dxfId="233" priority="619">
       <formula>_xlfn.ISFORMULA(E138)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:F106 F100:I102 F103 H103:I103 F104:I104 H105:I105">
-    <cfRule type="expression" dxfId="221" priority="188">
+    <cfRule type="expression" dxfId="232" priority="199">
       <formula>$B100=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106">
-    <cfRule type="expression" dxfId="220" priority="22">
+    <cfRule type="expression" dxfId="231" priority="34">
+      <formula>$B106&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="230" priority="33">
       <formula>$B106=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="219" priority="23">
-      <formula>$B106&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="218" priority="21">
+    <cfRule type="expression" dxfId="229" priority="32">
       <formula>$B106=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112:F114">
-    <cfRule type="expression" dxfId="217" priority="75">
+    <cfRule type="expression" dxfId="228" priority="86">
       <formula>$B112=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F114">
-    <cfRule type="expression" dxfId="216" priority="69">
-      <formula>$B114=3</formula>
+    <cfRule type="expression" dxfId="227" priority="82">
+      <formula>$B114&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="215" priority="70">
+    <cfRule type="expression" dxfId="226" priority="81">
       <formula>$B114=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="214" priority="71">
-      <formula>$B114&lt;2</formula>
+    <cfRule type="expression" dxfId="225" priority="80">
+      <formula>$B114=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:G105">
-    <cfRule type="expression" dxfId="213" priority="24">
+    <cfRule type="expression" dxfId="224" priority="35">
       <formula>$B105=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="212" priority="26">
+    <cfRule type="expression" dxfId="223" priority="37">
       <formula>$B105&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="211" priority="25">
+    <cfRule type="expression" dxfId="222" priority="36">
       <formula>$B105=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112:G113">
-    <cfRule type="expression" dxfId="210" priority="72">
+    <cfRule type="expression" dxfId="221" priority="83">
       <formula>$B112=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="209" priority="73">
+    <cfRule type="expression" dxfId="220" priority="84">
       <formula>$B112=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="208" priority="74">
+    <cfRule type="expression" dxfId="219" priority="85">
       <formula>$B112&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51:I54">
-    <cfRule type="expression" dxfId="207" priority="557">
+    <cfRule type="expression" dxfId="218" priority="570">
+      <formula>$B51&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="217" priority="569">
+      <formula>$B51=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="216" priority="568">
       <formula>$B51=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="206" priority="558">
-      <formula>$B51=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="205" priority="559">
-      <formula>$B51&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="204" priority="560">
+    <cfRule type="expression" dxfId="215" priority="571">
       <formula>$B51=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F100:I101">
-    <cfRule type="expression" dxfId="203" priority="379">
+    <cfRule type="expression" dxfId="214" priority="389">
+      <formula>$B100=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="213" priority="390">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="202" priority="380">
+    <cfRule type="expression" dxfId="212" priority="391">
       <formula>$B100&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="201" priority="378">
-      <formula>$B100=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F100:I102 F103 H103:I103 F104:I104 H105:I105 F105:F106">
-    <cfRule type="expression" dxfId="200" priority="189">
+    <cfRule type="expression" dxfId="211" priority="200">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="199" priority="190">
+    <cfRule type="expression" dxfId="210" priority="201">
       <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102:I104">
-    <cfRule type="expression" dxfId="198" priority="60">
+    <cfRule type="expression" dxfId="209" priority="71">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="58">
+    <cfRule type="expression" dxfId="208" priority="70">
+      <formula>$B102=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="207" priority="69">
       <formula>$B102=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="196" priority="59">
-      <formula>$B102=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:I106">
-    <cfRule type="expression" dxfId="195" priority="33">
+    <cfRule type="expression" dxfId="206" priority="44">
       <formula>$B105=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="194" priority="34">
+    <cfRule type="expression" dxfId="205" priority="45">
       <formula>$B105=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="193" priority="35">
+    <cfRule type="expression" dxfId="204" priority="46">
       <formula>$B105&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:I106">
-    <cfRule type="expression" dxfId="192" priority="183">
+    <cfRule type="expression" dxfId="203" priority="194">
       <formula>$B106&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="191" priority="182">
+    <cfRule type="expression" dxfId="202" priority="192">
+      <formula>$B106=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="201" priority="193">
       <formula>$B106=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="181">
-      <formula>$B106=3</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:U54 W53:AG54 A55:AG75 A107:AG108 A109:V112 A112:AG123 A124:U124 W124:AG124 A125:AG134 A129:V144 S173:AG173 U174:U187 W174:AG187 A188:AG192">
-    <cfRule type="expression" dxfId="189" priority="753">
+  <conditionalFormatting sqref="F53:U54 W53:AG54 A55:AG75 A107:AG108 A109:V112 A112:AG123 A124:U124 W124:AG124 A125:AG128 A129:B130 D129:AG130 A131:AG134 A131:V144 S174:AG174 U175:U188 W175:AG188 A189:AG193">
+    <cfRule type="expression" dxfId="200" priority="764">
       <formula>$B53=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:AG52 A52:E54">
-    <cfRule type="expression" dxfId="188" priority="551">
+    <cfRule type="expression" dxfId="199" priority="562">
       <formula>$B52=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G103">
-    <cfRule type="expression" dxfId="187" priority="57">
-      <formula>$B103&lt;2</formula>
+    <cfRule type="expression" dxfId="198" priority="66">
+      <formula>$B103=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="56">
+    <cfRule type="expression" dxfId="197" priority="67">
       <formula>$B103=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="55">
-      <formula>$B103=3</formula>
+    <cfRule type="expression" dxfId="196" priority="68">
+      <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G109:I110">
-    <cfRule type="expression" dxfId="184" priority="785">
+    <cfRule type="expression" dxfId="195" priority="793">
+      <formula>$B109=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="194" priority="794">
+      <formula>$B109=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="193" priority="795">
+      <formula>$B109&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="192" priority="796">
       <formula>$B109=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="183" priority="784">
-      <formula>$B109&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="182" priority="783">
-      <formula>$B109=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="181" priority="782">
-      <formula>$B109=3</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H148:H149 K165:L166">
-    <cfRule type="expression" dxfId="180" priority="667">
-      <formula>$B149=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="179" priority="668">
+  <conditionalFormatting sqref="H148:H149 K166:L167">
+    <cfRule type="expression" dxfId="191" priority="679">
       <formula>$B149&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="669">
+    <cfRule type="expression" dxfId="190" priority="680">
       <formula>$B149=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="189" priority="678">
+      <formula>$B149=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H148:H149">
-    <cfRule type="expression" dxfId="177" priority="1058">
-      <formula>$B149&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="176" priority="1060">
+    <cfRule type="expression" dxfId="188" priority="1071">
       <formula>$B149=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="175" priority="1057">
+    <cfRule type="expression" dxfId="187" priority="1068">
       <formula>$B149=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="186" priority="1069">
+      <formula>$B149&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5">
-    <cfRule type="expression" dxfId="174" priority="588">
+    <cfRule type="expression" dxfId="185" priority="599">
       <formula>$B5=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="589">
+    <cfRule type="expression" dxfId="184" priority="600">
       <formula>$B5=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="590">
+    <cfRule type="expression" dxfId="183" priority="601">
       <formula>$B5&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="171" priority="591">
+    <cfRule type="expression" dxfId="182" priority="602">
       <formula>$B5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J71:L73">
-    <cfRule type="expression" dxfId="170" priority="639">
+    <cfRule type="expression" dxfId="181" priority="650">
       <formula>_xlfn.ISFORMULA(J71)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="643">
+    <cfRule type="expression" dxfId="180" priority="654">
       <formula>$B71=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:Q99 J104:Q1048576">
-    <cfRule type="expression" dxfId="168" priority="649">
+    <cfRule type="expression" dxfId="179" priority="660">
       <formula>_xlfn.ISFORMULA(J1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:Q70">
-    <cfRule type="expression" dxfId="167" priority="644">
+    <cfRule type="expression" dxfId="178" priority="655">
       <formula>_xlfn.ISFORMULA(J68)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J69:S73">
-    <cfRule type="expression" dxfId="166" priority="637">
-      <formula>$B69&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="165" priority="635">
+    <cfRule type="expression" dxfId="177" priority="646">
       <formula>$B69=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="636">
+    <cfRule type="expression" dxfId="176" priority="647">
       <formula>$B69=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="175" priority="648">
+      <formula>$B69&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:V68 J69:S70 U69:V73">
-    <cfRule type="expression" dxfId="163" priority="648">
+    <cfRule type="expression" dxfId="174" priority="659">
       <formula>$B68=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:V68 U69:V73">
-    <cfRule type="expression" dxfId="162" priority="647">
-      <formula>$B68&lt;2</formula>
+    <cfRule type="expression" dxfId="173" priority="656">
+      <formula>$B68=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="646">
+    <cfRule type="expression" dxfId="172" priority="657">
       <formula>$B68=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="160" priority="645">
-      <formula>$B68=3</formula>
+    <cfRule type="expression" dxfId="171" priority="658">
+      <formula>$B68&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K81">
-    <cfRule type="expression" dxfId="159" priority="581">
+    <cfRule type="expression" dxfId="170" priority="592">
       <formula>_xlfn.ISFORMULA(K81)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K165:L166 H148:H149">
-    <cfRule type="expression" dxfId="158" priority="666">
+  <conditionalFormatting sqref="K166:L167 H148:H149">
+    <cfRule type="expression" dxfId="169" priority="677">
       <formula>$B149=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K100:M101">
-    <cfRule type="expression" dxfId="157" priority="334">
+    <cfRule type="expression" dxfId="168" priority="345">
       <formula>$B100&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="332">
+    <cfRule type="expression" dxfId="167" priority="344">
+      <formula>$B100=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="166" priority="343">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="155" priority="333">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K100:M104">
+    <cfRule type="expression" dxfId="165" priority="171">
+      <formula>$B100&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="164" priority="169">
+      <formula>$B100=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="163" priority="170">
       <formula>$B100=2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K100:M104">
-    <cfRule type="expression" dxfId="154" priority="158">
-      <formula>$B100=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="153" priority="159">
-      <formula>$B100=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="152" priority="160">
-      <formula>$B100&lt;2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K100:M106">
-    <cfRule type="expression" dxfId="151" priority="153">
+    <cfRule type="expression" dxfId="162" priority="164">
       <formula>$B100=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="149">
+    <cfRule type="expression" dxfId="161" priority="160">
       <formula>_xlfn.ISFORMULA(K100)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K102:M106">
-    <cfRule type="expression" dxfId="149" priority="151">
-      <formula>$B102=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="148" priority="152">
+    <cfRule type="expression" dxfId="160" priority="163">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="147" priority="150">
+    <cfRule type="expression" dxfId="159" priority="161">
       <formula>$B102=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="158" priority="162">
+      <formula>$B102=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K105:M105">
-    <cfRule type="expression" dxfId="146" priority="51">
-      <formula>$B105&lt;2</formula>
+    <cfRule type="expression" dxfId="157" priority="60">
+      <formula>$B105=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="50">
+    <cfRule type="expression" dxfId="156" priority="61">
       <formula>$B105=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="49">
-      <formula>$B105=3</formula>
+    <cfRule type="expression" dxfId="155" priority="62">
+      <formula>$B105&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K106:M106">
-    <cfRule type="expression" dxfId="143" priority="2">
-      <formula>$B106=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="142" priority="4">
+    <cfRule type="expression" dxfId="154" priority="15">
       <formula>$B106&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="3">
+    <cfRule type="expression" dxfId="153" priority="14">
       <formula>$B106=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="152" priority="13">
+      <formula>$B106=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K145:M146">
-    <cfRule type="expression" dxfId="140" priority="747">
+    <cfRule type="expression" dxfId="151" priority="757">
+      <formula>$B145=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="150" priority="760">
+      <formula>$B145=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="149" priority="758">
       <formula>$B145=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="139" priority="748">
+    <cfRule type="expression" dxfId="148" priority="759">
       <formula>$B145&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="138" priority="746">
-      <formula>$B145=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="137" priority="749">
-      <formula>$B145=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L115">
-    <cfRule type="expression" dxfId="136" priority="988">
+    <cfRule type="expression" dxfId="147" priority="996">
+      <formula>#REF!=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="146" priority="997">
+      <formula>#REF!&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="145" priority="998">
+      <formula>#REF!=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="144" priority="999">
       <formula>#REF!=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="135" priority="987">
-      <formula>#REF!=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="134" priority="986">
-      <formula>#REF!&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="133" priority="985">
-      <formula>#REF!=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="132" priority="595">
+    <cfRule type="expression" dxfId="143" priority="606">
       <formula>$B115=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L115:V115">
-    <cfRule type="expression" dxfId="131" priority="594">
+    <cfRule type="expression" dxfId="142" priority="605">
       <formula>$B115&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="593">
+    <cfRule type="expression" dxfId="141" priority="604">
       <formula>$B115=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="592">
+    <cfRule type="expression" dxfId="140" priority="603">
       <formula>$B115=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M105:M106">
-    <cfRule type="expression" dxfId="128" priority="18">
-      <formula>$B105=3</formula>
+    <cfRule type="expression" dxfId="139" priority="31">
+      <formula>$B105&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="127" priority="19">
+    <cfRule type="expression" dxfId="138" priority="30">
       <formula>$B105=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="20">
-      <formula>$B105&lt;2</formula>
+    <cfRule type="expression" dxfId="137" priority="29">
+      <formula>$B105=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N81">
-    <cfRule type="expression" dxfId="125" priority="576">
+    <cfRule type="expression" dxfId="136" priority="587">
       <formula>_xlfn.ISFORMULA(N81)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O100:O101">
-    <cfRule type="expression" dxfId="124" priority="316">
+    <cfRule type="expression" dxfId="135" priority="327">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="123" priority="318">
+    <cfRule type="expression" dxfId="134" priority="328">
+      <formula>$B100=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="133" priority="329">
       <formula>$B100&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="122" priority="317">
-      <formula>$B100=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O100:O106">
-    <cfRule type="expression" dxfId="121" priority="311">
+    <cfRule type="expression" dxfId="132" priority="319">
+      <formula>$B100=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="131" priority="320">
+      <formula>$B100=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="130" priority="321">
+      <formula>$B100&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="129" priority="322">
       <formula>$B100=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="310">
-      <formula>$B100&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="119" priority="309">
-      <formula>$B100=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="118" priority="308">
-      <formula>$B100=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="117" priority="307">
+    <cfRule type="expression" dxfId="128" priority="318">
       <formula>_xlfn.ISFORMULA(O100)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O102:O106">
-    <cfRule type="expression" dxfId="116" priority="306">
-      <formula>$B102&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="115" priority="305">
+    <cfRule type="expression" dxfId="127" priority="316">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="304">
+    <cfRule type="expression" dxfId="126" priority="315">
       <formula>$B102=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="125" priority="317">
+      <formula>$B102&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q71:Q73">
-    <cfRule type="expression" dxfId="113" priority="634">
+    <cfRule type="expression" dxfId="124" priority="645">
       <formula>_xlfn.ISFORMULA(Q71)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q100:Q106">
-    <cfRule type="expression" dxfId="112" priority="133">
+    <cfRule type="expression" dxfId="123" priority="144">
       <formula>_xlfn.ISFORMULA(Q100)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q152">
-    <cfRule type="expression" dxfId="111" priority="803">
-      <formula>$B153=3</formula>
+  <conditionalFormatting sqref="Q153">
+    <cfRule type="expression" dxfId="122" priority="814">
+      <formula>$B154=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="804">
-      <formula>$B153=2</formula>
+    <cfRule type="expression" dxfId="121" priority="815">
+      <formula>$B154=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="805">
-      <formula>$B153&lt;2</formula>
+    <cfRule type="expression" dxfId="120" priority="816">
+      <formula>$B154&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="806">
-      <formula>$B153=0</formula>
+    <cfRule type="expression" dxfId="119" priority="817">
+      <formula>$B154=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q100:R101">
-    <cfRule type="expression" dxfId="107" priority="286">
-      <formula>$B100&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="106" priority="285">
+    <cfRule type="expression" dxfId="118" priority="296">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="284">
+    <cfRule type="expression" dxfId="117" priority="295">
       <formula>$B100=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="116" priority="297">
+      <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q100:R103">
-    <cfRule type="expression" dxfId="104" priority="279">
+    <cfRule type="expression" dxfId="115" priority="290">
       <formula>$B100&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="278">
+    <cfRule type="expression" dxfId="114" priority="288">
+      <formula>$B100=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="289">
       <formula>$B100=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="277">
-      <formula>$B100=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q104:R104">
-    <cfRule type="expression" dxfId="101" priority="126">
+    <cfRule type="expression" dxfId="112" priority="137">
       <formula>$B104=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="127">
+    <cfRule type="expression" dxfId="111" priority="138">
       <formula>$B104=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="128">
+    <cfRule type="expression" dxfId="110" priority="139">
       <formula>$B104&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q105:R105">
-    <cfRule type="expression" dxfId="98" priority="46">
+    <cfRule type="expression" dxfId="109" priority="58">
+      <formula>$B105=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="57">
       <formula>$B105=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="48">
+    <cfRule type="expression" dxfId="107" priority="59">
       <formula>$B105&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="47">
-      <formula>$B105=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q106:R106">
-    <cfRule type="expression" dxfId="95" priority="121">
+    <cfRule type="expression" dxfId="106" priority="131">
+      <formula>$B106=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="132">
       <formula>$B106&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="120">
-      <formula>$B106=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="119">
+    <cfRule type="expression" dxfId="104" priority="130">
       <formula>$B106=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q71:S73">
-    <cfRule type="expression" dxfId="92" priority="638">
+    <cfRule type="expression" dxfId="103" priority="649">
       <formula>$B71=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q102:S103">
-    <cfRule type="expression" dxfId="91" priority="272">
+    <cfRule type="expression" dxfId="102" priority="283">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="270">
+    <cfRule type="expression" dxfId="101" priority="282">
+      <formula>$B102=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="281">
       <formula>$B102=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="271">
-      <formula>$B102=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q104:S104">
-    <cfRule type="expression" dxfId="88" priority="105">
+    <cfRule type="expression" dxfId="99" priority="116">
       <formula>$B104=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="106">
+    <cfRule type="expression" dxfId="98" priority="117">
       <formula>$B104=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="107">
+    <cfRule type="expression" dxfId="97" priority="118">
       <formula>$B104&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q105:S105">
-    <cfRule type="expression" dxfId="85" priority="45">
-      <formula>$B105&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="44">
+    <cfRule type="expression" dxfId="96" priority="55">
       <formula>$B105=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="43">
+    <cfRule type="expression" dxfId="95" priority="54">
       <formula>$B105=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="56">
+      <formula>$B105&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q106:S106">
-    <cfRule type="expression" dxfId="82" priority="114">
+    <cfRule type="expression" dxfId="93" priority="125">
       <formula>$B106&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="113">
+    <cfRule type="expression" dxfId="92" priority="124">
       <formula>$B106=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="112">
+    <cfRule type="expression" dxfId="91" priority="123">
       <formula>$B106=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q100:T106">
-    <cfRule type="expression" dxfId="79" priority="94">
+    <cfRule type="expression" dxfId="90" priority="105">
       <formula>$B100=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R152">
+    <cfRule type="expression" dxfId="89" priority="9">
+      <formula>$B152=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="11">
+      <formula>$B152=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="87" priority="10">
+      <formula>$B152&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="8">
+      <formula>$B152=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="7">
+      <formula>$B152&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="6">
+      <formula>$B152=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="5">
+      <formula>$B152=3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S100:S103">
-    <cfRule type="expression" dxfId="78" priority="263">
+    <cfRule type="expression" dxfId="82" priority="274">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="264">
+    <cfRule type="expression" dxfId="81" priority="275">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="265">
+    <cfRule type="expression" dxfId="80" priority="276">
       <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S105">
-    <cfRule type="expression" dxfId="75" priority="42">
+    <cfRule type="expression" dxfId="79" priority="53">
       <formula>$B105&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="41">
+    <cfRule type="expression" dxfId="78" priority="52">
       <formula>$B105=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="40">
+    <cfRule type="expression" dxfId="77" priority="51">
       <formula>$B105=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S155">
-    <cfRule type="expression" dxfId="72" priority="732">
-      <formula>$B155&lt;2</formula>
+  <conditionalFormatting sqref="S156">
+    <cfRule type="expression" dxfId="76" priority="744">
+      <formula>$B156=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="731">
-      <formula>$B155=2</formula>
+    <cfRule type="expression" dxfId="75" priority="741">
+      <formula>$B156=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="730">
-      <formula>$B155=3</formula>
+    <cfRule type="expression" dxfId="74" priority="742">
+      <formula>$B156=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="733">
-      <formula>$B155=0</formula>
+    <cfRule type="expression" dxfId="73" priority="743">
+      <formula>$B156&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S159:S160">
-    <cfRule type="expression" dxfId="68" priority="729">
-      <formula>$B159=0</formula>
+  <conditionalFormatting sqref="S160:S161">
+    <cfRule type="expression" dxfId="72" priority="739">
+      <formula>$B160&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="726">
-      <formula>$B159=3</formula>
+    <cfRule type="expression" dxfId="71" priority="737">
+      <formula>$B160=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="727">
-      <formula>$B159=2</formula>
+    <cfRule type="expression" dxfId="70" priority="740">
+      <formula>$B160=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="728">
-      <formula>$B159&lt;2</formula>
+    <cfRule type="expression" dxfId="69" priority="738">
+      <formula>$B160=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S100:T101">
-    <cfRule type="expression" dxfId="64" priority="256">
+    <cfRule type="expression" dxfId="68" priority="267">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="257">
+    <cfRule type="expression" dxfId="67" priority="268">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="258">
+    <cfRule type="expression" dxfId="66" priority="269">
       <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S104:T104">
-    <cfRule type="expression" dxfId="61" priority="97">
+    <cfRule type="expression" dxfId="65" priority="107">
+      <formula>$B104=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="108">
       <formula>$B104&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="96">
-      <formula>$B104=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="95">
+    <cfRule type="expression" dxfId="63" priority="106">
       <formula>$B104=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S106:T106">
-    <cfRule type="expression" dxfId="58" priority="93">
+    <cfRule type="expression" dxfId="62" priority="103">
+      <formula>$B106=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="104">
       <formula>$B106&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="92">
-      <formula>$B106=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="91">
+    <cfRule type="expression" dxfId="60" priority="102">
       <formula>$B106=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S93:V96">
-    <cfRule type="expression" dxfId="55" priority="627">
+    <cfRule type="expression" dxfId="59" priority="638">
       <formula>$B93=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S153:V154">
-    <cfRule type="expression" dxfId="54" priority="690">
-      <formula>$B153=3</formula>
+  <conditionalFormatting sqref="S154:V155">
+    <cfRule type="expression" dxfId="58" priority="701">
+      <formula>$B154=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="691">
-      <formula>$B153=2</formula>
+    <cfRule type="expression" dxfId="57" priority="702">
+      <formula>$B154=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="692">
-      <formula>$B153&lt;2</formula>
+    <cfRule type="expression" dxfId="56" priority="703">
+      <formula>$B154&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="693">
-      <formula>$B153=0</formula>
+    <cfRule type="expression" dxfId="55" priority="704">
+      <formula>$B154=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5">
-    <cfRule type="expression" dxfId="50" priority="486">
+    <cfRule type="expression" dxfId="54" priority="497">
       <formula>$B5&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="483">
+    <cfRule type="expression" dxfId="53" priority="494">
       <formula>$B5=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="484">
+    <cfRule type="expression" dxfId="52" priority="495">
       <formula>$B5=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="485">
+    <cfRule type="expression" dxfId="51" priority="496">
       <formula>$B5=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6">
-    <cfRule type="expression" dxfId="46" priority="1046">
-      <formula>$B5=3</formula>
+    <cfRule type="expression" dxfId="50" priority="1052">
+      <formula>$B5=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="1044">
+    <cfRule type="expression" dxfId="49" priority="1053">
+      <formula>$B5&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="1055">
       <formula>$B5=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="1041">
-      <formula>$B5=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="1042">
-      <formula>$B5&lt;2</formula>
+    <cfRule type="expression" dxfId="47" priority="1057">
+      <formula>$B5=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T100:T103">
-    <cfRule type="expression" dxfId="42" priority="249">
+    <cfRule type="expression" dxfId="46" priority="260">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="250">
+    <cfRule type="expression" dxfId="45" priority="262">
+      <formula>$B100&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="261">
       <formula>$B100=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="251">
-      <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T102:T105">
-    <cfRule type="expression" dxfId="39" priority="98">
+    <cfRule type="expression" dxfId="43" priority="109">
       <formula>$B102=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="99">
+    <cfRule type="expression" dxfId="42" priority="110">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="100">
+    <cfRule type="expression" dxfId="41" priority="111">
       <formula>$B102&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T103">
-    <cfRule type="expression" dxfId="36" priority="27">
+    <cfRule type="expression" dxfId="40" priority="38">
       <formula>$B103=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="28">
+    <cfRule type="expression" dxfId="39" priority="40">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="39">
       <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="29">
-      <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T105:T106">
-    <cfRule type="expression" dxfId="33" priority="39">
-      <formula>$B105&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="37">
+    <cfRule type="expression" dxfId="37" priority="48">
       <formula>$B105=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="38">
+    <cfRule type="expression" dxfId="36" priority="49">
       <formula>$B105=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="50">
+      <formula>$B105&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U109">
-    <cfRule type="expression" dxfId="30" priority="813">
-      <formula>$B108&lt;2</formula>
+    <cfRule type="expression" dxfId="34" priority="823">
+      <formula>$B108=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="814">
+    <cfRule type="expression" dxfId="33" priority="822">
+      <formula>$B108=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="825">
       <formula>$B108=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="811">
-      <formula>$B108=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="812">
-      <formula>$B108=2</formula>
+    <cfRule type="expression" dxfId="31" priority="824">
+      <formula>$B108&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U138:AG143">
-    <cfRule type="expression" dxfId="26" priority="434">
+    <cfRule type="expression" dxfId="30" priority="445">
       <formula>$B138=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W100:W106">
-    <cfRule type="expression" dxfId="25" priority="241">
+    <cfRule type="expression" dxfId="29" priority="249">
+      <formula>$B100=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="250">
+      <formula>$B100=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="251">
+      <formula>$B100&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="252">
       <formula>$B100=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="240">
-      <formula>$B100&lt;2</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W131">
+    <cfRule type="expression" dxfId="25" priority="12">
+      <formula>$B131=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="239">
-      <formula>$B100=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="238">
-      <formula>$B100=3</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W152">
+    <cfRule type="expression" dxfId="24" priority="1">
+      <formula>$B152=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W76:AG82">
-    <cfRule type="expression" dxfId="21" priority="532">
-      <formula>$B76=2</formula>
+    <cfRule type="expression" dxfId="23" priority="542">
+      <formula>$B76=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="533">
+    <cfRule type="expression" dxfId="22" priority="544">
       <formula>$B76&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="534">
+    <cfRule type="expression" dxfId="21" priority="545">
       <formula>$B76=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="531">
-      <formula>$B76=3</formula>
+    <cfRule type="expression" dxfId="20" priority="543">
+      <formula>$B76=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W98:AG99 A148:G149 I148:R149 A150:R150">
-    <cfRule type="expression" dxfId="17" priority="736">
+    <cfRule type="expression" dxfId="19" priority="747">
       <formula>$B98&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="735">
+    <cfRule type="expression" dxfId="18" priority="746">
       <formula>$B98=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W109:AG111">
-    <cfRule type="expression" dxfId="15" priority="510">
+    <cfRule type="expression" dxfId="17" priority="521">
       <formula>$B109=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W135:AG135">
-    <cfRule type="expression" dxfId="14" priority="504">
+    <cfRule type="expression" dxfId="16" priority="515">
       <formula>$B135=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="503">
+    <cfRule type="expression" dxfId="15" priority="514">
       <formula>$B135=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="506">
+    <cfRule type="expression" dxfId="14" priority="516">
+      <formula>$B135&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="517">
       <formula>$B135=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="505">
-      <formula>$B135&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W138:AG143">
-    <cfRule type="expression" dxfId="10" priority="432">
+    <cfRule type="expression" dxfId="12" priority="442">
+      <formula>$B138=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="443">
       <formula>$B138=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="433">
+    <cfRule type="expression" dxfId="10" priority="444">
       <formula>$B138&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="431">
-      <formula>$B138=3</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W152:AG152">
+    <cfRule type="expression" dxfId="9" priority="4">
+      <formula>$B152=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>$B152&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>$B152=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z100:AG106">
-    <cfRule type="expression" dxfId="7" priority="80">
-      <formula>$B100=3</formula>
+    <cfRule type="expression" dxfId="6" priority="94">
+      <formula>$B100=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="81">
+    <cfRule type="expression" dxfId="5" priority="93">
+      <formula>$B100&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="92">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="83">
-      <formula>$B100=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="82">
-      <formula>$B100&lt;2</formula>
+    <cfRule type="expression" dxfId="3" priority="91">
+      <formula>$B100=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z136:AG136">
-    <cfRule type="expression" dxfId="3" priority="481">
-      <formula>$B136&lt;2</formula>
+    <cfRule type="expression" dxfId="2" priority="490">
+      <formula>$B136=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="480">
+    <cfRule type="expression" dxfId="1" priority="491">
       <formula>$B136=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="479">
-      <formula>$B136=3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W131">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$B131=0</formula>
+    <cfRule type="expression" dxfId="0" priority="492">
+      <formula>$B136&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="15">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q152 Q154:Q192 Q185:R192" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q153 Q155:Q193 Q186:R193" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1950</formula1>
       <formula2>2025</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J130 J133:J134 J137:J144 J148:J192 K2:K9 K11:K48 K52:K54 K57:K59 K61:K63 K67:K79 K87 K97:K107 K109:K150 K152:K192 N1:N67 N71:N83 N88:N1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J130 J133:J134 J137:J144 N88:N1048576 K2:K9 K11:K48 K52:K54 K57:K59 K61:K63 K67:K79 K87 K97:K107 K109:K150 N1:N67 N71:N83 J148:J151 J153:K193" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M359:M369" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M360:M370" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Land Area, Power MWe, Excavation Volume,  Reactor Building Slab Roof Volume,	Reactor Building  Basement Volume, Reactor Building  Exterior Walls Volume,		Turbine Building Slab Roof Volume,	Turbine Building  Basement Volume,	Turbine Building  Exterior Wall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 L190:L1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 L191:L1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"$/acres, $/MWe, $/m^3, $/MWt"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P185:P338" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P186:P339" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P80 P82:P137 P144:P192" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P80 P82:P137 P144:P193" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O80 O82:O134 O137 O144:O192" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O80 O82:O134 O137 O144:O193" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"acres, MWe, m^3, MWt, Kg, Drums, kW, $, m^2, kg/s"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L80 L82:L113 L115:L137 L144:L192" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L80 L82:L113 L115:L137 L144:L193" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"$/m^2,$/MWeHour,$/FTE, $/acres, $/MWe, $/m^3, $/MWt, $/Kg, $/Drum, $/(kg.sec), $/SWU, unitless, $/kWe"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O135:O136" xr:uid="{00000000-0002-0000-0000-000008000000}">
@@ -21458,10 +21870,10 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E192" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E193" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>"standard, nonstandard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R192" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R193" xr:uid="{00000000-0002-0000-0000-00000D000000}">
       <formula1>"NA, General, Labor, Material, Equipment,Lab and Mat and Equip, 'Lab and Equip"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L114" xr:uid="{00000000-0002-0000-0000-00000E000000}">
@@ -21480,7 +21892,7 @@
     <hyperlink ref="U131" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
     <hyperlink ref="U135" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
     <hyperlink ref="U136" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="U169" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="U170" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21498,20 +21910,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="156" t="s">
         <v>428</v>
       </c>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="149" t="s">
+      <c r="C1" s="153" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="150"/>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
+      <c r="A2" s="154"/>
+      <c r="B2" s="154"/>
+      <c r="C2" s="154"/>
     </row>
     <row r="3" spans="1:5" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
@@ -21949,7 +22361,7 @@
       <c r="A42" s="29" t="s">
         <v>453</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="139" t="s">
         <v>319</v>
       </c>
       <c r="C42" s="11">
@@ -22415,12 +22827,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="153" t="s">
+      <c r="A2" s="157" t="s">
         <v>483</v>
       </c>
-      <c r="B2" s="154"/>
-      <c r="C2" s="154"/>
-      <c r="D2" s="155"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="159"/>
     </row>
     <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
@@ -22477,12 +22889,12 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="153" t="s">
+      <c r="A7" s="157" t="s">
         <v>363</v>
       </c>
-      <c r="B7" s="154"/>
-      <c r="C7" s="154"/>
-      <c r="D7" s="155"/>
+      <c r="B7" s="158"/>
+      <c r="C7" s="158"/>
+      <c r="D7" s="159"/>
     </row>
     <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
@@ -22541,12 +22953,12 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="153" t="s">
+      <c r="A12" s="157" t="s">
         <v>236</v>
       </c>
-      <c r="B12" s="154"/>
-      <c r="C12" s="154"/>
-      <c r="D12" s="155"/>
+      <c r="B12" s="158"/>
+      <c r="C12" s="158"/>
+      <c r="D12" s="159"/>
     </row>
     <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="20" t="s">
@@ -22645,12 +23057,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="153" t="s">
+      <c r="A20" s="157" t="s">
         <v>513</v>
       </c>
-      <c r="B20" s="154"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="155"/>
+      <c r="B20" s="158"/>
+      <c r="C20" s="158"/>
+      <c r="D20" s="159"/>
     </row>
     <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="20" t="s">
@@ -22779,12 +23191,12 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="153" t="s">
+      <c r="A30" s="157" t="s">
         <v>526</v>
       </c>
-      <c r="B30" s="154"/>
-      <c r="C30" s="154"/>
-      <c r="D30" s="155"/>
+      <c r="B30" s="158"/>
+      <c r="C30" s="158"/>
+      <c r="D30" s="159"/>
     </row>
     <row r="31" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="20" t="s">
@@ -22859,12 +23271,12 @@
       <c r="D36" s="26"/>
     </row>
     <row r="37" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="153" t="s">
+      <c r="A37" s="157" t="s">
         <v>534</v>
       </c>
-      <c r="B37" s="154"/>
-      <c r="C37" s="154"/>
-      <c r="D37" s="155"/>
+      <c r="B37" s="158"/>
+      <c r="C37" s="158"/>
+      <c r="D37" s="159"/>
     </row>
     <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="20" t="s">
@@ -22951,12 +23363,12 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="153" t="s">
+      <c r="A44" s="157" t="s">
         <v>547</v>
       </c>
-      <c r="B44" s="154"/>
-      <c r="C44" s="154"/>
-      <c r="D44" s="155"/>
+      <c r="B44" s="158"/>
+      <c r="C44" s="158"/>
+      <c r="D44" s="159"/>
     </row>
     <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="20" t="s">
@@ -22973,12 +23385,12 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="153" t="s">
+      <c r="A46" s="157" t="s">
         <v>550</v>
       </c>
-      <c r="B46" s="154"/>
-      <c r="C46" s="154"/>
-      <c r="D46" s="155"/>
+      <c r="B46" s="158"/>
+      <c r="C46" s="158"/>
+      <c r="D46" s="159"/>
     </row>
     <row r="47" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="20" t="s">
@@ -23023,12 +23435,12 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="153" t="s">
+      <c r="A50" s="157" t="s">
         <v>557</v>
       </c>
-      <c r="B50" s="154"/>
-      <c r="C50" s="154"/>
-      <c r="D50" s="155"/>
+      <c r="B50" s="158"/>
+      <c r="C50" s="158"/>
+      <c r="D50" s="159"/>
     </row>
     <row r="51" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="20" t="s">
@@ -24422,13 +24834,13 @@
       <c r="B9">
         <v>0.08</v>
       </c>
-      <c r="C9" s="156" t="s">
+      <c r="C9" s="160" t="s">
         <v>571</v>
       </c>
-      <c r="D9" s="156" t="s">
+      <c r="D9" s="160" t="s">
         <v>572</v>
       </c>
-      <c r="E9" s="156" t="s">
+      <c r="E9" s="160" t="s">
         <v>573</v>
       </c>
     </row>
@@ -24439,9 +24851,9 @@
       <c r="B10">
         <v>0</v>
       </c>
-      <c r="C10" s="157"/>
-      <c r="D10" s="157"/>
-      <c r="E10" s="157"/>
+      <c r="C10" s="161"/>
+      <c r="D10" s="161"/>
+      <c r="E10" s="161"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -24450,9 +24862,9 @@
       <c r="B11">
         <v>0</v>
       </c>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
+      <c r="C11" s="161"/>
+      <c r="D11" s="161"/>
+      <c r="E11" s="161"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
@@ -24461,9 +24873,9 @@
       <c r="B12">
         <v>0.18443169820109739</v>
       </c>
-      <c r="C12" s="157"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="157"/>
+      <c r="C12" s="161"/>
+      <c r="D12" s="161"/>
+      <c r="E12" s="161"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -24472,9 +24884,9 @@
       <c r="B13">
         <v>0.24138000000000001</v>
       </c>
-      <c r="C13" s="157"/>
-      <c r="D13" s="157"/>
-      <c r="E13" s="157"/>
+      <c r="C13" s="161"/>
+      <c r="D13" s="161"/>
+      <c r="E13" s="161"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
@@ -24483,9 +24895,9 @@
       <c r="B14" s="82">
         <v>0.22962848022115531</v>
       </c>
-      <c r="C14" s="157"/>
-      <c r="D14" s="157"/>
-      <c r="E14" s="157"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="161"/>
+      <c r="E14" s="161"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -24494,9 +24906,9 @@
       <c r="B15">
         <v>0.41505377678599259</v>
       </c>
-      <c r="C15" s="157"/>
-      <c r="D15" s="157"/>
-      <c r="E15" s="157"/>
+      <c r="C15" s="161"/>
+      <c r="D15" s="161"/>
+      <c r="E15" s="161"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
@@ -24505,9 +24917,9 @@
       <c r="B16">
         <v>0.39914905811401719</v>
       </c>
-      <c r="C16" s="157"/>
-      <c r="D16" s="157"/>
-      <c r="E16" s="157"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
+      <c r="E16" s="161"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
@@ -24516,7 +24928,7 @@
       <c r="B17">
         <v>0.05</v>
       </c>
-      <c r="C17" s="157"/>
+      <c r="C17" s="161"/>
       <c r="D17" t="s">
         <v>574</v>
       </c>
@@ -24780,10 +25192,10 @@
       <c r="S3" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="158" t="s">
+      <c r="T3" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="U3" s="162" t="s">
+      <c r="U3" s="165" t="s">
         <v>42</v>
       </c>
       <c r="V3" s="105"/>
@@ -24883,8 +25295,8 @@
       <c r="S4" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="150"/>
-      <c r="U4" s="150"/>
+      <c r="T4" s="154"/>
+      <c r="U4" s="154"/>
       <c r="V4" s="105"/>
       <c r="W4" s="96" t="s">
         <v>43</v>
@@ -24976,10 +25388,10 @@
       <c r="S5" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="T5" s="158" t="s">
+      <c r="T5" s="162" t="s">
         <v>63</v>
       </c>
-      <c r="U5" s="162" t="s">
+      <c r="U5" s="165" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="105"/>
@@ -25072,8 +25484,8 @@
       <c r="S6" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="T6" s="150"/>
-      <c r="U6" s="150"/>
+      <c r="T6" s="154"/>
+      <c r="U6" s="154"/>
       <c r="V6" s="105"/>
       <c r="W6" s="96" t="s">
         <v>43</v>
@@ -25423,13 +25835,13 @@
       <c r="R11" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="S11" s="158" t="s">
+      <c r="S11" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="T11" s="158" t="s">
+      <c r="T11" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="161" t="s">
+      <c r="U11" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="105"/>
@@ -25526,9 +25938,9 @@
       <c r="R12" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="S12" s="159"/>
-      <c r="T12" s="159"/>
-      <c r="U12" s="159"/>
+      <c r="S12" s="163"/>
+      <c r="T12" s="163"/>
+      <c r="U12" s="163"/>
       <c r="V12" s="105"/>
       <c r="W12" s="96" t="s">
         <v>43</v>
@@ -25623,9 +26035,9 @@
       <c r="R13" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="S13" s="150"/>
-      <c r="T13" s="150"/>
-      <c r="U13" s="150"/>
+      <c r="S13" s="154"/>
+      <c r="T13" s="154"/>
+      <c r="U13" s="154"/>
       <c r="V13" s="105"/>
       <c r="W13" s="96" t="s">
         <v>43</v>
@@ -25976,13 +26388,13 @@
       <c r="R18" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S18" s="158" t="s">
+      <c r="S18" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T18" s="158" t="s">
+      <c r="T18" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U18" s="161" t="s">
+      <c r="U18" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V18" s="105"/>
@@ -26074,9 +26486,9 @@
       <c r="R19" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S19" s="159"/>
-      <c r="T19" s="159"/>
-      <c r="U19" s="159"/>
+      <c r="S19" s="163"/>
+      <c r="T19" s="163"/>
+      <c r="U19" s="163"/>
       <c r="V19" s="105"/>
       <c r="W19" s="96" t="s">
         <v>43</v>
@@ -26166,9 +26578,9 @@
       <c r="R20" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S20" s="150"/>
-      <c r="T20" s="150"/>
-      <c r="U20" s="150"/>
+      <c r="S20" s="154"/>
+      <c r="T20" s="154"/>
+      <c r="U20" s="154"/>
       <c r="V20" s="105"/>
       <c r="W20" s="96" t="s">
         <v>43</v>
@@ -26387,13 +26799,13 @@
       <c r="R23" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S23" s="158" t="s">
+      <c r="S23" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T23" s="158" t="s">
+      <c r="T23" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U23" s="161" t="s">
+      <c r="U23" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V23" s="105"/>
@@ -26485,9 +26897,9 @@
       <c r="R24" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S24" s="159"/>
-      <c r="T24" s="159"/>
-      <c r="U24" s="159"/>
+      <c r="S24" s="163"/>
+      <c r="T24" s="163"/>
+      <c r="U24" s="163"/>
       <c r="V24" s="105"/>
       <c r="W24" s="96" t="s">
         <v>43</v>
@@ -26577,9 +26989,9 @@
       <c r="R25" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S25" s="150"/>
-      <c r="T25" s="150"/>
-      <c r="U25" s="150"/>
+      <c r="S25" s="154"/>
+      <c r="T25" s="154"/>
+      <c r="U25" s="154"/>
       <c r="V25" s="105"/>
       <c r="W25" s="96" t="s">
         <v>43</v>
@@ -26798,13 +27210,13 @@
       <c r="R28" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S28" s="158" t="s">
+      <c r="S28" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T28" s="158" t="s">
+      <c r="T28" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U28" s="161" t="s">
+      <c r="U28" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V28" s="105"/>
@@ -26896,9 +27308,9 @@
       <c r="R29" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S29" s="159"/>
-      <c r="T29" s="159"/>
-      <c r="U29" s="159"/>
+      <c r="S29" s="163"/>
+      <c r="T29" s="163"/>
+      <c r="U29" s="163"/>
       <c r="V29" s="105"/>
       <c r="W29" s="96" t="s">
         <v>43</v>
@@ -26988,9 +27400,9 @@
       <c r="R30" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S30" s="150"/>
-      <c r="T30" s="150"/>
-      <c r="U30" s="150"/>
+      <c r="S30" s="154"/>
+      <c r="T30" s="154"/>
+      <c r="U30" s="154"/>
       <c r="V30" s="105"/>
       <c r="W30" s="96" t="s">
         <v>43</v>
@@ -27209,13 +27621,13 @@
       <c r="R33" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S33" s="158" t="s">
+      <c r="S33" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T33" s="158" t="s">
+      <c r="T33" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U33" s="161" t="s">
+      <c r="U33" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V33" s="105"/>
@@ -27307,9 +27719,9 @@
       <c r="R34" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S34" s="159"/>
-      <c r="T34" s="159"/>
-      <c r="U34" s="159"/>
+      <c r="S34" s="163"/>
+      <c r="T34" s="163"/>
+      <c r="U34" s="163"/>
       <c r="V34" s="105"/>
       <c r="W34" s="96" t="s">
         <v>43</v>
@@ -27399,9 +27811,9 @@
       <c r="R35" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S35" s="150"/>
-      <c r="T35" s="150"/>
-      <c r="U35" s="150"/>
+      <c r="S35" s="154"/>
+      <c r="T35" s="154"/>
+      <c r="U35" s="154"/>
       <c r="V35" s="105"/>
       <c r="W35" s="96" t="s">
         <v>43</v>
@@ -27620,13 +28032,13 @@
       <c r="R38" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S38" s="158" t="s">
+      <c r="S38" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T38" s="158" t="s">
+      <c r="T38" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U38" s="161" t="s">
+      <c r="U38" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V38" s="105"/>
@@ -27718,9 +28130,9 @@
       <c r="R39" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S39" s="159"/>
-      <c r="T39" s="159"/>
-      <c r="U39" s="159"/>
+      <c r="S39" s="163"/>
+      <c r="T39" s="163"/>
+      <c r="U39" s="163"/>
       <c r="V39" s="105"/>
       <c r="W39" s="96" t="s">
         <v>43</v>
@@ -27810,9 +28222,9 @@
       <c r="R40" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S40" s="150"/>
-      <c r="T40" s="150"/>
-      <c r="U40" s="150"/>
+      <c r="S40" s="154"/>
+      <c r="T40" s="154"/>
+      <c r="U40" s="154"/>
       <c r="V40" s="105"/>
       <c r="W40" s="96" t="s">
         <v>43</v>
@@ -28170,13 +28582,13 @@
       <c r="R45" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S45" s="158" t="s">
+      <c r="S45" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T45" s="158" t="s">
+      <c r="T45" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U45" s="161" t="s">
+      <c r="U45" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V45" s="105"/>
@@ -28268,9 +28680,9 @@
       <c r="R46" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S46" s="159"/>
-      <c r="T46" s="159"/>
-      <c r="U46" s="159"/>
+      <c r="S46" s="163"/>
+      <c r="T46" s="163"/>
+      <c r="U46" s="163"/>
       <c r="V46" s="105"/>
       <c r="W46" s="96" t="s">
         <v>43</v>
@@ -28360,9 +28772,9 @@
       <c r="R47" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S47" s="150"/>
-      <c r="T47" s="150"/>
-      <c r="U47" s="150"/>
+      <c r="S47" s="154"/>
+      <c r="T47" s="154"/>
+      <c r="U47" s="154"/>
       <c r="V47" s="105"/>
       <c r="W47" s="96" t="s">
         <v>43</v>
@@ -28728,13 +29140,13 @@
       <c r="R52" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S52" s="158" t="s">
+      <c r="S52" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T52" s="158" t="s">
+      <c r="T52" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U52" s="161" t="s">
+      <c r="U52" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V52" s="105"/>
@@ -28826,9 +29238,9 @@
       <c r="R53" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S53" s="159"/>
-      <c r="T53" s="159"/>
-      <c r="U53" s="159"/>
+      <c r="S53" s="163"/>
+      <c r="T53" s="163"/>
+      <c r="U53" s="163"/>
       <c r="V53" s="105"/>
       <c r="W53" s="96" t="s">
         <v>43</v>
@@ -28918,9 +29330,9 @@
       <c r="R54" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S54" s="150"/>
-      <c r="T54" s="150"/>
-      <c r="U54" s="150"/>
+      <c r="S54" s="154"/>
+      <c r="T54" s="154"/>
+      <c r="U54" s="154"/>
       <c r="V54" s="105"/>
       <c r="W54" s="96" t="s">
         <v>43</v>
@@ -29144,13 +29556,13 @@
       <c r="R57" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S57" s="158" t="s">
+      <c r="S57" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T57" s="158" t="s">
+      <c r="T57" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U57" s="161" t="s">
+      <c r="U57" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V57" s="105"/>
@@ -29242,9 +29654,9 @@
       <c r="R58" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S58" s="159"/>
-      <c r="T58" s="159"/>
-      <c r="U58" s="159"/>
+      <c r="S58" s="163"/>
+      <c r="T58" s="163"/>
+      <c r="U58" s="163"/>
       <c r="V58" s="105"/>
       <c r="W58" s="96" t="s">
         <v>43</v>
@@ -29334,9 +29746,9 @@
       <c r="R59" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S59" s="150"/>
-      <c r="T59" s="150"/>
-      <c r="U59" s="150"/>
+      <c r="S59" s="154"/>
+      <c r="T59" s="154"/>
+      <c r="U59" s="154"/>
       <c r="V59" s="105"/>
       <c r="W59" s="96" t="s">
         <v>43</v>
@@ -29562,13 +29974,13 @@
       <c r="R62" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S62" s="158" t="s">
+      <c r="S62" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T62" s="158" t="s">
+      <c r="T62" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U62" s="161" t="s">
+      <c r="U62" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V62" s="105"/>
@@ -29660,9 +30072,9 @@
       <c r="R63" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S63" s="159"/>
-      <c r="T63" s="159"/>
-      <c r="U63" s="159"/>
+      <c r="S63" s="163"/>
+      <c r="T63" s="163"/>
+      <c r="U63" s="163"/>
       <c r="V63" s="105"/>
       <c r="W63" s="96" t="s">
         <v>43</v>
@@ -29752,9 +30164,9 @@
       <c r="R64" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S64" s="150"/>
-      <c r="T64" s="150"/>
-      <c r="U64" s="150"/>
+      <c r="S64" s="154"/>
+      <c r="T64" s="154"/>
+      <c r="U64" s="154"/>
       <c r="V64" s="105"/>
       <c r="W64" s="96" t="s">
         <v>43</v>
@@ -29973,13 +30385,13 @@
       <c r="R67" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S67" s="158" t="s">
+      <c r="S67" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T67" s="158" t="s">
+      <c r="T67" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U67" s="161" t="s">
+      <c r="U67" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V67" s="105"/>
@@ -30071,9 +30483,9 @@
       <c r="R68" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S68" s="159"/>
-      <c r="T68" s="159"/>
-      <c r="U68" s="159"/>
+      <c r="S68" s="163"/>
+      <c r="T68" s="163"/>
+      <c r="U68" s="163"/>
       <c r="V68" s="105"/>
       <c r="W68" s="96" t="s">
         <v>43</v>
@@ -30163,9 +30575,9 @@
       <c r="R69" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S69" s="150"/>
-      <c r="T69" s="150"/>
-      <c r="U69" s="150"/>
+      <c r="S69" s="154"/>
+      <c r="T69" s="154"/>
+      <c r="U69" s="154"/>
       <c r="V69" s="105"/>
       <c r="W69" s="96" t="s">
         <v>43</v>
@@ -30523,13 +30935,13 @@
       <c r="R74" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S74" s="158" t="s">
+      <c r="S74" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="T74" s="158" t="s">
+      <c r="T74" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U74" s="161" t="s">
+      <c r="U74" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V74" s="105"/>
@@ -30621,9 +31033,9 @@
       <c r="R75" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S75" s="159"/>
-      <c r="T75" s="159"/>
-      <c r="U75" s="159"/>
+      <c r="S75" s="163"/>
+      <c r="T75" s="163"/>
+      <c r="U75" s="163"/>
       <c r="V75" s="105"/>
       <c r="W75" s="96" t="s">
         <v>43</v>
@@ -30713,9 +31125,9 @@
       <c r="R76" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S76" s="150"/>
-      <c r="T76" s="150"/>
-      <c r="U76" s="150"/>
+      <c r="S76" s="154"/>
+      <c r="T76" s="154"/>
+      <c r="U76" s="154"/>
       <c r="V76" s="105"/>
       <c r="W76" s="96" t="s">
         <v>43</v>
@@ -30934,13 +31346,13 @@
       <c r="R79" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S79" s="158" t="s">
+      <c r="S79" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="T79" s="158" t="s">
+      <c r="T79" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U79" s="161" t="s">
+      <c r="U79" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V79" s="105"/>
@@ -31032,9 +31444,9 @@
       <c r="R80" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S80" s="159"/>
-      <c r="T80" s="159"/>
-      <c r="U80" s="159"/>
+      <c r="S80" s="163"/>
+      <c r="T80" s="163"/>
+      <c r="U80" s="163"/>
       <c r="V80" s="105"/>
       <c r="W80" s="96" t="s">
         <v>43</v>
@@ -31124,9 +31536,9 @@
       <c r="R81" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S81" s="150"/>
-      <c r="T81" s="150"/>
-      <c r="U81" s="150"/>
+      <c r="S81" s="154"/>
+      <c r="T81" s="154"/>
+      <c r="U81" s="154"/>
       <c r="V81" s="105"/>
       <c r="W81" s="96" t="s">
         <v>43</v>
@@ -31497,13 +31909,13 @@
       <c r="R86" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S86" s="158" t="s">
+      <c r="S86" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="T86" s="158" t="s">
+      <c r="T86" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U86" s="161" t="s">
+      <c r="U86" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V86" s="105"/>
@@ -31595,9 +32007,9 @@
       <c r="R87" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S87" s="159"/>
-      <c r="T87" s="159"/>
-      <c r="U87" s="159"/>
+      <c r="S87" s="163"/>
+      <c r="T87" s="163"/>
+      <c r="U87" s="163"/>
       <c r="V87" s="105"/>
       <c r="W87" s="96" t="s">
         <v>43</v>
@@ -31687,9 +32099,9 @@
       <c r="R88" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S88" s="150"/>
-      <c r="T88" s="150"/>
-      <c r="U88" s="150"/>
+      <c r="S88" s="154"/>
+      <c r="T88" s="154"/>
+      <c r="U88" s="154"/>
       <c r="V88" s="105"/>
       <c r="W88" s="96" t="s">
         <v>43</v>
@@ -32056,13 +32468,13 @@
       <c r="R93" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S93" s="158" t="s">
+      <c r="S93" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T93" s="158" t="s">
+      <c r="T93" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U93" s="161" t="s">
+      <c r="U93" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V93" s="105"/>
@@ -32154,9 +32566,9 @@
       <c r="R94" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S94" s="159"/>
-      <c r="T94" s="159"/>
-      <c r="U94" s="159"/>
+      <c r="S94" s="163"/>
+      <c r="T94" s="163"/>
+      <c r="U94" s="163"/>
       <c r="V94" s="105"/>
       <c r="W94" s="96" t="s">
         <v>43</v>
@@ -32246,9 +32658,9 @@
       <c r="R95" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S95" s="150"/>
-      <c r="T95" s="150"/>
-      <c r="U95" s="150"/>
+      <c r="S95" s="154"/>
+      <c r="T95" s="154"/>
+      <c r="U95" s="154"/>
       <c r="V95" s="105"/>
       <c r="W95" s="96" t="s">
         <v>43</v>
@@ -32467,13 +32879,13 @@
       <c r="R98" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S98" s="158" t="s">
+      <c r="S98" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T98" s="158" t="s">
+      <c r="T98" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U98" s="161" t="s">
+      <c r="U98" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V98" s="105"/>
@@ -32565,9 +32977,9 @@
       <c r="R99" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S99" s="159"/>
-      <c r="T99" s="159"/>
-      <c r="U99" s="159"/>
+      <c r="S99" s="163"/>
+      <c r="T99" s="163"/>
+      <c r="U99" s="163"/>
       <c r="V99" s="105"/>
       <c r="W99" s="96" t="s">
         <v>43</v>
@@ -32657,9 +33069,9 @@
       <c r="R100" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S100" s="150"/>
-      <c r="T100" s="150"/>
-      <c r="U100" s="150"/>
+      <c r="S100" s="154"/>
+      <c r="T100" s="154"/>
+      <c r="U100" s="154"/>
       <c r="V100" s="105"/>
       <c r="W100" s="96" t="s">
         <v>43</v>
@@ -33038,13 +33450,13 @@
       <c r="R105" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S105" s="158" t="s">
+      <c r="S105" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T105" s="158" t="s">
+      <c r="T105" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U105" s="161" t="s">
+      <c r="U105" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V105" s="105"/>
@@ -33143,9 +33555,9 @@
       <c r="R106" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S106" s="159"/>
-      <c r="T106" s="159"/>
-      <c r="U106" s="159"/>
+      <c r="S106" s="163"/>
+      <c r="T106" s="163"/>
+      <c r="U106" s="163"/>
       <c r="V106" s="105"/>
       <c r="W106" s="96" t="s">
         <v>43</v>
@@ -33235,9 +33647,9 @@
       <c r="R107" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S107" s="150"/>
-      <c r="T107" s="150"/>
-      <c r="U107" s="150"/>
+      <c r="S107" s="154"/>
+      <c r="T107" s="154"/>
+      <c r="U107" s="154"/>
       <c r="V107" s="105"/>
       <c r="W107" s="96" t="s">
         <v>43</v>
@@ -33609,13 +34021,13 @@
       <c r="R112" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S112" s="158" t="s">
+      <c r="S112" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="T112" s="158" t="s">
+      <c r="T112" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U112" s="161" t="s">
+      <c r="U112" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V112" s="105"/>
@@ -33707,9 +34119,9 @@
       <c r="R113" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S113" s="159"/>
-      <c r="T113" s="159"/>
-      <c r="U113" s="159"/>
+      <c r="S113" s="163"/>
+      <c r="T113" s="163"/>
+      <c r="U113" s="163"/>
       <c r="V113" s="105"/>
       <c r="W113" s="96" t="s">
         <v>43</v>
@@ -33799,9 +34211,9 @@
       <c r="R114" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S114" s="150"/>
-      <c r="T114" s="150"/>
-      <c r="U114" s="150"/>
+      <c r="S114" s="154"/>
+      <c r="T114" s="154"/>
+      <c r="U114" s="154"/>
       <c r="V114" s="105"/>
       <c r="W114" s="96" t="s">
         <v>43</v>
@@ -34033,13 +34445,13 @@
       <c r="R117" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S117" s="158" t="s">
+      <c r="S117" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T117" s="158" t="s">
+      <c r="T117" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U117" s="161" t="s">
+      <c r="U117" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V117" s="105"/>
@@ -34138,9 +34550,9 @@
       <c r="R118" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S118" s="159"/>
-      <c r="T118" s="159"/>
-      <c r="U118" s="159"/>
+      <c r="S118" s="163"/>
+      <c r="T118" s="163"/>
+      <c r="U118" s="163"/>
       <c r="V118" s="105"/>
       <c r="W118" s="96" t="s">
         <v>43</v>
@@ -34237,9 +34649,9 @@
       <c r="R119" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S119" s="150"/>
-      <c r="T119" s="150"/>
-      <c r="U119" s="150"/>
+      <c r="S119" s="154"/>
+      <c r="T119" s="154"/>
+      <c r="U119" s="154"/>
       <c r="V119" s="105"/>
       <c r="W119" s="96" t="s">
         <v>43</v>
@@ -34472,13 +34884,13 @@
       <c r="R122" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S122" s="158" t="s">
+      <c r="S122" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T122" s="158" t="s">
+      <c r="T122" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U122" s="161" t="s">
+      <c r="U122" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V122" s="105"/>
@@ -34570,9 +34982,9 @@
       <c r="R123" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S123" s="159"/>
-      <c r="T123" s="159"/>
-      <c r="U123" s="159"/>
+      <c r="S123" s="163"/>
+      <c r="T123" s="163"/>
+      <c r="U123" s="163"/>
       <c r="V123" s="105"/>
       <c r="W123" s="96" t="s">
         <v>43</v>
@@ -34662,9 +35074,9 @@
       <c r="R124" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S124" s="150"/>
-      <c r="T124" s="150"/>
-      <c r="U124" s="150"/>
+      <c r="S124" s="154"/>
+      <c r="T124" s="154"/>
+      <c r="U124" s="154"/>
       <c r="V124" s="105"/>
       <c r="W124" s="96" t="s">
         <v>43</v>
@@ -34883,13 +35295,13 @@
       <c r="R127" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S127" s="158" t="s">
+      <c r="S127" s="162" t="s">
         <v>588</v>
       </c>
-      <c r="T127" s="158" t="s">
+      <c r="T127" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U127" s="161" t="s">
+      <c r="U127" s="164" t="s">
         <v>76</v>
       </c>
       <c r="V127" s="105"/>
@@ -34981,9 +35393,9 @@
       <c r="R128" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S128" s="159"/>
-      <c r="T128" s="159"/>
-      <c r="U128" s="159"/>
+      <c r="S128" s="163"/>
+      <c r="T128" s="163"/>
+      <c r="U128" s="163"/>
       <c r="V128" s="105"/>
       <c r="W128" s="96" t="s">
         <v>43</v>
@@ -35073,9 +35485,9 @@
       <c r="R129" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="S129" s="150"/>
-      <c r="T129" s="150"/>
-      <c r="U129" s="150"/>
+      <c r="S129" s="154"/>
+      <c r="T129" s="154"/>
+      <c r="U129" s="154"/>
       <c r="V129" s="105"/>
       <c r="W129" s="96" t="s">
         <v>43</v>
@@ -42306,10 +42718,10 @@
       <c r="R225" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="S225" s="160" t="s">
+      <c r="S225" s="166" t="s">
         <v>344</v>
       </c>
-      <c r="T225" s="160" t="s">
+      <c r="T225" s="166" t="s">
         <v>345</v>
       </c>
       <c r="U225" s="105"/>
@@ -42392,8 +42804,8 @@
       <c r="R226" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="S226" s="159"/>
-      <c r="T226" s="159"/>
+      <c r="S226" s="163"/>
+      <c r="T226" s="163"/>
       <c r="U226" s="105"/>
       <c r="V226" s="105"/>
       <c r="W226" s="96" t="s">
@@ -42481,8 +42893,8 @@
       <c r="R227" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="S227" s="159"/>
-      <c r="T227" s="159"/>
+      <c r="S227" s="163"/>
+      <c r="T227" s="163"/>
       <c r="U227" s="105"/>
       <c r="V227" s="105"/>
       <c r="W227" s="96" t="s">
@@ -42570,8 +42982,8 @@
       <c r="R228" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="S228" s="159"/>
-      <c r="T228" s="159"/>
+      <c r="S228" s="163"/>
+      <c r="T228" s="163"/>
       <c r="U228" s="105"/>
       <c r="V228" s="105"/>
       <c r="W228" s="96" t="s">
@@ -42652,8 +43064,8 @@
       <c r="R229" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="S229" s="159"/>
-      <c r="T229" s="159"/>
+      <c r="S229" s="163"/>
+      <c r="T229" s="163"/>
       <c r="U229" s="105"/>
       <c r="V229" s="105"/>
       <c r="W229" s="96" t="s">
@@ -42734,8 +43146,8 @@
       <c r="R230" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="S230" s="150"/>
-      <c r="T230" s="150"/>
+      <c r="S230" s="154"/>
+      <c r="T230" s="154"/>
       <c r="U230" s="105"/>
       <c r="V230" s="105"/>
       <c r="W230" s="96" t="s">
@@ -43494,7 +43906,7 @@
       <c r="R242" s="101" t="s">
         <v>73</v>
       </c>
-      <c r="S242" s="158" t="s">
+      <c r="S242" s="162" t="s">
         <v>320</v>
       </c>
       <c r="T242" s="101"/>
@@ -43552,7 +43964,7 @@
       <c r="R243" s="101" t="s">
         <v>73</v>
       </c>
-      <c r="S243" s="159"/>
+      <c r="S243" s="163"/>
       <c r="T243" s="101"/>
       <c r="U243" s="101"/>
       <c r="V243" s="101"/>
@@ -43616,7 +44028,7 @@
       <c r="R244" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="S244" s="159"/>
+      <c r="S244" s="163"/>
       <c r="T244" s="105"/>
       <c r="U244" s="105"/>
       <c r="V244" s="105"/>
@@ -43673,7 +44085,7 @@
       <c r="R245" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="S245" s="150"/>
+      <c r="S245" s="154"/>
       <c r="T245" s="105"/>
       <c r="U245" s="105"/>
       <c r="V245" s="105"/>
@@ -45078,19 +45490,47 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="S242:S245"/>
-    <mergeCell ref="U33:U35"/>
-    <mergeCell ref="U98:U100"/>
-    <mergeCell ref="U67:U69"/>
-    <mergeCell ref="U117:U119"/>
-    <mergeCell ref="U52:U54"/>
-    <mergeCell ref="U79:U81"/>
-    <mergeCell ref="U38:U40"/>
-    <mergeCell ref="U112:U114"/>
-    <mergeCell ref="T122:T124"/>
-    <mergeCell ref="S67:S69"/>
-    <mergeCell ref="T67:T69"/>
-    <mergeCell ref="T127:T129"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="S225:S230"/>
+    <mergeCell ref="S122:S124"/>
+    <mergeCell ref="U57:U59"/>
+    <mergeCell ref="S38:S40"/>
+    <mergeCell ref="U62:U64"/>
+    <mergeCell ref="T117:T119"/>
+    <mergeCell ref="S112:S114"/>
+    <mergeCell ref="S57:S59"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="U28:U30"/>
+    <mergeCell ref="U93:U95"/>
+    <mergeCell ref="S127:S129"/>
+    <mergeCell ref="T225:T230"/>
+    <mergeCell ref="S74:S76"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T74:T76"/>
+    <mergeCell ref="T112:T114"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="S117:S119"/>
+    <mergeCell ref="U45:U47"/>
+    <mergeCell ref="T93:T95"/>
+    <mergeCell ref="S98:S100"/>
+    <mergeCell ref="S105:S107"/>
+    <mergeCell ref="U74:U76"/>
+    <mergeCell ref="T62:T64"/>
+    <mergeCell ref="U105:U107"/>
+    <mergeCell ref="T38:T40"/>
+    <mergeCell ref="S52:S54"/>
+    <mergeCell ref="S86:S88"/>
+    <mergeCell ref="U86:U88"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="T57:T59"/>
+    <mergeCell ref="T33:T35"/>
+    <mergeCell ref="T18:T20"/>
+    <mergeCell ref="T98:T100"/>
+    <mergeCell ref="T45:T47"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="S18:S20"/>
     <mergeCell ref="U122:U124"/>
     <mergeCell ref="U18:U20"/>
@@ -45107,47 +45547,19 @@
     <mergeCell ref="T28:T30"/>
     <mergeCell ref="S45:S47"/>
     <mergeCell ref="S79:S81"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="T57:T59"/>
-    <mergeCell ref="T33:T35"/>
-    <mergeCell ref="T18:T20"/>
-    <mergeCell ref="T98:T100"/>
-    <mergeCell ref="T45:T47"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T74:T76"/>
-    <mergeCell ref="T112:T114"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="S117:S119"/>
-    <mergeCell ref="U45:U47"/>
-    <mergeCell ref="T93:T95"/>
-    <mergeCell ref="S98:S100"/>
-    <mergeCell ref="S105:S107"/>
-    <mergeCell ref="U74:U76"/>
-    <mergeCell ref="T62:T64"/>
-    <mergeCell ref="U105:U107"/>
-    <mergeCell ref="T38:T40"/>
-    <mergeCell ref="S52:S54"/>
-    <mergeCell ref="S86:S88"/>
-    <mergeCell ref="U86:U88"/>
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="S225:S230"/>
-    <mergeCell ref="S122:S124"/>
-    <mergeCell ref="U57:U59"/>
-    <mergeCell ref="S38:S40"/>
-    <mergeCell ref="U62:U64"/>
-    <mergeCell ref="T117:T119"/>
-    <mergeCell ref="S112:S114"/>
-    <mergeCell ref="S57:S59"/>
-    <mergeCell ref="S28:S30"/>
-    <mergeCell ref="U28:U30"/>
-    <mergeCell ref="U93:U95"/>
-    <mergeCell ref="S127:S129"/>
-    <mergeCell ref="T225:T230"/>
-    <mergeCell ref="S74:S76"/>
+    <mergeCell ref="S242:S245"/>
+    <mergeCell ref="U33:U35"/>
+    <mergeCell ref="U98:U100"/>
+    <mergeCell ref="U67:U69"/>
+    <mergeCell ref="U117:U119"/>
+    <mergeCell ref="U52:U54"/>
+    <mergeCell ref="U79:U81"/>
+    <mergeCell ref="U38:U40"/>
+    <mergeCell ref="U112:U114"/>
+    <mergeCell ref="T122:T124"/>
+    <mergeCell ref="S67:S69"/>
+    <mergeCell ref="T67:T69"/>
+    <mergeCell ref="T127:T129"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannbn/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FDA0AA-A281-F041-BB3D-1C90CC64D0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9618D5C-A140-5F40-95A5-312EBA168CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cost Database" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4672" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4676" uniqueCount="747">
   <si>
     <t>Account</t>
   </si>
@@ -2357,6 +2357,18 @@
   <si>
     <t>Primary Loop Purification</t>
   </si>
+  <si>
+    <t>UO2 Learning</t>
+  </si>
+  <si>
+    <t>TRISO Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># UO2 learning rate = 0.02 per doubling. This is an inferred effective rate that gives a 12.6% reduction by unit 100, consistent with the approximately 8–15% fabrication-cost reduction associated with increased UO2 plant throughput in AFC-CBR Module D1-1, Section D1-1.10.2 and Figure D1-1.6. </t>
+  </si>
+  <si>
+    <t># TRISO learning rate = 0.13 per doubling. This is an inferred effective rate that gives a 60.4% reduction by unit 100, approximately representing the reduction from the report’s ~$25,000/kgU current-production estimate toward its ~$10,000/kgU automated-production target in AFC-CBR Module D1-3, Section D1-3.8 and Tables D1-3-8 through D1-3-10.</t>
+  </si>
 </sst>
 </file>
 
@@ -2371,7 +2383,7 @@
     <numFmt numFmtId="168" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2496,6 +2508,12 @@
       <sz val="13"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2708,7 +2726,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3077,21 +3095,21 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3099,8 +3117,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3125,15 +3143,17 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -5488,6 +5508,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF208E70-AB10-8224-E903-7971C5164110}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5961,7 +6035,7 @@
       <c r="S3" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="143" t="s">
+      <c r="T3" s="147" t="s">
         <v>41</v>
       </c>
       <c r="U3" s="150" t="s">
@@ -6586,13 +6660,13 @@
       <c r="R11" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="S11" s="143" t="s">
+      <c r="S11" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="T11" s="143" t="s">
+      <c r="T11" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="148" t="s">
+      <c r="U11" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="49"/>
@@ -6909,13 +6983,13 @@
       <c r="R15" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S15" s="143" t="s">
+      <c r="S15" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="T15" s="143" t="s">
+      <c r="T15" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U15" s="148" t="s">
+      <c r="U15" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V15" s="49"/>
@@ -7455,13 +7529,13 @@
       <c r="R22" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S22" s="143" t="s">
+      <c r="S22" s="147" t="s">
         <v>105</v>
       </c>
-      <c r="T22" s="143" t="s">
+      <c r="T22" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U22" s="148" t="s">
+      <c r="U22" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V22" s="49"/>
@@ -7764,13 +7838,13 @@
       <c r="R26" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S26" s="143" t="s">
+      <c r="S26" s="147" t="s">
         <v>105</v>
       </c>
-      <c r="T26" s="143" t="s">
+      <c r="T26" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U26" s="148" t="s">
+      <c r="U26" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V26" s="49"/>
@@ -8081,13 +8155,13 @@
       <c r="R30" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S30" s="143" t="s">
+      <c r="S30" s="147" t="s">
         <v>105</v>
       </c>
-      <c r="T30" s="143" t="s">
+      <c r="T30" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U30" s="148" t="s">
+      <c r="U30" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V30" s="49"/>
@@ -8588,13 +8662,13 @@
       <c r="R37" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S37" s="143" t="s">
+      <c r="S37" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="T37" s="143" t="s">
+      <c r="T37" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U37" s="148" t="s">
+      <c r="U37" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V37" s="49"/>
@@ -8895,13 +8969,13 @@
       <c r="R41" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S41" s="143" t="s">
+      <c r="S41" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="T41" s="143" t="s">
+      <c r="T41" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U41" s="148" t="s">
+      <c r="U41" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V41" s="49"/>
@@ -9256,13 +9330,13 @@
       <c r="R46" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S46" s="143" t="s">
+      <c r="S46" s="147" t="s">
         <v>105</v>
       </c>
-      <c r="T46" s="143" t="s">
+      <c r="T46" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U46" s="148" t="s">
+      <c r="U46" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V46" s="49"/>
@@ -9707,16 +9781,16 @@
       <c r="R52" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S52" s="143" t="s">
+      <c r="S52" s="147" t="s">
         <v>105</v>
       </c>
-      <c r="T52" s="143" t="s">
+      <c r="T52" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U52" s="148" t="s">
+      <c r="U52" s="146" t="s">
         <v>76</v>
       </c>
-      <c r="V52" s="149" t="s">
+      <c r="V52" s="152" t="s">
         <v>162</v>
       </c>
       <c r="W52" s="74" t="s">
@@ -10063,13 +10137,13 @@
       <c r="R57" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S57" s="143" t="s">
+      <c r="S57" s="147" t="s">
         <v>105</v>
       </c>
-      <c r="T57" s="143" t="s">
+      <c r="T57" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U57" s="148" t="s">
+      <c r="U57" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V57" s="49"/>
@@ -10372,13 +10446,13 @@
       <c r="R61" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S61" s="143" t="s">
+      <c r="S61" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="T61" s="143" t="s">
+      <c r="T61" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="U61" s="148" t="s">
+      <c r="U61" s="146" t="s">
         <v>76</v>
       </c>
       <c r="V61" s="49"/>
@@ -10876,7 +10950,7 @@
       <c r="S68" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T68" s="146" t="s">
+      <c r="T68" s="148" t="s">
         <v>197</v>
       </c>
       <c r="U68" s="55"/>
@@ -11557,10 +11631,10 @@
       <c r="S76" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="T76" s="146" t="s">
+      <c r="T76" s="148" t="s">
         <v>210</v>
       </c>
-      <c r="U76" s="152" t="s">
+      <c r="U76" s="149" t="s">
         <v>211</v>
       </c>
       <c r="V76" s="58" t="s">
@@ -12738,7 +12812,7 @@
       <c r="T89" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="U89" s="152" t="s">
+      <c r="U89" s="149" t="s">
         <v>211</v>
       </c>
       <c r="V89" s="49"/>
@@ -14470,13 +14544,13 @@
       <c r="S109" s="58" t="s">
         <v>272</v>
       </c>
-      <c r="T109" s="146" t="s">
+      <c r="T109" s="148" t="s">
         <v>273</v>
       </c>
       <c r="U109" s="151" t="s">
         <v>274</v>
       </c>
-      <c r="V109" s="146"/>
+      <c r="V109" s="148"/>
       <c r="W109" s="74" t="s">
         <v>157</v>
       </c>
@@ -15761,7 +15835,7 @@
         <v>296</v>
       </c>
       <c r="U123" s="80"/>
-      <c r="V123" s="146" t="s">
+      <c r="V123" s="148" t="s">
         <v>311</v>
       </c>
       <c r="W123" s="74" t="s">
@@ -16885,10 +16959,10 @@
       <c r="R138" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S138" s="147" t="s">
+      <c r="S138" s="143" t="s">
         <v>344</v>
       </c>
-      <c r="T138" s="147" t="s">
+      <c r="T138" s="143" t="s">
         <v>345</v>
       </c>
       <c r="U138" s="49"/>
@@ -17414,7 +17488,7 @@
       <c r="AF144" s="76"/>
       <c r="AG144" s="74"/>
     </row>
-    <row r="145" spans="1:33" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:34" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="53">
         <v>251</v>
       </c>
@@ -17455,10 +17529,10 @@
       <c r="R145" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S145" s="146" t="s">
+      <c r="S145" s="148" t="s">
         <v>354</v>
       </c>
-      <c r="T145" s="146" t="s">
+      <c r="T145" s="148" t="s">
         <v>355</v>
       </c>
       <c r="U145" s="49"/>
@@ -17501,7 +17575,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="53">
         <v>252</v>
       </c>
@@ -17584,7 +17658,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="53">
         <v>253</v>
       </c>
@@ -17669,7 +17743,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="53">
         <v>254</v>
       </c>
@@ -17760,7 +17834,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="53">
         <v>254</v>
       </c>
@@ -17799,7 +17873,7 @@
       </c>
       <c r="J149" s="65"/>
       <c r="K149" s="65">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="L149" s="49" t="s">
         <v>186</v>
@@ -17811,7 +17885,7 @@
       <c r="O149" s="49"/>
       <c r="P149" s="49"/>
       <c r="Q149" s="65">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="R149" s="49" t="s">
         <v>219</v>
@@ -17821,7 +17895,7 @@
       <c r="U149" s="49"/>
       <c r="V149" s="49"/>
       <c r="W149" s="74" t="s">
-        <v>157</v>
+        <v>743</v>
       </c>
       <c r="X149" s="77">
         <f t="shared" si="38"/>
@@ -17835,12 +17909,10 @@
         <v>44</v>
       </c>
       <c r="AA149" s="76">
-        <f t="shared" si="40"/>
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AB149" s="76">
-        <f t="shared" si="41"/>
-        <v>325</v>
+        <v>575</v>
       </c>
       <c r="AC149" s="74" t="s">
         <v>44</v>
@@ -17857,8 +17929,11 @@
       <c r="AG149" s="74" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="150" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AH149" s="167" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="150" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="53">
         <v>254</v>
       </c>
@@ -17893,7 +17968,7 @@
       <c r="I150" s="45"/>
       <c r="J150" s="65"/>
       <c r="K150" s="65">
-        <v>10000</v>
+        <v>10900</v>
       </c>
       <c r="L150" s="49" t="s">
         <v>186</v>
@@ -17905,7 +17980,7 @@
       <c r="O150" s="49"/>
       <c r="P150" s="49"/>
       <c r="Q150" s="65">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="R150" s="49" t="s">
         <v>219</v>
@@ -17915,7 +17990,7 @@
       <c r="U150" s="49"/>
       <c r="V150" s="49"/>
       <c r="W150" s="74" t="s">
-        <v>157</v>
+        <v>744</v>
       </c>
       <c r="X150" s="77">
         <f t="shared" si="38"/>
@@ -17929,12 +18004,12 @@
         <v>44</v>
       </c>
       <c r="AA150" s="76">
-        <f t="shared" si="40"/>
-        <v>9000</v>
+        <f>0.5*K150</f>
+        <v>5450</v>
       </c>
       <c r="AB150" s="76">
-        <f t="shared" si="41"/>
-        <v>13000</v>
+        <f>3*K150</f>
+        <v>32700</v>
       </c>
       <c r="AC150" s="74" t="s">
         <v>44</v>
@@ -17951,8 +18026,11 @@
       <c r="AG150" s="74" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="151" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AH150" s="168" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="151" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="37">
         <v>26</v>
       </c>
@@ -18042,7 +18120,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="37">
         <v>27</v>
       </c>
@@ -18109,7 +18187,7 @@
       <c r="AF152" s="76"/>
       <c r="AG152" s="74"/>
     </row>
-    <row r="153" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="50">
         <v>30</v>
       </c>
@@ -18161,7 +18239,7 @@
       <c r="AF153" s="76"/>
       <c r="AG153" s="74"/>
     </row>
-    <row r="154" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:34" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="50">
         <v>31</v>
       </c>
@@ -18205,7 +18283,7 @@
       <c r="AF154" s="76"/>
       <c r="AG154" s="74"/>
     </row>
-    <row r="155" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="50">
         <v>32</v>
       </c>
@@ -18249,7 +18327,7 @@
       <c r="AF155" s="76"/>
       <c r="AG155" s="74"/>
     </row>
-    <row r="156" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="37">
         <v>33</v>
       </c>
@@ -18294,7 +18372,7 @@
       <c r="R156" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="S156" s="143" t="s">
+      <c r="S156" s="147" t="s">
         <v>320</v>
       </c>
       <c r="T156" s="46"/>
@@ -18338,7 +18416,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="37">
         <v>34</v>
       </c>
@@ -18418,7 +18496,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="37">
         <v>35</v>
       </c>
@@ -18498,7 +18576,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="37">
         <v>36</v>
       </c>
@@ -18578,7 +18656,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="37">
         <v>40</v>
       </c>
@@ -19550,14 +19628,14 @@
       <c r="P174" s="49"/>
       <c r="Q174" s="65"/>
       <c r="R174" s="49"/>
-      <c r="S174" s="146" t="s">
+      <c r="S174" s="148" t="s">
         <v>403</v>
       </c>
-      <c r="T174" s="146" t="s">
+      <c r="T174" s="148" t="s">
         <v>403</v>
       </c>
       <c r="U174" s="49"/>
-      <c r="V174" s="146" t="s">
+      <c r="V174" s="148" t="s">
         <v>404</v>
       </c>
       <c r="W174" s="74"/>
@@ -20548,6 +20626,43 @@
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="T26:T28"/>
+    <mergeCell ref="T41:T43"/>
+    <mergeCell ref="V109:V110"/>
+    <mergeCell ref="T61:T63"/>
+    <mergeCell ref="T76:T80"/>
+    <mergeCell ref="S138:S143"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="V174:V188"/>
+    <mergeCell ref="S30:S32"/>
+    <mergeCell ref="S15:S17"/>
+    <mergeCell ref="T37:T39"/>
+    <mergeCell ref="T46:T48"/>
+    <mergeCell ref="T22:T24"/>
+    <mergeCell ref="U52:U54"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="U26:U28"/>
+    <mergeCell ref="T52:T54"/>
+    <mergeCell ref="V123:V124"/>
+    <mergeCell ref="S156:S159"/>
+    <mergeCell ref="T145:T150"/>
+    <mergeCell ref="V52:V54"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="T57:T59"/>
+    <mergeCell ref="T15:T17"/>
+    <mergeCell ref="S41:S43"/>
+    <mergeCell ref="U109:U110"/>
+    <mergeCell ref="T68:T73"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S22:S24"/>
+    <mergeCell ref="U22:U24"/>
+    <mergeCell ref="T30:T32"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="U37:U39"/>
+    <mergeCell ref="T109:T110"/>
     <mergeCell ref="T138:T143"/>
     <mergeCell ref="U30:U32"/>
     <mergeCell ref="S52:S54"/>
@@ -20564,43 +20679,6 @@
     <mergeCell ref="S57:S59"/>
     <mergeCell ref="S37:S39"/>
     <mergeCell ref="U89:U99"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="T57:T59"/>
-    <mergeCell ref="T15:T17"/>
-    <mergeCell ref="S41:S43"/>
-    <mergeCell ref="U109:U110"/>
-    <mergeCell ref="T68:T73"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S22:S24"/>
-    <mergeCell ref="U22:U24"/>
-    <mergeCell ref="T30:T32"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="U37:U39"/>
-    <mergeCell ref="T109:T110"/>
-    <mergeCell ref="S138:S143"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="V174:V188"/>
-    <mergeCell ref="S30:S32"/>
-    <mergeCell ref="S15:S17"/>
-    <mergeCell ref="T37:T39"/>
-    <mergeCell ref="T46:T48"/>
-    <mergeCell ref="T22:T24"/>
-    <mergeCell ref="U52:U54"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="U26:U28"/>
-    <mergeCell ref="T52:T54"/>
-    <mergeCell ref="V123:V124"/>
-    <mergeCell ref="S156:S159"/>
-    <mergeCell ref="T145:T150"/>
-    <mergeCell ref="V52:V54"/>
-    <mergeCell ref="T26:T28"/>
-    <mergeCell ref="T41:T43"/>
-    <mergeCell ref="V109:V110"/>
-    <mergeCell ref="T61:T63"/>
-    <mergeCell ref="T76:T80"/>
   </mergeCells>
   <conditionalFormatting sqref="A100:B106">
     <cfRule type="expression" dxfId="312" priority="586">
@@ -20677,17 +20755,17 @@
       <formula>$B76=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A98:V99 D100:D106 A125:V126 A129:B130 D129:V130 A131:V143 A144:AG147 A148:G149 I148:AG149 A150:AG151 A152:V152 A153:AG173">
+  <conditionalFormatting sqref="A98:V99 D100:D106 A125:V126 A129:B130 D129:V130 A131:V143 A144:AG147 A148:G149 I148:AG149 A150:AG151 A152:V152 A153:AG173 W145:W150">
     <cfRule type="expression" dxfId="293" priority="633">
       <formula>$B98&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A112:V114 U116:V122 U123:U124 A127:S128 U127:V128 A144:AG147 A148:G149 I148:AG149 A150:AG151 A153:AG173 A138:B143 U138:V143 U146:V152 A5:S6 A109:F111 X152:AG152 A1:AG4 U5:AG6">
+  <conditionalFormatting sqref="A112:V114 U116:V122 U123:U124 A127:S128 U127:V128 A144:AG147 A148:G149 I148:AG149 A150:AG151 A153:AG173 A138:B143 U138:V143 U146:V152 A5:S6 A109:F111 X152:AG152 A1:AG4 U5:AG6 W145:W150">
     <cfRule type="expression" dxfId="292" priority="797">
       <formula>$B1=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A125:V126 A129:B130 D129:V130 A131:V143 A98:V99 D100:D106 A152:V152 A144:AG147 A148:G149 I148:AG149 A150:AG151 A153:AG173">
+  <conditionalFormatting sqref="A125:V126 A129:B130 D129:V130 A131:V143 A98:V99 D100:D106 A152:V152 A144:AG147 A148:G149 I148:AG149 A150:AG151 A153:AG173 W145:W150">
     <cfRule type="expression" dxfId="291" priority="632">
       <formula>$B98=2</formula>
     </cfRule>
@@ -20811,7 +20889,7 @@
       <formula>$B136=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A144:AG147 A148:G149 I148:AG149 A150:AG151 A152:V153 A153:AG173">
+  <conditionalFormatting sqref="A144:AG147 A148:G149 I148:AG149 A150:AG151 A152:V153 A153:AG173 W145:W150">
     <cfRule type="expression" dxfId="261" priority="566">
       <formula>$B144=0</formula>
     </cfRule>
@@ -24747,7 +24825,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" customWidth="1"/>
@@ -24936,6 +25014,22 @@
         <v>575</v>
       </c>
     </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="B18">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B19">
+        <v>0.13</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C9:C17"/>
@@ -24943,6 +25037,7 @@
     <mergeCell ref="D9:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -25195,7 +25290,7 @@
       <c r="T3" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="U3" s="165" t="s">
+      <c r="U3" s="166" t="s">
         <v>42</v>
       </c>
       <c r="V3" s="105"/>
@@ -25391,7 +25486,7 @@
       <c r="T5" s="162" t="s">
         <v>63</v>
       </c>
-      <c r="U5" s="165" t="s">
+      <c r="U5" s="166" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="105"/>
@@ -25841,7 +25936,7 @@
       <c r="T11" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="164" t="s">
+      <c r="U11" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="105"/>
@@ -26394,7 +26489,7 @@
       <c r="T18" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U18" s="164" t="s">
+      <c r="U18" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V18" s="105"/>
@@ -26805,7 +26900,7 @@
       <c r="T23" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U23" s="164" t="s">
+      <c r="U23" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V23" s="105"/>
@@ -27216,7 +27311,7 @@
       <c r="T28" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U28" s="164" t="s">
+      <c r="U28" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V28" s="105"/>
@@ -27627,7 +27722,7 @@
       <c r="T33" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U33" s="164" t="s">
+      <c r="U33" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V33" s="105"/>
@@ -28038,7 +28133,7 @@
       <c r="T38" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U38" s="164" t="s">
+      <c r="U38" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V38" s="105"/>
@@ -28588,7 +28683,7 @@
       <c r="T45" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U45" s="164" t="s">
+      <c r="U45" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V45" s="105"/>
@@ -29146,7 +29241,7 @@
       <c r="T52" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U52" s="164" t="s">
+      <c r="U52" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V52" s="105"/>
@@ -29562,7 +29657,7 @@
       <c r="T57" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U57" s="164" t="s">
+      <c r="U57" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V57" s="105"/>
@@ -29980,7 +30075,7 @@
       <c r="T62" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U62" s="164" t="s">
+      <c r="U62" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V62" s="105"/>
@@ -30391,7 +30486,7 @@
       <c r="T67" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U67" s="164" t="s">
+      <c r="U67" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V67" s="105"/>
@@ -30941,7 +31036,7 @@
       <c r="T74" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U74" s="164" t="s">
+      <c r="U74" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V74" s="105"/>
@@ -31352,7 +31447,7 @@
       <c r="T79" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U79" s="164" t="s">
+      <c r="U79" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V79" s="105"/>
@@ -31915,7 +32010,7 @@
       <c r="T86" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U86" s="164" t="s">
+      <c r="U86" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V86" s="105"/>
@@ -32474,7 +32569,7 @@
       <c r="T93" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U93" s="164" t="s">
+      <c r="U93" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V93" s="105"/>
@@ -32885,7 +32980,7 @@
       <c r="T98" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U98" s="164" t="s">
+      <c r="U98" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V98" s="105"/>
@@ -33456,7 +33551,7 @@
       <c r="T105" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U105" s="164" t="s">
+      <c r="U105" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V105" s="105"/>
@@ -34027,7 +34122,7 @@
       <c r="T112" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U112" s="164" t="s">
+      <c r="U112" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V112" s="105"/>
@@ -34451,7 +34546,7 @@
       <c r="T117" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U117" s="164" t="s">
+      <c r="U117" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V117" s="105"/>
@@ -34890,7 +34985,7 @@
       <c r="T122" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U122" s="164" t="s">
+      <c r="U122" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V122" s="105"/>
@@ -35301,7 +35396,7 @@
       <c r="T127" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="U127" s="164" t="s">
+      <c r="U127" s="165" t="s">
         <v>76</v>
       </c>
       <c r="V127" s="105"/>
@@ -42718,10 +42813,10 @@
       <c r="R225" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="S225" s="166" t="s">
+      <c r="S225" s="164" t="s">
         <v>344</v>
       </c>
-      <c r="T225" s="166" t="s">
+      <c r="T225" s="164" t="s">
         <v>345</v>
       </c>
       <c r="U225" s="105"/>
@@ -45490,21 +45585,45 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="S225:S230"/>
-    <mergeCell ref="S122:S124"/>
-    <mergeCell ref="U57:U59"/>
-    <mergeCell ref="S38:S40"/>
-    <mergeCell ref="U62:U64"/>
-    <mergeCell ref="T117:T119"/>
-    <mergeCell ref="S112:S114"/>
-    <mergeCell ref="S57:S59"/>
-    <mergeCell ref="S28:S30"/>
-    <mergeCell ref="U28:U30"/>
-    <mergeCell ref="U93:U95"/>
-    <mergeCell ref="S127:S129"/>
-    <mergeCell ref="T225:T230"/>
-    <mergeCell ref="S74:S76"/>
+    <mergeCell ref="S242:S245"/>
+    <mergeCell ref="U33:U35"/>
+    <mergeCell ref="U98:U100"/>
+    <mergeCell ref="U67:U69"/>
+    <mergeCell ref="U117:U119"/>
+    <mergeCell ref="U52:U54"/>
+    <mergeCell ref="U79:U81"/>
+    <mergeCell ref="U38:U40"/>
+    <mergeCell ref="U112:U114"/>
+    <mergeCell ref="T122:T124"/>
+    <mergeCell ref="S67:S69"/>
+    <mergeCell ref="T67:T69"/>
+    <mergeCell ref="T127:T129"/>
+    <mergeCell ref="S18:S20"/>
+    <mergeCell ref="U122:U124"/>
+    <mergeCell ref="U18:U20"/>
+    <mergeCell ref="T79:T81"/>
+    <mergeCell ref="U127:U129"/>
+    <mergeCell ref="U23:U25"/>
+    <mergeCell ref="T105:T107"/>
+    <mergeCell ref="T52:T54"/>
+    <mergeCell ref="T86:T88"/>
+    <mergeCell ref="S93:S95"/>
+    <mergeCell ref="S62:S64"/>
+    <mergeCell ref="S33:S35"/>
+    <mergeCell ref="T23:T25"/>
+    <mergeCell ref="T28:T30"/>
+    <mergeCell ref="S45:S47"/>
+    <mergeCell ref="S79:S81"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="T57:T59"/>
+    <mergeCell ref="T33:T35"/>
+    <mergeCell ref="T18:T20"/>
+    <mergeCell ref="T98:T100"/>
+    <mergeCell ref="T45:T47"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="S11:S13"/>
     <mergeCell ref="T74:T76"/>
     <mergeCell ref="T112:T114"/>
@@ -45521,45 +45640,21 @@
     <mergeCell ref="S52:S54"/>
     <mergeCell ref="S86:S88"/>
     <mergeCell ref="U86:U88"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="T57:T59"/>
-    <mergeCell ref="T33:T35"/>
-    <mergeCell ref="T18:T20"/>
-    <mergeCell ref="T98:T100"/>
-    <mergeCell ref="T45:T47"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="S18:S20"/>
-    <mergeCell ref="U122:U124"/>
-    <mergeCell ref="U18:U20"/>
-    <mergeCell ref="T79:T81"/>
-    <mergeCell ref="U127:U129"/>
-    <mergeCell ref="U23:U25"/>
-    <mergeCell ref="T105:T107"/>
-    <mergeCell ref="T52:T54"/>
-    <mergeCell ref="T86:T88"/>
-    <mergeCell ref="S93:S95"/>
-    <mergeCell ref="S62:S64"/>
-    <mergeCell ref="S33:S35"/>
-    <mergeCell ref="T23:T25"/>
-    <mergeCell ref="T28:T30"/>
-    <mergeCell ref="S45:S47"/>
-    <mergeCell ref="S79:S81"/>
-    <mergeCell ref="S242:S245"/>
-    <mergeCell ref="U33:U35"/>
-    <mergeCell ref="U98:U100"/>
-    <mergeCell ref="U67:U69"/>
-    <mergeCell ref="U117:U119"/>
-    <mergeCell ref="U52:U54"/>
-    <mergeCell ref="U79:U81"/>
-    <mergeCell ref="U38:U40"/>
-    <mergeCell ref="U112:U114"/>
-    <mergeCell ref="T122:T124"/>
-    <mergeCell ref="S67:S69"/>
-    <mergeCell ref="T67:T69"/>
-    <mergeCell ref="T127:T129"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="S225:S230"/>
+    <mergeCell ref="S122:S124"/>
+    <mergeCell ref="U57:U59"/>
+    <mergeCell ref="S38:S40"/>
+    <mergeCell ref="U62:U64"/>
+    <mergeCell ref="T117:T119"/>
+    <mergeCell ref="S112:S114"/>
+    <mergeCell ref="S57:S59"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="U28:U30"/>
+    <mergeCell ref="U93:U95"/>
+    <mergeCell ref="S127:S129"/>
+    <mergeCell ref="T225:T230"/>
+    <mergeCell ref="S74:S76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -34887,20 +34887,25 @@
       <c r="I28" s="93"/>
       <c r="J28" s="141"/>
       <c r="K28" s="120">
-        <f>493700000/(40000*1000)</f>
-        <v>12.342499999999999</v>
-      </c>
-      <c r="L28" s="100" t="s">
-        <v>186</v>
-      </c>
-      <c r="M28" s="155" t="s">
-        <v>721</v>
+        <v>6171250</v>
+      </c>
+      <c r="L28" s="100" t="inlineStr">
+        <is>
+          <t>$/(reactors/year)</t>
+        </is>
+      </c>
+      <c r="M28" s="155" t="inlineStr">
+        <is>
+          <t>Servicing Rate</t>
+        </is>
       </c>
       <c r="N28" s="121">
         <v>1</v>
       </c>
-      <c r="O28" s="100" t="s">
-        <v>188</v>
+      <c r="O28" s="100" t="inlineStr">
+        <is>
+          <t>reactors/year</t>
+        </is>
       </c>
       <c r="P28" s="123">
         <v>1</v>
@@ -34935,11 +34940,11 @@
       </c>
       <c r="AA28" s="147">
         <f t="shared" si="24"/>
-        <v>11.10825</v>
+        <v>5554125</v>
       </c>
       <c r="AB28" s="147">
         <f t="shared" si="25"/>
-        <v>16.045249999999999</v>
+        <v>8022625</v>
       </c>
       <c r="AC28" s="145" t="s">
         <v>44</v>
@@ -39608,67 +39613,71 @@
         <v>48</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="57" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:33" ht="43" x14ac:dyDescent="0.2">
       <c r="A91" s="90">
-        <v>747.3</v>
+        <v>747.24</v>
       </c>
       <c r="B91" s="92">
-        <f t="shared" si="43"/>
-        <v>3</v>
-      </c>
-      <c r="C91" s="109" t="s">
-        <v>694</v>
+        <f>IF(ISNUMBER(A91),IF(AND(A91=INT(A91),MOD(A91,10)=0),0,IF(AND(A91=INT(A91),LEN(A91)=2),1,IF(AND(A91=INT(A91),LEN(A91)=3),2,LEN(A91)-FIND(".",A91)+2))),"")</f>
+        <v>4</v>
+      </c>
+      <c r="C91" s="109" t="inlineStr">
+        <is>
+          <t>Used Fuel Storage Additional Overpacks</t>
+        </is>
       </c>
       <c r="D91" s="93" t="str">
-        <f t="shared" si="44"/>
-        <v xml:space="preserve">                  Annualized Helium Replenishment</v>
+        <f>REPT("   ",B91*2)&amp;C91</f>
+        <v xml:space="preserve">                        Used Fuel Storage Additional Overpacks</v>
       </c>
       <c r="E91" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="F91" s="189" t="s">
-        <v>606</v>
-      </c>
-      <c r="G91" s="94">
-        <v>1</v>
-      </c>
+      <c r="F91" s="93"/>
+      <c r="G91" s="94"/>
       <c r="H91" s="93"/>
       <c r="I91" s="93"/>
       <c r="J91" s="120"/>
       <c r="K91" s="99">
-        <v>170</v>
-      </c>
-      <c r="L91" s="103" t="s">
-        <v>186</v>
-      </c>
-      <c r="M91" s="110" t="s">
-        <v>794</v>
-      </c>
-      <c r="N91" s="103"/>
-      <c r="O91" s="103" t="s">
-        <v>188</v>
-      </c>
-      <c r="P91" s="101"/>
+        <v>200000</v>
+      </c>
+      <c r="L91" s="103" t="inlineStr">
+        <is>
+          <t>$/(reactors/year)</t>
+        </is>
+      </c>
+      <c r="M91" s="110" t="inlineStr">
+        <is>
+          <t>Servicing Rate</t>
+        </is>
+      </c>
+      <c r="N91" s="103">
+        <v>1</v>
+      </c>
+      <c r="O91" s="103" t="inlineStr">
+        <is>
+          <t>reactors/year</t>
+        </is>
+      </c>
+      <c r="P91" s="101">
+        <v>1</v>
+      </c>
       <c r="Q91" s="101">
-        <v>2024</v>
-      </c>
-      <c r="R91" s="103" t="s">
-        <v>153</v>
-      </c>
-      <c r="S91" s="110" t="s">
-        <v>305</v>
-      </c>
-      <c r="T91" s="111" t="s">
-        <v>305</v>
-      </c>
-      <c r="U91" s="182" t="s">
-        <v>306</v>
-      </c>
-      <c r="V91" s="103" t="s">
-        <v>307</v>
-      </c>
-      <c r="W91" s="96" t="s">
-        <v>43</v>
+        <v>2009</v>
+      </c>
+      <c r="R91" s="103" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="S91" s="110"/>
+      <c r="T91" s="111"/>
+      <c r="U91" s="182"/>
+      <c r="V91" s="103"/>
+      <c r="W91" s="96" t="inlineStr">
+        <is>
+          <t>No Learning</t>
+        </is>
       </c>
       <c r="X91" s="104">
         <v>0</v>
@@ -39676,92 +39685,148 @@
       <c r="Y91" s="104">
         <v>0</v>
       </c>
-      <c r="Z91" s="96" t="s">
-        <v>44</v>
+      <c r="Z91" s="96" t="inlineStr">
+        <is>
+          <t>Lognormal</t>
+        </is>
       </c>
       <c r="AA91" s="97">
-        <f>0.9*K91</f>
-        <v>153</v>
+        <f>0.8*K91</f>
+        <v>160000</v>
       </c>
       <c r="AB91" s="97">
-        <f>1.3*K91</f>
-        <v>221</v>
-      </c>
-      <c r="AC91" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD91" s="97" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE91" s="97" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF91" s="97" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG91" s="96" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="92" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+        <f>2*K91</f>
+        <v>400000</v>
+      </c>
+      <c r="AC91" s="96" t="inlineStr">
+        <is>
+          <t>Lognormal</t>
+        </is>
+      </c>
+      <c r="AD91" s="97">
+        <v>0.1</v>
+      </c>
+      <c r="AE91" s="97">
+        <v>1</v>
+      </c>
+      <c r="AF91" s="97">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="96" t="inlineStr">
+        <is>
+          <t>Truncated Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" spans="1:33" ht="57" x14ac:dyDescent="0.2">
       <c r="A92" s="90">
-        <v>747.4</v>
+        <v>747.3</v>
       </c>
       <c r="B92" s="92">
         <f t="shared" si="43"/>
         <v>3</v>
       </c>
       <c r="C92" s="109" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D92" s="93" t="str">
         <f t="shared" si="44"/>
-        <v xml:space="preserve">                  Annualized Other Supplies and Utilities</v>
-      </c>
-      <c r="E92" s="93"/>
-      <c r="F92" s="93"/>
-      <c r="G92" s="94"/>
+        <v xml:space="preserve">                  Annualized Helium Replenishment</v>
+      </c>
+      <c r="E92" s="93" t="s">
+        <v>35</v>
+      </c>
+      <c r="F92" s="189" t="s">
+        <v>606</v>
+      </c>
+      <c r="G92" s="94">
+        <v>1</v>
+      </c>
       <c r="H92" s="93"/>
       <c r="I92" s="93"/>
-      <c r="J92" s="181"/>
-      <c r="K92" s="99"/>
-      <c r="L92" s="103"/>
-      <c r="M92" s="110"/>
+      <c r="J92" s="120"/>
+      <c r="K92" s="99">
+        <v>170</v>
+      </c>
+      <c r="L92" s="103" t="s">
+        <v>186</v>
+      </c>
+      <c r="M92" s="110" t="s">
+        <v>794</v>
+      </c>
       <c r="N92" s="103"/>
-      <c r="O92" s="103"/>
+      <c r="O92" s="103" t="s">
+        <v>188</v>
+      </c>
       <c r="P92" s="101"/>
-      <c r="Q92" s="101"/>
-      <c r="R92" s="103"/>
-      <c r="S92" s="110"/>
-      <c r="T92" s="111"/>
-      <c r="U92" s="182"/>
-      <c r="V92" s="103"/>
-      <c r="W92" s="96"/>
-      <c r="X92" s="104"/>
-      <c r="Y92" s="104"/>
-      <c r="Z92" s="96"/>
-      <c r="AA92" s="97"/>
-      <c r="AB92" s="97"/>
-      <c r="AC92" s="96"/>
-      <c r="AD92" s="97"/>
-      <c r="AE92" s="97"/>
-      <c r="AF92" s="97"/>
-      <c r="AG92" s="96"/>
+      <c r="Q92" s="101">
+        <v>2024</v>
+      </c>
+      <c r="R92" s="103" t="s">
+        <v>153</v>
+      </c>
+      <c r="S92" s="110" t="s">
+        <v>305</v>
+      </c>
+      <c r="T92" s="111" t="s">
+        <v>305</v>
+      </c>
+      <c r="U92" s="182" t="s">
+        <v>306</v>
+      </c>
+      <c r="V92" s="103" t="s">
+        <v>307</v>
+      </c>
+      <c r="W92" s="96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92" s="104">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="104">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA92" s="97">
+        <f>0.9*K91</f>
+        <v>153</v>
+      </c>
+      <c r="AB92" s="97">
+        <f>1.3*K91</f>
+        <v>221</v>
+      </c>
+      <c r="AC92" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD92" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE92" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF92" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG92" s="96" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="93" spans="1:33" ht="15" x14ac:dyDescent="0.2">
       <c r="A93" s="90">
-        <v>747.5</v>
+        <v>747.4</v>
       </c>
       <c r="B93" s="92">
         <f t="shared" si="43"/>
         <v>3</v>
       </c>
       <c r="C93" s="109" t="s">
-        <v>795</v>
+        <v>696</v>
       </c>
       <c r="D93" s="93" t="str">
         <f t="shared" si="44"/>
-        <v xml:space="preserve">                  Servicing Vehicle O&amp;M</v>
+        <v xml:space="preserve">                  Annualized Other Supplies and Utilities</v>
       </c>
       <c r="E93" s="93"/>
       <c r="F93" s="93"/>
@@ -39793,110 +39858,71 @@
       <c r="AF93" s="97"/>
       <c r="AG93" s="96"/>
     </row>
-    <row r="94" spans="1:33" ht="29" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:33" ht="15" x14ac:dyDescent="0.2">
       <c r="A94" s="90">
-        <v>747.51</v>
+        <v>747.5</v>
       </c>
       <c r="B94" s="92">
         <f t="shared" si="43"/>
-        <v>4</v>
-      </c>
-      <c r="C94" s="168" t="s">
-        <v>796</v>
+        <v>3</v>
+      </c>
+      <c r="C94" s="109" t="s">
+        <v>795</v>
       </c>
       <c r="D94" s="93" t="str">
         <f t="shared" si="44"/>
-        <v xml:space="preserve">                        Reactor Transport Vehicles O&amp;M</v>
-      </c>
-      <c r="E94" s="93" t="s">
-        <v>35</v>
-      </c>
-      <c r="F94" s="93" t="s">
-        <v>761</v>
-      </c>
-      <c r="G94" s="94">
-        <v>1</v>
-      </c>
+        <v xml:space="preserve">                  Servicing Vehicle O&amp;M</v>
+      </c>
+      <c r="E94" s="93"/>
+      <c r="F94" s="93"/>
+      <c r="G94" s="94"/>
       <c r="H94" s="93"/>
       <c r="I94" s="93"/>
-      <c r="J94" s="181">
-        <f>36*200000+1000000</f>
-        <v>8200000</v>
-      </c>
+      <c r="J94" s="181"/>
       <c r="K94" s="99"/>
       <c r="L94" s="103"/>
       <c r="M94" s="110"/>
       <c r="N94" s="103"/>
       <c r="O94" s="103"/>
       <c r="P94" s="101"/>
-      <c r="Q94" s="101">
-        <v>2024</v>
-      </c>
-      <c r="R94" s="103" t="s">
-        <v>73</v>
-      </c>
+      <c r="Q94" s="101"/>
+      <c r="R94" s="103"/>
       <c r="S94" s="110"/>
       <c r="T94" s="111"/>
       <c r="U94" s="182"/>
       <c r="V94" s="103"/>
-      <c r="W94" s="96" t="s">
-        <v>43</v>
-      </c>
-      <c r="X94" s="104">
-        <f t="shared" ref="X94:X97" si="83">0.9*$J94</f>
-        <v>7380000</v>
-      </c>
-      <c r="Y94" s="104">
-        <f t="shared" ref="Y94:Y97" si="84">1.5*J94</f>
-        <v>12300000</v>
-      </c>
-      <c r="Z94" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA94" s="97">
-        <f t="shared" ref="AA94:AA97" si="85">0.9*K94</f>
-        <v>0</v>
-      </c>
-      <c r="AB94" s="97">
-        <f t="shared" ref="AB94:AB97" si="86">1.3*K94</f>
-        <v>0</v>
-      </c>
-      <c r="AC94" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD94" s="97" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE94" s="97" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF94" s="97" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG94" s="96" t="s">
-        <v>48</v>
-      </c>
+      <c r="W94" s="96"/>
+      <c r="X94" s="104"/>
+      <c r="Y94" s="104"/>
+      <c r="Z94" s="96"/>
+      <c r="AA94" s="97"/>
+      <c r="AB94" s="97"/>
+      <c r="AC94" s="96"/>
+      <c r="AD94" s="97"/>
+      <c r="AE94" s="97"/>
+      <c r="AF94" s="97"/>
+      <c r="AG94" s="96"/>
     </row>
     <row r="95" spans="1:33" ht="29" x14ac:dyDescent="0.2">
       <c r="A95" s="90">
-        <v>747.52</v>
+        <v>747.51</v>
       </c>
       <c r="B95" s="92">
         <f t="shared" si="43"/>
         <v>4</v>
       </c>
       <c r="C95" s="168" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D95" s="93" t="str">
         <f t="shared" si="44"/>
-        <v xml:space="preserve">                        Helium Transport Trucks O&amp;M</v>
+        <v xml:space="preserve">                        Reactor Transport Vehicles O&amp;M</v>
       </c>
       <c r="E95" s="93" t="s">
         <v>35</v>
       </c>
       <c r="F95" s="93" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G95" s="94">
         <v>1</v>
@@ -39904,8 +39930,8 @@
       <c r="H95" s="93"/>
       <c r="I95" s="93"/>
       <c r="J95" s="181">
-        <f>4*200000+500000</f>
-        <v>1300000</v>
+        <f>36*200000+1000000</f>
+        <v>8200000</v>
       </c>
       <c r="K95" s="99"/>
       <c r="L95" s="103"/>
@@ -39927,22 +39953,22 @@
         <v>43</v>
       </c>
       <c r="X95" s="104">
-        <f t="shared" si="83"/>
-        <v>1170000</v>
+        <f t="shared" ref="X94:X98" si="83">0.9*$J94</f>
+        <v>7380000</v>
       </c>
       <c r="Y95" s="104">
-        <f t="shared" si="84"/>
-        <v>1950000</v>
+        <f t="shared" ref="Y94:Y98" si="84">1.5*J94</f>
+        <v>12300000</v>
       </c>
       <c r="Z95" s="96" t="s">
         <v>44</v>
       </c>
       <c r="AA95" s="97">
-        <f t="shared" si="85"/>
+        <f t="shared" ref="AA94:AA98" si="85">0.9*K94</f>
         <v>0</v>
       </c>
       <c r="AB95" s="97">
-        <f t="shared" si="86"/>
+        <f t="shared" ref="AB94:AB98" si="86">1.3*K94</f>
         <v>0</v>
       </c>
       <c r="AC95" s="96" t="s">
@@ -39963,24 +39989,24 @@
     </row>
     <row r="96" spans="1:33" ht="29" x14ac:dyDescent="0.2">
       <c r="A96" s="90">
-        <v>747.53</v>
+        <v>747.52</v>
       </c>
       <c r="B96" s="92">
         <f t="shared" si="43"/>
         <v>4</v>
       </c>
       <c r="C96" s="168" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D96" s="93" t="str">
         <f t="shared" si="44"/>
-        <v xml:space="preserve">                        Water Tanker Trucks O&amp;M</v>
+        <v xml:space="preserve">                        Helium Transport Trucks O&amp;M</v>
       </c>
       <c r="E96" s="93" t="s">
         <v>35</v>
       </c>
       <c r="F96" s="93" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G96" s="94">
         <v>1</v>
@@ -39988,8 +40014,8 @@
       <c r="H96" s="93"/>
       <c r="I96" s="93"/>
       <c r="J96" s="181">
-        <f>4*200000+400000</f>
-        <v>1200000</v>
+        <f>4*200000+500000</f>
+        <v>1300000</v>
       </c>
       <c r="K96" s="99"/>
       <c r="L96" s="103"/>
@@ -40012,11 +40038,11 @@
       </c>
       <c r="X96" s="104">
         <f t="shared" si="83"/>
-        <v>1080000</v>
+        <v>1170000</v>
       </c>
       <c r="Y96" s="104">
         <f t="shared" si="84"/>
-        <v>1800000</v>
+        <v>1950000</v>
       </c>
       <c r="Z96" s="96" t="s">
         <v>44</v>
@@ -40047,24 +40073,24 @@
     </row>
     <row r="97" spans="1:33" ht="29" x14ac:dyDescent="0.2">
       <c r="A97" s="90">
-        <v>747.54</v>
+        <v>747.53</v>
       </c>
       <c r="B97" s="92">
         <f t="shared" si="43"/>
         <v>4</v>
       </c>
       <c r="C97" s="168" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D97" s="93" t="str">
         <f t="shared" si="44"/>
-        <v xml:space="preserve">                        Maintenance Trucks O&amp;M</v>
+        <v xml:space="preserve">                        Water Tanker Trucks O&amp;M</v>
       </c>
       <c r="E97" s="93" t="s">
         <v>35</v>
       </c>
       <c r="F97" s="93" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G97" s="94">
         <v>1</v>
@@ -40072,8 +40098,8 @@
       <c r="H97" s="93"/>
       <c r="I97" s="93"/>
       <c r="J97" s="181">
-        <f>10*2*200000+1000000</f>
-        <v>5000000</v>
+        <f>4*200000+400000</f>
+        <v>1200000</v>
       </c>
       <c r="K97" s="99"/>
       <c r="L97" s="103"/>
@@ -40096,11 +40122,11 @@
       </c>
       <c r="X97" s="104">
         <f t="shared" si="83"/>
-        <v>4500000</v>
+        <v>1080000</v>
       </c>
       <c r="Y97" s="104">
         <f t="shared" si="84"/>
-        <v>7500000</v>
+        <v>1800000</v>
       </c>
       <c r="Z97" s="96" t="s">
         <v>44</v>
@@ -40129,65 +40155,104 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:33" ht="29" x14ac:dyDescent="0.2">
       <c r="A98" s="90">
-        <v>75</v>
+        <v>747.54</v>
       </c>
       <c r="B98" s="92">
         <f t="shared" si="43"/>
-        <v>1</v>
-      </c>
-      <c r="C98" s="109" t="s">
-        <v>402</v>
+        <v>4</v>
+      </c>
+      <c r="C98" s="168" t="s">
+        <v>799</v>
       </c>
       <c r="D98" s="93" t="str">
         <f t="shared" si="44"/>
-        <v xml:space="preserve">      Capital Plant Expenditures</v>
-      </c>
-      <c r="E98" s="93"/>
-      <c r="F98" s="93"/>
-      <c r="G98" s="113"/>
-      <c r="H98" s="114"/>
-      <c r="I98" s="114"/>
-      <c r="J98" s="192"/>
-      <c r="K98" s="115"/>
-      <c r="L98" s="116"/>
-      <c r="M98" s="116"/>
-      <c r="N98" s="116"/>
-      <c r="O98" s="116"/>
-      <c r="P98" s="115"/>
-      <c r="Q98" s="116"/>
-      <c r="R98" s="116"/>
-      <c r="S98" s="116"/>
-      <c r="T98" s="116"/>
-      <c r="U98" s="116"/>
-      <c r="V98" s="116"/>
-      <c r="W98" s="116"/>
-      <c r="X98" s="115"/>
-      <c r="Y98" s="115"/>
-      <c r="Z98" s="116"/>
-      <c r="AA98" s="115"/>
-      <c r="AB98" s="115"/>
-      <c r="AC98" s="116"/>
-      <c r="AD98" s="115"/>
-      <c r="AE98" s="115"/>
-      <c r="AF98" s="115"/>
-      <c r="AG98" s="116"/>
+        <v xml:space="preserve">                        Maintenance Trucks O&amp;M</v>
+      </c>
+      <c r="E98" s="93" t="s">
+        <v>35</v>
+      </c>
+      <c r="F98" s="93" t="s">
+        <v>767</v>
+      </c>
+      <c r="G98" s="94">
+        <v>1</v>
+      </c>
+      <c r="H98" s="93"/>
+      <c r="I98" s="93"/>
+      <c r="J98" s="181">
+        <f>10*2*200000+1000000</f>
+        <v>5000000</v>
+      </c>
+      <c r="K98" s="99"/>
+      <c r="L98" s="103"/>
+      <c r="M98" s="110"/>
+      <c r="N98" s="103"/>
+      <c r="O98" s="103"/>
+      <c r="P98" s="101"/>
+      <c r="Q98" s="101">
+        <v>2024</v>
+      </c>
+      <c r="R98" s="103" t="s">
+        <v>73</v>
+      </c>
+      <c r="S98" s="110"/>
+      <c r="T98" s="111"/>
+      <c r="U98" s="182"/>
+      <c r="V98" s="103"/>
+      <c r="W98" s="96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98" s="104">
+        <f t="shared" si="83"/>
+        <v>4500000</v>
+      </c>
+      <c r="Y98" s="104">
+        <f t="shared" si="84"/>
+        <v>7500000</v>
+      </c>
+      <c r="Z98" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA98" s="97">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="AB98" s="97">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="AC98" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD98" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE98" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF98" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG98" s="96" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="99" spans="1:33" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="90">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B99" s="92">
         <f t="shared" si="43"/>
         <v>1</v>
       </c>
       <c r="C99" s="109" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="D99" s="93" t="str">
         <f t="shared" si="44"/>
-        <v xml:space="preserve">      Annualized Decommissioning Cost</v>
+        <v xml:space="preserve">      Capital Plant Expenditures</v>
       </c>
       <c r="E99" s="93"/>
       <c r="F99" s="93"/>
@@ -40218,6 +40283,51 @@
       <c r="AE99" s="115"/>
       <c r="AF99" s="115"/>
       <c r="AG99" s="116"/>
+    </row>
+    <row r="100" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+      <c r="A100" s="90">
+        <v>78</v>
+      </c>
+      <c r="B100" s="92">
+        <f t="shared" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="C100" s="109" t="s">
+        <v>420</v>
+      </c>
+      <c r="D100" s="93" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">      Annualized Decommissioning Cost</v>
+      </c>
+      <c r="E100" s="93"/>
+      <c r="F100" s="93"/>
+      <c r="G100" s="113"/>
+      <c r="H100" s="114"/>
+      <c r="I100" s="114"/>
+      <c r="J100" s="192"/>
+      <c r="K100" s="115"/>
+      <c r="L100" s="116"/>
+      <c r="M100" s="116"/>
+      <c r="N100" s="116"/>
+      <c r="O100" s="116"/>
+      <c r="P100" s="115"/>
+      <c r="Q100" s="116"/>
+      <c r="R100" s="116"/>
+      <c r="S100" s="116"/>
+      <c r="T100" s="116"/>
+      <c r="U100" s="116"/>
+      <c r="V100" s="116"/>
+      <c r="W100" s="116"/>
+      <c r="X100" s="115"/>
+      <c r="Y100" s="115"/>
+      <c r="Z100" s="116"/>
+      <c r="AA100" s="115"/>
+      <c r="AB100" s="115"/>
+      <c r="AC100" s="116"/>
+      <c r="AD100" s="115"/>
+      <c r="AE100" s="115"/>
+      <c r="AF100" s="115"/>
+      <c r="AG100" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -40271,17 +40381,17 @@
       <formula>$B2=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:AG99">
+  <conditionalFormatting sqref="A2:AG100">
     <cfRule type="expression" dxfId="39" priority="12">
       <formula>$B2=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C94:C97">
+  <conditionalFormatting sqref="C94:C98">
     <cfRule type="expression" dxfId="38" priority="7">
       <formula>$B94=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F94:F97">
+  <conditionalFormatting sqref="F94:F98">
     <cfRule type="expression" dxfId="37" priority="6">
       <formula>$B94=0</formula>
     </cfRule>
@@ -40419,31 +40529,31 @@
       <formula>$B82=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W94:AG97">
+  <conditionalFormatting sqref="W94:AG98">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$B94=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Z99">
+  <conditionalFormatting sqref="X2:Z100">
     <cfRule type="expression" dxfId="2" priority="51">
       <formula>AND(ISBLANK($X2),ISBLANK($Y2),ISBLANK($Z2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AC99">
+  <conditionalFormatting sqref="AA2:AC100">
     <cfRule type="expression" dxfId="1" priority="50">
       <formula>AND(ISBLANK($AA2),ISBLANK($AB2),ISBLANK($AC2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AG99">
+  <conditionalFormatting sqref="AD2:AG100">
     <cfRule type="expression" dxfId="0" priority="49">
       <formula>AND(ISBLANK($AD2),ISBLANK($AE2),ISBLANK($AF2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E99" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E100" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"standard, nonstandard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O99" xr:uid="{00000000-0002-0000-0600-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O100" xr:uid="{00000000-0002-0000-0600-000001000000}">
       <formula1>"acres,MWe,m^3,MWt,Kg,Drums,kW,$,m^2,kg/s,Rx/yr"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R90:R97 R2:R88" xr:uid="{00000000-0002-0000-0600-000002000000}">
@@ -40466,13 +40576,13 @@
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K9 K11:K31 K33:K97 N1:N1048576" xr:uid="{00000000-0002-0000-0600-000007000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M272:M282" xr:uid="{00000000-0002-0000-0600-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M272:M283" xr:uid="{00000000-0002-0000-0600-000008000000}">
       <formula1>"Land Area, Power MWe, Excavation Volume,  Reactor Building Slab Roof Volume,	Reactor Building  Basement Volume, Reactor Building  Exterior Walls Volume,		Turbine Building Slab Roof Volume,	Turbine Building  Basement Volume,	Turbine Building  Exterior Wall"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 L100:L1048576" xr:uid="{00000000-0002-0000-0600-000009000000}">
       <formula1>"$/acres, $/MWe, $/m^3, $/MWt"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P100:P251" xr:uid="{00000000-0002-0000-0600-00000A000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P100:P252" xr:uid="{00000000-0002-0000-0600-00000A000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannbn/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{856AC7A1-0F71-8C45-AAE1-4260C3605B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2FB290-26B1-554A-A94D-44F6D4F1EC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cost Database" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,6 @@
     <definedName name="UC_m_in">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -693,7 +692,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3756" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3758" uniqueCount="821">
   <si>
     <t>Account</t>
   </si>
@@ -4285,42 +4284,55 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4344,26 +4356,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4376,20 +4375,52 @@
     <cellStyle name="Normal 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Normal 2 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="442">
+  <dxfs count="418">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4401,7 +4432,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4422,7 +4453,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4438,29 +4476,9 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4472,35 +4490,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4516,15 +4506,9 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4536,6 +4520,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -4543,48 +4534,9 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4594,6 +4546,11 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
@@ -4603,7 +4560,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4617,6 +4574,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -4627,6 +4591,11 @@
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -4640,42 +4609,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4689,6 +4623,40 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
@@ -4719,7 +4687,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4731,14 +4699,11 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -4750,6 +4715,39 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -4758,6 +4756,41 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4773,14 +4806,16 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4792,21 +4827,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79992065187536243"/>
@@ -4830,7 +4850,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4844,9 +4864,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4877,27 +4916,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
       </font>
@@ -4919,7 +4937,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4934,41 +4952,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4984,23 +4967,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -5014,9 +4988,21 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -5054,16 +5040,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
@@ -5073,7 +5049,21 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5094,7 +5084,21 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5106,6 +5110,18 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
@@ -5115,9 +5131,728 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -5129,16 +5864,41 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray0625"/>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -5152,7 +5912,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5171,14 +5931,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5192,42 +5952,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5243,15 +5968,9 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -5263,14 +5982,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5284,6 +5996,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -5291,7 +6010,120 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5305,6 +6137,18 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
@@ -5319,10 +6163,11 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -5335,751 +6180,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6100,6 +6200,53 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i/>
@@ -6109,53 +6256,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i/>
@@ -6165,27 +6265,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i/>
@@ -6195,287 +6274,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i/>
@@ -6487,16 +6285,350 @@
     <dxf>
       <font>
         <b/>
-        <i/>
       </font>
+    </dxf>
+    <dxf>
       <fill>
-        <patternFill patternType="gray125"/>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -6510,7 +6642,18 @@
     <dxf>
       <font>
         <b/>
+        <i/>
       </font>
+      <fill>
+        <patternFill patternType="gray0625"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -6522,7 +6665,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6536,7 +6679,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6550,14 +6693,16 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -6567,6 +6712,11 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
@@ -6574,11 +6724,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
@@ -6609,7 +6754,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6621,14 +6766,11 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -6640,6 +6782,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -6668,7 +6817,52 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6682,7 +6876,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6696,6 +6890,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -6717,9 +6918,48 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -6729,11 +6969,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
@@ -6748,6 +6983,44 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79992065187536243"/>
@@ -6755,6 +7028,11 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
@@ -6778,9 +7056,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -6804,6 +7087,11 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
@@ -6818,11 +7106,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
@@ -6830,6 +7113,25 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79992065187536243"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
@@ -6837,6 +7139,18 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79992065187536243"/>
@@ -6844,6 +7158,40 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79992065187536243"/>
@@ -6851,21 +7199,10 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
       <fill>
-        <patternFill patternType="gray0625"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray0625"/>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -6878,516 +7215,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79992065187536243"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7582,6 +7410,60 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{335E1344-0016-F7AC-577D-9A5B9731F579}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{154C3AE1-AFC7-B5EB-F6D5-A7763ABF5DD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7833,6 +7715,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>584200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5DFB71D-AB1C-DC0E-E2DE-BC70AEE47C11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8014,6 +7950,60 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0F0495A-DF4D-D90B-BFCF-FF48EB22C229}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1FE3D30-98A5-5937-305E-816C0A8B486C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8811,7 +8801,7 @@
       <c r="T3" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="U3" s="218" t="s">
+      <c r="U3" s="225" t="s">
         <v>42</v>
       </c>
       <c r="V3" s="49"/>
@@ -8907,8 +8897,8 @@
       <c r="S4" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
       <c r="V4" s="49"/>
       <c r="W4" s="74" t="s">
         <v>43</v>
@@ -8999,7 +8989,7 @@
       <c r="T5" s="201" t="s">
         <v>57</v>
       </c>
-      <c r="U5" s="218" t="s">
+      <c r="U5" s="225" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="49"/>
@@ -9091,7 +9081,7 @@
       <c r="T6" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="U6" s="214"/>
+      <c r="U6" s="217"/>
       <c r="V6" s="49"/>
       <c r="W6" s="74" t="s">
         <v>43</v>
@@ -9439,7 +9429,7 @@
       <c r="T11" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="213" t="s">
+      <c r="U11" s="222" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="49"/>
@@ -9532,9 +9522,9 @@
       <c r="R12" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="S12" s="212"/>
-      <c r="T12" s="212"/>
-      <c r="U12" s="212"/>
+      <c r="S12" s="216"/>
+      <c r="T12" s="216"/>
+      <c r="U12" s="216"/>
       <c r="V12" s="49"/>
       <c r="W12" s="74" t="s">
         <v>77</v>
@@ -9625,9 +9615,9 @@
       <c r="R13" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="S13" s="214"/>
-      <c r="T13" s="214"/>
-      <c r="U13" s="214"/>
+      <c r="S13" s="217"/>
+      <c r="T13" s="217"/>
+      <c r="U13" s="217"/>
       <c r="V13" s="49"/>
       <c r="W13" s="74" t="s">
         <v>77</v>
@@ -9667,8 +9657,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:33" s="238" customFormat="1" ht="43" x14ac:dyDescent="0.2">
-      <c r="A14" s="232">
+    <row r="14" spans="1:33" s="213" customFormat="1" ht="43" x14ac:dyDescent="0.2">
+      <c r="A14" s="207">
         <v>211.4</v>
       </c>
       <c r="B14" s="38">
@@ -9682,20 +9672,20 @@
 "")</f>
         <v>3</v>
       </c>
-      <c r="C14" s="233" t="s">
+      <c r="C14" s="208" t="s">
         <v>613</v>
       </c>
-      <c r="D14" s="234" t="str">
+      <c r="D14" s="209" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">                  Roads</v>
       </c>
-      <c r="E14" s="235" t="s">
+      <c r="E14" s="210" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="235"/>
-      <c r="G14" s="235"/>
-      <c r="H14" s="235"/>
-      <c r="I14" s="235"/>
+      <c r="F14" s="210"/>
+      <c r="G14" s="210"/>
+      <c r="H14" s="210"/>
+      <c r="I14" s="210"/>
       <c r="J14" s="43"/>
       <c r="K14" s="44">
         <f>0.7*7873200*1.609/1000</f>
@@ -9715,14 +9705,14 @@
       <c r="Q14" s="65">
         <v>2025</v>
       </c>
-      <c r="R14" s="236" t="s">
+      <c r="R14" s="211" t="s">
         <v>39</v>
       </c>
       <c r="S14" s="130" t="s">
         <v>616</v>
       </c>
       <c r="T14" s="47"/>
-      <c r="U14" s="237"/>
+      <c r="U14" s="212"/>
       <c r="V14" s="49"/>
       <c r="W14" s="74" t="s">
         <v>77</v>
@@ -9762,26 +9752,26 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:33" s="238" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="232">
+    <row r="15" spans="1:33" s="213" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="207">
         <v>211.9</v>
       </c>
       <c r="B15" s="38">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="C15" s="239" t="s">
+      <c r="C15" s="214" t="s">
         <v>617</v>
       </c>
-      <c r="D15" s="235" t="str">
+      <c r="D15" s="210" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">                  Security Fencing</v>
       </c>
-      <c r="E15" s="235"/>
-      <c r="F15" s="235"/>
-      <c r="G15" s="235"/>
-      <c r="H15" s="235"/>
-      <c r="I15" s="235"/>
+      <c r="E15" s="210"/>
+      <c r="F15" s="210"/>
+      <c r="G15" s="210"/>
+      <c r="H15" s="210"/>
+      <c r="I15" s="210"/>
       <c r="J15" s="43"/>
       <c r="K15" s="44"/>
       <c r="L15" s="45"/>
@@ -9790,10 +9780,10 @@
       <c r="O15" s="45"/>
       <c r="P15" s="46"/>
       <c r="Q15" s="65"/>
-      <c r="R15" s="236"/>
+      <c r="R15" s="211"/>
       <c r="S15" s="47"/>
       <c r="T15" s="47"/>
-      <c r="U15" s="237"/>
+      <c r="U15" s="212"/>
       <c r="V15" s="49"/>
       <c r="W15" s="74"/>
       <c r="X15" s="77"/>
@@ -9807,28 +9797,28 @@
       <c r="AF15" s="76"/>
       <c r="AG15" s="74"/>
     </row>
-    <row r="16" spans="1:33" s="238" customFormat="1" ht="43" x14ac:dyDescent="0.2">
-      <c r="A16" s="232">
+    <row r="16" spans="1:33" s="213" customFormat="1" ht="43" x14ac:dyDescent="0.2">
+      <c r="A16" s="207">
         <v>211.91</v>
       </c>
       <c r="B16" s="38">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="C16" s="239" t="s">
+      <c r="C16" s="214" t="s">
         <v>618</v>
       </c>
-      <c r="D16" s="235" t="str">
+      <c r="D16" s="210" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">                        Security Fencing Limited</v>
       </c>
-      <c r="E16" s="235" t="s">
+      <c r="E16" s="210" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="235"/>
-      <c r="G16" s="235"/>
-      <c r="H16" s="235"/>
-      <c r="I16" s="235"/>
+      <c r="F16" s="210"/>
+      <c r="G16" s="210"/>
+      <c r="H16" s="210"/>
+      <c r="I16" s="210"/>
       <c r="J16" s="43"/>
       <c r="K16" s="44">
         <f>0.47*273*3.2808</f>
@@ -9848,12 +9838,14 @@
       <c r="Q16" s="65">
         <v>2025</v>
       </c>
-      <c r="R16" s="236"/>
+      <c r="R16" s="211" t="s">
+        <v>39</v>
+      </c>
       <c r="S16" s="130" t="s">
         <v>616</v>
       </c>
       <c r="T16" s="47"/>
-      <c r="U16" s="237"/>
+      <c r="U16" s="212"/>
       <c r="V16" s="49"/>
       <c r="W16" s="74" t="s">
         <v>77</v>
@@ -9893,28 +9885,28 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:33" s="238" customFormat="1" ht="43" x14ac:dyDescent="0.2">
-      <c r="A17" s="232">
-        <v>211.93</v>
+    <row r="17" spans="1:33" s="213" customFormat="1" ht="43" x14ac:dyDescent="0.2">
+      <c r="A17" s="207">
+        <v>211.92</v>
       </c>
       <c r="B17" s="38">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="C17" s="239" t="s">
+      <c r="C17" s="214" t="s">
         <v>621</v>
       </c>
-      <c r="D17" s="235" t="str">
+      <c r="D17" s="210" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">                        Security Fencing Protected</v>
       </c>
-      <c r="E17" s="235" t="s">
+      <c r="E17" s="210" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="235"/>
-      <c r="G17" s="235"/>
-      <c r="H17" s="235"/>
-      <c r="I17" s="235"/>
+      <c r="F17" s="210"/>
+      <c r="G17" s="210"/>
+      <c r="H17" s="210"/>
+      <c r="I17" s="210"/>
       <c r="J17" s="43"/>
       <c r="K17" s="44">
         <f>0.7*15746*3.2808</f>
@@ -9934,12 +9926,14 @@
       <c r="Q17" s="65">
         <v>2025</v>
       </c>
-      <c r="R17" s="236"/>
+      <c r="R17" s="211" t="s">
+        <v>39</v>
+      </c>
       <c r="S17" s="130" t="s">
         <v>616</v>
       </c>
       <c r="T17" s="47"/>
-      <c r="U17" s="237"/>
+      <c r="U17" s="212"/>
       <c r="V17" s="49"/>
       <c r="W17" s="74" t="s">
         <v>77</v>
@@ -10074,7 +10068,7 @@
       <c r="T19" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U19" s="213" t="s">
+      <c r="U19" s="222" t="s">
         <v>76</v>
       </c>
       <c r="V19" s="49"/>
@@ -10160,9 +10154,9 @@
       <c r="R20" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S20" s="212"/>
-      <c r="T20" s="212"/>
-      <c r="U20" s="212"/>
+      <c r="S20" s="216"/>
+      <c r="T20" s="216"/>
+      <c r="U20" s="216"/>
       <c r="V20" s="49"/>
       <c r="W20" s="74" t="s">
         <v>77</v>
@@ -10246,9 +10240,9 @@
       <c r="R21" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S21" s="214"/>
-      <c r="T21" s="214"/>
-      <c r="U21" s="214"/>
+      <c r="S21" s="217"/>
+      <c r="T21" s="217"/>
+      <c r="U21" s="217"/>
       <c r="V21" s="49"/>
       <c r="W21" s="74" t="s">
         <v>77</v>
@@ -10620,7 +10614,7 @@
       <c r="T26" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U26" s="213" t="s">
+      <c r="U26" s="222" t="s">
         <v>76</v>
       </c>
       <c r="V26" s="49"/>
@@ -10706,9 +10700,9 @@
       <c r="R27" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S27" s="212"/>
-      <c r="T27" s="212"/>
-      <c r="U27" s="212"/>
+      <c r="S27" s="216"/>
+      <c r="T27" s="216"/>
+      <c r="U27" s="216"/>
       <c r="V27" s="49"/>
       <c r="W27" s="74" t="s">
         <v>77</v>
@@ -10792,9 +10786,9 @@
       <c r="R28" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S28" s="214"/>
-      <c r="T28" s="214"/>
-      <c r="U28" s="214"/>
+      <c r="S28" s="217"/>
+      <c r="T28" s="217"/>
+      <c r="U28" s="217"/>
       <c r="V28" s="49"/>
       <c r="W28" s="74" t="s">
         <v>77</v>
@@ -10929,7 +10923,7 @@
       <c r="T30" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U30" s="213" t="s">
+      <c r="U30" s="222" t="s">
         <v>76</v>
       </c>
       <c r="V30" s="49"/>
@@ -11015,9 +11009,9 @@
       <c r="R31" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S31" s="212"/>
-      <c r="T31" s="212"/>
-      <c r="U31" s="212"/>
+      <c r="S31" s="216"/>
+      <c r="T31" s="216"/>
+      <c r="U31" s="216"/>
       <c r="V31" s="49"/>
       <c r="W31" s="74" t="s">
         <v>77</v>
@@ -11101,9 +11095,9 @@
       <c r="R32" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S32" s="214"/>
-      <c r="T32" s="214"/>
-      <c r="U32" s="214"/>
+      <c r="S32" s="217"/>
+      <c r="T32" s="217"/>
+      <c r="U32" s="217"/>
       <c r="V32" s="49"/>
       <c r="W32" s="74" t="s">
         <v>77</v>
@@ -11246,7 +11240,7 @@
       <c r="T34" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U34" s="213" t="s">
+      <c r="U34" s="222" t="s">
         <v>76</v>
       </c>
       <c r="V34" s="49"/>
@@ -11336,9 +11330,9 @@
       <c r="R35" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S35" s="212"/>
-      <c r="T35" s="212"/>
-      <c r="U35" s="212"/>
+      <c r="S35" s="216"/>
+      <c r="T35" s="216"/>
+      <c r="U35" s="216"/>
       <c r="V35" s="49"/>
       <c r="W35" s="74" t="s">
         <v>77</v>
@@ -11426,9 +11420,9 @@
       <c r="R36" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S36" s="214"/>
-      <c r="T36" s="214"/>
-      <c r="U36" s="214"/>
+      <c r="S36" s="217"/>
+      <c r="T36" s="217"/>
+      <c r="U36" s="217"/>
       <c r="V36" s="49"/>
       <c r="W36" s="74" t="s">
         <v>77</v>
@@ -11753,7 +11747,7 @@
       <c r="T41" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U41" s="213" t="s">
+      <c r="U41" s="222" t="s">
         <v>76</v>
       </c>
       <c r="V41" s="49"/>
@@ -11837,9 +11831,9 @@
       <c r="R42" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S42" s="212"/>
-      <c r="T42" s="212"/>
-      <c r="U42" s="212"/>
+      <c r="S42" s="216"/>
+      <c r="T42" s="216"/>
+      <c r="U42" s="216"/>
       <c r="V42" s="49"/>
       <c r="W42" s="74" t="s">
         <v>77</v>
@@ -11923,9 +11917,9 @@
       <c r="R43" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S43" s="214"/>
-      <c r="T43" s="214"/>
-      <c r="U43" s="214"/>
+      <c r="S43" s="217"/>
+      <c r="T43" s="217"/>
+      <c r="U43" s="217"/>
       <c r="V43" s="49"/>
       <c r="W43" s="74" t="s">
         <v>77</v>
@@ -12060,7 +12054,7 @@
       <c r="T45" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U45" s="213" t="s">
+      <c r="U45" s="222" t="s">
         <v>76</v>
       </c>
       <c r="V45" s="49"/>
@@ -12146,9 +12140,9 @@
       <c r="R46" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S46" s="212"/>
-      <c r="T46" s="212"/>
-      <c r="U46" s="212"/>
+      <c r="S46" s="216"/>
+      <c r="T46" s="216"/>
+      <c r="U46" s="216"/>
       <c r="V46" s="49"/>
       <c r="W46" s="74" t="s">
         <v>77</v>
@@ -12232,9 +12226,9 @@
       <c r="R47" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S47" s="214"/>
-      <c r="T47" s="214"/>
-      <c r="U47" s="214"/>
+      <c r="S47" s="217"/>
+      <c r="T47" s="217"/>
+      <c r="U47" s="217"/>
       <c r="V47" s="49"/>
       <c r="W47" s="74" t="s">
         <v>77</v>
@@ -12421,7 +12415,7 @@
       <c r="T50" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U50" s="213" t="s">
+      <c r="U50" s="222" t="s">
         <v>76</v>
       </c>
       <c r="V50" s="49"/>
@@ -12507,9 +12501,9 @@
       <c r="R51" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S51" s="212"/>
-      <c r="T51" s="212"/>
-      <c r="U51" s="212"/>
+      <c r="S51" s="216"/>
+      <c r="T51" s="216"/>
+      <c r="U51" s="216"/>
       <c r="V51" s="49"/>
       <c r="W51" s="74" t="s">
         <v>77</v>
@@ -12593,9 +12587,9 @@
       <c r="R52" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S52" s="214"/>
-      <c r="T52" s="214"/>
-      <c r="U52" s="214"/>
+      <c r="S52" s="217"/>
+      <c r="T52" s="217"/>
+      <c r="U52" s="217"/>
       <c r="V52" s="49"/>
       <c r="W52" s="74" t="s">
         <v>77</v>
@@ -12872,10 +12866,10 @@
       <c r="T56" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U56" s="213" t="s">
+      <c r="U56" s="222" t="s">
         <v>76</v>
       </c>
-      <c r="V56" s="221" t="s">
+      <c r="V56" s="224" t="s">
         <v>162</v>
       </c>
       <c r="W56" s="74" t="s">
@@ -12960,10 +12954,10 @@
       <c r="R57" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S57" s="212"/>
-      <c r="T57" s="212"/>
-      <c r="U57" s="212"/>
-      <c r="V57" s="212"/>
+      <c r="S57" s="216"/>
+      <c r="T57" s="216"/>
+      <c r="U57" s="216"/>
+      <c r="V57" s="216"/>
       <c r="W57" s="74" t="s">
         <v>77</v>
       </c>
@@ -13046,10 +13040,10 @@
       <c r="R58" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S58" s="214"/>
-      <c r="T58" s="214"/>
-      <c r="U58" s="214"/>
-      <c r="V58" s="214"/>
+      <c r="S58" s="217"/>
+      <c r="T58" s="217"/>
+      <c r="U58" s="217"/>
+      <c r="V58" s="217"/>
       <c r="W58" s="74" t="s">
         <v>77</v>
       </c>
@@ -13228,7 +13222,7 @@
       <c r="T61" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U61" s="213" t="s">
+      <c r="U61" s="222" t="s">
         <v>76</v>
       </c>
       <c r="V61" s="49"/>
@@ -13314,9 +13308,9 @@
       <c r="R62" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S62" s="212"/>
-      <c r="T62" s="212"/>
-      <c r="U62" s="212"/>
+      <c r="S62" s="216"/>
+      <c r="T62" s="216"/>
+      <c r="U62" s="216"/>
       <c r="V62" s="49"/>
       <c r="W62" s="74" t="s">
         <v>77</v>
@@ -13400,9 +13394,9 @@
       <c r="R63" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S63" s="214"/>
-      <c r="T63" s="214"/>
-      <c r="U63" s="214"/>
+      <c r="S63" s="217"/>
+      <c r="T63" s="217"/>
+      <c r="U63" s="217"/>
       <c r="V63" s="49"/>
       <c r="W63" s="74" t="s">
         <v>77</v>
@@ -13537,7 +13531,7 @@
       <c r="T65" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="U65" s="213" t="s">
+      <c r="U65" s="222" t="s">
         <v>76</v>
       </c>
       <c r="V65" s="49"/>
@@ -13623,9 +13617,9 @@
       <c r="R66" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S66" s="212"/>
-      <c r="T66" s="212"/>
-      <c r="U66" s="212"/>
+      <c r="S66" s="216"/>
+      <c r="T66" s="216"/>
+      <c r="U66" s="216"/>
       <c r="V66" s="49"/>
       <c r="W66" s="74" t="s">
         <v>77</v>
@@ -13709,9 +13703,9 @@
       <c r="R67" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S67" s="214"/>
-      <c r="T67" s="214"/>
-      <c r="U67" s="214"/>
+      <c r="S67" s="217"/>
+      <c r="T67" s="217"/>
+      <c r="U67" s="217"/>
       <c r="V67" s="49"/>
       <c r="W67" s="74" t="s">
         <v>77</v>
@@ -14035,7 +14029,7 @@
       <c r="S72" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T72" s="216" t="s">
+      <c r="T72" s="220" t="s">
         <v>197</v>
       </c>
       <c r="U72" s="55"/>
@@ -14126,7 +14120,7 @@
       <c r="S73" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T73" s="212"/>
+      <c r="T73" s="216"/>
       <c r="U73" s="55"/>
       <c r="V73" s="49"/>
       <c r="W73" s="74" t="s">
@@ -14222,7 +14216,7 @@
       <c r="S74" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T74" s="212"/>
+      <c r="T74" s="216"/>
       <c r="U74" s="55"/>
       <c r="V74" s="49"/>
       <c r="W74" s="74" t="s">
@@ -14325,7 +14319,7 @@
       <c r="S75" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T75" s="212"/>
+      <c r="T75" s="216"/>
       <c r="U75" s="55"/>
       <c r="V75" s="58" t="s">
         <v>203</v>
@@ -14423,7 +14417,7 @@
       <c r="S76" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T76" s="212"/>
+      <c r="T76" s="216"/>
       <c r="U76" s="55"/>
       <c r="V76" s="58"/>
       <c r="W76" s="74" t="s">
@@ -14519,7 +14513,7 @@
       <c r="S77" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="T77" s="214"/>
+      <c r="T77" s="217"/>
       <c r="U77" s="55"/>
       <c r="V77" s="58"/>
       <c r="W77" s="74" t="s">
@@ -14716,10 +14710,10 @@
       <c r="S80" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="T80" s="216" t="s">
+      <c r="T80" s="220" t="s">
         <v>210</v>
       </c>
-      <c r="U80" s="217" t="s">
+      <c r="U80" s="226" t="s">
         <v>211</v>
       </c>
       <c r="V80" s="58" t="s">
@@ -14815,8 +14809,8 @@
       <c r="S81" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="T81" s="212"/>
-      <c r="U81" s="212"/>
+      <c r="T81" s="216"/>
+      <c r="U81" s="216"/>
       <c r="V81" s="49"/>
       <c r="W81" s="74" t="s">
         <v>213</v>
@@ -14919,8 +14913,8 @@
       <c r="S82" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="T82" s="212"/>
-      <c r="U82" s="212"/>
+      <c r="T82" s="216"/>
+      <c r="U82" s="216"/>
       <c r="V82" s="49"/>
       <c r="W82" s="74" t="s">
         <v>157</v>
@@ -15015,8 +15009,8 @@
       <c r="S83" s="58" t="s">
         <v>221</v>
       </c>
-      <c r="T83" s="212"/>
-      <c r="U83" s="212"/>
+      <c r="T83" s="216"/>
+      <c r="U83" s="216"/>
       <c r="V83" s="49"/>
       <c r="W83" s="74" t="s">
         <v>157</v>
@@ -15119,8 +15113,8 @@
       <c r="S84" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="T84" s="214"/>
-      <c r="U84" s="214"/>
+      <c r="T84" s="217"/>
+      <c r="U84" s="217"/>
       <c r="V84" s="49"/>
       <c r="W84" s="74" t="s">
         <v>226</v>
@@ -15690,7 +15684,7 @@
       <c r="T90" s="204" t="s">
         <v>809</v>
       </c>
-      <c r="U90" s="212"/>
+      <c r="U90" s="216"/>
       <c r="V90" s="49" t="s">
         <v>810</v>
       </c>
@@ -15762,7 +15756,7 @@
       <c r="R91" s="49"/>
       <c r="S91" s="58"/>
       <c r="T91" s="49"/>
-      <c r="U91" s="211"/>
+      <c r="U91" s="219"/>
       <c r="V91" s="49"/>
       <c r="W91" s="74"/>
       <c r="X91" s="77"/>
@@ -15814,7 +15808,7 @@
       <c r="R92" s="49"/>
       <c r="S92" s="58"/>
       <c r="T92" s="58"/>
-      <c r="U92" s="211"/>
+      <c r="U92" s="219"/>
       <c r="V92" s="49"/>
       <c r="W92" s="74"/>
       <c r="X92" s="77"/>
@@ -15897,7 +15891,7 @@
       <c r="T93" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="U93" s="217" t="s">
+      <c r="U93" s="226" t="s">
         <v>211</v>
       </c>
       <c r="V93" s="49"/>
@@ -16005,7 +15999,7 @@
       <c r="T94" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="U94" s="212"/>
+      <c r="U94" s="216"/>
       <c r="V94" s="49"/>
       <c r="W94" s="74" t="s">
         <v>226</v>
@@ -16104,7 +16098,7 @@
       <c r="T95" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="U95" s="212"/>
+      <c r="U95" s="216"/>
       <c r="V95" s="49"/>
       <c r="W95" s="74" t="s">
         <v>228</v>
@@ -16201,7 +16195,7 @@
       <c r="T96" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="U96" s="212"/>
+      <c r="U96" s="216"/>
       <c r="V96" s="49"/>
       <c r="W96" s="74" t="s">
         <v>228</v>
@@ -16292,7 +16286,7 @@
       <c r="T97" s="58" t="s">
         <v>231</v>
       </c>
-      <c r="U97" s="212"/>
+      <c r="U97" s="216"/>
       <c r="V97" s="49"/>
       <c r="W97" s="74" t="s">
         <v>157</v>
@@ -16383,7 +16377,7 @@
       <c r="T98" s="58" t="s">
         <v>231</v>
       </c>
-      <c r="U98" s="212"/>
+      <c r="U98" s="216"/>
       <c r="V98" s="49"/>
       <c r="W98" s="74" t="s">
         <v>157</v>
@@ -16472,7 +16466,7 @@
         <v>242</v>
       </c>
       <c r="T99" s="58"/>
-      <c r="U99" s="212"/>
+      <c r="U99" s="216"/>
       <c r="V99" s="49"/>
       <c r="W99" s="74" t="s">
         <v>157</v>
@@ -16561,7 +16555,7 @@
         <v>242</v>
       </c>
       <c r="T100" s="58"/>
-      <c r="U100" s="212"/>
+      <c r="U100" s="216"/>
       <c r="V100" s="49"/>
       <c r="W100" s="74" t="s">
         <v>157</v>
@@ -17434,11 +17428,11 @@
       <c r="S110" s="58" t="s">
         <v>256</v>
       </c>
-      <c r="T110" s="216" t="s">
+      <c r="T110" s="220" t="s">
         <v>257</v>
       </c>
-      <c r="U110" s="219"/>
-      <c r="V110" s="219"/>
+      <c r="U110" s="218"/>
+      <c r="V110" s="218"/>
       <c r="W110" s="74" t="s">
         <v>157</v>
       </c>
@@ -17506,9 +17500,9 @@
       <c r="Q111" s="65"/>
       <c r="R111" s="49"/>
       <c r="S111" s="58"/>
-      <c r="T111" s="216"/>
-      <c r="U111" s="211"/>
-      <c r="V111" s="211"/>
+      <c r="T111" s="220"/>
+      <c r="U111" s="219"/>
+      <c r="V111" s="219"/>
       <c r="W111" s="74"/>
       <c r="X111" s="77"/>
       <c r="Y111" s="77"/>
@@ -18683,7 +18677,7 @@
       <c r="U124" s="80" t="s">
         <v>306</v>
       </c>
-      <c r="V124" s="211" t="s">
+      <c r="V124" s="219" t="s">
         <v>307</v>
       </c>
       <c r="W124" s="74" t="s">
@@ -18781,7 +18775,7 @@
       <c r="S125" s="58"/>
       <c r="T125" s="62"/>
       <c r="U125" s="80"/>
-      <c r="V125" s="211"/>
+      <c r="V125" s="219"/>
       <c r="W125" s="74" t="s">
         <v>43</v>
       </c>
@@ -19832,10 +19826,10 @@
       <c r="R139" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S139" s="210" t="s">
+      <c r="S139" s="221" t="s">
         <v>338</v>
       </c>
-      <c r="T139" s="210" t="s">
+      <c r="T139" s="221" t="s">
         <v>338</v>
       </c>
       <c r="U139" s="72" t="s">
@@ -19917,10 +19911,10 @@
       <c r="R140" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S140" s="210" t="s">
+      <c r="S140" s="221" t="s">
         <v>328</v>
       </c>
-      <c r="T140" s="210" t="s">
+      <c r="T140" s="221" t="s">
         <v>329</v>
       </c>
       <c r="U140" s="72" t="s">
@@ -19978,8 +19972,8 @@
       <c r="P141" s="49"/>
       <c r="Q141" s="65"/>
       <c r="R141" s="49"/>
-      <c r="S141" s="210"/>
-      <c r="T141" s="211"/>
+      <c r="S141" s="221"/>
+      <c r="T141" s="219"/>
       <c r="U141" s="49"/>
       <c r="V141" s="49"/>
       <c r="W141" s="74"/>
@@ -20042,10 +20036,10 @@
       <c r="R142" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S142" s="210" t="s">
+      <c r="S142" s="221" t="s">
         <v>344</v>
       </c>
-      <c r="T142" s="210" t="s">
+      <c r="T142" s="221" t="s">
         <v>345</v>
       </c>
       <c r="U142" s="49"/>
@@ -20134,8 +20128,8 @@
       <c r="R143" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S143" s="212"/>
-      <c r="T143" s="212"/>
+      <c r="S143" s="216"/>
+      <c r="T143" s="216"/>
       <c r="U143" s="49"/>
       <c r="V143" s="49"/>
       <c r="W143" s="74" t="s">
@@ -20222,8 +20216,8 @@
       <c r="R144" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S144" s="212"/>
-      <c r="T144" s="212"/>
+      <c r="S144" s="216"/>
+      <c r="T144" s="216"/>
       <c r="U144" s="49"/>
       <c r="V144" s="49"/>
       <c r="W144" s="74" t="s">
@@ -20398,8 +20392,8 @@
       <c r="R146" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S146" s="212"/>
-      <c r="T146" s="212"/>
+      <c r="S146" s="216"/>
+      <c r="T146" s="216"/>
       <c r="U146" s="49"/>
       <c r="V146" s="49"/>
       <c r="W146" s="74" t="s">
@@ -20486,8 +20480,8 @@
       <c r="R147" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S147" s="214"/>
-      <c r="T147" s="214"/>
+      <c r="S147" s="217"/>
+      <c r="T147" s="217"/>
       <c r="U147" s="49"/>
       <c r="V147" s="49"/>
       <c r="W147" s="74" t="s">
@@ -20555,8 +20549,8 @@
       <c r="P148" s="49"/>
       <c r="Q148" s="65"/>
       <c r="R148" s="49"/>
-      <c r="S148" s="210"/>
-      <c r="T148" s="211"/>
+      <c r="S148" s="221"/>
+      <c r="T148" s="219"/>
       <c r="U148" s="49"/>
       <c r="V148" s="49"/>
       <c r="W148" s="74"/>
@@ -20612,10 +20606,10 @@
       <c r="R149" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S149" s="216" t="s">
+      <c r="S149" s="220" t="s">
         <v>354</v>
       </c>
-      <c r="T149" s="216" t="s">
+      <c r="T149" s="220" t="s">
         <v>355</v>
       </c>
       <c r="U149" s="49"/>
@@ -20699,8 +20693,8 @@
       <c r="R150" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S150" s="212"/>
-      <c r="T150" s="212"/>
+      <c r="S150" s="216"/>
+      <c r="T150" s="216"/>
       <c r="U150" s="49"/>
       <c r="V150" s="49"/>
       <c r="W150" s="74" t="s">
@@ -20784,8 +20778,8 @@
       <c r="R151" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S151" s="212"/>
-      <c r="T151" s="212"/>
+      <c r="S151" s="216"/>
+      <c r="T151" s="216"/>
       <c r="U151" s="49"/>
       <c r="V151" s="49"/>
       <c r="W151" s="74" t="s">
@@ -21235,7 +21229,7 @@
       <c r="P156" s="50"/>
       <c r="Q156" s="67"/>
       <c r="R156" s="50"/>
-      <c r="S156" s="220"/>
+      <c r="S156" s="223"/>
       <c r="T156" s="50"/>
       <c r="U156" s="50"/>
       <c r="V156" s="50"/>
@@ -21279,7 +21273,7 @@
       <c r="P157" s="50"/>
       <c r="Q157" s="65"/>
       <c r="R157" s="49"/>
-      <c r="S157" s="220"/>
+      <c r="S157" s="223"/>
       <c r="T157" s="50"/>
       <c r="U157" s="50"/>
       <c r="V157" s="50"/>
@@ -21323,7 +21317,7 @@
       <c r="P158" s="50"/>
       <c r="Q158" s="65"/>
       <c r="R158" s="49"/>
-      <c r="S158" s="220"/>
+      <c r="S158" s="223"/>
       <c r="T158" s="50"/>
       <c r="U158" s="50"/>
       <c r="V158" s="50"/>
@@ -22437,12 +22431,12 @@
       <c r="R174" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S174" s="210" t="s">
+      <c r="S174" s="221" t="s">
         <v>397</v>
       </c>
-      <c r="T174" s="216"/>
+      <c r="T174" s="220"/>
       <c r="U174" s="80"/>
-      <c r="V174" s="211" t="s">
+      <c r="V174" s="219" t="s">
         <v>398</v>
       </c>
       <c r="W174" s="74" t="s">
@@ -22528,16 +22522,16 @@
       <c r="R175" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="S175" s="210" t="s">
+      <c r="S175" s="221" t="s">
         <v>400</v>
       </c>
-      <c r="T175" s="216" t="s">
+      <c r="T175" s="220" t="s">
         <v>401</v>
       </c>
       <c r="U175" s="80" t="s">
         <v>401</v>
       </c>
-      <c r="V175" s="211"/>
+      <c r="V175" s="219"/>
       <c r="W175" s="3" t="s">
         <v>59</v>
       </c>
@@ -22589,14 +22583,14 @@
       <c r="P176" s="49"/>
       <c r="Q176" s="65"/>
       <c r="R176" s="49"/>
-      <c r="S176" s="210" t="s">
+      <c r="S176" s="221" t="s">
         <v>403</v>
       </c>
-      <c r="T176" s="210" t="s">
+      <c r="T176" s="221" t="s">
         <v>403</v>
       </c>
       <c r="U176" s="49"/>
-      <c r="V176" s="210" t="s">
+      <c r="V176" s="221" t="s">
         <v>404</v>
       </c>
       <c r="W176" s="74"/>
@@ -22640,14 +22634,14 @@
       <c r="P177" s="49"/>
       <c r="Q177" s="65"/>
       <c r="R177" s="49"/>
-      <c r="S177" s="216" t="s">
+      <c r="S177" s="220" t="s">
         <v>403</v>
       </c>
-      <c r="T177" s="216" t="s">
+      <c r="T177" s="220" t="s">
         <v>403</v>
       </c>
       <c r="U177" s="49"/>
-      <c r="V177" s="216" t="s">
+      <c r="V177" s="220" t="s">
         <v>404</v>
       </c>
       <c r="W177" s="74"/>
@@ -22691,10 +22685,10 @@
       <c r="P178" s="49"/>
       <c r="Q178" s="65"/>
       <c r="R178" s="49"/>
-      <c r="S178" s="212"/>
-      <c r="T178" s="212"/>
+      <c r="S178" s="216"/>
+      <c r="T178" s="216"/>
       <c r="U178" s="49"/>
-      <c r="V178" s="212"/>
+      <c r="V178" s="216"/>
       <c r="W178" s="74"/>
       <c r="X178" s="77"/>
       <c r="Y178" s="77"/>
@@ -22736,10 +22730,10 @@
       <c r="P179" s="49"/>
       <c r="Q179" s="65"/>
       <c r="R179" s="49"/>
-      <c r="S179" s="212"/>
-      <c r="T179" s="212"/>
+      <c r="S179" s="216"/>
+      <c r="T179" s="216"/>
       <c r="U179" s="49"/>
-      <c r="V179" s="212"/>
+      <c r="V179" s="216"/>
       <c r="W179" s="74"/>
       <c r="X179" s="77"/>
       <c r="Y179" s="77"/>
@@ -22781,10 +22775,10 @@
       <c r="P180" s="49"/>
       <c r="Q180" s="65"/>
       <c r="R180" s="49"/>
-      <c r="S180" s="212"/>
-      <c r="T180" s="212"/>
+      <c r="S180" s="216"/>
+      <c r="T180" s="216"/>
       <c r="U180" s="49"/>
-      <c r="V180" s="212"/>
+      <c r="V180" s="216"/>
       <c r="W180" s="74"/>
       <c r="X180" s="77"/>
       <c r="Y180" s="77"/>
@@ -23638,11 +23632,38 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="T30:T32"/>
-    <mergeCell ref="T45:T47"/>
-    <mergeCell ref="V110:V111"/>
-    <mergeCell ref="T65:T67"/>
-    <mergeCell ref="T80:T84"/>
+    <mergeCell ref="T139:T144"/>
+    <mergeCell ref="U34:U36"/>
+    <mergeCell ref="S56:S58"/>
+    <mergeCell ref="T174:T180"/>
+    <mergeCell ref="U19:U21"/>
+    <mergeCell ref="U50:U52"/>
+    <mergeCell ref="S146:S151"/>
+    <mergeCell ref="U45:U47"/>
+    <mergeCell ref="S65:S67"/>
+    <mergeCell ref="U65:U67"/>
+    <mergeCell ref="U61:U63"/>
+    <mergeCell ref="S174:S180"/>
+    <mergeCell ref="U80:U84"/>
+    <mergeCell ref="S61:S63"/>
+    <mergeCell ref="S41:S43"/>
+    <mergeCell ref="U90:U100"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="T61:T63"/>
+    <mergeCell ref="T19:T21"/>
+    <mergeCell ref="S45:S47"/>
+    <mergeCell ref="U110:U111"/>
+    <mergeCell ref="T72:T77"/>
+    <mergeCell ref="S50:S52"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="U26:U28"/>
+    <mergeCell ref="T34:T36"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="U41:U43"/>
+    <mergeCell ref="T110:T111"/>
     <mergeCell ref="S139:S144"/>
     <mergeCell ref="T11:T13"/>
     <mergeCell ref="V174:V180"/>
@@ -23659,326 +23680,332 @@
     <mergeCell ref="S156:S159"/>
     <mergeCell ref="T146:T151"/>
     <mergeCell ref="V56:V58"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="T61:T63"/>
-    <mergeCell ref="T19:T21"/>
-    <mergeCell ref="S45:S47"/>
-    <mergeCell ref="U110:U111"/>
-    <mergeCell ref="T72:T77"/>
-    <mergeCell ref="S50:S52"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="U26:U28"/>
-    <mergeCell ref="T34:T36"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="U41:U43"/>
-    <mergeCell ref="T110:T111"/>
-    <mergeCell ref="T139:T144"/>
-    <mergeCell ref="U34:U36"/>
-    <mergeCell ref="S56:S58"/>
-    <mergeCell ref="T174:T180"/>
-    <mergeCell ref="U19:U21"/>
-    <mergeCell ref="U50:U52"/>
-    <mergeCell ref="S146:S151"/>
-    <mergeCell ref="U45:U47"/>
-    <mergeCell ref="S65:S67"/>
-    <mergeCell ref="U65:U67"/>
-    <mergeCell ref="U61:U63"/>
-    <mergeCell ref="S174:S180"/>
-    <mergeCell ref="U80:U84"/>
-    <mergeCell ref="S61:S63"/>
-    <mergeCell ref="S41:S43"/>
-    <mergeCell ref="U90:U100"/>
+    <mergeCell ref="T30:T32"/>
+    <mergeCell ref="T45:T47"/>
+    <mergeCell ref="V110:V111"/>
+    <mergeCell ref="T65:T67"/>
+    <mergeCell ref="T80:T84"/>
   </mergeCells>
+  <conditionalFormatting sqref="A14:B14 E14:R14 T14:AG14 A15:AG15 A16:R17 T16:AG17">
+    <cfRule type="expression" dxfId="417" priority="15">
+      <formula>$B14&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A101:B107">
-    <cfRule type="expression" dxfId="441" priority="614">
+    <cfRule type="expression" dxfId="416" priority="616">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="415" priority="615">
+      <formula>$B101=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="414" priority="614">
       <formula>$B101=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="440" priority="615">
-      <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="439" priority="616">
-      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110:F112 U117:V123 U124:U125 A139:B144 N146:V146 N147:R147 U147:V152 K148:R148 A152:T152 T156:V161 A162:V165 A166:J167">
-    <cfRule type="expression" dxfId="438" priority="830">
+    <cfRule type="expression" dxfId="413" priority="830">
       <formula>$B110=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A101:I107">
-    <cfRule type="expression" dxfId="437" priority="77">
+    <cfRule type="expression" dxfId="412" priority="77">
       <formula>$B101=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14:R14">
+    <cfRule type="expression" dxfId="411" priority="9">
+      <formula>$B14=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A151:R151">
-    <cfRule type="expression" dxfId="436" priority="778">
+    <cfRule type="expression" dxfId="410" priority="778">
       <formula>$B151=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A154:R161">
-    <cfRule type="expression" dxfId="435" priority="723">
+    <cfRule type="expression" dxfId="409" priority="724">
+      <formula>$B154=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="408" priority="726">
+      <formula>$B154=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="407" priority="723">
       <formula>$B154=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="434" priority="724">
-      <formula>$B154=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="433" priority="725">
+    <cfRule type="expression" dxfId="406" priority="725">
       <formula>$B154&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="432" priority="726">
-      <formula>$B154=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A128:S129 U128:V129 U170:V172">
-    <cfRule type="expression" dxfId="431" priority="623">
+    <cfRule type="expression" dxfId="405" priority="623">
       <formula>$B128=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109:U109">
-    <cfRule type="expression" dxfId="430" priority="831">
+    <cfRule type="expression" dxfId="404" priority="832">
+      <formula>$B109=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="403" priority="831">
       <formula>$B109=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="429" priority="832">
-      <formula>$B109=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="428" priority="833">
+    <cfRule type="expression" dxfId="402" priority="833">
       <formula>$B109&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="427" priority="834">
+    <cfRule type="expression" dxfId="401" priority="834">
       <formula>$B109=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78:V100 A108:V108 A174:R180">
-    <cfRule type="expression" dxfId="426" priority="528">
+    <cfRule type="expression" dxfId="400" priority="530">
+      <formula>$B78&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="399" priority="528">
       <formula>$B78=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="425" priority="529">
+    <cfRule type="expression" dxfId="398" priority="529">
       <formula>$B78=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="424" priority="530">
-      <formula>$B78&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80:V87">
-    <cfRule type="expression" dxfId="423" priority="618">
+    <cfRule type="expression" dxfId="397" priority="618">
       <formula>$B80=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:V100 D101:D107 A126:V127 A130:V144 A145:AG148 A149:G150 I149:AG150 A151:AG173">
-    <cfRule type="expression" dxfId="422" priority="663">
+    <cfRule type="expression" dxfId="396" priority="663">
       <formula>$B99&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113:V115 U117:V123 U124:U125 A128:S129 U128:V129 A145:AG148 A149:G150 I149:AG150 A151:AG173 A139:B144 U139:V144 U147:V152 A5:S6 A110:F112 A1:AG4 U5:AG6">
-    <cfRule type="expression" dxfId="421" priority="827">
+    <cfRule type="expression" dxfId="395" priority="827">
       <formula>$B1=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A126:V127 A130:V144 A99:V100 D101:D107 A145:AG148 A149:G150 I149:AG150 A151:AG173">
-    <cfRule type="expression" dxfId="420" priority="662">
+    <cfRule type="expression" dxfId="394" priority="662">
       <formula>$B99=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A126:V127">
-    <cfRule type="expression" dxfId="419" priority="798">
+    <cfRule type="expression" dxfId="393" priority="798">
       <formula>$B126=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A130:V144 A126:V127">
-    <cfRule type="expression" dxfId="418" priority="661">
+    <cfRule type="expression" dxfId="392" priority="661">
       <formula>$B126=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A153:V153">
-    <cfRule type="expression" dxfId="417" priority="759">
+    <cfRule type="expression" dxfId="391" priority="759">
       <formula>$B153=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="416" priority="760">
+    <cfRule type="expression" dxfId="390" priority="760">
       <formula>$B153=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="415" priority="761">
+    <cfRule type="expression" dxfId="389" priority="761">
       <formula>$B153&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="414" priority="762">
+    <cfRule type="expression" dxfId="388" priority="762">
       <formula>$B153=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A182:V193">
-    <cfRule type="expression" dxfId="413" priority="691">
+    <cfRule type="expression" dxfId="387" priority="691">
       <formula>$B182=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="412" priority="692">
+    <cfRule type="expression" dxfId="386" priority="692">
       <formula>$B182=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="411" priority="693">
+    <cfRule type="expression" dxfId="385" priority="693">
       <formula>$B182&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="410" priority="694">
+    <cfRule type="expression" dxfId="384" priority="694">
       <formula>$B182=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A110:F112 A113:V115 U117:V123 U124:U125 A128:S129 U128:V129 A139:B144 U139:V144 A145:V145 N146:V146 N147:R147 U147:V152 K148:R148 A152:T152 T156:V161 A162:V165 A166:J167 A168:L172 U170:V172">
-    <cfRule type="expression" dxfId="409" priority="828">
+    <cfRule type="expression" dxfId="383" priority="828">
       <formula>$B1=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="408" priority="829">
+    <cfRule type="expression" dxfId="382" priority="829">
       <formula>$B1&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A7:AG13 A174:R180 A18:AG55">
-    <cfRule type="expression" dxfId="407" priority="531">
+  <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A7:AG13 A18:AG55 A174:R180">
+    <cfRule type="expression" dxfId="381" priority="531">
       <formula>$B1=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:AG13 A18:AG52">
-    <cfRule type="expression" dxfId="406" priority="593">
+    <cfRule type="expression" dxfId="380" priority="594">
+      <formula>$B7=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="379" priority="595">
+      <formula>$B7&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="378" priority="593">
       <formula>$B7=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="405" priority="594">
-      <formula>$B7=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="404" priority="595">
-      <formula>$B7&lt;2</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14:AG17">
+    <cfRule type="expression" dxfId="377" priority="3">
+      <formula>$B14=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:AG15 A16:R17 T16:AG17 A14:B14 E14:R14 T14:AG14">
+    <cfRule type="expression" dxfId="376" priority="14">
+      <formula>$B14=2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:AG17">
+    <cfRule type="expression" dxfId="375" priority="12">
+      <formula>$B15=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:AG55 F56:AG56 A56:E58 F57:U58 W57:AG58 A59:AG79 A80:V86 A87:AG88 A101:B107 A113:AG124 A125:U125 W125:AG125 A126:AG135 A136:V136 A137:Y137 A138:AG138 S174:AG174 U175:U180 W175:AG180 A181:AG193 A98:AG98">
-    <cfRule type="expression" dxfId="403" priority="792">
+    <cfRule type="expression" dxfId="374" priority="792">
       <formula>$B53=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:AG55 F56:AG56 A56:E58 F57:U58 W57:AG58 A59:AG79 A80:V86 A87:AG88 A98:AG98 A101:B107 A113:AG124 A125:U125 W125:AG125 A126:AG135 A136:V136 A137:Y137 A138:AG138 S174:AG174 U175:U180 W175:AG180 A181:AG193">
-    <cfRule type="expression" dxfId="402" priority="793">
+    <cfRule type="expression" dxfId="373" priority="793">
       <formula>$B53&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:AG100">
-    <cfRule type="expression" dxfId="401" priority="106">
+    <cfRule type="expression" dxfId="372" priority="106">
       <formula>$B87=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A89:AG89">
-    <cfRule type="expression" dxfId="400" priority="103">
+    <cfRule type="expression" dxfId="371" priority="103">
       <formula>$B89=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="399" priority="104">
+    <cfRule type="expression" dxfId="370" priority="105">
+      <formula>$B89&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="369" priority="104">
       <formula>$B89=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="398" priority="105">
-      <formula>$B89&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A90:AG97">
-    <cfRule type="expression" dxfId="397" priority="564">
+    <cfRule type="expression" dxfId="368" priority="566">
+      <formula>$B90&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="367" priority="565">
+      <formula>$B90=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="366" priority="564">
       <formula>$B90=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="396" priority="565">
-      <formula>$B90=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="395" priority="566">
-      <formula>$B90&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98:AG100 D101:D107 A149:G150 I149:R150 A151:R151">
-    <cfRule type="expression" dxfId="394" priority="775">
+    <cfRule type="expression" dxfId="365" priority="775">
       <formula>$B98=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108:AG112">
-    <cfRule type="expression" dxfId="393" priority="548">
+    <cfRule type="expression" dxfId="364" priority="550">
+      <formula>$B108&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="363" priority="549">
+      <formula>$B108=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="362" priority="548">
       <formula>$B108=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="392" priority="549">
-      <formula>$B108=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="391" priority="550">
-      <formula>$B108&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A137:AG138">
-    <cfRule type="expression" dxfId="390" priority="523">
+    <cfRule type="expression" dxfId="361" priority="523">
       <formula>$B137=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A145:AG148 A149:G150 I149:AG150 A151:AG173">
-    <cfRule type="expression" dxfId="389" priority="596">
+    <cfRule type="expression" dxfId="360" priority="596">
       <formula>$B145=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A181:AG193 A59:AG79 A87:AG88 A126:AG135 A136:V136 A137:Y137 A138:AG138 A113:AG124 A80:V86 A101:B107 A53:AG55 F56:AG56 F57:U58 A56:E58 W57:AG58 A125:U125 W125:AG125 S174:AG174 U175:U180 W175:AG180">
-    <cfRule type="expression" dxfId="388" priority="791">
+    <cfRule type="expression" dxfId="359" priority="791">
       <formula>$B53=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101:C102">
-    <cfRule type="expression" dxfId="387" priority="468">
+    <cfRule type="expression" dxfId="358" priority="468">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="386" priority="469">
+    <cfRule type="expression" dxfId="357" priority="469">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="385" priority="470">
+    <cfRule type="expression" dxfId="356" priority="470">
       <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101:C104">
-    <cfRule type="expression" dxfId="384" priority="461">
+    <cfRule type="expression" dxfId="355" priority="462">
+      <formula>$B101=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="354" priority="463">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="353" priority="461">
       <formula>$B101=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="383" priority="462">
-      <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="382" priority="463">
-      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C106">
-    <cfRule type="expression" dxfId="381" priority="454">
+    <cfRule type="expression" dxfId="352" priority="455">
+      <formula>$B103=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="351" priority="454">
       <formula>$B103=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="380" priority="455">
-      <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="379" priority="456">
+    <cfRule type="expression" dxfId="350" priority="456">
       <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C105:C107">
-    <cfRule type="expression" dxfId="378" priority="447">
+    <cfRule type="expression" dxfId="349" priority="448">
+      <formula>$B105=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="348" priority="447">
       <formula>$B105=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="377" priority="448">
-      <formula>$B105=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="376" priority="449">
+    <cfRule type="expression" dxfId="347" priority="449">
       <formula>$B105&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C106:C107">
-    <cfRule type="expression" dxfId="375" priority="93">
+    <cfRule type="expression" dxfId="346" priority="95">
+      <formula>$B106&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="345" priority="93">
       <formula>$B106=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="374" priority="94">
+    <cfRule type="expression" dxfId="344" priority="94">
       <formula>$B106=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="373" priority="95">
-      <formula>$B106&lt;2</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:D14">
+    <cfRule type="expression" dxfId="343" priority="7">
+      <formula>$B14&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="342" priority="8">
+      <formula>$B14=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C139:T139 C140:R144">
-    <cfRule type="expression" dxfId="372" priority="650">
+    <cfRule type="expression" dxfId="341" priority="653">
+      <formula>$B139=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="340" priority="652">
+      <formula>$B139&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="339" priority="651">
+      <formula>$B139=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="338" priority="650">
       <formula>$B139=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="371" priority="651">
-      <formula>$B139=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="370" priority="652">
-      <formula>$B139&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="369" priority="653">
-      <formula>$B139=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D13 D86 D88:D138 D145:D201 D18:D84">
@@ -23991,6 +24018,16 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D15:D17">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D85">
     <cfRule type="colorScale" priority="628">
       <colorScale>
@@ -24022,937 +24059,894 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D101:E107">
-    <cfRule type="expression" dxfId="368" priority="440">
+    <cfRule type="expression" dxfId="337" priority="442">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="336" priority="441">
+      <formula>$B101=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="335" priority="440">
       <formula>$B101=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="367" priority="441">
-      <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="366" priority="442">
-      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E101:E107">
-    <cfRule type="expression" dxfId="365" priority="437">
+    <cfRule type="expression" dxfId="334" priority="437">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="364" priority="438">
+    <cfRule type="expression" dxfId="333" priority="439">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="332" priority="438">
       <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="363" priority="439">
-      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E87:Q87 Q128:Q129">
-    <cfRule type="expression" dxfId="362" priority="669">
+    <cfRule type="expression" dxfId="331" priority="669">
       <formula>_xlfn.ISFORMULA(E87)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E139:Q144">
-    <cfRule type="expression" dxfId="361" priority="649">
+    <cfRule type="expression" dxfId="330" priority="649">
       <formula>_xlfn.ISFORMULA(E139)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F107 F101:I103 F104 H104:I104 F105:I105 H106:I106">
-    <cfRule type="expression" dxfId="360" priority="229">
+    <cfRule type="expression" dxfId="329" priority="229">
       <formula>$B101=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="expression" dxfId="359" priority="62">
+    <cfRule type="expression" dxfId="328" priority="64">
+      <formula>$B107&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="327" priority="62">
       <formula>$B107=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="358" priority="63">
+    <cfRule type="expression" dxfId="326" priority="63">
       <formula>$B107=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="357" priority="64">
-      <formula>$B107&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F113:F115">
-    <cfRule type="expression" dxfId="356" priority="116">
+    <cfRule type="expression" dxfId="325" priority="116">
       <formula>$B113=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F115">
-    <cfRule type="expression" dxfId="355" priority="110">
+    <cfRule type="expression" dxfId="324" priority="110">
       <formula>$B115=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="354" priority="111">
+    <cfRule type="expression" dxfId="323" priority="111">
       <formula>$B115=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="353" priority="112">
+    <cfRule type="expression" dxfId="322" priority="112">
       <formula>$B115&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:G106">
-    <cfRule type="expression" dxfId="352" priority="65">
+    <cfRule type="expression" dxfId="321" priority="65">
       <formula>$B106=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="351" priority="66">
+    <cfRule type="expression" dxfId="320" priority="67">
+      <formula>$B106&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="319" priority="66">
       <formula>$B106=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="350" priority="67">
-      <formula>$B106&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F113:G114">
-    <cfRule type="expression" dxfId="349" priority="113">
+    <cfRule type="expression" dxfId="318" priority="114">
+      <formula>$B113=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="317" priority="113">
       <formula>$B113=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="348" priority="114">
-      <formula>$B113=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="347" priority="115">
+    <cfRule type="expression" dxfId="316" priority="115">
       <formula>$B113&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55:I58">
-    <cfRule type="expression" dxfId="346" priority="598">
+    <cfRule type="expression" dxfId="315" priority="598">
       <formula>$B55=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="345" priority="599">
+    <cfRule type="expression" dxfId="314" priority="599">
       <formula>$B55=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="344" priority="600">
+    <cfRule type="expression" dxfId="313" priority="600">
       <formula>$B55&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="343" priority="601">
+    <cfRule type="expression" dxfId="312" priority="601">
       <formula>$B55=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101:I102">
-    <cfRule type="expression" dxfId="342" priority="419">
+    <cfRule type="expression" dxfId="311" priority="419">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="341" priority="420">
+    <cfRule type="expression" dxfId="310" priority="421">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="309" priority="420">
       <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="340" priority="421">
-      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101:I103 F104 H104:I104 F105:I105 H106:I106 F106:F107">
-    <cfRule type="expression" dxfId="339" priority="230">
+    <cfRule type="expression" dxfId="308" priority="230">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="338" priority="231">
+    <cfRule type="expression" dxfId="307" priority="231">
       <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103:I105">
-    <cfRule type="expression" dxfId="337" priority="99">
+    <cfRule type="expression" dxfId="306" priority="99">
       <formula>$B103=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="336" priority="100">
+    <cfRule type="expression" dxfId="305" priority="101">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="304" priority="100">
       <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="335" priority="101">
-      <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:I107">
-    <cfRule type="expression" dxfId="334" priority="74">
+    <cfRule type="expression" dxfId="303" priority="76">
+      <formula>$B106&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="302" priority="75">
+      <formula>$B106=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="301" priority="74">
       <formula>$B106=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="333" priority="75">
-      <formula>$B106=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="332" priority="76">
-      <formula>$B106&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107:I107">
-    <cfRule type="expression" dxfId="331" priority="222">
+    <cfRule type="expression" dxfId="300" priority="224">
+      <formula>$B107&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="299" priority="223">
+      <formula>$B107=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="298" priority="222">
       <formula>$B107=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="330" priority="223">
-      <formula>$B107=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="329" priority="224">
-      <formula>$B107&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57:U58 W57:AG58 A59:AG79 A108:AG109 A110:V113 A113:AG124 A125:U125 W125:AG125 A126:AG135 A130:V145 S174:AG174 U175:U180 W175:AG180 A181:AG193">
-    <cfRule type="expression" dxfId="328" priority="794">
+    <cfRule type="expression" dxfId="297" priority="794">
       <formula>$B57=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56:AG56 A56:E58">
-    <cfRule type="expression" dxfId="327" priority="592">
+    <cfRule type="expression" dxfId="296" priority="592">
       <formula>$B56=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G104">
-    <cfRule type="expression" dxfId="326" priority="96">
+    <cfRule type="expression" dxfId="295" priority="98">
+      <formula>$B104&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="294" priority="97">
+      <formula>$B104=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="293" priority="96">
       <formula>$B104=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="325" priority="97">
-      <formula>$B104=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="324" priority="98">
-      <formula>$B104&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G110:I111">
-    <cfRule type="expression" dxfId="323" priority="823">
+    <cfRule type="expression" dxfId="292" priority="823">
       <formula>$B110=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="322" priority="824">
+    <cfRule type="expression" dxfId="291" priority="824">
       <formula>$B110=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="321" priority="825">
+    <cfRule type="expression" dxfId="290" priority="825">
       <formula>$B110&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="320" priority="826">
+    <cfRule type="expression" dxfId="289" priority="826">
       <formula>$B110=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H149:H150 K166:L167">
-    <cfRule type="expression" dxfId="319" priority="708">
+    <cfRule type="expression" dxfId="288" priority="708">
       <formula>$B150=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="318" priority="709">
+    <cfRule type="expression" dxfId="287" priority="709">
       <formula>$B150&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="317" priority="710">
+    <cfRule type="expression" dxfId="286" priority="710">
       <formula>$B150=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H149:H150">
-    <cfRule type="expression" dxfId="316" priority="1098">
+    <cfRule type="expression" dxfId="285" priority="1099">
+      <formula>$B150&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="284" priority="1101">
+      <formula>$B150=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="283" priority="1098">
       <formula>$B150=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="315" priority="1099">
-      <formula>$B150&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="314" priority="1101">
-      <formula>$B150=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5">
-    <cfRule type="expression" dxfId="313" priority="629">
+    <cfRule type="expression" dxfId="282" priority="629">
       <formula>$B5=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="312" priority="630">
+    <cfRule type="expression" dxfId="281" priority="632">
+      <formula>$B5=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="280" priority="631">
+      <formula>$B5&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="279" priority="630">
       <formula>$B5=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="311" priority="631">
-      <formula>$B5&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="310" priority="632">
-      <formula>$B5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J75:L77">
-    <cfRule type="expression" dxfId="309" priority="680">
+    <cfRule type="expression" dxfId="278" priority="684">
+      <formula>$B75=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="277" priority="680">
       <formula>_xlfn.ISFORMULA(J75)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="308" priority="684">
-      <formula>$B75=0</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:Q13 J108:Q1048576 J18:Q100">
-    <cfRule type="expression" dxfId="307" priority="690">
+  <conditionalFormatting sqref="J1:Q17">
+    <cfRule type="expression" dxfId="276" priority="13">
       <formula>_xlfn.ISFORMULA(J1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J18:Q100 J108:Q1048576">
+    <cfRule type="expression" dxfId="275" priority="690">
+      <formula>_xlfn.ISFORMULA(J18)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J72:Q74">
-    <cfRule type="expression" dxfId="306" priority="685">
+    <cfRule type="expression" dxfId="274" priority="685">
       <formula>_xlfn.ISFORMULA(J72)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J73:S77">
-    <cfRule type="expression" dxfId="305" priority="676">
+    <cfRule type="expression" dxfId="273" priority="676">
       <formula>$B73=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="304" priority="677">
+    <cfRule type="expression" dxfId="272" priority="677">
       <formula>$B73=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="303" priority="678">
+    <cfRule type="expression" dxfId="271" priority="678">
       <formula>$B73&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J72:V72 J73:S74 U73:V77">
-    <cfRule type="expression" dxfId="302" priority="689">
+    <cfRule type="expression" dxfId="270" priority="689">
       <formula>$B72=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J72:V72 U73:V77">
-    <cfRule type="expression" dxfId="301" priority="686">
+    <cfRule type="expression" dxfId="269" priority="686">
       <formula>$B72=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="300" priority="687">
+    <cfRule type="expression" dxfId="268" priority="687">
       <formula>$B72=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="299" priority="688">
+    <cfRule type="expression" dxfId="267" priority="688">
       <formula>$B72&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K85">
-    <cfRule type="expression" dxfId="298" priority="622">
+    <cfRule type="expression" dxfId="266" priority="622">
       <formula>_xlfn.ISFORMULA(K85)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K166:L167 H149:H150">
-    <cfRule type="expression" dxfId="297" priority="707">
+    <cfRule type="expression" dxfId="265" priority="707">
       <formula>$B150=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K101:M102">
-    <cfRule type="expression" dxfId="296" priority="373">
+    <cfRule type="expression" dxfId="264" priority="375">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="263" priority="374">
+      <formula>$B101=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="262" priority="373">
       <formula>$B101=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="295" priority="374">
-      <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="294" priority="375">
-      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K101:M105">
-    <cfRule type="expression" dxfId="293" priority="199">
+    <cfRule type="expression" dxfId="261" priority="201">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="260" priority="200">
+      <formula>$B101=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="259" priority="199">
       <formula>$B101=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="292" priority="200">
-      <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="291" priority="201">
-      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K101:M107">
-    <cfRule type="expression" dxfId="290" priority="190">
+    <cfRule type="expression" dxfId="258" priority="194">
+      <formula>$B101=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="257" priority="190">
       <formula>_xlfn.ISFORMULA(K101)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="289" priority="194">
-      <formula>$B101=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K103:M107">
-    <cfRule type="expression" dxfId="288" priority="191">
+    <cfRule type="expression" dxfId="256" priority="193">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="255" priority="192">
+      <formula>$B103=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="254" priority="191">
       <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="287" priority="192">
-      <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="286" priority="193">
-      <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K106:M106">
-    <cfRule type="expression" dxfId="285" priority="90">
+    <cfRule type="expression" dxfId="253" priority="92">
+      <formula>$B106&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="252" priority="91">
+      <formula>$B106=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="251" priority="90">
       <formula>$B106=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="284" priority="91">
-      <formula>$B106=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="283" priority="92">
-      <formula>$B106&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107:M107">
-    <cfRule type="expression" dxfId="282" priority="43">
+    <cfRule type="expression" dxfId="250" priority="45">
+      <formula>$B107&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="249" priority="43">
       <formula>$B107=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="281" priority="44">
+    <cfRule type="expression" dxfId="248" priority="44">
       <formula>$B107=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="280" priority="45">
-      <formula>$B107&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K146:M147">
-    <cfRule type="expression" dxfId="279" priority="787">
+    <cfRule type="expression" dxfId="247" priority="789">
+      <formula>$B146&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="246" priority="788">
+      <formula>$B146=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="245" priority="787">
       <formula>$B146=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="278" priority="788">
-      <formula>$B146=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="277" priority="789">
-      <formula>$B146&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="276" priority="790">
+    <cfRule type="expression" dxfId="244" priority="790">
       <formula>$B146=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L116">
-    <cfRule type="expression" dxfId="275" priority="636">
+    <cfRule type="expression" dxfId="243" priority="636">
       <formula>$B116=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="274" priority="1026">
+    <cfRule type="expression" dxfId="242" priority="1026">
       <formula>#REF!=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="273" priority="1027">
+    <cfRule type="expression" dxfId="241" priority="1027">
       <formula>#REF!&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="272" priority="1028">
+    <cfRule type="expression" dxfId="240" priority="1028">
       <formula>#REF!=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="271" priority="1029">
+    <cfRule type="expression" dxfId="239" priority="1029">
       <formula>#REF!=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L116:V116">
-    <cfRule type="expression" dxfId="270" priority="633">
+    <cfRule type="expression" dxfId="238" priority="635">
+      <formula>$B116&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="237" priority="633">
       <formula>$B116=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="269" priority="634">
+    <cfRule type="expression" dxfId="236" priority="634">
       <formula>$B116=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="268" priority="635">
-      <formula>$B116&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M106:M107">
-    <cfRule type="expression" dxfId="267" priority="59">
+    <cfRule type="expression" dxfId="235" priority="59">
       <formula>$B106=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="266" priority="60">
+    <cfRule type="expression" dxfId="234" priority="60">
       <formula>$B106=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="265" priority="61">
+    <cfRule type="expression" dxfId="233" priority="61">
       <formula>$B106&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N85">
-    <cfRule type="expression" dxfId="264" priority="617">
+    <cfRule type="expression" dxfId="232" priority="617">
       <formula>_xlfn.ISFORMULA(N85)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O14">
+    <cfRule type="expression" dxfId="231" priority="1">
+      <formula>$B14=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O101:O102">
-    <cfRule type="expression" dxfId="263" priority="357">
+    <cfRule type="expression" dxfId="230" priority="359">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="229" priority="358">
+      <formula>$B101=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="228" priority="357">
       <formula>$B101=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="262" priority="358">
-      <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="261" priority="359">
-      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O101:O107">
-    <cfRule type="expression" dxfId="260" priority="348">
+    <cfRule type="expression" dxfId="227" priority="352">
+      <formula>$B101=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="226" priority="351">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="225" priority="349">
+      <formula>$B101=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="224" priority="348">
       <formula>_xlfn.ISFORMULA(O101)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="259" priority="349">
-      <formula>$B101=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="258" priority="350">
+    <cfRule type="expression" dxfId="223" priority="350">
       <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="257" priority="351">
-      <formula>$B101&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="256" priority="352">
-      <formula>$B101=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O103:O107">
-    <cfRule type="expression" dxfId="255" priority="345">
+    <cfRule type="expression" dxfId="222" priority="346">
+      <formula>$B103=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="221" priority="347">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="220" priority="345">
       <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="254" priority="346">
-      <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="253" priority="347">
-      <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q75:Q77">
-    <cfRule type="expression" dxfId="252" priority="675">
+    <cfRule type="expression" dxfId="219" priority="675">
       <formula>_xlfn.ISFORMULA(Q75)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:Q107">
-    <cfRule type="expression" dxfId="251" priority="174">
+    <cfRule type="expression" dxfId="218" priority="174">
       <formula>_xlfn.ISFORMULA(Q101)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q153">
-    <cfRule type="expression" dxfId="250" priority="844">
+    <cfRule type="expression" dxfId="217" priority="847">
+      <formula>$B154=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="216" priority="846">
+      <formula>$B154&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="215" priority="845">
+      <formula>$B154=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="214" priority="844">
       <formula>$B154=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="249" priority="845">
-      <formula>$B154=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="248" priority="846">
-      <formula>$B154&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="247" priority="847">
-      <formula>$B154=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:R102">
-    <cfRule type="expression" dxfId="246" priority="325">
+    <cfRule type="expression" dxfId="213" priority="325">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="245" priority="326">
+    <cfRule type="expression" dxfId="212" priority="326">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="244" priority="327">
+    <cfRule type="expression" dxfId="211" priority="327">
       <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:R104">
-    <cfRule type="expression" dxfId="243" priority="318">
+    <cfRule type="expression" dxfId="210" priority="318">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="242" priority="319">
+    <cfRule type="expression" dxfId="209" priority="319">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="241" priority="320">
+    <cfRule type="expression" dxfId="208" priority="320">
       <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q105:R105">
-    <cfRule type="expression" dxfId="240" priority="167">
+    <cfRule type="expression" dxfId="207" priority="169">
+      <formula>$B105&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="206" priority="168">
+      <formula>$B105=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="205" priority="167">
       <formula>$B105=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="239" priority="168">
-      <formula>$B105=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="238" priority="169">
-      <formula>$B105&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q106:R106">
-    <cfRule type="expression" dxfId="237" priority="87">
+    <cfRule type="expression" dxfId="204" priority="88">
+      <formula>$B106=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="203" priority="87">
       <formula>$B106=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="236" priority="88">
-      <formula>$B106=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="235" priority="89">
+    <cfRule type="expression" dxfId="202" priority="89">
       <formula>$B106&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q107:R107">
-    <cfRule type="expression" dxfId="234" priority="160">
+    <cfRule type="expression" dxfId="201" priority="160">
       <formula>$B107=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="233" priority="161">
+    <cfRule type="expression" dxfId="200" priority="161">
       <formula>$B107=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="232" priority="162">
+    <cfRule type="expression" dxfId="199" priority="162">
       <formula>$B107&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q75:S77">
-    <cfRule type="expression" dxfId="231" priority="679">
+    <cfRule type="expression" dxfId="198" priority="679">
       <formula>$B75=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q103:S104">
-    <cfRule type="expression" dxfId="230" priority="311">
+    <cfRule type="expression" dxfId="197" priority="313">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="196" priority="312">
+      <formula>$B103=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="195" priority="311">
       <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="229" priority="312">
-      <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="228" priority="313">
-      <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q105:S105">
-    <cfRule type="expression" dxfId="227" priority="146">
+    <cfRule type="expression" dxfId="194" priority="148">
+      <formula>$B105&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="193" priority="147">
+      <formula>$B105=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="192" priority="146">
       <formula>$B105=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="226" priority="147">
-      <formula>$B105=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="225" priority="148">
-      <formula>$B105&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q106:S106">
-    <cfRule type="expression" dxfId="224" priority="84">
+    <cfRule type="expression" dxfId="191" priority="86">
+      <formula>$B106&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="190" priority="85">
+      <formula>$B106=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="189" priority="84">
       <formula>$B106=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="223" priority="85">
-      <formula>$B106=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="222" priority="86">
-      <formula>$B106&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q107:S107">
-    <cfRule type="expression" dxfId="221" priority="153">
+    <cfRule type="expression" dxfId="188" priority="153">
       <formula>$B107=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="220" priority="154">
+    <cfRule type="expression" dxfId="187" priority="154">
       <formula>$B107=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="219" priority="155">
+    <cfRule type="expression" dxfId="186" priority="155">
       <formula>$B107&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:T107">
-    <cfRule type="expression" dxfId="218" priority="135">
+    <cfRule type="expression" dxfId="185" priority="135">
       <formula>$B101=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S14">
+    <cfRule type="expression" dxfId="184" priority="5">
+      <formula>$B14=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="183" priority="4">
+      <formula>$B14&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S16:S17">
+    <cfRule type="expression" dxfId="182" priority="11">
+      <formula>$B16=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="181" priority="10">
+      <formula>$B16&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S101:S104">
-    <cfRule type="expression" dxfId="217" priority="304">
+    <cfRule type="expression" dxfId="180" priority="304">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="216" priority="305">
+    <cfRule type="expression" dxfId="179" priority="305">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="215" priority="306">
+    <cfRule type="expression" dxfId="178" priority="306">
       <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S106">
-    <cfRule type="expression" dxfId="214" priority="81">
+    <cfRule type="expression" dxfId="177" priority="83">
+      <formula>$B106&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="176" priority="82">
+      <formula>$B106=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="175" priority="81">
       <formula>$B106=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="213" priority="82">
-      <formula>$B106=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="212" priority="83">
-      <formula>$B106&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S156">
-    <cfRule type="expression" dxfId="211" priority="771">
+    <cfRule type="expression" dxfId="174" priority="772">
+      <formula>$B156=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="173" priority="771">
       <formula>$B156=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="210" priority="772">
-      <formula>$B156=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="209" priority="773">
+    <cfRule type="expression" dxfId="172" priority="774">
+      <formula>$B156=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="171" priority="773">
       <formula>$B156&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="208" priority="774">
-      <formula>$B156=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S160:S161">
-    <cfRule type="expression" dxfId="207" priority="767">
+    <cfRule type="expression" dxfId="170" priority="770">
+      <formula>$B160=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="169" priority="769">
+      <formula>$B160&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="168" priority="768">
+      <formula>$B160=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="167" priority="767">
       <formula>$B160=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="206" priority="768">
-      <formula>$B160=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="205" priority="769">
-      <formula>$B160&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="204" priority="770">
-      <formula>$B160=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S101:T102">
-    <cfRule type="expression" dxfId="203" priority="297">
+    <cfRule type="expression" dxfId="166" priority="297">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="202" priority="298">
+    <cfRule type="expression" dxfId="165" priority="298">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="201" priority="299">
+    <cfRule type="expression" dxfId="164" priority="299">
       <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S105:T105">
-    <cfRule type="expression" dxfId="200" priority="136">
+    <cfRule type="expression" dxfId="163" priority="137">
+      <formula>$B105=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="162" priority="138">
+      <formula>$B105&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="161" priority="136">
       <formula>$B105=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="199" priority="137">
-      <formula>$B105=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="198" priority="138">
-      <formula>$B105&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S107:T107">
-    <cfRule type="expression" dxfId="197" priority="132">
+    <cfRule type="expression" dxfId="160" priority="133">
+      <formula>$B107=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="159" priority="132">
       <formula>$B107=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="196" priority="133">
-      <formula>$B107=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="195" priority="134">
+    <cfRule type="expression" dxfId="158" priority="134">
       <formula>$B107&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S94:V97">
-    <cfRule type="expression" dxfId="194" priority="668">
+    <cfRule type="expression" dxfId="157" priority="668">
       <formula>$B94=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S154:V155">
-    <cfRule type="expression" dxfId="193" priority="731">
+    <cfRule type="expression" dxfId="156" priority="731">
       <formula>$B154=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="192" priority="732">
+    <cfRule type="expression" dxfId="155" priority="732">
       <formula>$B154=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="191" priority="733">
+    <cfRule type="expression" dxfId="154" priority="733">
       <formula>$B154&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="734">
+    <cfRule type="expression" dxfId="153" priority="734">
       <formula>$B154=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S14:AG14">
+    <cfRule type="expression" dxfId="152" priority="6">
+      <formula>$B14=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5">
-    <cfRule type="expression" dxfId="189" priority="524">
+    <cfRule type="expression" dxfId="151" priority="527">
+      <formula>$B5&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="150" priority="526">
+      <formula>$B5=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="149" priority="524">
       <formula>$B5=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="188" priority="525">
+    <cfRule type="expression" dxfId="148" priority="525">
       <formula>$B5=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="187" priority="526">
-      <formula>$B5=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="186" priority="527">
-      <formula>$B5&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6">
-    <cfRule type="expression" dxfId="185" priority="1082">
+    <cfRule type="expression" dxfId="147" priority="1083">
+      <formula>$B5&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="146" priority="1085">
+      <formula>$B5=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="145" priority="1087">
+      <formula>$B5=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="144" priority="1082">
       <formula>$B5=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="184" priority="1083">
-      <formula>$B5&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="183" priority="1085">
-      <formula>$B5=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="182" priority="1087">
-      <formula>$B5=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T101:T104">
-    <cfRule type="expression" dxfId="181" priority="290">
+    <cfRule type="expression" dxfId="143" priority="290">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="291">
+    <cfRule type="expression" dxfId="142" priority="291">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="179" priority="292">
+    <cfRule type="expression" dxfId="141" priority="292">
       <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T103:T106">
-    <cfRule type="expression" dxfId="178" priority="139">
+    <cfRule type="expression" dxfId="140" priority="141">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="139" priority="140">
+      <formula>$B103=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="138" priority="139">
       <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="177" priority="140">
-      <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="176" priority="141">
-      <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T104">
-    <cfRule type="expression" dxfId="175" priority="68">
+    <cfRule type="expression" dxfId="137" priority="70">
+      <formula>$B104&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="136" priority="68">
       <formula>$B104=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="69">
+    <cfRule type="expression" dxfId="135" priority="69">
       <formula>$B104=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="173" priority="70">
-      <formula>$B104&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T106:T107">
-    <cfRule type="expression" dxfId="172" priority="78">
+    <cfRule type="expression" dxfId="134" priority="79">
+      <formula>$B106=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="133" priority="78">
       <formula>$B106=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="171" priority="79">
-      <formula>$B106=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="170" priority="80">
+    <cfRule type="expression" dxfId="132" priority="80">
       <formula>$B106&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U110">
-    <cfRule type="expression" dxfId="169" priority="852">
+    <cfRule type="expression" dxfId="131" priority="852">
       <formula>$B109=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="853">
+    <cfRule type="expression" dxfId="130" priority="853">
       <formula>$B109=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="167" priority="854">
+    <cfRule type="expression" dxfId="129" priority="854">
       <formula>$B109&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="855">
+    <cfRule type="expression" dxfId="128" priority="855">
       <formula>$B109=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U139:AG144">
-    <cfRule type="expression" dxfId="165" priority="475">
+    <cfRule type="expression" dxfId="127" priority="475">
       <formula>$B139=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V16:AG17">
+    <cfRule type="expression" dxfId="126" priority="2">
+      <formula>$B16=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W101:W107">
-    <cfRule type="expression" dxfId="164" priority="279">
+    <cfRule type="expression" dxfId="125" priority="279">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="163" priority="280">
+    <cfRule type="expression" dxfId="124" priority="282">
+      <formula>$B101=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="123" priority="281">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="122" priority="280">
       <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="162" priority="281">
-      <formula>$B101&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="161" priority="282">
-      <formula>$B101=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W80:AG86">
-    <cfRule type="expression" dxfId="160" priority="572">
+    <cfRule type="expression" dxfId="121" priority="573">
+      <formula>$B80=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="120" priority="572">
       <formula>$B80=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="159" priority="573">
-      <formula>$B80=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="158" priority="574">
+    <cfRule type="expression" dxfId="119" priority="575">
+      <formula>$B80=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="118" priority="574">
       <formula>$B80&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="157" priority="575">
-      <formula>$B80=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W99:AG100 A149:G150 I149:R150 A151:R151">
-    <cfRule type="expression" dxfId="156" priority="776">
+    <cfRule type="expression" dxfId="117" priority="777">
+      <formula>$B99&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="116" priority="776">
       <formula>$B99=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="155" priority="777">
-      <formula>$B99&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W110:AG112">
-    <cfRule type="expression" dxfId="154" priority="551">
+    <cfRule type="expression" dxfId="115" priority="551">
       <formula>$B110=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W136:AG136">
-    <cfRule type="expression" dxfId="153" priority="544">
+    <cfRule type="expression" dxfId="114" priority="545">
+      <formula>$B136=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="546">
+      <formula>$B136&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="112" priority="547">
+      <formula>$B136=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="111" priority="544">
       <formula>$B136=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="152" priority="545">
-      <formula>$B136=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="151" priority="546">
-      <formula>$B136&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="150" priority="547">
-      <formula>$B136=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W139:AG144">
-    <cfRule type="expression" dxfId="149" priority="472">
+    <cfRule type="expression" dxfId="110" priority="474">
+      <formula>$B139&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="109" priority="473">
+      <formula>$B139=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="472">
       <formula>$B139=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="148" priority="473">
-      <formula>$B139=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="147" priority="474">
-      <formula>$B139&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z101:AG107">
-    <cfRule type="expression" dxfId="146" priority="121">
+    <cfRule type="expression" dxfId="107" priority="124">
+      <formula>$B101=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="123">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="122">
+      <formula>$B101=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="121">
       <formula>$B101=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="145" priority="122">
-      <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="144" priority="123">
-      <formula>$B101&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="143" priority="124">
-      <formula>$B101=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z137:AG137">
-    <cfRule type="expression" dxfId="142" priority="520">
+    <cfRule type="expression" dxfId="103" priority="522">
+      <formula>$B137&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="521">
+      <formula>$B137=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="520">
       <formula>$B137=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="141" priority="521">
-      <formula>$B137=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="140" priority="522">
-      <formula>$B137&lt;2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14:R14">
-    <cfRule type="expression" dxfId="14" priority="9">
-      <formula>$B14=3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14:B14 E14:R14 T14:AG14 A15:AG15 A16:R17 T16:AG17">
-    <cfRule type="expression" dxfId="13" priority="15">
-      <formula>$B14&lt;2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:AG15 A16:R17 T16:AG17 A14:B14 E14:R14 T14:AG14">
-    <cfRule type="expression" dxfId="12" priority="14">
-      <formula>$B14=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14:AG17">
-    <cfRule type="expression" dxfId="11" priority="3">
-      <formula>$B14=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:AG17">
-    <cfRule type="expression" dxfId="10" priority="12">
-      <formula>$B15=3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:D14">
-    <cfRule type="expression" dxfId="9" priority="7">
-      <formula>$B14&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8">
-      <formula>$B14=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15:D17">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J14:Q17">
-    <cfRule type="expression" dxfId="7" priority="13">
-      <formula>_xlfn.ISFORMULA(J14)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O14">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>$B14=3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S14">
-    <cfRule type="expression" dxfId="5" priority="4">
-      <formula>$B14&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>$B14=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S16:S17">
-    <cfRule type="expression" dxfId="3" priority="10">
-      <formula>$B16&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="11">
-      <formula>$B16=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S14:AG14">
-    <cfRule type="expression" dxfId="1" priority="6">
-      <formula>$B14=3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V16:AG17">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>$B16=3</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="17">
@@ -25043,20 +25037,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="225" t="s">
+      <c r="A1" s="230" t="s">
         <v>428</v>
       </c>
-      <c r="B1" s="224" t="s">
+      <c r="B1" s="229" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="222" t="s">
+      <c r="C1" s="227" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="223"/>
-      <c r="B2" s="223"/>
-      <c r="C2" s="223"/>
+      <c r="A2" s="228"/>
+      <c r="B2" s="228"/>
+      <c r="C2" s="228"/>
     </row>
     <row r="3" spans="1:5" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
@@ -25960,12 +25954,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="226" t="s">
+      <c r="A2" s="231" t="s">
         <v>483</v>
       </c>
-      <c r="B2" s="227"/>
-      <c r="C2" s="227"/>
-      <c r="D2" s="228"/>
+      <c r="B2" s="232"/>
+      <c r="C2" s="232"/>
+      <c r="D2" s="233"/>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
@@ -26022,12 +26016,12 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="226" t="s">
+      <c r="A7" s="231" t="s">
         <v>363</v>
       </c>
-      <c r="B7" s="227"/>
-      <c r="C7" s="227"/>
-      <c r="D7" s="228"/>
+      <c r="B7" s="232"/>
+      <c r="C7" s="232"/>
+      <c r="D7" s="233"/>
     </row>
     <row r="8" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
@@ -26086,12 +26080,12 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="226" t="s">
+      <c r="A12" s="231" t="s">
         <v>236</v>
       </c>
-      <c r="B12" s="227"/>
-      <c r="C12" s="227"/>
-      <c r="D12" s="228"/>
+      <c r="B12" s="232"/>
+      <c r="C12" s="232"/>
+      <c r="D12" s="233"/>
     </row>
     <row r="13" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="20" t="s">
@@ -26190,12 +26184,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="226" t="s">
+      <c r="A20" s="231" t="s">
         <v>513</v>
       </c>
-      <c r="B20" s="227"/>
-      <c r="C20" s="227"/>
-      <c r="D20" s="228"/>
+      <c r="B20" s="232"/>
+      <c r="C20" s="232"/>
+      <c r="D20" s="233"/>
     </row>
     <row r="21" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="20" t="s">
@@ -26324,12 +26318,12 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="226" t="s">
+      <c r="A30" s="231" t="s">
         <v>526</v>
       </c>
-      <c r="B30" s="227"/>
-      <c r="C30" s="227"/>
-      <c r="D30" s="228"/>
+      <c r="B30" s="232"/>
+      <c r="C30" s="232"/>
+      <c r="D30" s="233"/>
     </row>
     <row r="31" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="20" t="s">
@@ -26404,12 +26398,12 @@
       <c r="D36" s="26"/>
     </row>
     <row r="37" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="226" t="s">
+      <c r="A37" s="231" t="s">
         <v>534</v>
       </c>
-      <c r="B37" s="227"/>
-      <c r="C37" s="227"/>
-      <c r="D37" s="228"/>
+      <c r="B37" s="232"/>
+      <c r="C37" s="232"/>
+      <c r="D37" s="233"/>
     </row>
     <row r="38" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="20" t="s">
@@ -26496,12 +26490,12 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="226" t="s">
+      <c r="A44" s="231" t="s">
         <v>547</v>
       </c>
-      <c r="B44" s="227"/>
-      <c r="C44" s="227"/>
-      <c r="D44" s="228"/>
+      <c r="B44" s="232"/>
+      <c r="C44" s="232"/>
+      <c r="D44" s="233"/>
     </row>
     <row r="45" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="20" t="s">
@@ -26518,12 +26512,12 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="226" t="s">
+      <c r="A46" s="231" t="s">
         <v>550</v>
       </c>
-      <c r="B46" s="227"/>
-      <c r="C46" s="227"/>
-      <c r="D46" s="228"/>
+      <c r="B46" s="232"/>
+      <c r="C46" s="232"/>
+      <c r="D46" s="233"/>
     </row>
     <row r="47" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="20" t="s">
@@ -26568,12 +26562,12 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="226" t="s">
+      <c r="A50" s="231" t="s">
         <v>557</v>
       </c>
-      <c r="B50" s="227"/>
-      <c r="C50" s="227"/>
-      <c r="D50" s="228"/>
+      <c r="B50" s="232"/>
+      <c r="C50" s="232"/>
+      <c r="D50" s="233"/>
     </row>
     <row r="51" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="20" t="s">
@@ -27973,10 +27967,10 @@
       <c r="C9" s="202" t="s">
         <v>571</v>
       </c>
-      <c r="D9" s="231" t="s">
+      <c r="D9" s="236" t="s">
         <v>572</v>
       </c>
-      <c r="E9" s="229" t="s">
+      <c r="E9" s="234" t="s">
         <v>573</v>
       </c>
     </row>
@@ -27987,8 +27981,8 @@
       <c r="B10">
         <v>0</v>
       </c>
-      <c r="D10" s="230"/>
-      <c r="E10" s="230"/>
+      <c r="D10" s="235"/>
+      <c r="E10" s="235"/>
     </row>
     <row r="11" spans="1:5" ht="128" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -28000,8 +27994,8 @@
       <c r="C11" s="201" t="s">
         <v>574</v>
       </c>
-      <c r="D11" s="230"/>
-      <c r="E11" s="230"/>
+      <c r="D11" s="235"/>
+      <c r="E11" s="235"/>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
@@ -28013,8 +28007,8 @@
       <c r="C12" s="117" t="s">
         <v>571</v>
       </c>
-      <c r="D12" s="230"/>
-      <c r="E12" s="230"/>
+      <c r="D12" s="235"/>
+      <c r="E12" s="235"/>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -28026,8 +28020,8 @@
       <c r="C13" s="117" t="s">
         <v>571</v>
       </c>
-      <c r="D13" s="230"/>
-      <c r="E13" s="230"/>
+      <c r="D13" s="235"/>
+      <c r="E13" s="235"/>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
@@ -28039,8 +28033,8 @@
       <c r="C14" s="117" t="s">
         <v>571</v>
       </c>
-      <c r="D14" s="230"/>
-      <c r="E14" s="230"/>
+      <c r="D14" s="235"/>
+      <c r="E14" s="235"/>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -28052,8 +28046,8 @@
       <c r="C15" s="203" t="s">
         <v>571</v>
       </c>
-      <c r="D15" s="230"/>
-      <c r="E15" s="230"/>
+      <c r="D15" s="235"/>
+      <c r="E15" s="235"/>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
@@ -28065,8 +28059,8 @@
       <c r="C16" s="203" t="s">
         <v>571</v>
       </c>
-      <c r="D16" s="230"/>
-      <c r="E16" s="230"/>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
@@ -28539,10 +28533,10 @@
       <c r="S3" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="207" t="s">
+      <c r="T3" s="237" t="s">
         <v>608</v>
       </c>
-      <c r="U3" s="208" t="s">
+      <c r="U3" s="238" t="s">
         <v>42</v>
       </c>
       <c r="V3" s="103"/>
@@ -28635,8 +28629,8 @@
       <c r="S4" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="207"/>
-      <c r="U4" s="208"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="238"/>
       <c r="V4" s="103"/>
       <c r="W4" s="96" t="s">
         <v>43</v>
@@ -28721,10 +28715,10 @@
       <c r="S5" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="T5" s="207" t="s">
+      <c r="T5" s="237" t="s">
         <v>610</v>
       </c>
-      <c r="U5" s="208" t="s">
+      <c r="U5" s="238" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="103"/>
@@ -28810,8 +28804,8 @@
       <c r="S6" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="T6" s="207"/>
-      <c r="U6" s="208"/>
+      <c r="T6" s="237"/>
+      <c r="U6" s="238"/>
       <c r="V6" s="103"/>
       <c r="W6" s="96" t="s">
         <v>43</v>
@@ -29135,13 +29129,13 @@
       <c r="R11" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="S11" s="207" t="s">
+      <c r="S11" s="237" t="s">
         <v>74</v>
       </c>
-      <c r="T11" s="207" t="s">
+      <c r="T11" s="237" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="209" t="s">
+      <c r="U11" s="239" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="103"/>
@@ -29238,9 +29232,9 @@
       <c r="R12" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="S12" s="207"/>
-      <c r="T12" s="207"/>
-      <c r="U12" s="208"/>
+      <c r="S12" s="237"/>
+      <c r="T12" s="237"/>
+      <c r="U12" s="238"/>
       <c r="V12" s="103"/>
       <c r="W12" s="96" t="s">
         <v>43</v>
@@ -33386,211 +33380,211 @@
     <mergeCell ref="U11:U12"/>
   </mergeCells>
   <conditionalFormatting sqref="A19:C19">
-    <cfRule type="expression" dxfId="123" priority="3">
+    <cfRule type="expression" dxfId="100" priority="3">
       <formula>$B19&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="4">
+    <cfRule type="expression" dxfId="99" priority="4">
       <formula>$B19=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="5">
+    <cfRule type="expression" dxfId="98" priority="5">
       <formula>$B19=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:J56 A57:AG69 A2:AG14 W15:AG16 A17:AG18 D19:AG19 U49:AG56">
-    <cfRule type="expression" dxfId="120" priority="53">
+    <cfRule type="expression" dxfId="97" priority="53">
       <formula>$B2&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:K16 A20:AG26 A28:AG28 A29:R29 A30:AG48">
-    <cfRule type="expression" dxfId="119" priority="13">
+    <cfRule type="expression" dxfId="96" priority="13">
       <formula>$B15=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:P16 A20:AG26 A28:AG28 A29:R29 A30:AG48">
-    <cfRule type="expression" dxfId="118" priority="12">
+    <cfRule type="expression" dxfId="95" priority="12">
       <formula>$B15=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:V16 A20:AG26 A28:AG28 A29:R29 A30:AG48">
-    <cfRule type="expression" dxfId="117" priority="11">
+    <cfRule type="expression" dxfId="94" priority="11">
       <formula>$B15&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AG14 L15:AG16 A17:AG18 D19:AG19 A27:I27 A49:J56 N49:O56 U49:AG56 A57:AG69">
-    <cfRule type="expression" dxfId="116" priority="55">
+    <cfRule type="expression" dxfId="93" priority="55">
       <formula>$B2=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AG14 W15:AG16 A17:AG18 D19:AG19 A49:J56 U49:AG56 A57:AG69 N49:O56 A27:I27">
-    <cfRule type="expression" dxfId="115" priority="54">
+    <cfRule type="expression" dxfId="92" priority="54">
       <formula>$B2=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AG69">
-    <cfRule type="expression" dxfId="114" priority="2">
+    <cfRule type="expression" dxfId="91" priority="2">
       <formula>$B2=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:AG27">
-    <cfRule type="expression" dxfId="113" priority="19">
+    <cfRule type="expression" dxfId="90" priority="19">
       <formula>$B27&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J49:J56 J57:K69">
-    <cfRule type="expression" dxfId="112" priority="52">
+    <cfRule type="expression" dxfId="89" priority="52">
       <formula>AND(ISBLANK($J49),ISBLANK($K49),NOT(ISBLANK($E49)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J53:J56">
-    <cfRule type="expression" dxfId="111" priority="29">
+    <cfRule type="expression" dxfId="88" priority="29">
       <formula>_xlfn.ISFORMULA(J53)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="30">
+    <cfRule type="expression" dxfId="87" priority="30">
       <formula>$B53=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:K26 J28:K48">
-    <cfRule type="expression" dxfId="109" priority="10">
+    <cfRule type="expression" dxfId="86" priority="10">
       <formula>AND(ISBLANK($J2),ISBLANK($K2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:Q1048576 F66">
-    <cfRule type="expression" dxfId="108" priority="28">
+    <cfRule type="expression" dxfId="85" priority="28">
       <formula>_xlfn.ISFORMULA(F1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:V27">
-    <cfRule type="expression" dxfId="107" priority="14">
+    <cfRule type="expression" dxfId="84" priority="16">
+      <formula>$B27&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="15">
+      <formula>$B27=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="14">
       <formula>$B27=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="106" priority="15">
-      <formula>$B27=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="105" priority="16">
-      <formula>$B27&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:AG27">
-    <cfRule type="expression" dxfId="104" priority="17">
+    <cfRule type="expression" dxfId="81" priority="18">
+      <formula>$B27=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="17">
       <formula>$B27=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="103" priority="18">
-      <formula>$B27=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49:L50">
-    <cfRule type="expression" dxfId="102" priority="38">
+    <cfRule type="expression" dxfId="79" priority="41">
+      <formula>$B50=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="40">
+      <formula>$B50&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="39">
+      <formula>$B50=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="38">
       <formula>$B50=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="39">
-      <formula>$B50=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="40">
-      <formula>$B50&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="41">
-      <formula>$B50=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K51:L56">
-    <cfRule type="expression" dxfId="98" priority="36">
+    <cfRule type="expression" dxfId="75" priority="48">
+      <formula>$B51&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="36">
       <formula>$B51=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="46">
+    <cfRule type="expression" dxfId="73" priority="46">
       <formula>$B51=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="47">
+    <cfRule type="expression" dxfId="72" priority="47">
       <formula>$B51=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="95" priority="48">
-      <formula>$B51&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49:M56">
-    <cfRule type="expression" dxfId="94" priority="42">
+    <cfRule type="expression" dxfId="71" priority="42">
       <formula>$B49=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="43">
+    <cfRule type="expression" dxfId="70" priority="43">
       <formula>$B49=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49:O56">
-    <cfRule type="expression" dxfId="92" priority="44">
+    <cfRule type="expression" dxfId="69" priority="44">
       <formula>$B49&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M61:M64">
-    <cfRule type="expression" dxfId="91" priority="24">
+    <cfRule type="expression" dxfId="68" priority="27">
+      <formula>$B61&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="26">
+      <formula>$B61=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="25">
+      <formula>$B61=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="24">
       <formula>_xlfn.ISFORMULA(M61)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="90" priority="25">
-      <formula>$B61=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="26">
-      <formula>$B61=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="27">
-      <formula>$B61&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M66">
-    <cfRule type="expression" dxfId="87" priority="20">
+    <cfRule type="expression" dxfId="64" priority="22">
+      <formula>$B66=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="21">
+      <formula>$B66=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="20">
       <formula>_xlfn.ISFORMULA(M66)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="21">
-      <formula>$B66=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="22">
-      <formula>$B66=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="23">
+    <cfRule type="expression" dxfId="61" priority="23">
       <formula>$B66&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P49:T56">
-    <cfRule type="expression" dxfId="83" priority="32">
+    <cfRule type="expression" dxfId="60" priority="32">
       <formula>$B49=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="33">
+    <cfRule type="expression" dxfId="59" priority="33">
       <formula>$B49=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="34">
+    <cfRule type="expression" dxfId="58" priority="34">
       <formula>$B49&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15:V16">
-    <cfRule type="expression" dxfId="80" priority="56">
+    <cfRule type="expression" dxfId="57" priority="56">
       <formula>$B15=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S29:AG29">
-    <cfRule type="expression" dxfId="79" priority="6">
+    <cfRule type="expression" dxfId="56" priority="8">
+      <formula>$B29=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="7">
+      <formula>$B29=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="6">
       <formula>$B29&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="7">
-      <formula>$B29=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="8">
-      <formula>$B29=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W58:AG64">
-    <cfRule type="expression" dxfId="76" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>$B58=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:Z26 X28:Z69">
-    <cfRule type="expression" dxfId="75" priority="51">
+    <cfRule type="expression" dxfId="52" priority="51">
       <formula>AND(ISBLANK($X2),ISBLANK($Y2),ISBLANK($Z2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AC26 AA28:AC69">
-    <cfRule type="expression" dxfId="74" priority="50">
+    <cfRule type="expression" dxfId="51" priority="50">
       <formula>AND(ISBLANK($AA2),ISBLANK($AB2),ISBLANK($AC2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AG26 AD28:AG69">
-    <cfRule type="expression" dxfId="73" priority="49">
+    <cfRule type="expression" dxfId="50" priority="49">
       <formula>AND(ISBLANK($AD2),ISBLANK($AE2),ISBLANK($AF2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33891,10 +33885,10 @@
       <c r="S3" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="207" t="s">
+      <c r="T3" s="237" t="s">
         <v>608</v>
       </c>
-      <c r="U3" s="208" t="s">
+      <c r="U3" s="238" t="s">
         <v>42</v>
       </c>
       <c r="V3" s="103"/>
@@ -33987,8 +33981,8 @@
       <c r="S4" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="207"/>
-      <c r="U4" s="208"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="238"/>
       <c r="V4" s="103"/>
       <c r="W4" s="96" t="s">
         <v>43</v>
@@ -34073,10 +34067,10 @@
       <c r="S5" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="T5" s="207" t="s">
+      <c r="T5" s="237" t="s">
         <v>610</v>
       </c>
-      <c r="U5" s="208" t="s">
+      <c r="U5" s="238" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="103"/>
@@ -34162,8 +34156,8 @@
       <c r="S6" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="T6" s="207"/>
-      <c r="U6" s="208"/>
+      <c r="T6" s="237"/>
+      <c r="U6" s="238"/>
       <c r="V6" s="103"/>
       <c r="W6" s="96" t="s">
         <v>43</v>
@@ -34203,7 +34197,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="113" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" ht="99" x14ac:dyDescent="0.2">
       <c r="A7" s="90">
         <v>15</v>
       </c>
@@ -34487,13 +34481,13 @@
       <c r="R11" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="S11" s="207" t="s">
+      <c r="S11" s="237" t="s">
         <v>74</v>
       </c>
-      <c r="T11" s="207" t="s">
+      <c r="T11" s="237" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="209" t="s">
+      <c r="U11" s="239" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="103"/>
@@ -34590,9 +34584,9 @@
       <c r="R12" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="S12" s="207"/>
-      <c r="T12" s="207"/>
-      <c r="U12" s="208"/>
+      <c r="S12" s="237"/>
+      <c r="T12" s="237"/>
+      <c r="U12" s="238"/>
       <c r="V12" s="103"/>
       <c r="W12" s="96" t="s">
         <v>43</v>
@@ -41209,212 +41203,212 @@
     <mergeCell ref="U11:U12"/>
   </mergeCells>
   <conditionalFormatting sqref="A13:S13">
-    <cfRule type="expression" dxfId="72" priority="17">
+    <cfRule type="expression" dxfId="49" priority="17">
       <formula>$B13&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="18">
+    <cfRule type="expression" dxfId="48" priority="18">
       <formula>$B13=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="19">
+    <cfRule type="expression" dxfId="47" priority="19">
       <formula>$B13=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:S25">
-    <cfRule type="expression" dxfId="69" priority="20">
+    <cfRule type="expression" dxfId="46" priority="20">
       <formula>$B24&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:S34 A36:S36 A45:K45 A47:S49">
-    <cfRule type="expression" dxfId="68" priority="23">
+    <cfRule type="expression" dxfId="45" priority="23">
       <formula>$B33&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="24">
+    <cfRule type="expression" dxfId="44" priority="25">
+      <formula>$B33=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="24">
       <formula>$B33=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="25">
-      <formula>$B33=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AG12 A14:AG14 A15:R17 A18:AG23 A26:AG32 A35:AG35 A37:AG44 A46:AG46 A50:AG74 A75:J80 A81:AG99 T13:AG13 T15:AG17 T24:AG25 T33:AG34 T36:AG36 L45:AG45 T47:AG49 U75:AG80">
-    <cfRule type="expression" dxfId="65" priority="53">
+    <cfRule type="expression" dxfId="42" priority="53">
       <formula>$B2&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AG12 T13:AG13 A14:AG14 A15:R17 T15:AG17 A18:AG23 T24:AG25 A26:AG32 T33:AG34 A35:AG35 T36:AG36 A37:AG44 L45:AG45 A46:AG46 T47:AG49 A50:AG62 A63:R65 T63:AG65 A66:AG74 A75:J80 U75:AG80 A81:AG99 A24:R25 N75:O80">
-    <cfRule type="expression" dxfId="64" priority="54">
+    <cfRule type="expression" dxfId="41" priority="54">
       <formula>$B2=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AG12 T13:AG13 A14:AG14 A15:R17 T15:AG17 A18:AG32 T33:AG34 A35:AG35 T36:AG36 A37:AG44 L45:AG45 A46:AG46 T47:AG49 A50:AG62 A63:R65 T63:AG65 A66:AG74 A75:J80 N75:O80 U75:AG80 A81:AG99">
-    <cfRule type="expression" dxfId="63" priority="55">
+    <cfRule type="expression" dxfId="40" priority="55">
       <formula>$B2=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AG100">
-    <cfRule type="expression" dxfId="62" priority="12">
+    <cfRule type="expression" dxfId="39" priority="12">
       <formula>$B2=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C94:C98">
-    <cfRule type="expression" dxfId="61" priority="7">
+    <cfRule type="expression" dxfId="38" priority="7">
       <formula>$B94=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F94:F98">
-    <cfRule type="expression" dxfId="60" priority="6">
+    <cfRule type="expression" dxfId="37" priority="6">
       <formula>$B94=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79:J80">
-    <cfRule type="expression" dxfId="59" priority="28">
+    <cfRule type="expression" dxfId="36" priority="29">
+      <formula>$B79=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="28">
       <formula>_xlfn.ISFORMULA(J79)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="29">
-      <formula>$B79=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:K74 J75:J80 J81:K99">
-    <cfRule type="expression" dxfId="57" priority="52">
+    <cfRule type="expression" dxfId="34" priority="52">
       <formula>AND(ISBLANK($J2),ISBLANK($K2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:Q1048576 F91">
-    <cfRule type="expression" dxfId="56" priority="26">
+    <cfRule type="expression" dxfId="33" priority="26">
       <formula>_xlfn.ISFORMULA(F1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K75:L76">
-    <cfRule type="expression" dxfId="55" priority="37">
+    <cfRule type="expression" dxfId="32" priority="40">
+      <formula>$B76=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="39">
+      <formula>$B76&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="38">
+      <formula>$B76=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="37">
       <formula>$B76=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="38">
-      <formula>$B76=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="39">
-      <formula>$B76&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="40">
-      <formula>$B76=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K77:L80">
-    <cfRule type="expression" dxfId="51" priority="35">
+    <cfRule type="expression" dxfId="28" priority="45">
+      <formula>$B77=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="47">
+      <formula>$B77&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="46">
+      <formula>$B77=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="35">
       <formula>$B77=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="45">
-      <formula>$B77=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="46">
-      <formula>$B77=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="47">
-      <formula>$B77&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K75:M80">
-    <cfRule type="expression" dxfId="47" priority="41">
+    <cfRule type="expression" dxfId="24" priority="41">
       <formula>$B75=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="42">
+    <cfRule type="expression" dxfId="23" priority="42">
       <formula>$B75=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K75:O80">
-    <cfRule type="expression" dxfId="45" priority="43">
+    <cfRule type="expression" dxfId="22" priority="43">
       <formula>$B75&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M75">
-    <cfRule type="expression" dxfId="44" priority="8">
+    <cfRule type="expression" dxfId="21" priority="11">
+      <formula>$B75=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="10">
+      <formula>$B75=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="9">
+      <formula>$B75&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="8">
       <formula>_xlfn.ISFORMULA(M75)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="9">
-      <formula>$B75&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="10">
-      <formula>$B75=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="11">
-      <formula>$B75=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P75:T80">
-    <cfRule type="expression" dxfId="40" priority="31">
+    <cfRule type="expression" dxfId="17" priority="31">
       <formula>$B75=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="32">
+    <cfRule type="expression" dxfId="16" priority="32">
       <formula>$B75=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="33">
+    <cfRule type="expression" dxfId="15" priority="33">
       <formula>$B75&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R89:AG89">
-    <cfRule type="expression" dxfId="37" priority="48">
+    <cfRule type="expression" dxfId="14" priority="48">
       <formula>_xlfn.ISFORMULA(R89)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S15:S17">
-    <cfRule type="expression" dxfId="36" priority="13">
+    <cfRule type="expression" dxfId="13" priority="15">
+      <formula>$B15=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="14">
+      <formula>$B15=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="13">
       <formula>$B15&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="14">
-      <formula>$B15=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="15">
-      <formula>$B15=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S24:S25">
-    <cfRule type="expression" dxfId="33" priority="56">
+    <cfRule type="expression" dxfId="10" priority="56">
       <formula>$B24=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S63:S65">
-    <cfRule type="expression" dxfId="32" priority="21">
+    <cfRule type="expression" dxfId="9" priority="22">
+      <formula>$B63=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="21">
       <formula>$B63=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="22">
-      <formula>$B63=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W86">
-    <cfRule type="expression" dxfId="30" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>$B86=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W88">
-    <cfRule type="expression" dxfId="29" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$B88=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W90">
-    <cfRule type="expression" dxfId="28" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>$B90=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W82:AG85">
-    <cfRule type="expression" dxfId="27" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$B82=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W94:AG98">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$B94=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:Z100">
-    <cfRule type="expression" dxfId="25" priority="51">
+    <cfRule type="expression" dxfId="2" priority="51">
       <formula>AND(ISBLANK($X2),ISBLANK($Y2),ISBLANK($Z2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AC100">
-    <cfRule type="expression" dxfId="24" priority="50">
+    <cfRule type="expression" dxfId="1" priority="50">
       <formula>AND(ISBLANK($AA2),ISBLANK($AB2),ISBLANK($AC2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AG100">
-    <cfRule type="expression" dxfId="23" priority="49">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>AND(ISBLANK($AD2),ISBLANK($AE2),ISBLANK($AF2),NOT(ISBLANK($E2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -8553,9 +8553,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ196"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AH197"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="3" customWidth="1"/>
@@ -8592,7 +8592,7 @@
     <col min="35" max="16384" width="10.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="79" customFormat="1" ht="94.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" s="79" customFormat="1" ht="94.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="7" customFormat="1" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" s="7" customFormat="1" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A2" s="37">
         <v>10</v>
       </c>
@@ -8745,7 +8745,7 @@
       <c r="AF2" s="76"/>
       <c r="AG2" s="74"/>
     </row>
-    <row r="3" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" ht="45" customHeight="1" ns3:dyDescent="0.2">
       <c r="A3" s="37">
         <v>11</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A4" s="37">
         <v>12</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="113.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" ht="113.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A5" s="37">
         <v>13</v>
       </c>
@@ -9031,7 +9031,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A6" s="37">
         <v>14</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" ht="42.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A7" s="37">
         <v>15</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A8" s="50">
         <v>20</v>
       </c>
@@ -9268,7 +9268,7 @@
       <c r="AF8" s="76"/>
       <c r="AG8" s="74"/>
     </row>
-    <row r="9" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A9" s="37">
         <v>21</v>
       </c>
@@ -9320,7 +9320,7 @@
       <c r="AF9" s="76"/>
       <c r="AG9" s="74"/>
     </row>
-    <row r="10" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A10" s="53">
         <v>211</v>
       </c>
@@ -9372,7 +9372,7 @@
       <c r="AF10" s="76"/>
       <c r="AG10" s="74"/>
     </row>
-    <row r="11" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A11" s="54">
         <v>211.1</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A12" s="53">
         <v>211.2</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="147.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" ht="147.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A13" s="53">
         <v>211.3</v>
       </c>
@@ -9657,7 +9657,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:33" s="213" customFormat="1" ht="43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" s="213" customFormat="1" ht="43" ns3:dyDescent="0.2">
       <c r="A14" s="207">
         <v>211.4</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:33" s="213" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" s="213" customFormat="1" ht="15" ns3:dyDescent="0.2">
       <c r="A15" s="207">
         <v>211.9</v>
       </c>
@@ -9797,7 +9797,7 @@
       <c r="AF15" s="76"/>
       <c r="AG15" s="74"/>
     </row>
-    <row r="16" spans="1:33" s="213" customFormat="1" ht="43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" s="213" customFormat="1" ht="43" ns3:dyDescent="0.2">
       <c r="A16" s="207">
         <v>211.91</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:33" s="213" customFormat="1" ht="43" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" s="213" customFormat="1" ht="43" ns3:dyDescent="0.2">
       <c r="A17" s="207">
         <v>211.92</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A18" s="53">
         <v>212</v>
       </c>
@@ -10018,7 +10018,7 @@
       <c r="AF18" s="76"/>
       <c r="AG18" s="74"/>
     </row>
-    <row r="19" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A19" s="53">
         <v>212.1</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A20" s="53">
         <v>212.2</v>
       </c>
@@ -10196,7 +10196,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A21" s="53">
         <v>212.3</v>
       </c>
@@ -10282,7 +10282,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" ht="101.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A22" s="53">
         <v>212.4</v>
       </c>
@@ -10378,7 +10378,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" ht="101.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A23" s="53">
         <v>212.5</v>
       </c>
@@ -10474,7 +10474,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A24" s="53">
         <v>213</v>
       </c>
@@ -10519,7 +10519,7 @@
       <c r="AF24" s="76"/>
       <c r="AG24" s="74"/>
     </row>
-    <row r="25" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A25" s="53">
         <v>213.1</v>
       </c>
@@ -10564,7 +10564,7 @@
       <c r="AF25" s="76"/>
       <c r="AG25" s="74"/>
     </row>
-    <row r="26" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A26" s="53">
         <v>213.11</v>
       </c>
@@ -10656,7 +10656,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A27" s="53">
         <v>213.12</v>
       </c>
@@ -10742,7 +10742,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A28" s="53">
         <v>213.13</v>
       </c>
@@ -10828,7 +10828,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A29" s="53">
         <v>213.2</v>
       </c>
@@ -10873,7 +10873,7 @@
       <c r="AF29" s="76"/>
       <c r="AG29" s="74"/>
     </row>
-    <row r="30" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A30" s="53">
         <v>213.21</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A31" s="53">
         <v>213.22</v>
       </c>
@@ -11051,7 +11051,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A32" s="53">
         <v>213.23</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A33" s="53">
         <v>213.3</v>
       </c>
@@ -11186,7 +11186,7 @@
       <c r="AF33" s="76"/>
       <c r="AG33" s="74"/>
     </row>
-    <row r="34" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A34" s="53">
         <v>213.31</v>
       </c>
@@ -11282,7 +11282,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A35" s="53">
         <v>213.32</v>
       </c>
@@ -11372,7 +11372,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" ht="101.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A36" s="53">
         <v>213.33</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33" ht="101.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A37" s="53">
         <v>213.34</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A38" s="53">
         <v>214</v>
       </c>
@@ -11607,7 +11607,7 @@
       <c r="AF38" s="76"/>
       <c r="AG38" s="74"/>
     </row>
-    <row r="39" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A39" s="53">
         <v>214.1</v>
       </c>
@@ -11652,7 +11652,7 @@
       <c r="AF39" s="76"/>
       <c r="AG39" s="74"/>
     </row>
-    <row r="40" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A40" s="53">
         <v>214.11</v>
       </c>
@@ -11697,7 +11697,7 @@
       <c r="AF40" s="76"/>
       <c r="AG40" s="74"/>
     </row>
-    <row r="41" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A41" s="53">
         <v>214.11099999999999</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A42" s="53">
         <v>214.11199999999999</v>
       </c>
@@ -11873,7 +11873,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:33" s="33" customFormat="1" ht="74.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:33" s="33" customFormat="1" ht="74.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A43" s="53">
         <v>214.113</v>
       </c>
@@ -11959,7 +11959,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A44" s="53">
         <v>214.12</v>
       </c>
@@ -12004,7 +12004,7 @@
       <c r="AF44" s="76"/>
       <c r="AG44" s="74"/>
     </row>
-    <row r="45" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A45" s="53">
         <v>214.12100000000001</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A46" s="53">
         <v>214.12200000000001</v>
       </c>
@@ -12182,7 +12182,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:33" s="33" customFormat="1" ht="74.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:33" s="33" customFormat="1" ht="74.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A47" s="53">
         <v>214.12299999999999</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A48" s="53">
         <v>214.7</v>
       </c>
@@ -12313,7 +12313,7 @@
       <c r="AF48" s="76"/>
       <c r="AG48" s="74"/>
     </row>
-    <row r="49" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A49" s="53">
         <v>214.71</v>
       </c>
@@ -12365,7 +12365,7 @@
       <c r="AF49" s="76"/>
       <c r="AG49" s="74"/>
     </row>
-    <row r="50" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A50" s="53">
         <v>214.71100000000001</v>
       </c>
@@ -12457,7 +12457,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:33" s="33" customFormat="1" ht="49.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A51" s="53">
         <v>214.71199999999999</v>
       </c>
@@ -12543,7 +12543,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:33" s="33" customFormat="1" ht="74.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:33" s="33" customFormat="1" ht="74.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A52" s="53">
         <v>214.71299999999999</v>
       </c>
@@ -12629,7 +12629,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="185" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:33" ht="185" customHeight="1" ns3:dyDescent="0.2">
       <c r="A53" s="53">
         <v>214.72</v>
       </c>
@@ -12726,7 +12726,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:33" ht="22.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A54" s="53">
         <v>214.8</v>
       </c>
@@ -12771,7 +12771,7 @@
       <c r="AF54" s="76"/>
       <c r="AG54" s="74"/>
     </row>
-    <row r="55" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A55" s="53">
         <v>214.81</v>
       </c>
@@ -12816,7 +12816,7 @@
       <c r="AF55" s="76"/>
       <c r="AG55" s="74"/>
     </row>
-    <row r="56" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A56" s="53">
         <v>214.81100000000001</v>
       </c>
@@ -12910,7 +12910,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A57" s="53">
         <v>214.81200000000001</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A58" s="53">
         <v>214.81299999999999</v>
       </c>
@@ -13082,7 +13082,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A59" s="53">
         <v>215</v>
       </c>
@@ -13127,7 +13127,7 @@
       <c r="AF59" s="76"/>
       <c r="AG59" s="74"/>
     </row>
-    <row r="60" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A60" s="53">
         <v>215.1</v>
       </c>
@@ -13172,7 +13172,7 @@
       <c r="AF60" s="76"/>
       <c r="AG60" s="74"/>
     </row>
-    <row r="61" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A61" s="53">
         <v>215.11</v>
       </c>
@@ -13264,7 +13264,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A62" s="53">
         <v>215.12</v>
       </c>
@@ -13350,7 +13350,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A63" s="53">
         <v>215.13</v>
       </c>
@@ -13436,7 +13436,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A64" s="53">
         <v>215.4</v>
       </c>
@@ -13481,7 +13481,7 @@
       <c r="AF64" s="76"/>
       <c r="AG64" s="74"/>
     </row>
-    <row r="65" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A65" s="53">
         <v>215.41</v>
       </c>
@@ -13573,7 +13573,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A66" s="53">
         <v>215.42</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A67" s="53">
         <v>215.43</v>
       </c>
@@ -13745,7 +13745,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A68" s="37">
         <v>22</v>
       </c>
@@ -13790,7 +13790,7 @@
       <c r="AF68" s="76"/>
       <c r="AG68" s="74"/>
     </row>
-    <row r="69" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A69" s="53">
         <v>221</v>
       </c>
@@ -13835,7 +13835,7 @@
       <c r="AF69" s="76"/>
       <c r="AG69" s="74"/>
     </row>
-    <row r="70" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A70" s="53">
         <v>221.1</v>
       </c>
@@ -13880,7 +13880,7 @@
       <c r="AF70" s="76"/>
       <c r="AG70" s="74"/>
     </row>
-    <row r="71" spans="1:33" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:33" ht="112" customHeight="1" ns3:dyDescent="0.2">
       <c r="A71" s="53">
         <v>221.11</v>
       </c>
@@ -13975,7 +13975,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A72" s="53">
         <v>221.12</v>
       </c>
@@ -14072,7 +14072,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A73" s="53">
         <v>221.12</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A74" s="53">
         <v>221.12</v>
       </c>
@@ -14257,7 +14257,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A75" s="53">
         <v>221.13</v>
       </c>
@@ -14362,7 +14362,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A76" s="53">
         <v>221.13</v>
       </c>
@@ -14458,7 +14458,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A77" s="53">
         <v>221.13</v>
       </c>
@@ -14554,7 +14554,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A78" s="53">
         <v>221.2</v>
       </c>
@@ -14606,7 +14606,7 @@
       <c r="AF78" s="76"/>
       <c r="AG78" s="74"/>
     </row>
-    <row r="79" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A79" s="53">
         <v>221.21</v>
       </c>
@@ -14658,7 +14658,7 @@
       <c r="AF79" s="76"/>
       <c r="AG79" s="74"/>
     </row>
-    <row r="80" spans="1:33" s="33" customFormat="1" ht="74.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:33" s="33" customFormat="1" ht="74.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A80" s="53">
         <v>221.21100000000001</v>
       </c>
@@ -14757,7 +14757,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="81" spans="1:36" s="33" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:36" s="33" customFormat="1" ns3:dyDescent="0.15">
       <c r="A81" s="53">
         <v>221.21199999999999</v>
       </c>
@@ -14850,7 +14850,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="82" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" ns3:dyDescent="0.15">
       <c r="A82" s="53">
         <v>221.21299999999999</v>
       </c>
@@ -14954,7 +14954,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="83" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" ns3:dyDescent="0.15">
       <c r="A83" s="53">
         <v>221.21299999999999</v>
       </c>
@@ -15050,7 +15050,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" ns3:dyDescent="0.15">
       <c r="A84" s="53">
         <v>221.214</v>
       </c>
@@ -15154,7 +15154,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" ns3:dyDescent="0.15">
       <c r="A85" s="53">
         <v>221.214</v>
       </c>
@@ -15259,7 +15259,7 @@
       </c>
       <c r="AJ85" s="36"/>
     </row>
-    <row r="86" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" ns3:dyDescent="0.15">
       <c r="A86" s="53">
         <v>221.214</v>
       </c>
@@ -15357,7 +15357,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="87" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:36" s="33" customFormat="1" ht="53.25" customHeight="1" ns3:dyDescent="0.15">
       <c r="A87" s="53">
         <v>221.215</v>
       </c>
@@ -15453,7 +15453,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="88" spans="1:36" s="33" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:36" s="33" customFormat="1" ht="40" customHeight="1" ns3:dyDescent="0.2">
       <c r="A88" s="53">
         <v>221.21600000000001</v>
       </c>
@@ -15540,7 +15540,7 @@
       <c r="AF88" s="76"/>
       <c r="AG88" s="74"/>
     </row>
-    <row r="89" spans="1:36" s="33" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:36" s="33" customFormat="1" ht="40" customHeight="1" ns3:dyDescent="0.2">
       <c r="A89" s="53">
         <v>221.21600000000001</v>
       </c>
@@ -15627,7 +15627,7 @@
       <c r="AF89" s="76"/>
       <c r="AG89" s="74"/>
     </row>
-    <row r="90" spans="1:36" s="33" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:36" s="33" customFormat="1" ht="40" customHeight="1" ns3:dyDescent="0.2">
       <c r="A90" s="53">
         <v>221.21700000000001</v>
       </c>
@@ -15716,7 +15716,7 @@
       <c r="AF90" s="76"/>
       <c r="AG90" s="74"/>
     </row>
-    <row r="91" spans="1:36" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:36" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A91" s="53">
         <v>221.3</v>
       </c>
@@ -15770,7 +15770,7 @@
       <c r="AF91" s="76"/>
       <c r="AG91" s="74"/>
     </row>
-    <row r="92" spans="1:36" ht="25.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:36" ht="25.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A92" s="53">
         <v>221.31</v>
       </c>
@@ -15822,7 +15822,7 @@
       <c r="AF92" s="76"/>
       <c r="AG92" s="74"/>
     </row>
-    <row r="93" spans="1:36" ht="25.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:36" ht="25.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A93" s="53">
         <v>221.31100000000001</v>
       </c>
@@ -15933,7 +15933,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="94" spans="1:36" ht="25.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:36" ht="25.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A94" s="53">
         <v>221.31200000000001</v>
       </c>
@@ -16039,7 +16039,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="95" spans="1:36" ht="25.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:36" ht="25.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A95" s="53">
         <v>221.31100000000001</v>
       </c>
@@ -16138,7 +16138,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:36" ht="25.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:36" ht="25.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A96" s="53">
         <v>221.31200000000001</v>
       </c>
@@ -16235,7 +16235,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:33" ht="101.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A97" s="53">
         <v>221.31100000000001</v>
       </c>
@@ -16326,7 +16326,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:33" ht="101.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A98" s="53">
         <v>221.31200000000001</v>
       </c>
@@ -16417,7 +16417,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A99" s="53">
         <v>221.31100000000001</v>
       </c>
@@ -16506,7 +16506,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A100" s="53">
         <v>221.31200000000001</v>
       </c>
@@ -16595,7 +16595,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A101" s="53">
         <v>221.32</v>
       </c>
@@ -16647,7 +16647,7 @@
       <c r="AF101" s="76"/>
       <c r="AG101" s="74"/>
     </row>
-    <row r="102" spans="1:33" s="33" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:33" s="33" customFormat="1" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A102" s="53">
         <v>221.321</v>
       </c>
@@ -16754,7 +16754,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="103" spans="1:33" s="33" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:33" s="33" customFormat="1" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A103" s="53">
         <v>221.322</v>
       </c>
@@ -16857,7 +16857,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="122.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:33" ht="122.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A104" s="85">
         <v>221.33</v>
       </c>
@@ -16944,7 +16944,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="122.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:33" ht="122.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A105" s="85">
         <v>221.33</v>
       </c>
@@ -17030,7 +17030,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="122.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:33" ht="122.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A106" s="85">
         <v>221.33</v>
       </c>
@@ -17117,7 +17117,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="122.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:33" ht="122.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A107" s="85">
         <v>221.33</v>
       </c>
@@ -17202,7 +17202,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="122.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:33" ht="122.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A108" s="85">
         <v>221.34</v>
       </c>
@@ -17289,7 +17289,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="122.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:33" ht="122.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A109" s="85">
         <v>221.34</v>
       </c>
@@ -17374,7 +17374,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="122.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:33" ht="122.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A110" s="85">
         <v>221.34</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A111" s="53">
         <v>222</v>
       </c>
@@ -17515,7 +17515,7 @@
       <c r="AF111" s="76"/>
       <c r="AG111" s="74"/>
     </row>
-    <row r="112" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A112" s="53">
         <v>222.1</v>
       </c>
@@ -17567,7 +17567,7 @@
       <c r="AF112" s="76"/>
       <c r="AG112" s="74"/>
     </row>
-    <row r="113" spans="1:33" ht="109" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:33" ht="109" customHeight="1" ns3:dyDescent="0.2">
       <c r="A113" s="42">
         <v>222.11</v>
       </c>
@@ -17670,7 +17670,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A114" s="42">
         <v>222.12</v>
       </c>
@@ -17768,7 +17768,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="176" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:33" ht="176" customHeight="1" ns3:dyDescent="0.2">
       <c r="A115" s="42">
         <v>222.13</v>
       </c>
@@ -17866,7 +17866,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A116" s="53">
         <v>222.2</v>
       </c>
@@ -17964,7 +17964,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A117" s="53">
         <v>222.2</v>
       </c>
@@ -18062,7 +18062,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A118" s="53">
         <v>222.2</v>
       </c>
@@ -18162,7 +18162,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A119" s="53">
         <v>222.3</v>
       </c>
@@ -18214,7 +18214,7 @@
       <c r="AF119" s="76"/>
       <c r="AG119" s="74"/>
     </row>
-    <row r="120" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A120" s="53">
         <v>222.31</v>
       </c>
@@ -18314,7 +18314,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A121" s="53">
         <v>222.31</v>
       </c>
@@ -18414,7 +18414,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A122" s="53">
         <v>222.32</v>
       </c>
@@ -18514,7 +18514,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A123" s="53">
         <v>222.32</v>
       </c>
@@ -18614,7 +18614,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A124" s="53">
         <v>222.5</v>
       </c>
@@ -18718,7 +18718,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A125" s="53">
         <v>222.5</v>
       </c>
@@ -18806,7 +18806,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A126" s="53">
         <v>222.6</v>
       </c>
@@ -18862,7 +18862,7 @@
       <c r="AF126" s="76"/>
       <c r="AG126" s="74"/>
     </row>
-    <row r="127" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A127" s="53">
         <v>222.61</v>
       </c>
@@ -18957,7 +18957,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A128" s="53">
         <v>222.62</v>
       </c>
@@ -19055,7 +19055,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A129" s="53">
         <v>223</v>
       </c>
@@ -19100,7 +19100,7 @@
       <c r="AF129" s="76"/>
       <c r="AG129" s="74"/>
     </row>
-    <row r="130" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A130" s="53">
         <v>223.2</v>
       </c>
@@ -19145,7 +19145,7 @@
       <c r="AF130" s="76"/>
       <c r="AG130" s="74"/>
     </row>
-    <row r="131" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A131" s="53">
         <v>223.21</v>
       </c>
@@ -19233,7 +19233,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A132" s="53">
         <v>223.22</v>
       </c>
@@ -19321,7 +19321,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A133" s="53">
         <v>226</v>
       </c>
@@ -19407,7 +19407,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A134" s="53">
         <v>226</v>
       </c>
@@ -19508,7 +19508,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A135" s="53">
         <v>227</v>
       </c>
@@ -19602,7 +19602,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A136" s="53">
         <v>228</v>
       </c>
@@ -19691,7 +19691,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A137" s="37">
         <v>23</v>
       </c>
@@ -19736,7 +19736,7 @@
       <c r="AF137" s="76"/>
       <c r="AG137" s="74"/>
     </row>
-    <row r="138" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A138" s="53">
         <v>232</v>
       </c>
@@ -19781,7 +19781,7 @@
       <c r="AF138" s="76"/>
       <c r="AG138" s="74"/>
     </row>
-    <row r="139" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A139" s="53">
         <v>232.1</v>
       </c>
@@ -19874,7 +19874,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="76.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:33" ht="76.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A140" s="53">
         <v>236</v>
       </c>
@@ -19943,7 +19943,7 @@
       <c r="AF140" s="76"/>
       <c r="AG140" s="74"/>
     </row>
-    <row r="141" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A141" s="37">
         <v>24</v>
       </c>
@@ -19988,7 +19988,7 @@
       <c r="AF141" s="76"/>
       <c r="AG141" s="74"/>
     </row>
-    <row r="142" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A142" s="37">
         <v>241</v>
       </c>
@@ -20080,7 +20080,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A143" s="37">
         <v>242</v>
       </c>
@@ -20168,7 +20168,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A144" s="37">
         <v>243</v>
       </c>
@@ -20256,7 +20256,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A145" s="37">
         <v>244</v>
       </c>
@@ -20344,7 +20344,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A146" s="37">
         <v>245</v>
       </c>
@@ -20432,7 +20432,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A147" s="37">
         <v>246</v>
       </c>
@@ -20520,7 +20520,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A148" s="37">
         <v>25</v>
       </c>
@@ -20565,7 +20565,7 @@
       <c r="AF148" s="76"/>
       <c r="AG148" s="74"/>
     </row>
-    <row r="149" spans="1:33" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:33" ht="29" customHeight="1" ns3:dyDescent="0.2">
       <c r="A149" s="53">
         <v>251</v>
       </c>
@@ -20652,7 +20652,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A150" s="53">
         <v>252</v>
       </c>
@@ -20735,7 +20735,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A151" s="53">
         <v>253</v>
       </c>
@@ -20820,7 +20820,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A152" s="53">
         <v>254</v>
       </c>
@@ -20911,7 +20911,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A153" s="53">
         <v>254</v>
       </c>
@@ -21009,7 +21009,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A154" s="53">
         <v>254</v>
       </c>
@@ -21103,7 +21103,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A155" s="37">
         <v>26</v>
       </c>
@@ -21193,7 +21193,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A156" s="50">
         <v>30</v>
       </c>
@@ -21245,7 +21245,7 @@
       <c r="AF156" s="76"/>
       <c r="AG156" s="74"/>
     </row>
-    <row r="157" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A157" s="50">
         <v>31</v>
       </c>
@@ -21289,7 +21289,7 @@
       <c r="AF157" s="76"/>
       <c r="AG157" s="74"/>
     </row>
-    <row r="158" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A158" s="50">
         <v>32</v>
       </c>
@@ -21333,7 +21333,7 @@
       <c r="AF158" s="76"/>
       <c r="AG158" s="74"/>
     </row>
-    <row r="159" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A159" s="37">
         <v>33</v>
       </c>
@@ -21422,7 +21422,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A160" s="37">
         <v>34</v>
       </c>
@@ -21502,7 +21502,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A161" s="37">
         <v>35</v>
       </c>
@@ -21582,7 +21582,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A162" s="37">
         <v>36</v>
       </c>
@@ -21662,7 +21662,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A163" s="37">
         <v>40</v>
       </c>
@@ -21707,7 +21707,7 @@
       <c r="AF163" s="76"/>
       <c r="AG163" s="74"/>
     </row>
-    <row r="164" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A164" s="37">
         <v>41</v>
       </c>
@@ -21790,7 +21790,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A165" s="50">
         <v>60</v>
       </c>
@@ -21835,7 +21835,7 @@
       <c r="AF165" s="76"/>
       <c r="AG165" s="74"/>
     </row>
-    <row r="166" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A166" s="37">
         <v>62</v>
       </c>
@@ -21880,7 +21880,7 @@
       <c r="AF166" s="76"/>
       <c r="AG166" s="74"/>
     </row>
-    <row r="167" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A167" s="37">
         <v>70</v>
       </c>
@@ -21925,7 +21925,7 @@
       <c r="AF167" s="76"/>
       <c r="AG167" s="74"/>
     </row>
-    <row r="168" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A168" s="37">
         <v>71</v>
       </c>
@@ -21970,7 +21970,7 @@
       <c r="AF168" s="76"/>
       <c r="AG168" s="74"/>
     </row>
-    <row r="169" spans="1:33" ht="126.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:33" ht="126.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A169" s="53">
         <v>711</v>
       </c>
@@ -22057,7 +22057,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A170" s="53">
         <v>712</v>
       </c>
@@ -22148,7 +22148,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="151" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:33" ht="151" customHeight="1" ns3:dyDescent="0.2">
       <c r="A171" s="53">
         <v>713</v>
       </c>
@@ -22235,7 +22235,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A172" s="37">
         <v>72</v>
       </c>
@@ -22280,7 +22280,7 @@
       <c r="AF172" s="76"/>
       <c r="AG172" s="74"/>
     </row>
-    <row r="173" spans="1:33" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:33" ht="101.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A173" s="37">
         <v>721</v>
       </c>
@@ -22377,7 +22377,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A174" s="37">
         <v>721</v>
       </c>
@@ -22477,7 +22477,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="275.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:33" ht="275.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A175" s="37">
         <v>73</v>
       </c>
@@ -22554,7 +22554,7 @@
       <c r="AF175" s="76"/>
       <c r="AG175" s="74"/>
     </row>
-    <row r="176" spans="1:33" ht="225.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:33" ht="225.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A176" s="37">
         <v>75</v>
       </c>
@@ -22605,7 +22605,7 @@
       <c r="AF176" s="76"/>
       <c r="AG176" s="74"/>
     </row>
-    <row r="177" spans="1:33" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:33" ht="22.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A177" s="37">
         <v>751</v>
       </c>
@@ -22656,7 +22656,7 @@
       <c r="AF177" s="76"/>
       <c r="AG177" s="74"/>
     </row>
-    <row r="178" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A178" s="37">
         <v>752</v>
       </c>
@@ -22701,7 +22701,7 @@
       <c r="AF178" s="76"/>
       <c r="AG178" s="74"/>
     </row>
-    <row r="179" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A179" s="37">
         <v>753</v>
       </c>
@@ -22746,7 +22746,7 @@
       <c r="AF179" s="76"/>
       <c r="AG179" s="74"/>
     </row>
-    <row r="180" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A180" s="37">
         <v>754</v>
       </c>
@@ -22791,7 +22791,7 @@
       <c r="AF180" s="76"/>
       <c r="AG180" s="74"/>
     </row>
-    <row r="181" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A181" s="37">
         <v>755</v>
       </c>
@@ -22836,20 +22836,22 @@
       <c r="AF181" s="76"/>
       <c r="AG181" s="74"/>
     </row>
-    <row r="182" spans="1:33" ht="45.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:33" ht="45.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A182" s="37">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B182" s="38">
-        <f t="shared" si="52"/>
         <v>2</v>
       </c>
-      <c r="C182" s="55" t="s">
-        <v>410</v>
-      </c>
-      <c r="D182" s="39" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">            Annualized Moderator Booster Replacements</v>
+      <c r="C182" s="55" t="inlineStr">
+        <is>
+          <t>Annualized Integrated Heat Transfer Vessel Replacements</t>
+        </is>
+      </c>
+      <c r="D182" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Annualized Integrated Heat Transfer Vessel Replacements</t>
+        </is>
       </c>
       <c r="E182" s="39"/>
       <c r="F182" s="39"/>
@@ -22881,20 +22883,20 @@
       <c r="AF182" s="76"/>
       <c r="AG182" s="74"/>
     </row>
-    <row r="183" spans="1:33" ht="45.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:33" ht="45.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A183" s="37">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B183" s="38">
         <f t="shared" si="52"/>
         <v>2</v>
       </c>
       <c r="C183" s="55" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D183" s="39" t="str">
         <f t="shared" si="51"/>
-        <v xml:space="preserve">            Annualized Plant Maintenance (Misc.)</v>
+        <v xml:space="preserve">            Annualized Moderator Booster Replacements</v>
       </c>
       <c r="E183" s="39"/>
       <c r="F183" s="39"/>
@@ -22910,10 +22912,10 @@
       <c r="P183" s="49"/>
       <c r="Q183" s="65"/>
       <c r="R183" s="49"/>
-      <c r="S183" s="205"/>
-      <c r="T183" s="205"/>
+      <c r="S183" s="204"/>
+      <c r="T183" s="204"/>
       <c r="U183" s="49"/>
-      <c r="V183" s="205"/>
+      <c r="V183" s="204"/>
       <c r="W183" s="74"/>
       <c r="X183" s="77"/>
       <c r="Y183" s="77"/>
@@ -22926,20 +22928,20 @@
       <c r="AF183" s="76"/>
       <c r="AG183" s="74"/>
     </row>
-    <row r="184" spans="1:33" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:33" ht="45.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A184" s="37">
-        <v>759.1</v>
+        <v>759</v>
       </c>
       <c r="B184" s="38">
-        <f t="shared" ref="B184:B191" si="53">IF(ISNUMBER(A184),IF(AND(A184=INT(A184),MOD(A184,10)=0),0,IF(AND(A184=INT(A184),LEN(A184)=2),1,IF(AND(A184=INT(A184),LEN(A184)=3),2,LEN(A184)-FIND(".",A184)+2))),"")</f>
-        <v>3</v>
+        <f t="shared" si="52"/>
+        <v>2</v>
       </c>
       <c r="C184" s="55" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D184" s="39" t="str">
-        <f t="shared" ref="D184:D191" si="54">REPT("   ",B184*2)&amp;C184</f>
-        <v xml:space="preserve">                  Annualized Building and Structural Maintenance (Accounts 212–215)</v>
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">            Annualized Plant Maintenance (Misc.)</v>
       </c>
       <c r="E184" s="39"/>
       <c r="F184" s="39"/>
@@ -22971,20 +22973,20 @@
       <c r="AF184" s="76"/>
       <c r="AG184" s="74"/>
     </row>
-    <row r="185" spans="1:33" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:33" ht="56" customHeight="1" ns3:dyDescent="0.2">
       <c r="A185" s="37">
-        <v>759.2</v>
+        <v>759.1</v>
       </c>
       <c r="B185" s="38">
-        <f t="shared" si="53"/>
+        <f t="shared" ref="B184:B191" si="53">IF(ISNUMBER(A185),IF(AND(A185=INT(A185),MOD(A185,10)=0),0,IF(AND(A185=INT(A185),LEN(A185)=2),1,IF(AND(A185=INT(A185),LEN(A185)=3),2,LEN(A185)-FIND(".",A185)+2))),"")</f>
         <v>3</v>
       </c>
       <c r="C185" s="55" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D185" s="39" t="str">
-        <f t="shared" si="54"/>
-        <v xml:space="preserve">                  Annualized Main Heat Transport System Maintenance (Accounts 222.1–222.3 and 222.6)</v>
+        <f t="shared" ref="D184:D191" si="54">REPT("   ",B185*2)&amp;C185</f>
+        <v xml:space="preserve">                  Annualized Building and Structural Maintenance (Accounts 212–215)</v>
       </c>
       <c r="E185" s="39"/>
       <c r="F185" s="39"/>
@@ -23016,20 +23018,20 @@
       <c r="AF185" s="76"/>
       <c r="AG185" s="74"/>
     </row>
-    <row r="186" spans="1:33" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:33" ht="56" customHeight="1" ns3:dyDescent="0.2">
       <c r="A186" s="37">
-        <v>759.3</v>
+        <v>759.2</v>
       </c>
       <c r="B186" s="38">
         <f t="shared" si="53"/>
         <v>3</v>
       </c>
       <c r="C186" s="55" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D186" s="39" t="str">
         <f t="shared" si="54"/>
-        <v xml:space="preserve">                  Annualized Safety System Maintenance (Account 223)</v>
+        <v xml:space="preserve">                  Annualized Main Heat Transport System Maintenance (Accounts 222.1–222.3 and 222.6)</v>
       </c>
       <c r="E186" s="39"/>
       <c r="F186" s="39"/>
@@ -23061,20 +23063,20 @@
       <c r="AF186" s="76"/>
       <c r="AG186" s="74"/>
     </row>
-    <row r="187" spans="1:33" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:33" ht="56" customHeight="1" ns3:dyDescent="0.2">
       <c r="A187" s="37">
-        <v>759.4</v>
+        <v>759.3</v>
       </c>
       <c r="B187" s="38">
         <f t="shared" si="53"/>
         <v>3</v>
       </c>
       <c r="C187" s="55" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D187" s="39" t="str">
         <f t="shared" si="54"/>
-        <v xml:space="preserve">                  Annualized Reactor Plant Equipment Maintenance (Accounts 221.11, 226, and 228)</v>
+        <v xml:space="preserve">                  Annualized Safety System Maintenance (Account 223)</v>
       </c>
       <c r="E187" s="39"/>
       <c r="F187" s="39"/>
@@ -23106,20 +23108,20 @@
       <c r="AF187" s="76"/>
       <c r="AG187" s="74"/>
     </row>
-    <row r="188" spans="1:33" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:33" ht="56" customHeight="1" ns3:dyDescent="0.2">
       <c r="A188" s="37">
-        <v>759.5</v>
+        <v>759.4</v>
       </c>
       <c r="B188" s="38">
         <f t="shared" si="53"/>
         <v>3</v>
       </c>
       <c r="C188" s="55" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D188" s="39" t="str">
         <f t="shared" si="54"/>
-        <v xml:space="preserve">                  Annualized Reactor I&amp;C Maintenance (Account 227)</v>
+        <v xml:space="preserve">                  Annualized Reactor Plant Equipment Maintenance (Accounts 221.11, 226, and 228)</v>
       </c>
       <c r="E188" s="39"/>
       <c r="F188" s="39"/>
@@ -23151,20 +23153,20 @@
       <c r="AF188" s="76"/>
       <c r="AG188" s="74"/>
     </row>
-    <row r="189" spans="1:33" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:33" ht="56" customHeight="1" ns3:dyDescent="0.2">
       <c r="A189" s="37">
-        <v>759.6</v>
+        <v>759.5</v>
       </c>
       <c r="B189" s="38">
         <f t="shared" si="53"/>
         <v>3</v>
       </c>
       <c r="C189" s="55" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D189" s="39" t="str">
         <f t="shared" si="54"/>
-        <v xml:space="preserve">                  Annualized Energy Conversion System Maintenance (Account 23)</v>
+        <v xml:space="preserve">                  Annualized Reactor I&amp;C Maintenance (Account 227)</v>
       </c>
       <c r="E189" s="39"/>
       <c r="F189" s="39"/>
@@ -23196,20 +23198,20 @@
       <c r="AF189" s="76"/>
       <c r="AG189" s="74"/>
     </row>
-    <row r="190" spans="1:33" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:33" ht="56" customHeight="1" ns3:dyDescent="0.2">
       <c r="A190" s="37">
-        <v>759.7</v>
+        <v>759.6</v>
       </c>
       <c r="B190" s="38">
         <f t="shared" si="53"/>
         <v>3</v>
       </c>
       <c r="C190" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D190" s="39" t="str">
         <f t="shared" si="54"/>
-        <v xml:space="preserve">                  Annualized Electrical Equipment Maintenance (Account 24)</v>
+        <v xml:space="preserve">                  Annualized Energy Conversion System Maintenance (Account 23)</v>
       </c>
       <c r="E190" s="39"/>
       <c r="F190" s="39"/>
@@ -23241,20 +23243,20 @@
       <c r="AF190" s="76"/>
       <c r="AG190" s="74"/>
     </row>
-    <row r="191" spans="1:33" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:33" ht="56" customHeight="1" ns3:dyDescent="0.2">
       <c r="A191" s="37">
-        <v>759.8</v>
+        <v>759.7</v>
       </c>
       <c r="B191" s="38">
         <f t="shared" si="53"/>
         <v>3</v>
       </c>
       <c r="C191" s="55" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D191" s="39" t="str">
         <f t="shared" si="54"/>
-        <v xml:space="preserve">                  Annualized Miscellaneous Equipment Maintenance (Account 26)</v>
+        <v xml:space="preserve">                  Annualized Electrical Equipment Maintenance (Account 24)</v>
       </c>
       <c r="E191" s="39"/>
       <c r="F191" s="39"/>
@@ -23286,27 +23288,20 @@
       <c r="AF191" s="76"/>
       <c r="AG191" s="74"/>
     </row>
-    <row r="192" spans="1:33" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:33" ht="56" customHeight="1" ns3:dyDescent="0.2">
       <c r="A192" s="37">
-        <v>78</v>
+        <v>759.8</v>
       </c>
       <c r="B192" s="38">
-        <f>IF(ISNUMBER(A192),
-    IF(AND(A192=INT(A192), MOD(A192, 10) = 0), 0,
-        IF(AND(A192=INT(A192), LEN(A192)=2), 1,
-            IF(AND(A192=INT(A192), LEN(A192)=3), 2,
-                LEN(A192) - FIND(".", A192) + 2)
-        )
-    ),
-"")</f>
-        <v>1</v>
+        <f t="shared" si="53"/>
+        <v>3</v>
       </c>
       <c r="C192" s="55" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D192" s="39" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">      Annualized Decommissioning Cost</v>
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">                  Annualized Miscellaneous Equipment Maintenance (Account 26)</v>
       </c>
       <c r="E192" s="39"/>
       <c r="F192" s="39"/>
@@ -23314,20 +23309,18 @@
       <c r="H192" s="39"/>
       <c r="I192" s="39"/>
       <c r="J192" s="43"/>
-      <c r="K192" s="70"/>
+      <c r="K192" s="60"/>
       <c r="L192" s="49"/>
-      <c r="M192" s="45"/>
+      <c r="M192" s="58"/>
       <c r="N192" s="49"/>
       <c r="O192" s="49"/>
       <c r="P192" s="49"/>
       <c r="Q192" s="65"/>
       <c r="R192" s="49"/>
-      <c r="S192" s="58"/>
-      <c r="T192" s="58"/>
+      <c r="S192" s="205"/>
+      <c r="T192" s="205"/>
       <c r="U192" s="49"/>
-      <c r="V192" s="58" t="s">
-        <v>421</v>
-      </c>
+      <c r="V192" s="205"/>
       <c r="W192" s="74"/>
       <c r="X192" s="77"/>
       <c r="Y192" s="77"/>
@@ -23340,46 +23333,48 @@
       <c r="AF192" s="76"/>
       <c r="AG192" s="74"/>
     </row>
-    <row r="193" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:33" ht="53.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A193" s="37">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B193" s="38">
         <f>IF(ISNUMBER(A193),
-IF(AND(A193=INT(A193), MOD(A193, 10) = 0), 0,
-IF(AND(A193=INT(A193), LEN(A193)=2), 1,
-IF(AND(A193=INT(A193), LEN(A193)=3), 2,
-LEN(A193) - FIND(".", A193) + 2)
-)
-),
+    IF(AND(A193=INT(A193), MOD(A193, 10) = 0), 0,
+        IF(AND(A193=INT(A193), LEN(A193)=2), 1,
+            IF(AND(A193=INT(A193), LEN(A193)=3), 2,
+                LEN(A193) - FIND(".", A193) + 2)
+        )
+    ),
 "")</f>
-        <v>0</v>
-      </c>
-      <c r="C193" s="69" t="s">
-        <v>422</v>
+        <v>1</v>
+      </c>
+      <c r="C193" s="55" t="s">
+        <v>420</v>
       </c>
       <c r="D193" s="39" t="str">
         <f t="shared" si="51"/>
-        <v>Annualized Fuel Cost</v>
+        <v xml:space="preserve">      Annualized Decommissioning Cost</v>
       </c>
       <c r="E193" s="39"/>
       <c r="F193" s="39"/>
       <c r="G193" s="39"/>
       <c r="H193" s="39"/>
       <c r="I193" s="39"/>
-      <c r="J193" s="40"/>
-      <c r="K193" s="40"/>
-      <c r="L193" s="38"/>
-      <c r="M193" s="41"/>
-      <c r="N193" s="38"/>
-      <c r="O193" s="38"/>
-      <c r="P193" s="38"/>
-      <c r="Q193" s="40"/>
-      <c r="R193" s="38"/>
-      <c r="S193" s="41"/>
-      <c r="T193" s="38"/>
-      <c r="U193" s="38"/>
-      <c r="V193" s="38"/>
+      <c r="J193" s="43"/>
+      <c r="K193" s="70"/>
+      <c r="L193" s="49"/>
+      <c r="M193" s="45"/>
+      <c r="N193" s="49"/>
+      <c r="O193" s="49"/>
+      <c r="P193" s="49"/>
+      <c r="Q193" s="65"/>
+      <c r="R193" s="49"/>
+      <c r="S193" s="58"/>
+      <c r="T193" s="58"/>
+      <c r="U193" s="49"/>
+      <c r="V193" s="58" t="s">
+        <v>421</v>
+      </c>
       <c r="W193" s="74"/>
       <c r="X193" s="77"/>
       <c r="Y193" s="77"/>
@@ -23392,9 +23387,9 @@
       <c r="AF193" s="76"/>
       <c r="AG193" s="74"/>
     </row>
-    <row r="194" spans="1:33" ht="151" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A194" s="37">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B194" s="38">
         <f>IF(ISNUMBER(A194),
@@ -23405,90 +23400,48 @@
 )
 ),
 "")</f>
-        <v>1</v>
-      </c>
-      <c r="C194" s="55" t="s">
-        <v>423</v>
+        <v>0</v>
+      </c>
+      <c r="C194" s="69" t="s">
+        <v>422</v>
       </c>
       <c r="D194" s="39" t="str">
         <f t="shared" si="51"/>
-        <v xml:space="preserve">      Refueling Operations</v>
-      </c>
-      <c r="E194" s="39" t="s">
-        <v>268</v>
-      </c>
+        <v>Annualized Fuel Cost</v>
+      </c>
+      <c r="E194" s="39"/>
       <c r="F194" s="39"/>
       <c r="G194" s="39"/>
       <c r="H194" s="39"/>
       <c r="I194" s="39"/>
-      <c r="J194" s="43"/>
-      <c r="K194" s="60">
-        <v>178500</v>
-      </c>
-      <c r="L194" s="49" t="s">
-        <v>386</v>
-      </c>
-      <c r="M194" s="58" t="s">
-        <v>387</v>
-      </c>
-      <c r="N194" s="49"/>
-      <c r="O194" s="49"/>
-      <c r="P194" s="49">
-        <v>1</v>
-      </c>
-      <c r="Q194" s="65">
-        <v>2024</v>
-      </c>
-      <c r="R194" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S194" s="58"/>
-      <c r="T194" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="U194" s="49"/>
-      <c r="V194" s="49"/>
-      <c r="W194" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="X194" s="77">
-        <f>0.9*$J194</f>
-        <v>0</v>
-      </c>
-      <c r="Y194" s="77">
-        <f>1.5*J194</f>
-        <v>0</v>
-      </c>
-      <c r="Z194" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA194" s="76">
-        <f>0.9*K194</f>
-        <v>160650</v>
-      </c>
-      <c r="AB194" s="76">
-        <f>1.3*K194</f>
-        <v>232050</v>
-      </c>
-      <c r="AC194" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD194" s="76" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE194" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF194" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG194" s="74" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="195" spans="1:33" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J194" s="40"/>
+      <c r="K194" s="40"/>
+      <c r="L194" s="38"/>
+      <c r="M194" s="41"/>
+      <c r="N194" s="38"/>
+      <c r="O194" s="38"/>
+      <c r="P194" s="38"/>
+      <c r="Q194" s="40"/>
+      <c r="R194" s="38"/>
+      <c r="S194" s="41"/>
+      <c r="T194" s="38"/>
+      <c r="U194" s="38"/>
+      <c r="V194" s="38"/>
+      <c r="W194" s="74"/>
+      <c r="X194" s="77"/>
+      <c r="Y194" s="77"/>
+      <c r="Z194" s="74"/>
+      <c r="AA194" s="76"/>
+      <c r="AB194" s="76"/>
+      <c r="AC194" s="74"/>
+      <c r="AD194" s="76"/>
+      <c r="AE194" s="76"/>
+      <c r="AF194" s="76"/>
+      <c r="AG194" s="74"/>
+    </row>
+    <row r="195" spans="1:33" ht="151" customHeight="1" ns3:dyDescent="0.2">
       <c r="A195" s="37">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B195" s="38">
         <f>IF(ISNUMBER(A195),
@@ -23502,45 +23455,87 @@
         <v>1</v>
       </c>
       <c r="C195" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D195" s="39" t="str">
         <f t="shared" si="51"/>
-        <v xml:space="preserve">      Additional Nuclear Fuel</v>
-      </c>
-      <c r="E195" s="39"/>
+        <v xml:space="preserve">      Refueling Operations</v>
+      </c>
+      <c r="E195" s="39" t="s">
+        <v>268</v>
+      </c>
       <c r="F195" s="39"/>
       <c r="G195" s="39"/>
       <c r="H195" s="39"/>
       <c r="I195" s="39"/>
       <c r="J195" s="43"/>
-      <c r="K195" s="60"/>
-      <c r="L195" s="49"/>
-      <c r="M195" s="58"/>
+      <c r="K195" s="60">
+        <v>178500</v>
+      </c>
+      <c r="L195" s="49" t="s">
+        <v>386</v>
+      </c>
+      <c r="M195" s="58" t="s">
+        <v>387</v>
+      </c>
       <c r="N195" s="49"/>
       <c r="O195" s="49"/>
-      <c r="P195" s="49"/>
-      <c r="Q195" s="65"/>
-      <c r="R195" s="49"/>
+      <c r="P195" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q195" s="65">
+        <v>2024</v>
+      </c>
+      <c r="R195" s="49" t="s">
+        <v>53</v>
+      </c>
       <c r="S195" s="58"/>
-      <c r="T195" s="49"/>
+      <c r="T195" s="58" t="s">
+        <v>388</v>
+      </c>
       <c r="U195" s="49"/>
       <c r="V195" s="49"/>
-      <c r="W195" s="74"/>
-      <c r="X195" s="77"/>
-      <c r="Y195" s="77"/>
-      <c r="Z195" s="74"/>
-      <c r="AA195" s="76"/>
-      <c r="AB195" s="76"/>
-      <c r="AC195" s="74"/>
-      <c r="AD195" s="76"/>
-      <c r="AE195" s="76"/>
-      <c r="AF195" s="76"/>
-      <c r="AG195" s="74"/>
-    </row>
-    <row r="196" spans="1:33" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W195" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X195" s="77">
+        <f>0.9*$J195</f>
+        <v>0</v>
+      </c>
+      <c r="Y195" s="77">
+        <f>1.5*J195</f>
+        <v>0</v>
+      </c>
+      <c r="Z195" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA195" s="76">
+        <f>0.9*K195</f>
+        <v>160650</v>
+      </c>
+      <c r="AB195" s="76">
+        <f>1.3*K195</f>
+        <v>232050</v>
+      </c>
+      <c r="AC195" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD195" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE195" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF195" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG195" s="74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="196" spans="1:33" ht="26.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A196" s="37">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B196" s="38">
         <f>IF(ISNUMBER(A196),
@@ -23554,79 +23549,131 @@
         <v>1</v>
       </c>
       <c r="C196" s="55" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D196" s="39" t="str">
         <f t="shared" si="51"/>
-        <v xml:space="preserve">      Spent Fuel Management</v>
-      </c>
-      <c r="E196" s="39" t="s">
-        <v>35</v>
-      </c>
+        <v xml:space="preserve">      Additional Nuclear Fuel</v>
+      </c>
+      <c r="E196" s="39"/>
       <c r="F196" s="39"/>
       <c r="G196" s="39"/>
       <c r="H196" s="39"/>
       <c r="I196" s="39"/>
       <c r="J196" s="43"/>
-      <c r="K196" s="60">
-        <v>1</v>
-      </c>
-      <c r="L196" s="49" t="s">
-        <v>426</v>
-      </c>
-      <c r="M196" s="58" t="s">
-        <v>427</v>
-      </c>
+      <c r="K196" s="60"/>
+      <c r="L196" s="49"/>
+      <c r="M196" s="58"/>
       <c r="N196" s="49"/>
       <c r="O196" s="49"/>
-      <c r="P196" s="49">
-        <v>1</v>
-      </c>
-      <c r="Q196" s="65">
-        <v>2024</v>
-      </c>
-      <c r="R196" s="49" t="s">
-        <v>86</v>
-      </c>
+      <c r="P196" s="49"/>
+      <c r="Q196" s="65"/>
+      <c r="R196" s="49"/>
       <c r="S196" s="58"/>
       <c r="T196" s="49"/>
       <c r="U196" s="49"/>
       <c r="V196" s="49"/>
-      <c r="W196" s="74" t="s">
+      <c r="W196" s="74"/>
+      <c r="X196" s="77"/>
+      <c r="Y196" s="77"/>
+      <c r="Z196" s="74"/>
+      <c r="AA196" s="76"/>
+      <c r="AB196" s="76"/>
+      <c r="AC196" s="74"/>
+      <c r="AD196" s="76"/>
+      <c r="AE196" s="76"/>
+      <c r="AF196" s="76"/>
+      <c r="AG196" s="74"/>
+    </row>
+    <row r="197" spans="1:33" ht="51.75" customHeight="1" ns3:dyDescent="0.2">
+      <c r="A197" s="37">
+        <v>83</v>
+      </c>
+      <c r="B197" s="38">
+        <f>IF(ISNUMBER(A197),
+IF(AND(A197=INT(A197), MOD(A197, 10) = 0), 0,
+IF(AND(A197=INT(A197), LEN(A197)=2), 1,
+IF(AND(A197=INT(A197), LEN(A197)=3), 2,
+LEN(A197) - FIND(".", A197) + 2)
+)
+),
+"")</f>
+        <v>1</v>
+      </c>
+      <c r="C197" s="55" t="s">
+        <v>425</v>
+      </c>
+      <c r="D197" s="39" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">      Spent Fuel Management</v>
+      </c>
+      <c r="E197" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F197" s="39"/>
+      <c r="G197" s="39"/>
+      <c r="H197" s="39"/>
+      <c r="I197" s="39"/>
+      <c r="J197" s="43"/>
+      <c r="K197" s="60">
+        <v>1</v>
+      </c>
+      <c r="L197" s="49" t="s">
+        <v>426</v>
+      </c>
+      <c r="M197" s="58" t="s">
+        <v>427</v>
+      </c>
+      <c r="N197" s="49"/>
+      <c r="O197" s="49"/>
+      <c r="P197" s="49">
+        <v>1</v>
+      </c>
+      <c r="Q197" s="65">
+        <v>2024</v>
+      </c>
+      <c r="R197" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="S197" s="58"/>
+      <c r="T197" s="49"/>
+      <c r="U197" s="49"/>
+      <c r="V197" s="49"/>
+      <c r="W197" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="X196" s="77">
-        <f>0.9*$J196</f>
-        <v>0</v>
-      </c>
-      <c r="Y196" s="77">
-        <f>1.5*J196</f>
-        <v>0</v>
-      </c>
-      <c r="Z196" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA196" s="76">
-        <f>0.9*K196</f>
+      <c r="X197" s="77">
+        <f>0.9*$J197</f>
+        <v>0</v>
+      </c>
+      <c r="Y197" s="77">
+        <f>1.5*J197</f>
+        <v>0</v>
+      </c>
+      <c r="Z197" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA197" s="76">
+        <f>0.9*K197</f>
         <v>0.9</v>
       </c>
-      <c r="AB196" s="76">
-        <f>1.3*K196</f>
+      <c r="AB197" s="76">
+        <f>1.3*K197</f>
         <v>1.3</v>
       </c>
-      <c r="AC196" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD196" s="76" t="s">
+      <c r="AC197" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD197" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="AE196" s="76" t="s">
+      <c r="AE197" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="AF196" s="76" t="s">
+      <c r="AF197" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="AG196" s="74" t="s">
+      <c r="AG197" s="74" t="s">
         <v>48</v>
       </c>
     </row>
@@ -24950,76 +24997,76 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="17">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q194:R201 Q155:Q201 Q2:Q153" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q194:R201 Q155:Q201 Q2:Q153" ns2:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1950</formula1>
       <formula2>2025</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J134:J135 J138:J145 J149:J193 K2:K9 K56:K58 K61:K63 K65:K67 K71:K83 K88 K98:K108 K110:K151 K153:K193 N109:N1048576 N75:N87 N89:N107 N1:N71 J2:J131 K11:K52" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J134:J135 J138:J145 J149:J193 K2:K9 K56:K58 K61:K63 K65:K67 K71:K83 K88 K98:K108 K110:K151 K153:K193 N109:N1048576 N75:N87 N89:N107 N1:N71 J2:J131 K11:K52" ns2:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M360:M370" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M360:M370" ns2:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Land Area, Power MWe, Excavation Volume,  Reactor Building Slab Roof Volume,	Reactor Building  Basement Volume, Reactor Building  Exterior Walls Volume,		Turbine Building Slab Roof Volume,	Turbine Building  Basement Volume,	Turbine Building  Exterior Wall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 L194:L1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 L194:L1048576" ns2:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"$/acres, $/MWe, $/m^3, $/MWt"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P194:P339" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P194:P339" ns2:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P145:P201 P86:P138 P2:P84" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P145:P201 P86:P138 P2:P84" ns2:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O145:O201 O86:O135 O138 O2:O13 O18:O84 O15" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O145:O201 O86:O135 O138 O2:O13 O18:O84 O15" ns2:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"acres, MWe, m^3, MWt, Kg, Drums, kW, $, m^2, kg/s"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L145:L201 L86:L114 L116:L138 L2:L13 L18:L84 L15" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L145:L201 L86:L114 L116:L138 L2:L13 L18:L84 L15" ns2:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"$/m^2,$/MWeHour,$/FTE, $/acres, $/MWe, $/m^3, $/MWt, $/Kg, $/Drum, $/(kg.sec), $/SWU, unitless, $/kWe"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O136:O137" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O136:O137" ns2:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"acres, MWe, m^3, MWt, Kg, Drums, kW, $, m^2, kg/s, kWe"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L85 L139:L144" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L85 L139:L144" ns2:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>"$/MWeHour,$/FTE, $/acres, $/MWe, $/m^3, $/MWt, $/Kg, $/Drum, $/(kg.sec), $/SWU, unitless"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O85 O139:O144" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O85 O139:O144" ns2:uid="{00000000-0002-0000-0000-00000A000000}">
       <formula1>"acres, MWe, m^3, MWt, Kg, Drums, kW, $"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P85 P139:P144" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P85 P139:P144" ns2:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E201" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E201" ns2:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>"standard, nonstandard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R201" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R201" ns2:uid="{00000000-0002-0000-0000-00000D000000}">
       <formula1>"NA, General, Labor, Material, Equipment,Lab and Mat and Equip, 'Lab and Equip"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L115" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L115" ns2:uid="{00000000-0002-0000-0000-00000E000000}">
       <formula1>"$/heatpipe,$/m^2,$/MWeHour,$/FTE, $/acres, $/MWe, $/m^3, $/MWt, $/Kg, $/Drum, $/(kg.sec), $/SWU, unitless, $/kWe"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O16:O17 O14" xr:uid="{404860D7-E1E0-6A4B-A6BA-FCD332FF61FE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O16:O17 O14" ns2:uid="{404860D7-E1E0-6A4B-A6BA-FCD332FF61FE}">
       <formula1>"m,acres, MWe, m^3, MWt, Kg, Drums, kW, $, m^2, kg/s"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L16:L17 L14" xr:uid="{F79DC16A-CFBC-5E4B-AA4C-06A7E72D0753}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L16:L17 L14" ns2:uid="{F79DC16A-CFBC-5E4B-AA4C-06A7E72D0753}">
       <formula1>"$/m,$/m^2,$/MWeHour,$/FTE, $/acres, $/MWe, $/m^3, $/MWt, $/Kg, $/Drum, $/(kg.sec), $/SWU, unitless, $/kWe"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="U5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="U22" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="U23" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="U37" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="U53" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="U113" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="U124" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="U134" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="U135" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="U139" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="U140" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="U173" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="U3" ns4:id="rId1" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U5" ns4:id="rId2" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="U22" ns4:id="rId3" ns2:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="U23" ns4:id="rId4" ns2:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="U37" ns4:id="rId5" ns2:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="U53" ns4:id="rId6" ns2:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="U113" ns4:id="rId7" ns2:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="U124" ns4:id="rId8" ns2:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="U134" ns4:id="rId9" ns2:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="U135" ns4:id="rId10" ns2:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="U139" ns4:id="rId11" ns2:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="U140" ns4:id="rId12" ns2:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="U173" ns4:id="rId13" ns2:uid="{00000000-0004-0000-0000-00000C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost Database" sheetId="1" r:id="Ra6ad543c9d44473d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MARVEL_Cost" sheetId="2" r:id="R6ed59536b00e4688"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Variables" sheetId="3" r:id="R28656b16e27a4f7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inflation Adjustment" sheetId="4" r:id="Rc2102c44b4df4727"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economics Parameters" sheetId="5" r:id="Re9d62dbb14f04944"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Central Facility Database" sheetId="6" r:id="R7ba09e4ef963496c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost Database" sheetId="1" r:id="R8cc44493ef054a9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MARVEL_Cost" sheetId="2" r:id="Re4aa994d4c6e4113"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Variables" sheetId="3" r:id="R35fa29f8c23f47a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inflation Adjustment" sheetId="4" r:id="R2599c6bc273d4be8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economics Parameters" sheetId="5" r:id="Rd77e61a29aa64e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Central Facility Database" sheetId="6" r:id="Rbc74ca9b80be4fad"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CRF">#REF!</x:definedName>
@@ -23987,18 +23987,18 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="R0281d7ce810e4451"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="R82b232edbd624732"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="Reb6f65dd0e1a47d8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="Ra4002a568e124ac2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="R7524d5683ae44095"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U109" r:id="R78622f477640423d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U120" r:id="R1ad73cd1835e4784"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U130" r:id="R15f7cc3e99024840"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U131" r:id="R453a2e4fd8a54c20"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U135" r:id="R69e2a49543e5492c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U136" r:id="R91a2632a9a404bdd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U169" r:id="Re400fd8edc2e403f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="R64a7bc95d2b244be"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="Rbea2ed0682ad42c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="R8bd514e035814680"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="R73f75fcec6b64441"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="R4d545bf921944e39"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U109" r:id="Recffc00ba694489e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U120" r:id="R5fd6063ac96a46ef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U130" r:id="R6efd8303c6174cea"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U131" r:id="Rc54f9c7a66614c55"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U135" r:id="R59f7d1cdc1e04726"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U136" r:id="R24533926a3b443e3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U169" r:id="Racff3a829c8a4959"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -27301,7 +27301,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a13f44cb7ee40fe"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R610ab24701144f01"/>
 </x:worksheet>
 </file>
 
@@ -27454,7 +27454,7 @@
         </x:is>
       </x:c>
       <x:c r="B11" t="n">
-        <x:v>0</x:v>
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
